--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="14" spans="1:33">
+    <row r="6" spans="1:33">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1759,10 +1759,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
@@ -1778,14 +1778,14 @@
       </c>
       <c r="V6" s="1">
         <f t="shared" ref="V6:V69" si="5">X6*10</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="W6" s="1">
         <f t="shared" ref="W6:W69" si="6">X6*10</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="X6" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="1">
         <v>1</v>
@@ -1830,7 +1830,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:H70" si="7">AG9*Z7*AA7/10</f>
+        <f>AG9*Z7*AA7/10</f>
         <v>252</v>
       </c>
       <c r="I7" s="1">
@@ -1880,14 +1880,14 @@
       </c>
       <c r="V7" s="1">
         <f t="shared" si="5"/>
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="W7" s="1">
         <f t="shared" si="6"/>
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="X7" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y7" s="1">
         <v>2</v>
@@ -1933,7 +1933,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="H7:H70" si="7">AG10*Z8*AA8/10</f>
         <v>616</v>
       </c>
       <c r="I8" s="1">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="V8" s="1">
         <f t="shared" si="5"/>
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="W8" s="1">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="X8" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y8" s="1">
         <v>3</v>
@@ -2088,14 +2088,14 @@
       </c>
       <c r="V9" s="1">
         <f t="shared" si="5"/>
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="W9" s="1">
         <f t="shared" si="6"/>
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="X9" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Y9" s="1">
         <v>4</v>
@@ -2192,14 +2192,14 @@
       </c>
       <c r="V10" s="1">
         <f t="shared" si="5"/>
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="W10" s="1">
         <f t="shared" si="6"/>
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="X10" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Y10" s="1">
         <v>5</v>
@@ -2296,14 +2296,14 @@
       </c>
       <c r="V11" s="1">
         <f t="shared" si="5"/>
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="W11" s="1">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="X11" s="1">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y11" s="1">
         <v>6</v>
@@ -2400,14 +2400,14 @@
       </c>
       <c r="V12" s="1">
         <f t="shared" si="5"/>
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="W12" s="1">
         <f t="shared" si="6"/>
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="X12" s="1">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y12" s="1">
         <v>7</v>
@@ -2505,14 +2505,14 @@
       </c>
       <c r="V13" s="1">
         <f t="shared" si="5"/>
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="W13" s="1">
         <f t="shared" si="6"/>
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="X13" s="1">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y13" s="1">
         <v>8</v>
@@ -2610,14 +2610,14 @@
       </c>
       <c r="V14" s="1">
         <f t="shared" si="5"/>
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="W14" s="1">
         <f t="shared" si="6"/>
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="X14" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Y14" s="1">
         <v>9</v>
@@ -2715,14 +2715,14 @@
       </c>
       <c r="V15" s="1">
         <f t="shared" si="5"/>
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="W15" s="1">
         <f t="shared" si="6"/>
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="X15" s="1">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="Y15" s="1">
         <v>10</v>
@@ -2820,14 +2820,14 @@
       </c>
       <c r="V16" s="1">
         <f t="shared" si="5"/>
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="W16" s="1">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="X16" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Y16" s="1">
         <v>11</v>
@@ -2925,14 +2925,14 @@
       </c>
       <c r="V17" s="1">
         <f t="shared" si="5"/>
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="W17" s="1">
         <f t="shared" si="6"/>
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="X17" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y17" s="1">
         <v>12</v>
@@ -3030,14 +3030,14 @@
       </c>
       <c r="V18" s="1">
         <f t="shared" si="5"/>
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="W18" s="1">
         <f t="shared" si="6"/>
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="X18" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Y18" s="1">
         <v>13</v>
@@ -3135,14 +3135,14 @@
       </c>
       <c r="V19" s="1">
         <f t="shared" si="5"/>
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="W19" s="1">
         <f t="shared" si="6"/>
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="X19" s="1">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y19" s="1">
         <v>14</v>
@@ -3240,14 +3240,14 @@
       </c>
       <c r="V20" s="1">
         <f t="shared" si="5"/>
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="W20" s="1">
         <f t="shared" si="6"/>
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="X20" s="1">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="Y20" s="1">
         <v>15</v>
@@ -3345,14 +3345,14 @@
       </c>
       <c r="V21" s="1">
         <f t="shared" si="5"/>
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="W21" s="1">
         <f t="shared" si="6"/>
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="X21" s="1">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Y21" s="1">
         <v>16</v>
@@ -3450,14 +3450,14 @@
       </c>
       <c r="V22" s="1">
         <f t="shared" si="5"/>
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="W22" s="1">
         <f t="shared" si="6"/>
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="X22" s="1">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="Y22" s="1">
         <v>17</v>
@@ -3555,14 +3555,14 @@
       </c>
       <c r="V23" s="1">
         <f t="shared" si="5"/>
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="W23" s="1">
         <f t="shared" si="6"/>
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="X23" s="1">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Y23" s="1">
         <v>18</v>
@@ -3660,14 +3660,14 @@
       </c>
       <c r="V24" s="1">
         <f t="shared" si="5"/>
-        <v>280</v>
+        <v>190</v>
       </c>
       <c r="W24" s="1">
         <f t="shared" si="6"/>
-        <v>280</v>
+        <v>190</v>
       </c>
       <c r="X24" s="1">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Y24" s="1">
         <v>19</v>
@@ -3765,14 +3765,14 @@
       </c>
       <c r="V25" s="1">
         <f t="shared" si="5"/>
-        <v>290</v>
+        <v>200</v>
       </c>
       <c r="W25" s="1">
         <f t="shared" si="6"/>
-        <v>290</v>
+        <v>200</v>
       </c>
       <c r="X25" s="1">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="Y25" s="1">
         <v>20</v>
@@ -3870,14 +3870,14 @@
       </c>
       <c r="V26" s="1">
         <f t="shared" si="5"/>
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="W26" s="1">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="X26" s="1">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="Y26" s="1">
         <v>21</v>
@@ -3975,14 +3975,14 @@
       </c>
       <c r="V27" s="1">
         <f t="shared" si="5"/>
-        <v>310</v>
+        <v>220</v>
       </c>
       <c r="W27" s="1">
         <f t="shared" si="6"/>
-        <v>310</v>
+        <v>220</v>
       </c>
       <c r="X27" s="1">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="Y27" s="1">
         <v>22</v>
@@ -4063,8 +4063,8 @@
         <v>23</v>
       </c>
       <c r="Q28" s="2">
-        <f>Q27+5</f>
-        <v>55</v>
+        <f t="shared" ref="Q28:Q77" si="12">Q27+3</f>
+        <v>53</v>
       </c>
       <c r="R28" s="1">
         <v>0</v>
@@ -4080,20 +4080,20 @@
       </c>
       <c r="V28" s="1">
         <f t="shared" si="5"/>
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="W28" s="1">
         <f t="shared" si="6"/>
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="X28" s="1">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="Y28" s="1">
         <v>23</v>
       </c>
       <c r="Z28" s="2">
-        <f t="shared" ref="Z28:Z33" si="12">Z27+500</f>
+        <f t="shared" ref="Z28:Z33" si="13">Z27+500</f>
         <v>2500</v>
       </c>
       <c r="AA28" s="2">
@@ -4168,8 +4168,8 @@
         <v>24</v>
       </c>
       <c r="Q29" s="2">
-        <f t="shared" ref="Q29:Q77" si="13">Q28+5</f>
-        <v>60</v>
+        <f t="shared" si="12"/>
+        <v>56</v>
       </c>
       <c r="R29" s="1">
         <v>0</v>
@@ -4185,20 +4185,20 @@
       </c>
       <c r="V29" s="1">
         <f t="shared" si="5"/>
-        <v>330</v>
+        <v>240</v>
       </c>
       <c r="W29" s="1">
         <f t="shared" si="6"/>
-        <v>330</v>
+        <v>240</v>
       </c>
       <c r="X29" s="1">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="Y29" s="1">
         <v>24</v>
       </c>
       <c r="Z29" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3000</v>
       </c>
       <c r="AA29" s="2">
@@ -4273,8 +4273,8 @@
         <v>25</v>
       </c>
       <c r="Q30" s="2">
-        <f t="shared" si="13"/>
-        <v>65</v>
+        <f t="shared" si="12"/>
+        <v>59</v>
       </c>
       <c r="R30" s="1">
         <v>0</v>
@@ -4290,20 +4290,20 @@
       </c>
       <c r="V30" s="1">
         <f t="shared" si="5"/>
-        <v>340</v>
+        <v>250</v>
       </c>
       <c r="W30" s="1">
         <f t="shared" si="6"/>
-        <v>340</v>
+        <v>250</v>
       </c>
       <c r="X30" s="1">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Y30" s="1">
         <v>25</v>
       </c>
       <c r="Z30" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3500</v>
       </c>
       <c r="AA30" s="2">
@@ -4378,8 +4378,8 @@
         <v>26</v>
       </c>
       <c r="Q31" s="2">
-        <f t="shared" si="13"/>
-        <v>70</v>
+        <f t="shared" si="12"/>
+        <v>62</v>
       </c>
       <c r="R31" s="1">
         <v>0</v>
@@ -4395,20 +4395,20 @@
       </c>
       <c r="V31" s="1">
         <f t="shared" si="5"/>
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="W31" s="1">
         <f t="shared" si="6"/>
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="X31" s="1">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Y31" s="1">
         <v>26</v>
       </c>
       <c r="Z31" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="AA31" s="2">
@@ -4483,8 +4483,8 @@
         <v>27</v>
       </c>
       <c r="Q32" s="2">
-        <f t="shared" si="13"/>
-        <v>75</v>
+        <f t="shared" si="12"/>
+        <v>65</v>
       </c>
       <c r="R32" s="1">
         <v>0</v>
@@ -4500,20 +4500,20 @@
       </c>
       <c r="V32" s="1">
         <f t="shared" si="5"/>
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="W32" s="1">
         <f t="shared" si="6"/>
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="X32" s="1">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="Y32" s="1">
         <v>27</v>
       </c>
       <c r="Z32" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4500</v>
       </c>
       <c r="AA32" s="2">
@@ -4588,8 +4588,8 @@
         <v>28</v>
       </c>
       <c r="Q33" s="2">
-        <f t="shared" si="13"/>
-        <v>80</v>
+        <f t="shared" si="12"/>
+        <v>68</v>
       </c>
       <c r="R33" s="1">
         <v>0</v>
@@ -4605,20 +4605,20 @@
       </c>
       <c r="V33" s="1">
         <f t="shared" si="5"/>
-        <v>370</v>
+        <v>280</v>
       </c>
       <c r="W33" s="1">
         <f t="shared" si="6"/>
-        <v>370</v>
+        <v>280</v>
       </c>
       <c r="X33" s="1">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="Y33" s="1">
         <v>28</v>
       </c>
       <c r="Z33" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="AA33" s="2">
@@ -4693,8 +4693,8 @@
         <v>29</v>
       </c>
       <c r="Q34" s="2">
-        <f t="shared" si="13"/>
-        <v>85</v>
+        <f t="shared" si="12"/>
+        <v>71</v>
       </c>
       <c r="R34" s="1">
         <v>0</v>
@@ -4710,14 +4710,14 @@
       </c>
       <c r="V34" s="1">
         <f t="shared" si="5"/>
-        <v>380</v>
+        <v>290</v>
       </c>
       <c r="W34" s="1">
         <f t="shared" si="6"/>
-        <v>380</v>
+        <v>290</v>
       </c>
       <c r="X34" s="1">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Y34" s="1">
         <v>29</v>
@@ -4798,8 +4798,8 @@
         <v>30</v>
       </c>
       <c r="Q35" s="2">
-        <f t="shared" si="13"/>
-        <v>90</v>
+        <f t="shared" si="12"/>
+        <v>74</v>
       </c>
       <c r="R35" s="1">
         <v>0</v>
@@ -4815,14 +4815,14 @@
       </c>
       <c r="V35" s="1">
         <f t="shared" si="5"/>
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="W35" s="1">
         <f t="shared" si="6"/>
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="X35" s="1">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="Y35" s="1">
         <v>30</v>
@@ -4903,8 +4903,8 @@
         <v>31</v>
       </c>
       <c r="Q36" s="2">
-        <f t="shared" si="13"/>
-        <v>95</v>
+        <f t="shared" si="12"/>
+        <v>77</v>
       </c>
       <c r="R36" s="1">
         <v>0</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="V36" s="1">
         <f t="shared" si="5"/>
-        <v>400</v>
+        <v>310</v>
       </c>
       <c r="W36" s="1">
         <f t="shared" si="6"/>
-        <v>400</v>
+        <v>310</v>
       </c>
       <c r="X36" s="1">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Y36" s="1">
         <v>31</v>
@@ -5008,8 +5008,8 @@
         <v>32</v>
       </c>
       <c r="Q37" s="2">
-        <f t="shared" si="13"/>
-        <v>100</v>
+        <f t="shared" si="12"/>
+        <v>80</v>
       </c>
       <c r="R37" s="1">
         <v>0</v>
@@ -5025,14 +5025,14 @@
       </c>
       <c r="V37" s="1">
         <f t="shared" si="5"/>
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="W37" s="1">
         <f t="shared" si="6"/>
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="X37" s="1">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Y37" s="1">
         <v>32</v>
@@ -5113,8 +5113,8 @@
         <v>33</v>
       </c>
       <c r="Q38" s="2">
-        <f t="shared" si="13"/>
-        <v>105</v>
+        <f t="shared" si="12"/>
+        <v>83</v>
       </c>
       <c r="R38" s="1">
         <v>0</v>
@@ -5130,14 +5130,14 @@
       </c>
       <c r="V38" s="1">
         <f t="shared" si="5"/>
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="W38" s="1">
         <f t="shared" si="6"/>
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="X38" s="1">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="Y38" s="1">
         <v>33</v>
@@ -5218,8 +5218,8 @@
         <v>34</v>
       </c>
       <c r="Q39" s="2">
-        <f t="shared" si="13"/>
-        <v>110</v>
+        <f t="shared" si="12"/>
+        <v>86</v>
       </c>
       <c r="R39" s="1">
         <v>0</v>
@@ -5235,14 +5235,14 @@
       </c>
       <c r="V39" s="1">
         <f t="shared" si="5"/>
-        <v>430</v>
+        <v>340</v>
       </c>
       <c r="W39" s="1">
         <f t="shared" si="6"/>
-        <v>430</v>
+        <v>340</v>
       </c>
       <c r="X39" s="1">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Y39" s="1">
         <v>34</v>
@@ -5323,8 +5323,8 @@
         <v>35</v>
       </c>
       <c r="Q40" s="2">
-        <f t="shared" si="13"/>
-        <v>115</v>
+        <f t="shared" si="12"/>
+        <v>89</v>
       </c>
       <c r="R40" s="1">
         <v>0</v>
@@ -5340,14 +5340,14 @@
       </c>
       <c r="V40" s="1">
         <f t="shared" si="5"/>
-        <v>440</v>
+        <v>350</v>
       </c>
       <c r="W40" s="1">
         <f t="shared" si="6"/>
-        <v>440</v>
+        <v>350</v>
       </c>
       <c r="X40" s="1">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Y40" s="1">
         <v>35</v>
@@ -5429,8 +5429,8 @@
         <v>36</v>
       </c>
       <c r="Q41" s="2">
-        <f t="shared" si="13"/>
-        <v>120</v>
+        <f t="shared" si="12"/>
+        <v>92</v>
       </c>
       <c r="R41" s="1">
         <v>0</v>
@@ -5446,14 +5446,14 @@
       </c>
       <c r="V41" s="1">
         <f t="shared" si="5"/>
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="W41" s="1">
         <f t="shared" si="6"/>
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="X41" s="1">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Y41" s="1">
         <v>36</v>
@@ -5534,8 +5534,8 @@
         <v>37</v>
       </c>
       <c r="Q42" s="2">
-        <f t="shared" si="13"/>
-        <v>125</v>
+        <f t="shared" si="12"/>
+        <v>95</v>
       </c>
       <c r="R42" s="1">
         <v>0</v>
@@ -5551,14 +5551,14 @@
       </c>
       <c r="V42" s="1">
         <f t="shared" si="5"/>
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="W42" s="1">
         <f t="shared" si="6"/>
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="X42" s="1">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Y42" s="1">
         <v>37</v>
@@ -5639,8 +5639,8 @@
         <v>38</v>
       </c>
       <c r="Q43" s="2">
-        <f t="shared" si="13"/>
-        <v>130</v>
+        <f t="shared" si="12"/>
+        <v>98</v>
       </c>
       <c r="R43" s="1">
         <v>0</v>
@@ -5656,14 +5656,14 @@
       </c>
       <c r="V43" s="1">
         <f t="shared" si="5"/>
-        <v>470</v>
+        <v>380</v>
       </c>
       <c r="W43" s="1">
         <f t="shared" si="6"/>
-        <v>470</v>
+        <v>380</v>
       </c>
       <c r="X43" s="1">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Y43" s="1">
         <v>38</v>
@@ -5744,8 +5744,8 @@
         <v>39</v>
       </c>
       <c r="Q44" s="2">
-        <f t="shared" si="13"/>
-        <v>135</v>
+        <f t="shared" si="12"/>
+        <v>101</v>
       </c>
       <c r="R44" s="1">
         <v>0</v>
@@ -5761,14 +5761,14 @@
       </c>
       <c r="V44" s="1">
         <f t="shared" si="5"/>
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="W44" s="1">
         <f t="shared" si="6"/>
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="X44" s="1">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="Y44" s="1">
         <v>39</v>
@@ -5849,8 +5849,8 @@
         <v>40</v>
       </c>
       <c r="Q45" s="2">
-        <f t="shared" si="13"/>
-        <v>140</v>
+        <f t="shared" si="12"/>
+        <v>104</v>
       </c>
       <c r="R45" s="1">
         <v>0</v>
@@ -5866,14 +5866,14 @@
       </c>
       <c r="V45" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="W45" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="X45" s="1">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Y45" s="1">
         <v>40</v>
@@ -5948,14 +5948,14 @@
         <v>160</v>
       </c>
       <c r="O46" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P46" s="6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q46" s="2">
-        <f t="shared" si="13"/>
-        <v>145</v>
+        <f t="shared" si="12"/>
+        <v>107</v>
       </c>
       <c r="R46" s="1">
         <v>0</v>
@@ -5971,14 +5971,14 @@
       </c>
       <c r="V46" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="W46" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="X46" s="1">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Y46" s="1">
         <v>40</v>
@@ -6052,14 +6052,14 @@
         <v>160</v>
       </c>
       <c r="O47" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P47" s="6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q47" s="2">
-        <f t="shared" si="13"/>
-        <v>150</v>
+        <f t="shared" si="12"/>
+        <v>110</v>
       </c>
       <c r="R47" s="1">
         <v>0</v>
@@ -6075,14 +6075,14 @@
       </c>
       <c r="V47" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="W47" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="X47" s="1">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="Y47" s="1">
         <v>40</v>
@@ -6157,14 +6157,14 @@
         <v>160</v>
       </c>
       <c r="O48" s="1">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P48" s="6">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q48" s="2">
-        <f t="shared" si="13"/>
-        <v>155</v>
+        <f t="shared" si="12"/>
+        <v>113</v>
       </c>
       <c r="R48" s="1">
         <v>0</v>
@@ -6180,14 +6180,14 @@
       </c>
       <c r="V48" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="W48" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="X48" s="1">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Y48" s="1">
         <v>40</v>
@@ -6262,14 +6262,14 @@
         <v>160</v>
       </c>
       <c r="O49" s="1">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P49" s="6">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q49" s="2">
-        <f t="shared" si="13"/>
-        <v>160</v>
+        <f t="shared" si="12"/>
+        <v>116</v>
       </c>
       <c r="R49" s="1">
         <v>0</v>
@@ -6285,14 +6285,14 @@
       </c>
       <c r="V49" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="W49" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="X49" s="1">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Y49" s="1">
         <v>40</v>
@@ -6367,14 +6367,14 @@
         <v>160</v>
       </c>
       <c r="O50" s="1">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P50" s="6">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q50" s="2">
-        <f t="shared" si="13"/>
-        <v>165</v>
+        <f t="shared" si="12"/>
+        <v>119</v>
       </c>
       <c r="R50" s="1">
         <v>0</v>
@@ -6390,14 +6390,14 @@
       </c>
       <c r="V50" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="W50" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="X50" s="1">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Y50" s="1">
         <v>40</v>
@@ -6472,14 +6472,14 @@
         <v>160</v>
       </c>
       <c r="O51" s="1">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="P51" s="6">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q51" s="2">
-        <f t="shared" si="13"/>
-        <v>170</v>
+        <f t="shared" si="12"/>
+        <v>122</v>
       </c>
       <c r="R51" s="1">
         <v>0</v>
@@ -6495,14 +6495,14 @@
       </c>
       <c r="V51" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="W51" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="X51" s="1">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Y51" s="1">
         <v>40</v>
@@ -6577,14 +6577,14 @@
         <v>160</v>
       </c>
       <c r="O52" s="1">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="P52" s="6">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="Q52" s="2">
-        <f t="shared" si="13"/>
-        <v>175</v>
+        <f t="shared" si="12"/>
+        <v>125</v>
       </c>
       <c r="R52" s="1">
         <v>0</v>
@@ -6600,14 +6600,14 @@
       </c>
       <c r="V52" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="W52" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="X52" s="1">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Y52" s="1">
         <v>40</v>
@@ -6682,14 +6682,14 @@
         <v>160</v>
       </c>
       <c r="O53" s="1">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="P53" s="6">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Q53" s="2">
-        <f t="shared" si="13"/>
-        <v>180</v>
+        <f t="shared" si="12"/>
+        <v>128</v>
       </c>
       <c r="R53" s="1">
         <v>0</v>
@@ -6705,14 +6705,14 @@
       </c>
       <c r="V53" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="W53" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="X53" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y53" s="1">
         <v>40</v>
@@ -6787,14 +6787,14 @@
         <v>160</v>
       </c>
       <c r="O54" s="1">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P54" s="6">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="Q54" s="2">
-        <f t="shared" si="13"/>
-        <v>185</v>
+        <f t="shared" si="12"/>
+        <v>131</v>
       </c>
       <c r="R54" s="1">
         <v>0</v>
@@ -6892,14 +6892,14 @@
         <v>160</v>
       </c>
       <c r="O55" s="1">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="P55" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q55" s="2">
-        <f t="shared" si="13"/>
-        <v>190</v>
+        <f t="shared" si="12"/>
+        <v>134</v>
       </c>
       <c r="R55" s="1">
         <v>0</v>
@@ -6915,14 +6915,14 @@
       </c>
       <c r="V55" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="W55" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="X55" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y55" s="1">
         <v>40</v>
@@ -6997,14 +6997,14 @@
         <v>160</v>
       </c>
       <c r="O56" s="1">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="P56" s="6">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="Q56" s="2">
-        <f t="shared" si="13"/>
-        <v>195</v>
+        <f t="shared" si="12"/>
+        <v>137</v>
       </c>
       <c r="R56" s="1">
         <v>0</v>
@@ -7020,14 +7020,14 @@
       </c>
       <c r="V56" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="W56" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="X56" s="1">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Y56" s="1">
         <v>40</v>
@@ -7102,14 +7102,14 @@
         <v>160</v>
       </c>
       <c r="O57" s="1">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P57" s="6">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="Q57" s="2">
-        <f t="shared" si="13"/>
-        <v>200</v>
+        <f t="shared" si="12"/>
+        <v>140</v>
       </c>
       <c r="R57" s="1">
         <v>0</v>
@@ -7125,14 +7125,14 @@
       </c>
       <c r="V57" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="W57" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="X57" s="1">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Y57" s="1">
         <v>40</v>
@@ -7207,14 +7207,14 @@
         <v>160</v>
       </c>
       <c r="O58" s="1">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="P58" s="6">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="Q58" s="2">
-        <f t="shared" si="13"/>
-        <v>205</v>
+        <f t="shared" si="12"/>
+        <v>143</v>
       </c>
       <c r="R58" s="1">
         <v>0</v>
@@ -7230,14 +7230,14 @@
       </c>
       <c r="V58" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="W58" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="X58" s="1">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Y58" s="1">
         <v>40</v>
@@ -7312,14 +7312,14 @@
         <v>160</v>
       </c>
       <c r="O59" s="1">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="P59" s="6">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="Q59" s="2">
-        <f t="shared" si="13"/>
-        <v>210</v>
+        <f t="shared" si="12"/>
+        <v>146</v>
       </c>
       <c r="R59" s="1">
         <v>0</v>
@@ -7335,14 +7335,14 @@
       </c>
       <c r="V59" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>540</v>
       </c>
       <c r="W59" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>540</v>
       </c>
       <c r="X59" s="1">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y59" s="1">
         <v>40</v>
@@ -7417,14 +7417,14 @@
         <v>160</v>
       </c>
       <c r="O60" s="1">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="P60" s="6">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="Q60" s="2">
-        <f t="shared" si="13"/>
-        <v>215</v>
+        <f t="shared" si="12"/>
+        <v>149</v>
       </c>
       <c r="R60" s="1">
         <v>0</v>
@@ -7440,14 +7440,14 @@
       </c>
       <c r="V60" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>550</v>
       </c>
       <c r="W60" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>550</v>
       </c>
       <c r="X60" s="1">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Y60" s="1">
         <v>40</v>
@@ -7522,14 +7522,14 @@
         <v>160</v>
       </c>
       <c r="O61" s="1">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="P61" s="6">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="Q61" s="2">
-        <f t="shared" si="13"/>
-        <v>220</v>
+        <f t="shared" si="12"/>
+        <v>152</v>
       </c>
       <c r="R61" s="1">
         <v>0</v>
@@ -7545,14 +7545,14 @@
       </c>
       <c r="V61" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>560</v>
       </c>
       <c r="W61" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>560</v>
       </c>
       <c r="X61" s="1">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="Y61" s="1">
         <v>40</v>
@@ -7627,14 +7627,14 @@
         <v>160</v>
       </c>
       <c r="O62" s="1">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P62" s="6">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="Q62" s="2">
-        <f t="shared" si="13"/>
-        <v>225</v>
+        <f t="shared" si="12"/>
+        <v>155</v>
       </c>
       <c r="R62" s="1">
         <v>0</v>
@@ -7650,14 +7650,14 @@
       </c>
       <c r="V62" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>570</v>
       </c>
       <c r="W62" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>570</v>
       </c>
       <c r="X62" s="1">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="Y62" s="1">
         <v>40</v>
@@ -7732,14 +7732,14 @@
         <v>160</v>
       </c>
       <c r="O63" s="1">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="P63" s="6">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="Q63" s="2">
-        <f t="shared" si="13"/>
-        <v>230</v>
+        <f t="shared" si="12"/>
+        <v>158</v>
       </c>
       <c r="R63" s="1">
         <v>0</v>
@@ -7755,14 +7755,14 @@
       </c>
       <c r="V63" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>580</v>
       </c>
       <c r="W63" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>580</v>
       </c>
       <c r="X63" s="1">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Y63" s="1">
         <v>40</v>
@@ -7837,14 +7837,14 @@
         <v>160</v>
       </c>
       <c r="O64" s="1">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="P64" s="6">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="Q64" s="2">
-        <f t="shared" si="13"/>
-        <v>235</v>
+        <f t="shared" si="12"/>
+        <v>161</v>
       </c>
       <c r="R64" s="1">
         <v>0</v>
@@ -7860,14 +7860,14 @@
       </c>
       <c r="V64" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>590</v>
       </c>
       <c r="W64" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>590</v>
       </c>
       <c r="X64" s="1">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="Y64" s="1">
         <v>40</v>
@@ -7942,14 +7942,14 @@
         <v>160</v>
       </c>
       <c r="O65" s="1">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="P65" s="6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q65" s="2">
-        <f t="shared" si="13"/>
-        <v>240</v>
+        <f t="shared" si="12"/>
+        <v>164</v>
       </c>
       <c r="R65" s="1">
         <v>0</v>
@@ -7965,14 +7965,14 @@
       </c>
       <c r="V65" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>600</v>
       </c>
       <c r="W65" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>600</v>
       </c>
       <c r="X65" s="1">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="Y65" s="1">
         <v>40</v>
@@ -8047,14 +8047,14 @@
         <v>160</v>
       </c>
       <c r="O66" s="1">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P66" s="6">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="Q66" s="2">
-        <f t="shared" si="13"/>
-        <v>245</v>
+        <f t="shared" si="12"/>
+        <v>167</v>
       </c>
       <c r="R66" s="1">
         <v>0</v>
@@ -8070,14 +8070,14 @@
       </c>
       <c r="V66" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>610</v>
       </c>
       <c r="W66" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>610</v>
       </c>
       <c r="X66" s="1">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="Y66" s="1">
         <v>40</v>
@@ -8152,14 +8152,14 @@
         <v>160</v>
       </c>
       <c r="O67" s="1">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="P67" s="6">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="Q67" s="2">
-        <f t="shared" si="13"/>
-        <v>250</v>
+        <f t="shared" si="12"/>
+        <v>170</v>
       </c>
       <c r="R67" s="1">
         <v>0</v>
@@ -8175,14 +8175,14 @@
       </c>
       <c r="V67" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>620</v>
       </c>
       <c r="W67" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>620</v>
       </c>
       <c r="X67" s="1">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Y67" s="1">
         <v>40</v>
@@ -8257,14 +8257,14 @@
         <v>160</v>
       </c>
       <c r="O68" s="1">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="P68" s="6">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="Q68" s="2">
-        <f t="shared" si="13"/>
-        <v>255</v>
+        <f t="shared" si="12"/>
+        <v>173</v>
       </c>
       <c r="R68" s="1">
         <v>0</v>
@@ -8280,14 +8280,14 @@
       </c>
       <c r="V68" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>630</v>
       </c>
       <c r="W68" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>630</v>
       </c>
       <c r="X68" s="1">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="Y68" s="1">
         <v>40</v>
@@ -8362,14 +8362,14 @@
         <v>160</v>
       </c>
       <c r="O69" s="1">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="P69" s="6">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="Q69" s="2">
-        <f t="shared" si="13"/>
-        <v>260</v>
+        <f t="shared" si="12"/>
+        <v>176</v>
       </c>
       <c r="R69" s="1">
         <v>0</v>
@@ -8385,14 +8385,14 @@
       </c>
       <c r="V69" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
+        <v>640</v>
       </c>
       <c r="W69" s="1">
         <f t="shared" si="6"/>
-        <v>490</v>
+        <v>640</v>
       </c>
       <c r="X69" s="1">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="Y69" s="1">
         <v>40</v>
@@ -8467,14 +8467,14 @@
         <v>160</v>
       </c>
       <c r="O70" s="1">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P70" s="6">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Q70" s="2">
-        <f t="shared" si="13"/>
-        <v>265</v>
+        <f t="shared" si="12"/>
+        <v>179</v>
       </c>
       <c r="R70" s="1">
         <v>0</v>
@@ -8490,14 +8490,14 @@
       </c>
       <c r="V70" s="1">
         <f t="shared" ref="V70:V77" si="21">X70*10</f>
-        <v>490</v>
+        <v>650</v>
       </c>
       <c r="W70" s="1">
         <f t="shared" ref="W70:W77" si="22">X70*10</f>
-        <v>490</v>
+        <v>650</v>
       </c>
       <c r="X70" s="1">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="Y70" s="1">
         <v>40</v>
@@ -8572,14 +8572,14 @@
         <v>160</v>
       </c>
       <c r="O71" s="1">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="P71" s="6">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="Q71" s="2">
-        <f t="shared" si="13"/>
-        <v>270</v>
+        <f t="shared" si="12"/>
+        <v>182</v>
       </c>
       <c r="R71" s="1">
         <v>0</v>
@@ -8595,14 +8595,14 @@
       </c>
       <c r="V71" s="1">
         <f t="shared" si="21"/>
-        <v>490</v>
+        <v>660</v>
       </c>
       <c r="W71" s="1">
         <f t="shared" si="22"/>
-        <v>490</v>
+        <v>660</v>
       </c>
       <c r="X71" s="1">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="Y71" s="1">
         <v>40</v>
@@ -8677,14 +8677,14 @@
         <v>160</v>
       </c>
       <c r="O72" s="1">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="P72" s="6">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="Q72" s="2">
-        <f t="shared" si="13"/>
-        <v>275</v>
+        <f t="shared" si="12"/>
+        <v>185</v>
       </c>
       <c r="R72" s="1">
         <v>0</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="V72" s="1">
         <f t="shared" si="21"/>
-        <v>490</v>
+        <v>670</v>
       </c>
       <c r="W72" s="1">
         <f t="shared" si="22"/>
-        <v>490</v>
+        <v>670</v>
       </c>
       <c r="X72" s="1">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="Y72" s="1">
         <v>40</v>
@@ -8782,14 +8782,14 @@
         <v>160</v>
       </c>
       <c r="O73" s="1">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="P73" s="6">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="Q73" s="2">
-        <f t="shared" si="13"/>
-        <v>280</v>
+        <f t="shared" si="12"/>
+        <v>188</v>
       </c>
       <c r="R73" s="1">
         <v>0</v>
@@ -8805,14 +8805,14 @@
       </c>
       <c r="V73" s="1">
         <f t="shared" si="21"/>
-        <v>490</v>
+        <v>680</v>
       </c>
       <c r="W73" s="1">
         <f t="shared" si="22"/>
-        <v>490</v>
+        <v>680</v>
       </c>
       <c r="X73" s="1">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="Y73" s="1">
         <v>40</v>
@@ -8887,14 +8887,14 @@
         <v>160</v>
       </c>
       <c r="O74" s="1">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="P74" s="6">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="Q74" s="2">
-        <f t="shared" si="13"/>
-        <v>285</v>
+        <f t="shared" si="12"/>
+        <v>191</v>
       </c>
       <c r="R74" s="1">
         <v>0</v>
@@ -8910,14 +8910,14 @@
       </c>
       <c r="V74" s="1">
         <f t="shared" si="21"/>
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="W74" s="1">
         <f t="shared" si="22"/>
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="X74" s="1">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="Y74" s="1">
         <v>40</v>
@@ -8992,14 +8992,14 @@
         <v>160</v>
       </c>
       <c r="O75" s="1">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="P75" s="6">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q75" s="2">
-        <f t="shared" si="13"/>
-        <v>290</v>
+        <f t="shared" si="12"/>
+        <v>194</v>
       </c>
       <c r="R75" s="1">
         <v>0</v>
@@ -9015,14 +9015,14 @@
       </c>
       <c r="V75" s="1">
         <f t="shared" si="21"/>
-        <v>490</v>
+        <v>700</v>
       </c>
       <c r="W75" s="1">
         <f t="shared" si="22"/>
-        <v>490</v>
+        <v>700</v>
       </c>
       <c r="X75" s="1">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="Y75" s="1">
         <v>40</v>
@@ -9097,14 +9097,14 @@
         <v>160</v>
       </c>
       <c r="O76" s="1">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="P76" s="6">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="Q76" s="2">
-        <f t="shared" si="13"/>
-        <v>295</v>
+        <f t="shared" si="12"/>
+        <v>197</v>
       </c>
       <c r="R76" s="1">
         <v>0</v>
@@ -9120,14 +9120,14 @@
       </c>
       <c r="V76" s="1">
         <f t="shared" si="21"/>
-        <v>490</v>
+        <v>710</v>
       </c>
       <c r="W76" s="1">
         <f t="shared" si="22"/>
-        <v>490</v>
+        <v>710</v>
       </c>
       <c r="X76" s="1">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="Y76" s="1">
         <v>40</v>
@@ -9202,14 +9202,14 @@
         <v>160</v>
       </c>
       <c r="O77" s="1">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="P77" s="6">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="Q77" s="2">
-        <f t="shared" si="13"/>
-        <v>300</v>
+        <f t="shared" si="12"/>
+        <v>200</v>
       </c>
       <c r="R77" s="1">
         <v>0</v>
@@ -9225,14 +9225,14 @@
       </c>
       <c r="V77" s="1">
         <f t="shared" si="21"/>
-        <v>490</v>
+        <v>720</v>
       </c>
       <c r="W77" s="1">
         <f t="shared" si="22"/>
-        <v>490</v>
+        <v>720</v>
       </c>
       <c r="X77" s="1">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="Y77" s="1">
         <v>40</v>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -1830,16 +1830,13 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <f>AG9*Z7*AA7/10</f>
-        <v>252</v>
+        <v>150</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J7" s="1">
-        <f>Y7*Z7*AC7</f>
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="1"/>
@@ -1933,16 +1930,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="1">
-        <f t="shared" ref="H7:H70" si="7">AG10*Z8*AA8/10</f>
-        <v>616</v>
+        <v>200</v>
       </c>
       <c r="I8" s="1">
-        <f t="shared" si="0"/>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J8" s="1">
-        <f>Y8*Z8*AC8</f>
-        <v>16800</v>
+        <v>3000</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="1"/>
@@ -1967,7 +1961,7 @@
         <v>3</v>
       </c>
       <c r="Q8" s="2">
-        <f t="shared" ref="Q8:Q45" si="8">Q7+2</f>
+        <f t="shared" ref="Q8:Q45" si="7">Q7+2</f>
         <v>12</v>
       </c>
       <c r="R8" s="1">
@@ -2037,16 +2031,13 @@
         <v>4</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" si="7"/>
-        <v>1040</v>
+        <v>300</v>
       </c>
       <c r="I9" s="1">
-        <f t="shared" si="0"/>
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" ref="J7:J72" si="9">Y9*Z9*AC9</f>
-        <v>38400</v>
+        <v>6000</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="1"/>
@@ -2071,7 +2062,7 @@
         <v>4</v>
       </c>
       <c r="Q9" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="R9" s="1">
@@ -2141,16 +2132,13 @@
         <v>5</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="7"/>
-        <v>1836</v>
+        <v>400</v>
       </c>
       <c r="I10" s="1">
-        <f t="shared" si="0"/>
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="9"/>
-        <v>90000</v>
+        <v>12000</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="1"/>
@@ -2175,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="R10" s="1">
@@ -2245,16 +2233,13 @@
         <v>6</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="7"/>
-        <v>2660</v>
+        <v>500</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="0"/>
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="9"/>
-        <v>168000</v>
+        <v>20000</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" si="1"/>
@@ -2279,7 +2264,7 @@
         <v>6</v>
       </c>
       <c r="Q11" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="R11" s="1">
@@ -2348,17 +2333,14 @@
       <c r="G12" s="1">
         <v>7</v>
       </c>
-      <c r="H12" s="1">
-        <f t="shared" si="7"/>
-        <v>4416</v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="0"/>
-        <v>1584</v>
-      </c>
-      <c r="J12" s="1">
-        <f t="shared" si="9"/>
-        <v>257040</v>
+      <c r="H12" s="2">
+        <v>700</v>
+      </c>
+      <c r="I12" s="2">
+        <v>490</v>
+      </c>
+      <c r="J12" s="2">
+        <v>35000</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="1"/>
@@ -2383,7 +2365,7 @@
         <v>7</v>
       </c>
       <c r="Q12" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="R12" s="1">
@@ -2423,7 +2405,7 @@
         <v>6</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" ref="AC8:AC75" si="10">AC11+AG11</f>
+        <f t="shared" ref="AC8:AC75" si="8">AC11+AG11</f>
         <v>153</v>
       </c>
       <c r="AD12" s="1">
@@ -2454,7 +2436,7 @@
         <v>8</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="H7:H70" si="9">AG15*Z13*AA13/10</f>
         <v>7308</v>
       </c>
       <c r="I13" s="1">
@@ -2462,7 +2444,7 @@
         <v>2548</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J7:J72" si="10">Y13*Z13*AC13</f>
         <v>380800</v>
       </c>
       <c r="K13" s="1">
@@ -2488,7 +2470,7 @@
         <v>8</v>
       </c>
       <c r="Q13" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="R13" s="1">
@@ -2528,7 +2510,7 @@
         <v>7</v>
       </c>
       <c r="AC13" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>170</v>
       </c>
       <c r="AD13" s="1">
@@ -2559,7 +2541,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>9920</v>
       </c>
       <c r="I14" s="1">
@@ -2567,7 +2549,7 @@
         <v>4352</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>544320</v>
       </c>
       <c r="K14" s="1">
@@ -2593,7 +2575,7 @@
         <v>9</v>
       </c>
       <c r="Q14" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="R14" s="1">
@@ -2633,7 +2615,7 @@
         <v>8</v>
       </c>
       <c r="AC14" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>189</v>
       </c>
       <c r="AD14" s="1">
@@ -2664,7 +2646,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>14652</v>
       </c>
       <c r="I15" s="1">
@@ -2672,7 +2654,7 @@
         <v>6156</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>763200</v>
       </c>
       <c r="K15" s="1">
@@ -2698,7 +2680,7 @@
         <v>10</v>
       </c>
       <c r="Q15" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="R15" s="1">
@@ -2738,7 +2720,7 @@
         <v>9</v>
       </c>
       <c r="AC15" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>212</v>
       </c>
       <c r="AD15" s="1">
@@ -2769,7 +2751,7 @@
         <v>11</v>
       </c>
       <c r="H16" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>21320</v>
       </c>
       <c r="I16" s="1">
@@ -2777,7 +2759,7 @@
         <v>9200</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1060400</v>
       </c>
       <c r="K16" s="1">
@@ -2803,7 +2785,7 @@
         <v>11</v>
       </c>
       <c r="Q16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="R16" s="1">
@@ -2843,7 +2825,7 @@
         <v>10</v>
       </c>
       <c r="AC16" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>241</v>
       </c>
       <c r="AD16" s="1">
@@ -2874,7 +2856,7 @@
         <v>12</v>
       </c>
       <c r="H17" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>36550</v>
       </c>
       <c r="I17" s="1">
@@ -2882,7 +2864,7 @@
         <v>15950</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1632000</v>
       </c>
       <c r="K17" s="1">
@@ -2908,7 +2890,7 @@
         <v>12</v>
       </c>
       <c r="Q17" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="R17" s="1">
@@ -2948,7 +2930,7 @@
         <v>11</v>
       </c>
       <c r="AC17" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>272</v>
       </c>
       <c r="AD17" s="1">
@@ -2979,7 +2961,7 @@
         <v>13</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>53580</v>
       </c>
       <c r="I18" s="1">
@@ -2987,7 +2969,7 @@
         <v>22320</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2410200</v>
       </c>
       <c r="K18" s="1">
@@ -3013,7 +2995,7 @@
         <v>13</v>
       </c>
       <c r="Q18" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
       <c r="R18" s="1">
@@ -3053,7 +3035,7 @@
         <v>12</v>
       </c>
       <c r="AC18" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>309</v>
       </c>
       <c r="AD18" s="1">
@@ -3084,7 +3066,7 @@
         <v>14</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>85330</v>
       </c>
       <c r="I19" s="1">
@@ -3092,7 +3074,7 @@
         <v>33670</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3430000</v>
       </c>
       <c r="K19" s="1">
@@ -3118,7 +3100,7 @@
         <v>14</v>
       </c>
       <c r="Q19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>34</v>
       </c>
       <c r="R19" s="1">
@@ -3158,7 +3140,7 @@
         <v>13</v>
       </c>
       <c r="AC19" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>350</v>
       </c>
       <c r="AD19" s="1">
@@ -3189,7 +3171,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>136880</v>
       </c>
       <c r="I20" s="1">
@@ -3197,7 +3179,7 @@
         <v>45920</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4716000</v>
       </c>
       <c r="K20" s="1">
@@ -3223,7 +3205,7 @@
         <v>15</v>
       </c>
       <c r="Q20" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
       <c r="R20" s="1">
@@ -3263,7 +3245,7 @@
         <v>14</v>
       </c>
       <c r="AC20" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>393</v>
       </c>
       <c r="AD20" s="1">
@@ -3294,7 +3276,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>170190</v>
       </c>
       <c r="I21" s="1">
@@ -3302,7 +3284,7 @@
         <v>58050</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6336000</v>
       </c>
       <c r="K21" s="1">
@@ -3328,7 +3310,7 @@
         <v>16</v>
       </c>
       <c r="Q21" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>38</v>
       </c>
       <c r="R21" s="1">
@@ -3368,7 +3350,7 @@
         <v>15</v>
       </c>
       <c r="AC21" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>440</v>
       </c>
       <c r="AD21" s="1">
@@ -3399,7 +3381,7 @@
         <v>17</v>
       </c>
       <c r="H22" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>247900</v>
       </c>
       <c r="I22" s="1">
@@ -3407,7 +3389,7 @@
         <v>75200</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8381000</v>
       </c>
       <c r="K22" s="1">
@@ -3433,7 +3415,7 @@
         <v>17</v>
       </c>
       <c r="Q22" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
       <c r="R22" s="1">
@@ -3473,7 +3455,7 @@
         <v>16</v>
       </c>
       <c r="AC22" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>493</v>
       </c>
       <c r="AD22" s="1">
@@ -3504,7 +3486,7 @@
         <v>18</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>349320</v>
       </c>
       <c r="I23" s="1">
@@ -3512,7 +3494,7 @@
         <v>108120</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11923200</v>
       </c>
       <c r="K23" s="1">
@@ -3538,7 +3520,7 @@
         <v>18</v>
       </c>
       <c r="Q23" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>42</v>
       </c>
       <c r="R23" s="1">
@@ -3578,7 +3560,7 @@
         <v>17</v>
       </c>
       <c r="AC23" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>552</v>
       </c>
       <c r="AD23" s="1">
@@ -3609,7 +3591,7 @@
         <v>19</v>
       </c>
       <c r="H24" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>439460</v>
       </c>
       <c r="I24" s="1">
@@ -3617,7 +3599,7 @@
         <v>148680</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>16305800</v>
       </c>
       <c r="K24" s="1">
@@ -3643,7 +3625,7 @@
         <v>19</v>
       </c>
       <c r="Q24" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
       <c r="R24" s="1">
@@ -3683,7 +3665,7 @@
         <v>18</v>
       </c>
       <c r="AC24" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>613</v>
       </c>
       <c r="AD24" s="1">
@@ -3714,7 +3696,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>594080</v>
       </c>
       <c r="I25" s="1">
@@ -3722,7 +3704,7 @@
         <v>185440</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21760000</v>
       </c>
       <c r="K25" s="1">
@@ -3748,7 +3730,7 @@
         <v>20</v>
       </c>
       <c r="Q25" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>46</v>
       </c>
       <c r="R25" s="1">
@@ -3788,7 +3770,7 @@
         <v>19</v>
       </c>
       <c r="AC25" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="AD25" s="1">
@@ -3819,7 +3801,7 @@
         <v>21</v>
       </c>
       <c r="H26" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>791820</v>
       </c>
       <c r="I26" s="1">
@@ -3827,7 +3809,7 @@
         <v>241200</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>28387800</v>
       </c>
       <c r="K26" s="1">
@@ -3853,7 +3835,7 @@
         <v>21</v>
       </c>
       <c r="Q26" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>48</v>
       </c>
       <c r="R26" s="1">
@@ -3893,7 +3875,7 @@
         <v>20</v>
       </c>
       <c r="AC26" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>751</v>
       </c>
       <c r="AD26" s="1">
@@ -3924,7 +3906,7 @@
         <v>22</v>
       </c>
       <c r="H27" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1050200</v>
       </c>
       <c r="I27" s="1">
@@ -3932,7 +3914,7 @@
         <v>298200</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>36256000</v>
       </c>
       <c r="K27" s="1">
@@ -3958,7 +3940,7 @@
         <v>22</v>
       </c>
       <c r="Q27" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="R27" s="1">
@@ -3998,7 +3980,7 @@
         <v>21</v>
       </c>
       <c r="AC27" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>824</v>
       </c>
       <c r="AD27" s="1">
@@ -4029,7 +4011,7 @@
         <v>23</v>
       </c>
       <c r="H28" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1479250</v>
       </c>
       <c r="I28" s="1">
@@ -4037,7 +4019,7 @@
         <v>401500</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>51922500</v>
       </c>
       <c r="K28" s="1">
@@ -4103,7 +4085,7 @@
         <v>22</v>
       </c>
       <c r="AC28" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>903</v>
       </c>
       <c r="AD28" s="1">
@@ -4134,7 +4116,7 @@
         <v>24</v>
       </c>
       <c r="H29" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2030100</v>
       </c>
       <c r="I29" s="1">
@@ -4142,7 +4124,7 @@
         <v>545100</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>70992000</v>
       </c>
       <c r="K29" s="1">
@@ -4208,7 +4190,7 @@
         <v>23</v>
       </c>
       <c r="AC29" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>986</v>
       </c>
       <c r="AD29" s="1">
@@ -4239,7 +4221,7 @@
         <v>25</v>
       </c>
       <c r="H30" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2559550</v>
       </c>
       <c r="I30" s="1">
@@ -4247,7 +4229,7 @@
         <v>697200</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>94062500</v>
       </c>
       <c r="K30" s="1">
@@ -4313,7 +4295,7 @@
         <v>24</v>
       </c>
       <c r="AC30" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1075</v>
       </c>
       <c r="AD30" s="1">
@@ -4344,7 +4326,7 @@
         <v>26</v>
       </c>
       <c r="H31" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3124400</v>
       </c>
       <c r="I31" s="1">
@@ -4352,7 +4334,7 @@
         <v>890000</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>121888000</v>
       </c>
       <c r="K31" s="1">
@@ -4418,7 +4400,7 @@
         <v>25</v>
       </c>
       <c r="AC31" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1172</v>
       </c>
       <c r="AD31" s="1">
@@ -4449,7 +4431,7 @@
         <v>27</v>
       </c>
       <c r="H32" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3874950</v>
       </c>
       <c r="I32" s="1">
@@ -4457,7 +4439,7 @@
         <v>1134900</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>154669500</v>
       </c>
       <c r="K32" s="1">
@@ -4523,7 +4505,7 @@
         <v>26</v>
       </c>
       <c r="AC32" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1273</v>
       </c>
       <c r="AD32" s="1">
@@ -4554,7 +4536,7 @@
         <v>28</v>
       </c>
       <c r="H33" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4689500</v>
       </c>
       <c r="I33" s="1">
@@ -4562,7 +4544,7 @@
         <v>1363500</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>192640000</v>
       </c>
       <c r="K33" s="1">
@@ -4628,7 +4610,7 @@
         <v>27</v>
       </c>
       <c r="AC33" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1376</v>
       </c>
       <c r="AD33" s="1">
@@ -4659,7 +4641,7 @@
         <v>29</v>
       </c>
       <c r="H34" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6781800</v>
       </c>
       <c r="I34" s="1">
@@ -4667,7 +4649,7 @@
         <v>1730400</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>258042000</v>
       </c>
       <c r="K34" s="1">
@@ -4733,7 +4715,7 @@
         <v>28</v>
       </c>
       <c r="AC34" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1483</v>
       </c>
       <c r="AD34" s="1">
@@ -4764,7 +4746,7 @@
         <v>30</v>
       </c>
       <c r="H35" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>8894900</v>
       </c>
       <c r="I35" s="1">
@@ -4772,7 +4754,7 @@
         <v>2172100</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>334320000</v>
       </c>
       <c r="K35" s="1">
@@ -4838,7 +4820,7 @@
         <v>29</v>
       </c>
       <c r="AC35" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1592</v>
       </c>
       <c r="AD35" s="1">
@@ -4869,7 +4851,7 @@
         <v>31</v>
       </c>
       <c r="H36" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>11069600</v>
       </c>
       <c r="I36" s="1">
@@ -4877,7 +4859,7 @@
         <v>2616000</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>422840000</v>
       </c>
       <c r="K36" s="1">
@@ -4943,7 +4925,7 @@
         <v>30</v>
       </c>
       <c r="AC36" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1705</v>
       </c>
       <c r="AD36" s="1">
@@ -4974,7 +4956,7 @@
         <v>32</v>
       </c>
       <c r="H37" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>12885300</v>
       </c>
       <c r="I37" s="1">
@@ -4982,7 +4964,7 @@
         <v>3152700</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>527616000</v>
       </c>
       <c r="K37" s="1">
@@ -5048,7 +5030,7 @@
         <v>31</v>
       </c>
       <c r="AC37" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1832</v>
       </c>
       <c r="AD37" s="1">
@@ -5079,7 +5061,7 @@
         <v>33</v>
       </c>
       <c r="H38" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>15943000</v>
       </c>
       <c r="I38" s="1">
@@ -5087,7 +5069,7 @@
         <v>4064000</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>647790000</v>
       </c>
       <c r="K38" s="1">
@@ -5153,7 +5135,7 @@
         <v>32</v>
       </c>
       <c r="AC38" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>1963</v>
       </c>
       <c r="AD38" s="1">
@@ -5184,7 +5166,7 @@
         <v>34</v>
       </c>
       <c r="H39" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>19750800</v>
       </c>
       <c r="I39" s="1">
@@ -5192,7 +5174,7 @@
         <v>5187600</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>856800000</v>
       </c>
       <c r="K39" s="1">
@@ -5258,7 +5240,7 @@
         <v>33</v>
       </c>
       <c r="AC39" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2100</v>
       </c>
       <c r="AD39" s="1">
@@ -5289,7 +5271,7 @@
         <v>35</v>
       </c>
       <c r="H40" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>24837400</v>
       </c>
       <c r="I40" s="1">
@@ -5297,7 +5279,7 @@
         <v>6521200</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1097110000</v>
       </c>
       <c r="K40" s="1">
@@ -5363,7 +5345,7 @@
         <v>34</v>
       </c>
       <c r="AC40" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2239</v>
       </c>
       <c r="AD40" s="1">
@@ -5395,7 +5377,7 @@
         <v>36</v>
       </c>
       <c r="H41" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>33121600</v>
       </c>
       <c r="I41" s="1">
@@ -5403,7 +5385,7 @@
         <v>7784000</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1375488000</v>
       </c>
       <c r="K41" s="1">
@@ -5469,7 +5451,7 @@
         <v>35</v>
       </c>
       <c r="AC41" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2388</v>
       </c>
       <c r="AD41" s="1">
@@ -5500,7 +5482,7 @@
         <v>37</v>
       </c>
       <c r="H42" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>39378600</v>
       </c>
       <c r="I42" s="1">
@@ -5508,7 +5490,7 @@
         <v>9655200</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1690974000</v>
       </c>
       <c r="K42" s="1">
@@ -5574,7 +5556,7 @@
         <v>36</v>
       </c>
       <c r="AC42" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2539</v>
       </c>
       <c r="AD42" s="1">
@@ -5605,7 +5587,7 @@
         <v>38</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>47402000</v>
       </c>
       <c r="I43" s="1">
@@ -5613,7 +5595,7 @@
         <v>11174000</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2048960000</v>
       </c>
       <c r="K43" s="1">
@@ -5679,7 +5661,7 @@
         <v>37</v>
       </c>
       <c r="AC43" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2696</v>
       </c>
       <c r="AD43" s="1">
@@ -5710,7 +5692,7 @@
         <v>39</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>62202500</v>
       </c>
       <c r="I44" s="1">
@@ -5718,7 +5700,7 @@
         <v>14915000</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2787525000</v>
       </c>
       <c r="K44" s="1">
@@ -5784,7 +5766,7 @@
         <v>38</v>
       </c>
       <c r="AC44" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2859</v>
       </c>
       <c r="AD44" s="1">
@@ -5815,7 +5797,7 @@
         <v>40</v>
       </c>
       <c r="H45" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>80907000</v>
       </c>
       <c r="I45" s="1">
@@ -5823,7 +5805,7 @@
         <v>19071000</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3631200000</v>
       </c>
       <c r="K45" s="1">
@@ -5889,7 +5871,7 @@
         <v>39</v>
       </c>
       <c r="AC45" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3026</v>
       </c>
       <c r="AD45" s="1">
@@ -5920,7 +5902,7 @@
         <v>41</v>
       </c>
       <c r="H46" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>100943500</v>
       </c>
       <c r="I46" s="1">
@@ -5928,7 +5910,7 @@
         <v>22795500</v>
       </c>
       <c r="J46" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4478600000</v>
       </c>
       <c r="K46" s="1">
@@ -5994,7 +5976,7 @@
         <v>39</v>
       </c>
       <c r="AC46" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3199</v>
       </c>
       <c r="AD46" s="1">
@@ -6024,7 +6006,7 @@
         <v>42</v>
       </c>
       <c r="H47" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>116572000</v>
       </c>
       <c r="I47" s="1">
@@ -6032,7 +6014,7 @@
         <v>26988000</v>
       </c>
       <c r="J47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5404800000</v>
       </c>
       <c r="K47" s="1">
@@ -6098,7 +6080,7 @@
         <v>39</v>
       </c>
       <c r="AC47" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3378</v>
       </c>
       <c r="AD47" s="1">
@@ -6129,7 +6111,7 @@
         <v>43</v>
       </c>
       <c r="H48" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>139180500</v>
       </c>
       <c r="I48" s="1">
@@ -6137,7 +6119,7 @@
         <v>31414500</v>
       </c>
       <c r="J48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6406200000</v>
       </c>
       <c r="K48" s="1">
@@ -6203,7 +6185,7 @@
         <v>39</v>
       </c>
       <c r="AC48" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3559</v>
       </c>
       <c r="AD48" s="1">
@@ -6234,7 +6216,7 @@
         <v>44</v>
       </c>
       <c r="H49" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>172135000</v>
       </c>
       <c r="I49" s="1">
@@ -6242,7 +6224,7 @@
         <v>35295000</v>
       </c>
       <c r="J49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7500000000</v>
       </c>
       <c r="K49" s="1">
@@ -6308,7 +6290,7 @@
         <v>39</v>
       </c>
       <c r="AC49" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3750</v>
       </c>
       <c r="AD49" s="1">
@@ -6339,7 +6321,7 @@
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>200766500</v>
       </c>
       <c r="I50" s="1">
@@ -6347,7 +6329,7 @@
         <v>40969500</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8674600000</v>
       </c>
       <c r="K50" s="1">
@@ -6413,7 +6395,7 @@
         <v>39</v>
       </c>
       <c r="AC50" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3943</v>
       </c>
       <c r="AD50" s="1">
@@ -6444,7 +6426,7 @@
         <v>46</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>231474000</v>
       </c>
       <c r="I51" s="1">
@@ -6452,7 +6434,7 @@
         <v>45162000</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9936000000</v>
       </c>
       <c r="K51" s="1">
@@ -6518,7 +6500,7 @@
         <v>39</v>
       </c>
       <c r="AC51" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>4140</v>
       </c>
       <c r="AD51" s="1">
@@ -6549,7 +6531,7 @@
         <v>47</v>
       </c>
       <c r="H52" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>255261500</v>
       </c>
       <c r="I52" s="1">
@@ -6557,7 +6539,7 @@
         <v>49939500</v>
       </c>
       <c r="J52" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11281400000</v>
       </c>
       <c r="K52" s="1">
@@ -6623,7 +6605,7 @@
         <v>39</v>
       </c>
       <c r="AC52" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>4339</v>
       </c>
       <c r="AD52" s="1">
@@ -6654,7 +6636,7 @@
         <v>48</v>
       </c>
       <c r="H53" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>277319000</v>
       </c>
       <c r="I53" s="1">
@@ -6662,7 +6644,7 @@
         <v>54327000</v>
       </c>
       <c r="J53" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12740000000</v>
       </c>
       <c r="K53" s="1">
@@ -6728,7 +6710,7 @@
         <v>39</v>
       </c>
       <c r="AC53" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>4550</v>
       </c>
       <c r="AD53" s="1">
@@ -6759,7 +6741,7 @@
         <v>49</v>
       </c>
       <c r="H54" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>302317500</v>
       </c>
       <c r="I54" s="1">
@@ -6767,7 +6749,7 @@
         <v>61717500</v>
       </c>
       <c r="J54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14319000000</v>
       </c>
       <c r="K54" s="1">
@@ -6833,7 +6815,7 @@
         <v>39</v>
       </c>
       <c r="AC54" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>4773</v>
       </c>
       <c r="AD54" s="1">
@@ -6864,7 +6846,7 @@
         <v>50</v>
       </c>
       <c r="H55" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>330776000</v>
       </c>
       <c r="I55" s="1">
@@ -6872,7 +6854,7 @@
         <v>69576000</v>
       </c>
       <c r="J55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>16000000000</v>
       </c>
       <c r="K55" s="1">
@@ -6938,7 +6920,7 @@
         <v>39</v>
       </c>
       <c r="AC55" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>5000</v>
       </c>
       <c r="AD55" s="1">
@@ -6969,7 +6951,7 @@
         <v>51</v>
       </c>
       <c r="H56" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>354390500</v>
       </c>
       <c r="I56" s="1">
@@ -6977,7 +6959,7 @@
         <v>75250500</v>
       </c>
       <c r="J56" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>17778600000</v>
       </c>
       <c r="K56" s="1">
@@ -7043,7 +7025,7 @@
         <v>39</v>
       </c>
       <c r="AC56" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>5229</v>
       </c>
       <c r="AD56" s="1">
@@ -7074,7 +7056,7 @@
         <v>52</v>
       </c>
       <c r="H57" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>390807000</v>
       </c>
       <c r="I57" s="1">
@@ -7082,7 +7064,7 @@
         <v>80379000</v>
       </c>
       <c r="J57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>19663200000</v>
       </c>
       <c r="K57" s="1">
@@ -7148,7 +7130,7 @@
         <v>39</v>
       </c>
       <c r="AC57" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>5462</v>
       </c>
       <c r="AD57" s="1">
@@ -7179,7 +7161,7 @@
         <v>53</v>
       </c>
       <c r="H58" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>422379500</v>
       </c>
       <c r="I58" s="1">
@@ -7187,7 +7169,7 @@
         <v>86326500</v>
       </c>
       <c r="J58" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21663800000</v>
       </c>
       <c r="K58" s="1">
@@ -7253,7 +7235,7 @@
         <v>39</v>
       </c>
       <c r="AC58" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>5701</v>
       </c>
       <c r="AD58" s="1">
@@ -7284,7 +7266,7 @@
         <v>54</v>
       </c>
       <c r="H59" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>454990000</v>
       </c>
       <c r="I59" s="1">
@@ -7292,7 +7274,7 @@
         <v>93210000</v>
       </c>
       <c r="J59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>23768000000</v>
       </c>
       <c r="K59" s="1">
@@ -7358,7 +7340,7 @@
         <v>39</v>
       </c>
       <c r="AC59" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>5942</v>
       </c>
       <c r="AD59" s="1">
@@ -7389,7 +7371,7 @@
         <v>55</v>
       </c>
       <c r="H60" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>488638500</v>
       </c>
       <c r="I60" s="1">
@@ -7397,7 +7379,7 @@
         <v>98689500</v>
       </c>
       <c r="J60" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>26010600000</v>
       </c>
       <c r="K60" s="1">
@@ -7463,7 +7445,7 @@
         <v>39</v>
       </c>
       <c r="AC60" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>6193</v>
       </c>
       <c r="AD60" s="1">
@@ -7494,7 +7476,7 @@
         <v>56</v>
       </c>
       <c r="H61" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>515713000</v>
       </c>
       <c r="I61" s="1">
@@ -7502,7 +7484,7 @@
         <v>107679000</v>
       </c>
       <c r="J61" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>28380000000</v>
       </c>
       <c r="K61" s="1">
@@ -7568,7 +7550,7 @@
         <v>39</v>
       </c>
       <c r="AC61" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>6450</v>
       </c>
       <c r="AD61" s="1">
@@ -7599,7 +7581,7 @@
         <v>57</v>
       </c>
       <c r="H62" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>551091500</v>
       </c>
       <c r="I62" s="1">
@@ -7607,7 +7589,7 @@
         <v>115264500</v>
       </c>
       <c r="J62" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30879800000</v>
       </c>
       <c r="K62" s="1">
@@ -7673,7 +7655,7 @@
         <v>39</v>
       </c>
       <c r="AC62" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>6713</v>
       </c>
       <c r="AD62" s="1">
@@ -7704,7 +7686,7 @@
         <v>58</v>
       </c>
       <c r="H63" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>583356000</v>
       </c>
       <c r="I63" s="1">
@@ -7712,7 +7694,7 @@
         <v>123084000</v>
       </c>
       <c r="J63" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>33513600000</v>
       </c>
       <c r="K63" s="1">
@@ -7778,7 +7760,7 @@
         <v>39</v>
       </c>
       <c r="AC63" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>6982</v>
       </c>
       <c r="AD63" s="1">
@@ -7809,7 +7791,7 @@
         <v>59</v>
       </c>
       <c r="H64" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>611987500</v>
       </c>
       <c r="I64" s="1">
@@ -7817,7 +7799,7 @@
         <v>131137500</v>
       </c>
       <c r="J64" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>36265000000</v>
       </c>
       <c r="K64" s="1">
@@ -7883,7 +7865,7 @@
         <v>39</v>
       </c>
       <c r="AC64" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>7253</v>
       </c>
       <c r="AD64" s="1">
@@ -7914,7 +7896,7 @@
         <v>60</v>
       </c>
       <c r="H65" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>658957000</v>
       </c>
       <c r="I65" s="1">
@@ -7922,7 +7904,7 @@
         <v>137397000</v>
       </c>
       <c r="J65" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>39156000000</v>
       </c>
       <c r="K65" s="1">
@@ -7988,7 +7970,7 @@
         <v>39</v>
       </c>
       <c r="AC65" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>7530</v>
       </c>
       <c r="AD65" s="1">
@@ -8019,7 +8001,7 @@
         <v>61</v>
       </c>
       <c r="H66" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>716998500</v>
       </c>
       <c r="I66" s="1">
@@ -8027,7 +8009,7 @@
         <v>145840500</v>
       </c>
       <c r="J66" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>42179400000</v>
       </c>
       <c r="K66" s="1">
@@ -8093,7 +8075,7 @@
         <v>39</v>
       </c>
       <c r="AC66" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>7811</v>
       </c>
       <c r="AD66" s="1">
@@ -8124,7 +8106,7 @@
         <v>62</v>
       </c>
       <c r="H67" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>753242000</v>
       </c>
       <c r="I67" s="1">
@@ -8132,7 +8114,7 @@
         <v>153426000</v>
       </c>
       <c r="J67" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>45326400000</v>
       </c>
       <c r="K67" s="1">
@@ -8198,7 +8180,7 @@
         <v>39</v>
       </c>
       <c r="AC67" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>8094</v>
       </c>
       <c r="AD67" s="1">
@@ -8229,7 +8211,7 @@
         <v>63</v>
       </c>
       <c r="H68" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>785160500</v>
       </c>
       <c r="I68" s="1">
@@ -8237,7 +8219,7 @@
         <v>160036500</v>
       </c>
       <c r="J68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>48644600000</v>
       </c>
       <c r="K68" s="1">
@@ -8303,7 +8285,7 @@
         <v>39</v>
       </c>
       <c r="AC68" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>8387</v>
       </c>
       <c r="AD68" s="1">
@@ -8334,7 +8316,7 @@
         <v>64</v>
       </c>
       <c r="H69" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>822615000</v>
       </c>
       <c r="I69" s="1">
@@ -8342,7 +8324,7 @@
         <v>171405000</v>
       </c>
       <c r="J69" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>52164000000</v>
       </c>
       <c r="K69" s="1">
@@ -8408,7 +8390,7 @@
         <v>39</v>
       </c>
       <c r="AC69" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>8694</v>
       </c>
       <c r="AD69" s="1">
@@ -8439,7 +8421,7 @@
         <v>65</v>
       </c>
       <c r="H70" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>887576500</v>
       </c>
       <c r="I70" s="1">
@@ -8447,7 +8429,7 @@
         <v>185581500</v>
       </c>
       <c r="J70" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>55831000000</v>
       </c>
       <c r="K70" s="1">
@@ -8513,7 +8495,7 @@
         <v>39</v>
       </c>
       <c r="AC70" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>9005</v>
       </c>
       <c r="AD70" s="1">
@@ -8552,7 +8534,7 @@
         <v>194064000</v>
       </c>
       <c r="J71" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>59635200000</v>
       </c>
       <c r="K71" s="1">
@@ -8618,7 +8600,7 @@
         <v>39</v>
       </c>
       <c r="AC71" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>9318</v>
       </c>
       <c r="AD71" s="1">
@@ -8657,7 +8639,7 @@
         <v>201415500</v>
       </c>
       <c r="J72" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>63591000000</v>
       </c>
       <c r="K72" s="1">
@@ -8723,7 +8705,7 @@
         <v>39</v>
       </c>
       <c r="AC72" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>9635</v>
       </c>
       <c r="AD72" s="1">
@@ -8828,7 +8810,7 @@
         <v>39</v>
       </c>
       <c r="AC73" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>9966</v>
       </c>
       <c r="AD73" s="1">
@@ -8933,7 +8915,7 @@
         <v>39</v>
       </c>
       <c r="AC74" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>10303</v>
       </c>
       <c r="AD74" s="1">
@@ -9038,7 +9020,7 @@
         <v>39</v>
       </c>
       <c r="AC75" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>10650</v>
       </c>
       <c r="AD75" s="1">

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" ht="14" spans="1:33">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="1">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="I8" s="1">
         <v>60</v>
@@ -2031,7 +2031,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="I9" s="1">
         <v>120</v>
@@ -2132,7 +2132,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="1">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I10" s="1">
         <v>200</v>
@@ -2233,7 +2233,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="1">
-        <v>500</v>
+        <v>1900</v>
       </c>
       <c r="I11" s="1">
         <v>300</v>
@@ -2334,7 +2334,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="2">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="I12" s="2">
         <v>490</v>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -2436,16 +2436,13 @@
         <v>8</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" ref="H7:H70" si="9">AG15*Z13*AA13/10</f>
-        <v>7308</v>
+        <v>4500</v>
       </c>
       <c r="I13" s="1">
-        <f t="shared" si="0"/>
-        <v>2548</v>
+        <v>700</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" ref="J7:J72" si="10">Y13*Z13*AC13</f>
-        <v>380800</v>
+        <v>58000</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="1"/>
@@ -2541,16 +2538,13 @@
         <v>9</v>
       </c>
       <c r="H14" s="1">
-        <f t="shared" si="9"/>
-        <v>9920</v>
+        <v>6500</v>
       </c>
       <c r="I14" s="1">
-        <f t="shared" si="0"/>
-        <v>4352</v>
+        <v>1000</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" si="10"/>
-        <v>544320</v>
+        <v>90000</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="1"/>
@@ -2646,16 +2640,13 @@
         <v>10</v>
       </c>
       <c r="H15" s="1">
-        <f t="shared" si="9"/>
-        <v>14652</v>
+        <v>9000</v>
       </c>
       <c r="I15" s="1">
-        <f t="shared" si="0"/>
-        <v>6156</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="10"/>
-        <v>763200</v>
+        <v>140000</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="1"/>
@@ -2751,16 +2742,13 @@
         <v>11</v>
       </c>
       <c r="H16" s="1">
-        <f t="shared" si="9"/>
-        <v>21320</v>
+        <v>13000</v>
       </c>
       <c r="I16" s="1">
-        <f t="shared" si="0"/>
-        <v>9200</v>
+        <v>2400</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="10"/>
-        <v>1060400</v>
+        <v>200000</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="1"/>
@@ -2856,16 +2844,13 @@
         <v>12</v>
       </c>
       <c r="H17" s="1">
-        <f t="shared" si="9"/>
-        <v>36550</v>
+        <v>19000</v>
       </c>
       <c r="I17" s="1">
-        <f t="shared" si="0"/>
-        <v>15950</v>
+        <v>3600</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="10"/>
-        <v>1632000</v>
+        <v>300000</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="1"/>
@@ -2920,7 +2905,7 @@
         <v>12</v>
       </c>
       <c r="Z17" s="2">
-        <f t="shared" ref="Z17:Z22" si="11">Z16+100</f>
+        <f t="shared" ref="Z17:Z22" si="9">Z16+100</f>
         <v>500</v>
       </c>
       <c r="AA17" s="2">
@@ -2961,7 +2946,7 @@
         <v>13</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="H7:H70" si="10">AG20*Z18*AA18/10</f>
         <v>53580</v>
       </c>
       <c r="I18" s="1">
@@ -2969,7 +2954,7 @@
         <v>22320</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="J7:J72" si="11">Y18*Z18*AC18</f>
         <v>2410200</v>
       </c>
       <c r="K18" s="1">
@@ -3025,7 +3010,7 @@
         <v>13</v>
       </c>
       <c r="Z18" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>600</v>
       </c>
       <c r="AA18" s="2">
@@ -3066,7 +3051,7 @@
         <v>14</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>85330</v>
       </c>
       <c r="I19" s="1">
@@ -3074,7 +3059,7 @@
         <v>33670</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3430000</v>
       </c>
       <c r="K19" s="1">
@@ -3130,7 +3115,7 @@
         <v>14</v>
       </c>
       <c r="Z19" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>700</v>
       </c>
       <c r="AA19" s="2">
@@ -3171,7 +3156,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>136880</v>
       </c>
       <c r="I20" s="1">
@@ -3179,7 +3164,7 @@
         <v>45920</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4716000</v>
       </c>
       <c r="K20" s="1">
@@ -3235,7 +3220,7 @@
         <v>15</v>
       </c>
       <c r="Z20" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>800</v>
       </c>
       <c r="AA20" s="2">
@@ -3276,7 +3261,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>170190</v>
       </c>
       <c r="I21" s="1">
@@ -3284,7 +3269,7 @@
         <v>58050</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6336000</v>
       </c>
       <c r="K21" s="1">
@@ -3340,7 +3325,7 @@
         <v>16</v>
       </c>
       <c r="Z21" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>900</v>
       </c>
       <c r="AA21" s="2">
@@ -3381,7 +3366,7 @@
         <v>17</v>
       </c>
       <c r="H22" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>247900</v>
       </c>
       <c r="I22" s="1">
@@ -3389,7 +3374,7 @@
         <v>75200</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8381000</v>
       </c>
       <c r="K22" s="1">
@@ -3445,7 +3430,7 @@
         <v>17</v>
       </c>
       <c r="Z22" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="AA22" s="2">
@@ -3486,7 +3471,7 @@
         <v>18</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>349320</v>
       </c>
       <c r="I23" s="1">
@@ -3494,7 +3479,7 @@
         <v>108120</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>11923200</v>
       </c>
       <c r="K23" s="1">
@@ -3591,7 +3576,7 @@
         <v>19</v>
       </c>
       <c r="H24" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>439460</v>
       </c>
       <c r="I24" s="1">
@@ -3599,7 +3584,7 @@
         <v>148680</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>16305800</v>
       </c>
       <c r="K24" s="1">
@@ -3696,7 +3681,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>594080</v>
       </c>
       <c r="I25" s="1">
@@ -3704,7 +3689,7 @@
         <v>185440</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>21760000</v>
       </c>
       <c r="K25" s="1">
@@ -3801,7 +3786,7 @@
         <v>21</v>
       </c>
       <c r="H26" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>791820</v>
       </c>
       <c r="I26" s="1">
@@ -3809,7 +3794,7 @@
         <v>241200</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>28387800</v>
       </c>
       <c r="K26" s="1">
@@ -3906,7 +3891,7 @@
         <v>22</v>
       </c>
       <c r="H27" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1050200</v>
       </c>
       <c r="I27" s="1">
@@ -3914,7 +3899,7 @@
         <v>298200</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>36256000</v>
       </c>
       <c r="K27" s="1">
@@ -4011,7 +3996,7 @@
         <v>23</v>
       </c>
       <c r="H28" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1479250</v>
       </c>
       <c r="I28" s="1">
@@ -4019,7 +4004,7 @@
         <v>401500</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51922500</v>
       </c>
       <c r="K28" s="1">
@@ -4116,7 +4101,7 @@
         <v>24</v>
       </c>
       <c r="H29" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2030100</v>
       </c>
       <c r="I29" s="1">
@@ -4124,7 +4109,7 @@
         <v>545100</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>70992000</v>
       </c>
       <c r="K29" s="1">
@@ -4221,7 +4206,7 @@
         <v>25</v>
       </c>
       <c r="H30" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2559550</v>
       </c>
       <c r="I30" s="1">
@@ -4229,7 +4214,7 @@
         <v>697200</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>94062500</v>
       </c>
       <c r="K30" s="1">
@@ -4326,7 +4311,7 @@
         <v>26</v>
       </c>
       <c r="H31" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3124400</v>
       </c>
       <c r="I31" s="1">
@@ -4334,7 +4319,7 @@
         <v>890000</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>121888000</v>
       </c>
       <c r="K31" s="1">
@@ -4431,7 +4416,7 @@
         <v>27</v>
       </c>
       <c r="H32" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3874950</v>
       </c>
       <c r="I32" s="1">
@@ -4439,7 +4424,7 @@
         <v>1134900</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>154669500</v>
       </c>
       <c r="K32" s="1">
@@ -4536,7 +4521,7 @@
         <v>28</v>
       </c>
       <c r="H33" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4689500</v>
       </c>
       <c r="I33" s="1">
@@ -4544,7 +4529,7 @@
         <v>1363500</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>192640000</v>
       </c>
       <c r="K33" s="1">
@@ -4641,7 +4626,7 @@
         <v>29</v>
       </c>
       <c r="H34" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6781800</v>
       </c>
       <c r="I34" s="1">
@@ -4649,7 +4634,7 @@
         <v>1730400</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>258042000</v>
       </c>
       <c r="K34" s="1">
@@ -4746,7 +4731,7 @@
         <v>30</v>
       </c>
       <c r="H35" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8894900</v>
       </c>
       <c r="I35" s="1">
@@ -4754,7 +4739,7 @@
         <v>2172100</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>334320000</v>
       </c>
       <c r="K35" s="1">
@@ -4851,7 +4836,7 @@
         <v>31</v>
       </c>
       <c r="H36" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11069600</v>
       </c>
       <c r="I36" s="1">
@@ -4859,7 +4844,7 @@
         <v>2616000</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>422840000</v>
       </c>
       <c r="K36" s="1">
@@ -4956,7 +4941,7 @@
         <v>32</v>
       </c>
       <c r="H37" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12885300</v>
       </c>
       <c r="I37" s="1">
@@ -4964,7 +4949,7 @@
         <v>3152700</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>527616000</v>
       </c>
       <c r="K37" s="1">
@@ -5061,7 +5046,7 @@
         <v>33</v>
       </c>
       <c r="H38" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>15943000</v>
       </c>
       <c r="I38" s="1">
@@ -5069,7 +5054,7 @@
         <v>4064000</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>647790000</v>
       </c>
       <c r="K38" s="1">
@@ -5166,7 +5151,7 @@
         <v>34</v>
       </c>
       <c r="H39" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>19750800</v>
       </c>
       <c r="I39" s="1">
@@ -5174,7 +5159,7 @@
         <v>5187600</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>856800000</v>
       </c>
       <c r="K39" s="1">
@@ -5271,7 +5256,7 @@
         <v>35</v>
       </c>
       <c r="H40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>24837400</v>
       </c>
       <c r="I40" s="1">
@@ -5279,7 +5264,7 @@
         <v>6521200</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1097110000</v>
       </c>
       <c r="K40" s="1">
@@ -5377,7 +5362,7 @@
         <v>36</v>
       </c>
       <c r="H41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>33121600</v>
       </c>
       <c r="I41" s="1">
@@ -5385,7 +5370,7 @@
         <v>7784000</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1375488000</v>
       </c>
       <c r="K41" s="1">
@@ -5482,7 +5467,7 @@
         <v>37</v>
       </c>
       <c r="H42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>39378600</v>
       </c>
       <c r="I42" s="1">
@@ -5490,7 +5475,7 @@
         <v>9655200</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1690974000</v>
       </c>
       <c r="K42" s="1">
@@ -5587,7 +5572,7 @@
         <v>38</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>47402000</v>
       </c>
       <c r="I43" s="1">
@@ -5595,7 +5580,7 @@
         <v>11174000</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2048960000</v>
       </c>
       <c r="K43" s="1">
@@ -5692,7 +5677,7 @@
         <v>39</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>62202500</v>
       </c>
       <c r="I44" s="1">
@@ -5700,7 +5685,7 @@
         <v>14915000</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2787525000</v>
       </c>
       <c r="K44" s="1">
@@ -5797,7 +5782,7 @@
         <v>40</v>
       </c>
       <c r="H45" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>80907000</v>
       </c>
       <c r="I45" s="1">
@@ -5805,7 +5790,7 @@
         <v>19071000</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3631200000</v>
       </c>
       <c r="K45" s="1">
@@ -5902,7 +5887,7 @@
         <v>41</v>
       </c>
       <c r="H46" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>100943500</v>
       </c>
       <c r="I46" s="1">
@@ -5910,7 +5895,7 @@
         <v>22795500</v>
       </c>
       <c r="J46" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4478600000</v>
       </c>
       <c r="K46" s="1">
@@ -6006,7 +5991,7 @@
         <v>42</v>
       </c>
       <c r="H47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>116572000</v>
       </c>
       <c r="I47" s="1">
@@ -6014,7 +5999,7 @@
         <v>26988000</v>
       </c>
       <c r="J47" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5404800000</v>
       </c>
       <c r="K47" s="1">
@@ -6111,7 +6096,7 @@
         <v>43</v>
       </c>
       <c r="H48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>139180500</v>
       </c>
       <c r="I48" s="1">
@@ -6119,7 +6104,7 @@
         <v>31414500</v>
       </c>
       <c r="J48" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6406200000</v>
       </c>
       <c r="K48" s="1">
@@ -6216,7 +6201,7 @@
         <v>44</v>
       </c>
       <c r="H49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>172135000</v>
       </c>
       <c r="I49" s="1">
@@ -6224,7 +6209,7 @@
         <v>35295000</v>
       </c>
       <c r="J49" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7500000000</v>
       </c>
       <c r="K49" s="1">
@@ -6321,7 +6306,7 @@
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>200766500</v>
       </c>
       <c r="I50" s="1">
@@ -6329,7 +6314,7 @@
         <v>40969500</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8674600000</v>
       </c>
       <c r="K50" s="1">
@@ -6426,7 +6411,7 @@
         <v>46</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>231474000</v>
       </c>
       <c r="I51" s="1">
@@ -6434,7 +6419,7 @@
         <v>45162000</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9936000000</v>
       </c>
       <c r="K51" s="1">
@@ -6531,7 +6516,7 @@
         <v>47</v>
       </c>
       <c r="H52" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>255261500</v>
       </c>
       <c r="I52" s="1">
@@ -6539,7 +6524,7 @@
         <v>49939500</v>
       </c>
       <c r="J52" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>11281400000</v>
       </c>
       <c r="K52" s="1">
@@ -6636,7 +6621,7 @@
         <v>48</v>
       </c>
       <c r="H53" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>277319000</v>
       </c>
       <c r="I53" s="1">
@@ -6644,7 +6629,7 @@
         <v>54327000</v>
       </c>
       <c r="J53" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>12740000000</v>
       </c>
       <c r="K53" s="1">
@@ -6741,7 +6726,7 @@
         <v>49</v>
       </c>
       <c r="H54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>302317500</v>
       </c>
       <c r="I54" s="1">
@@ -6749,7 +6734,7 @@
         <v>61717500</v>
       </c>
       <c r="J54" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>14319000000</v>
       </c>
       <c r="K54" s="1">
@@ -6846,7 +6831,7 @@
         <v>50</v>
       </c>
       <c r="H55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>330776000</v>
       </c>
       <c r="I55" s="1">
@@ -6854,7 +6839,7 @@
         <v>69576000</v>
       </c>
       <c r="J55" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>16000000000</v>
       </c>
       <c r="K55" s="1">
@@ -6951,7 +6936,7 @@
         <v>51</v>
       </c>
       <c r="H56" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>354390500</v>
       </c>
       <c r="I56" s="1">
@@ -6959,7 +6944,7 @@
         <v>75250500</v>
       </c>
       <c r="J56" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>17778600000</v>
       </c>
       <c r="K56" s="1">
@@ -7056,7 +7041,7 @@
         <v>52</v>
       </c>
       <c r="H57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>390807000</v>
       </c>
       <c r="I57" s="1">
@@ -7064,7 +7049,7 @@
         <v>80379000</v>
       </c>
       <c r="J57" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>19663200000</v>
       </c>
       <c r="K57" s="1">
@@ -7161,7 +7146,7 @@
         <v>53</v>
       </c>
       <c r="H58" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>422379500</v>
       </c>
       <c r="I58" s="1">
@@ -7169,7 +7154,7 @@
         <v>86326500</v>
       </c>
       <c r="J58" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>21663800000</v>
       </c>
       <c r="K58" s="1">
@@ -7266,7 +7251,7 @@
         <v>54</v>
       </c>
       <c r="H59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>454990000</v>
       </c>
       <c r="I59" s="1">
@@ -7274,7 +7259,7 @@
         <v>93210000</v>
       </c>
       <c r="J59" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23768000000</v>
       </c>
       <c r="K59" s="1">
@@ -7371,7 +7356,7 @@
         <v>55</v>
       </c>
       <c r="H60" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>488638500</v>
       </c>
       <c r="I60" s="1">
@@ -7379,7 +7364,7 @@
         <v>98689500</v>
       </c>
       <c r="J60" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>26010600000</v>
       </c>
       <c r="K60" s="1">
@@ -7476,7 +7461,7 @@
         <v>56</v>
       </c>
       <c r="H61" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>515713000</v>
       </c>
       <c r="I61" s="1">
@@ -7484,7 +7469,7 @@
         <v>107679000</v>
       </c>
       <c r="J61" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>28380000000</v>
       </c>
       <c r="K61" s="1">
@@ -7581,7 +7566,7 @@
         <v>57</v>
       </c>
       <c r="H62" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>551091500</v>
       </c>
       <c r="I62" s="1">
@@ -7589,7 +7574,7 @@
         <v>115264500</v>
       </c>
       <c r="J62" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>30879800000</v>
       </c>
       <c r="K62" s="1">
@@ -7686,7 +7671,7 @@
         <v>58</v>
       </c>
       <c r="H63" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>583356000</v>
       </c>
       <c r="I63" s="1">
@@ -7694,7 +7679,7 @@
         <v>123084000</v>
       </c>
       <c r="J63" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>33513600000</v>
       </c>
       <c r="K63" s="1">
@@ -7791,7 +7776,7 @@
         <v>59</v>
       </c>
       <c r="H64" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>611987500</v>
       </c>
       <c r="I64" s="1">
@@ -7799,7 +7784,7 @@
         <v>131137500</v>
       </c>
       <c r="J64" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>36265000000</v>
       </c>
       <c r="K64" s="1">
@@ -7896,7 +7881,7 @@
         <v>60</v>
       </c>
       <c r="H65" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>658957000</v>
       </c>
       <c r="I65" s="1">
@@ -7904,7 +7889,7 @@
         <v>137397000</v>
       </c>
       <c r="J65" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>39156000000</v>
       </c>
       <c r="K65" s="1">
@@ -8001,7 +7986,7 @@
         <v>61</v>
       </c>
       <c r="H66" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>716998500</v>
       </c>
       <c r="I66" s="1">
@@ -8009,7 +7994,7 @@
         <v>145840500</v>
       </c>
       <c r="J66" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>42179400000</v>
       </c>
       <c r="K66" s="1">
@@ -8106,7 +8091,7 @@
         <v>62</v>
       </c>
       <c r="H67" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>753242000</v>
       </c>
       <c r="I67" s="1">
@@ -8114,7 +8099,7 @@
         <v>153426000</v>
       </c>
       <c r="J67" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>45326400000</v>
       </c>
       <c r="K67" s="1">
@@ -8211,7 +8196,7 @@
         <v>63</v>
       </c>
       <c r="H68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>785160500</v>
       </c>
       <c r="I68" s="1">
@@ -8219,7 +8204,7 @@
         <v>160036500</v>
       </c>
       <c r="J68" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>48644600000</v>
       </c>
       <c r="K68" s="1">
@@ -8316,7 +8301,7 @@
         <v>64</v>
       </c>
       <c r="H69" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>822615000</v>
       </c>
       <c r="I69" s="1">
@@ -8324,7 +8309,7 @@
         <v>171405000</v>
       </c>
       <c r="J69" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>52164000000</v>
       </c>
       <c r="K69" s="1">
@@ -8421,7 +8406,7 @@
         <v>65</v>
       </c>
       <c r="H70" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>887576500</v>
       </c>
       <c r="I70" s="1">
@@ -8429,7 +8414,7 @@
         <v>185581500</v>
       </c>
       <c r="J70" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>55831000000</v>
       </c>
       <c r="K70" s="1">
@@ -8534,7 +8519,7 @@
         <v>194064000</v>
       </c>
       <c r="J71" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>59635200000</v>
       </c>
       <c r="K71" s="1">
@@ -8639,7 +8624,7 @@
         <v>201415500</v>
       </c>
       <c r="J72" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>63591000000</v>
       </c>
       <c r="K72" s="1">

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -1733,26 +1733,25 @@
         <v>10</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" ref="I6:I69" si="0">AB6*AG4*Z6/10</f>
         <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>100</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" ref="K6:K69" si="1">Y6*5</f>
+        <f t="shared" ref="K6:K69" si="0">Y6*5</f>
         <v>5</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L69" si="2">Y6*3</f>
+        <f t="shared" ref="L6:L69" si="1">Y6*3</f>
         <v>3</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M69" si="3">Y6*2</f>
+        <f t="shared" ref="M6:M69" si="2">Y6*2</f>
         <v>2</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" ref="N6:N69" si="4">Y6*4</f>
+        <f t="shared" ref="N6:N69" si="3">Y6*4</f>
         <v>4</v>
       </c>
       <c r="O6" s="1">
@@ -1777,11 +1776,11 @@
         <v>0</v>
       </c>
       <c r="V6" s="1">
-        <f t="shared" ref="V6:V69" si="5">X6*10</f>
+        <f t="shared" ref="V6:V69" si="4">X6*10</f>
         <v>10</v>
       </c>
       <c r="W6" s="1">
-        <f t="shared" ref="W6:W69" si="6">X6*10</f>
+        <f t="shared" ref="W6:W69" si="5">X6*10</f>
         <v>10</v>
       </c>
       <c r="X6" s="1">
@@ -1839,19 +1838,19 @@
         <v>1800</v>
       </c>
       <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L7" s="1">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="L7" s="1">
+        <v>6</v>
+      </c>
+      <c r="M7" s="1">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="M7" s="1">
+        <v>4</v>
+      </c>
+      <c r="N7" s="1">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="N7" s="1">
-        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="O7" s="1">
@@ -1876,11 +1875,11 @@
         <v>0</v>
       </c>
       <c r="V7" s="1">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="W7" s="1">
         <f t="shared" si="5"/>
-        <v>20</v>
-      </c>
-      <c r="W7" s="1">
-        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="X7" s="1">
@@ -1939,19 +1938,19 @@
         <v>3000</v>
       </c>
       <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="L8" s="1">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L8" s="1">
+        <v>9</v>
+      </c>
+      <c r="M8" s="1">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="M8" s="1">
+        <v>6</v>
+      </c>
+      <c r="N8" s="1">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="N8" s="1">
-        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="O8" s="1">
@@ -1961,7 +1960,7 @@
         <v>3</v>
       </c>
       <c r="Q8" s="2">
-        <f t="shared" ref="Q8:Q45" si="7">Q7+2</f>
+        <f t="shared" ref="Q8:Q45" si="6">Q7+2</f>
         <v>12</v>
       </c>
       <c r="R8" s="1">
@@ -1977,11 +1976,11 @@
         <v>0</v>
       </c>
       <c r="V8" s="1">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="W8" s="1">
         <f t="shared" si="5"/>
-        <v>30</v>
-      </c>
-      <c r="W8" s="1">
-        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="X8" s="1">
@@ -2040,19 +2039,19 @@
         <v>6000</v>
       </c>
       <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="L9" s="1">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L9" s="1">
+        <v>12</v>
+      </c>
+      <c r="M9" s="1">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="M9" s="1">
+        <v>8</v>
+      </c>
+      <c r="N9" s="1">
         <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="N9" s="1">
-        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="O9" s="1">
@@ -2062,7 +2061,7 @@
         <v>4</v>
       </c>
       <c r="Q9" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="R9" s="1">
@@ -2078,11 +2077,11 @@
         <v>0</v>
       </c>
       <c r="V9" s="1">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="W9" s="1">
         <f t="shared" si="5"/>
-        <v>40</v>
-      </c>
-      <c r="W9" s="1">
-        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="X9" s="1">
@@ -2141,19 +2140,19 @@
         <v>12000</v>
       </c>
       <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="L10" s="1">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="L10" s="1">
+        <v>15</v>
+      </c>
+      <c r="M10" s="1">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="N10" s="1">
-        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="O10" s="1">
@@ -2163,7 +2162,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="R10" s="1">
@@ -2179,11 +2178,11 @@
         <v>0</v>
       </c>
       <c r="V10" s="1">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="W10" s="1">
         <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="W10" s="1">
-        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="X10" s="1">
@@ -2242,19 +2241,19 @@
         <v>20000</v>
       </c>
       <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="L11" s="1">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="L11" s="1">
+        <v>18</v>
+      </c>
+      <c r="M11" s="1">
         <f t="shared" si="2"/>
-        <v>18</v>
-      </c>
-      <c r="M11" s="1">
+        <v>12</v>
+      </c>
+      <c r="N11" s="1">
         <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="N11" s="1">
-        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="O11" s="1">
@@ -2264,7 +2263,7 @@
         <v>6</v>
       </c>
       <c r="Q11" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="R11" s="1">
@@ -2280,11 +2279,11 @@
         <v>0</v>
       </c>
       <c r="V11" s="1">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="W11" s="1">
         <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="W11" s="1">
-        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="X11" s="1">
@@ -2343,19 +2342,19 @@
         <v>35000</v>
       </c>
       <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="L12" s="1">
         <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="L12" s="1">
+        <v>21</v>
+      </c>
+      <c r="M12" s="1">
         <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-      <c r="M12" s="1">
+        <v>14</v>
+      </c>
+      <c r="N12" s="1">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="N12" s="1">
-        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="O12" s="1">
@@ -2365,7 +2364,7 @@
         <v>7</v>
       </c>
       <c r="Q12" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="R12" s="1">
@@ -2381,11 +2380,11 @@
         <v>0</v>
       </c>
       <c r="V12" s="1">
+        <f t="shared" si="4"/>
+        <v>70</v>
+      </c>
+      <c r="W12" s="1">
         <f t="shared" si="5"/>
-        <v>70</v>
-      </c>
-      <c r="W12" s="1">
-        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="X12" s="1">
@@ -2405,7 +2404,7 @@
         <v>6</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" ref="AC8:AC75" si="8">AC11+AG11</f>
+        <f t="shared" ref="AC8:AC75" si="7">AC11+AG11</f>
         <v>153</v>
       </c>
       <c r="AD12" s="1">
@@ -2445,19 +2444,19 @@
         <v>58000</v>
       </c>
       <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="L13" s="1">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="L13" s="1">
+        <v>24</v>
+      </c>
+      <c r="M13" s="1">
         <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
-      <c r="M13" s="1">
+        <v>16</v>
+      </c>
+      <c r="N13" s="1">
         <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="N13" s="1">
-        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="O13" s="1">
@@ -2467,7 +2466,7 @@
         <v>8</v>
       </c>
       <c r="Q13" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="R13" s="1">
@@ -2483,11 +2482,11 @@
         <v>0</v>
       </c>
       <c r="V13" s="1">
+        <f t="shared" si="4"/>
+        <v>80</v>
+      </c>
+      <c r="W13" s="1">
         <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="W13" s="1">
-        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="X13" s="1">
@@ -2507,7 +2506,7 @@
         <v>7</v>
       </c>
       <c r="AC13" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>170</v>
       </c>
       <c r="AD13" s="1">
@@ -2547,19 +2546,19 @@
         <v>90000</v>
       </c>
       <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="L14" s="1">
         <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="L14" s="1">
+        <v>27</v>
+      </c>
+      <c r="M14" s="1">
         <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="M14" s="1">
+        <v>18</v>
+      </c>
+      <c r="N14" s="1">
         <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="N14" s="1">
-        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="O14" s="1">
@@ -2569,7 +2568,7 @@
         <v>9</v>
       </c>
       <c r="Q14" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="R14" s="1">
@@ -2585,11 +2584,11 @@
         <v>0</v>
       </c>
       <c r="V14" s="1">
+        <f t="shared" si="4"/>
+        <v>90</v>
+      </c>
+      <c r="W14" s="1">
         <f t="shared" si="5"/>
-        <v>90</v>
-      </c>
-      <c r="W14" s="1">
-        <f t="shared" si="6"/>
         <v>90</v>
       </c>
       <c r="X14" s="1">
@@ -2609,7 +2608,7 @@
         <v>8</v>
       </c>
       <c r="AC14" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>189</v>
       </c>
       <c r="AD14" s="1">
@@ -2649,19 +2648,19 @@
         <v>140000</v>
       </c>
       <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L15" s="1">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="L15" s="1">
+        <v>30</v>
+      </c>
+      <c r="M15" s="1">
         <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="M15" s="1">
+        <v>20</v>
+      </c>
+      <c r="N15" s="1">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="N15" s="1">
-        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="O15" s="1">
@@ -2671,7 +2670,7 @@
         <v>10</v>
       </c>
       <c r="Q15" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="R15" s="1">
@@ -2687,11 +2686,11 @@
         <v>0</v>
       </c>
       <c r="V15" s="1">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="W15" s="1">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="W15" s="1">
-        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="X15" s="1">
@@ -2711,7 +2710,7 @@
         <v>9</v>
       </c>
       <c r="AC15" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>212</v>
       </c>
       <c r="AD15" s="1">
@@ -2751,19 +2750,19 @@
         <v>200000</v>
       </c>
       <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="L16" s="1">
         <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
-      <c r="L16" s="1">
+        <v>33</v>
+      </c>
+      <c r="M16" s="1">
         <f t="shared" si="2"/>
-        <v>33</v>
-      </c>
-      <c r="M16" s="1">
+        <v>22</v>
+      </c>
+      <c r="N16" s="1">
         <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="N16" s="1">
-        <f t="shared" si="4"/>
         <v>44</v>
       </c>
       <c r="O16" s="1">
@@ -2773,7 +2772,7 @@
         <v>11</v>
       </c>
       <c r="Q16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="R16" s="1">
@@ -2789,11 +2788,11 @@
         <v>0</v>
       </c>
       <c r="V16" s="1">
+        <f t="shared" si="4"/>
+        <v>110</v>
+      </c>
+      <c r="W16" s="1">
         <f t="shared" si="5"/>
-        <v>110</v>
-      </c>
-      <c r="W16" s="1">
-        <f t="shared" si="6"/>
         <v>110</v>
       </c>
       <c r="X16" s="1">
@@ -2813,7 +2812,7 @@
         <v>10</v>
       </c>
       <c r="AC16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>241</v>
       </c>
       <c r="AD16" s="1">
@@ -2853,19 +2852,19 @@
         <v>300000</v>
       </c>
       <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="L17" s="1">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="L17" s="1">
+        <v>36</v>
+      </c>
+      <c r="M17" s="1">
         <f t="shared" si="2"/>
-        <v>36</v>
-      </c>
-      <c r="M17" s="1">
+        <v>24</v>
+      </c>
+      <c r="N17" s="1">
         <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="N17" s="1">
-        <f t="shared" si="4"/>
         <v>48</v>
       </c>
       <c r="O17" s="1">
@@ -2875,7 +2874,7 @@
         <v>12</v>
       </c>
       <c r="Q17" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="R17" s="1">
@@ -2891,13 +2890,13 @@
         <v>0</v>
       </c>
       <c r="V17" s="1">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+      <c r="W17" s="1">
         <f t="shared" si="5"/>
         <v>120</v>
       </c>
-      <c r="W17" s="1">
-        <f t="shared" si="6"/>
-        <v>120</v>
-      </c>
       <c r="X17" s="1">
         <v>12</v>
       </c>
@@ -2905,7 +2904,7 @@
         <v>12</v>
       </c>
       <c r="Z17" s="2">
-        <f t="shared" ref="Z17:Z22" si="9">Z16+100</f>
+        <f t="shared" ref="Z17:Z22" si="8">Z16+100</f>
         <v>500</v>
       </c>
       <c r="AA17" s="2">
@@ -2915,7 +2914,7 @@
         <v>11</v>
       </c>
       <c r="AC17" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>272</v>
       </c>
       <c r="AD17" s="1">
@@ -2946,31 +2945,28 @@
         <v>13</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" ref="H7:H70" si="10">AG20*Z18*AA18/10</f>
-        <v>53580</v>
+        <v>27000</v>
       </c>
       <c r="I18" s="1">
+        <v>6000</v>
+      </c>
+      <c r="J18" s="1">
+        <v>450000</v>
+      </c>
+      <c r="K18" s="1">
         <f t="shared" si="0"/>
-        <v>22320</v>
-      </c>
-      <c r="J18" s="1">
-        <f t="shared" ref="J7:J72" si="11">Y18*Z18*AC18</f>
-        <v>2410200</v>
-      </c>
-      <c r="K18" s="1">
+        <v>65</v>
+      </c>
+      <c r="L18" s="1">
         <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="L18" s="1">
+        <v>39</v>
+      </c>
+      <c r="M18" s="1">
         <f t="shared" si="2"/>
-        <v>39</v>
-      </c>
-      <c r="M18" s="1">
+        <v>26</v>
+      </c>
+      <c r="N18" s="1">
         <f t="shared" si="3"/>
-        <v>26</v>
-      </c>
-      <c r="N18" s="1">
-        <f t="shared" si="4"/>
         <v>52</v>
       </c>
       <c r="O18" s="1">
@@ -2980,7 +2976,7 @@
         <v>13</v>
       </c>
       <c r="Q18" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="R18" s="1">
@@ -2996,13 +2992,13 @@
         <v>0</v>
       </c>
       <c r="V18" s="1">
+        <f t="shared" si="4"/>
+        <v>130</v>
+      </c>
+      <c r="W18" s="1">
         <f t="shared" si="5"/>
         <v>130</v>
       </c>
-      <c r="W18" s="1">
-        <f t="shared" si="6"/>
-        <v>130</v>
-      </c>
       <c r="X18" s="1">
         <v>13</v>
       </c>
@@ -3010,7 +3006,7 @@
         <v>13</v>
       </c>
       <c r="Z18" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>600</v>
       </c>
       <c r="AA18" s="2">
@@ -3020,7 +3016,7 @@
         <v>12</v>
       </c>
       <c r="AC18" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>309</v>
       </c>
       <c r="AD18" s="1">
@@ -3051,31 +3047,28 @@
         <v>14</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="10"/>
-        <v>85330</v>
+        <v>34000</v>
       </c>
       <c r="I19" s="1">
+        <v>9600</v>
+      </c>
+      <c r="J19" s="1">
+        <v>650000</v>
+      </c>
+      <c r="K19" s="1">
         <f t="shared" si="0"/>
-        <v>33670</v>
-      </c>
-      <c r="J19" s="1">
-        <f t="shared" si="11"/>
-        <v>3430000</v>
-      </c>
-      <c r="K19" s="1">
+        <v>70</v>
+      </c>
+      <c r="L19" s="1">
         <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="L19" s="1">
+        <v>42</v>
+      </c>
+      <c r="M19" s="1">
         <f t="shared" si="2"/>
-        <v>42</v>
-      </c>
-      <c r="M19" s="1">
+        <v>28</v>
+      </c>
+      <c r="N19" s="1">
         <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-      <c r="N19" s="1">
-        <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="O19" s="1">
@@ -3085,7 +3078,7 @@
         <v>14</v>
       </c>
       <c r="Q19" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>34</v>
       </c>
       <c r="R19" s="1">
@@ -3101,13 +3094,13 @@
         <v>0</v>
       </c>
       <c r="V19" s="1">
+        <f t="shared" si="4"/>
+        <v>140</v>
+      </c>
+      <c r="W19" s="1">
         <f t="shared" si="5"/>
         <v>140</v>
       </c>
-      <c r="W19" s="1">
-        <f t="shared" si="6"/>
-        <v>140</v>
-      </c>
       <c r="X19" s="1">
         <v>14</v>
       </c>
@@ -3115,7 +3108,7 @@
         <v>14</v>
       </c>
       <c r="Z19" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>700</v>
       </c>
       <c r="AA19" s="2">
@@ -3125,7 +3118,7 @@
         <v>13</v>
       </c>
       <c r="AC19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>350</v>
       </c>
       <c r="AD19" s="1">
@@ -3156,31 +3149,28 @@
         <v>15</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" si="10"/>
-        <v>136880</v>
+        <v>42000</v>
       </c>
       <c r="I20" s="1">
+        <v>14000</v>
+      </c>
+      <c r="J20" s="1">
+        <v>950000</v>
+      </c>
+      <c r="K20" s="1">
         <f t="shared" si="0"/>
-        <v>45920</v>
-      </c>
-      <c r="J20" s="1">
-        <f t="shared" si="11"/>
-        <v>4716000</v>
-      </c>
-      <c r="K20" s="1">
+        <v>75</v>
+      </c>
+      <c r="L20" s="1">
         <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="L20" s="1">
+        <v>45</v>
+      </c>
+      <c r="M20" s="1">
         <f t="shared" si="2"/>
-        <v>45</v>
-      </c>
-      <c r="M20" s="1">
+        <v>30</v>
+      </c>
+      <c r="N20" s="1">
         <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="N20" s="1">
-        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="O20" s="1">
@@ -3190,7 +3180,7 @@
         <v>15</v>
       </c>
       <c r="Q20" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>36</v>
       </c>
       <c r="R20" s="1">
@@ -3206,13 +3196,13 @@
         <v>0</v>
       </c>
       <c r="V20" s="1">
+        <f t="shared" si="4"/>
+        <v>150</v>
+      </c>
+      <c r="W20" s="1">
         <f t="shared" si="5"/>
         <v>150</v>
       </c>
-      <c r="W20" s="1">
-        <f t="shared" si="6"/>
-        <v>150</v>
-      </c>
       <c r="X20" s="1">
         <v>15</v>
       </c>
@@ -3220,7 +3210,7 @@
         <v>15</v>
       </c>
       <c r="Z20" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>800</v>
       </c>
       <c r="AA20" s="2">
@@ -3230,7 +3220,7 @@
         <v>14</v>
       </c>
       <c r="AC20" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>393</v>
       </c>
       <c r="AD20" s="1">
@@ -3261,31 +3251,28 @@
         <v>16</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" si="10"/>
-        <v>170190</v>
+        <v>51000</v>
       </c>
       <c r="I21" s="1">
+        <v>20000</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1350000</v>
+      </c>
+      <c r="K21" s="1">
         <f t="shared" si="0"/>
-        <v>58050</v>
-      </c>
-      <c r="J21" s="1">
-        <f t="shared" si="11"/>
-        <v>6336000</v>
-      </c>
-      <c r="K21" s="1">
+        <v>80</v>
+      </c>
+      <c r="L21" s="1">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="L21" s="1">
+        <v>48</v>
+      </c>
+      <c r="M21" s="1">
         <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="M21" s="1">
+        <v>32</v>
+      </c>
+      <c r="N21" s="1">
         <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="N21" s="1">
-        <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="O21" s="1">
@@ -3295,7 +3282,7 @@
         <v>16</v>
       </c>
       <c r="Q21" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
       <c r="R21" s="1">
@@ -3311,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="V21" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="W21" s="1">
         <f t="shared" si="5"/>
         <v>160</v>
       </c>
-      <c r="W21" s="1">
-        <f t="shared" si="6"/>
-        <v>160</v>
-      </c>
       <c r="X21" s="1">
         <v>16</v>
       </c>
@@ -3325,7 +3312,7 @@
         <v>16</v>
       </c>
       <c r="Z21" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>900</v>
       </c>
       <c r="AA21" s="2">
@@ -3335,7 +3322,7 @@
         <v>15</v>
       </c>
       <c r="AC21" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>440</v>
       </c>
       <c r="AD21" s="1">
@@ -3366,31 +3353,28 @@
         <v>17</v>
       </c>
       <c r="H22" s="1">
-        <f t="shared" si="10"/>
-        <v>247900</v>
+        <v>61000</v>
       </c>
       <c r="I22" s="1">
+        <v>27000</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1900000</v>
+      </c>
+      <c r="K22" s="1">
         <f t="shared" si="0"/>
-        <v>75200</v>
-      </c>
-      <c r="J22" s="1">
-        <f t="shared" si="11"/>
-        <v>8381000</v>
-      </c>
-      <c r="K22" s="1">
+        <v>85</v>
+      </c>
+      <c r="L22" s="1">
         <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-      <c r="L22" s="1">
+        <v>51</v>
+      </c>
+      <c r="M22" s="1">
         <f t="shared" si="2"/>
-        <v>51</v>
-      </c>
-      <c r="M22" s="1">
+        <v>34</v>
+      </c>
+      <c r="N22" s="1">
         <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="N22" s="1">
-        <f t="shared" si="4"/>
         <v>68</v>
       </c>
       <c r="O22" s="1">
@@ -3400,7 +3384,7 @@
         <v>17</v>
       </c>
       <c r="Q22" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="R22" s="1">
@@ -3416,13 +3400,13 @@
         <v>0</v>
       </c>
       <c r="V22" s="1">
+        <f t="shared" si="4"/>
+        <v>170</v>
+      </c>
+      <c r="W22" s="1">
         <f t="shared" si="5"/>
         <v>170</v>
       </c>
-      <c r="W22" s="1">
-        <f t="shared" si="6"/>
-        <v>170</v>
-      </c>
       <c r="X22" s="1">
         <v>17</v>
       </c>
@@ -3430,7 +3414,7 @@
         <v>17</v>
       </c>
       <c r="Z22" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1000</v>
       </c>
       <c r="AA22" s="2">
@@ -3440,7 +3424,7 @@
         <v>16</v>
       </c>
       <c r="AC22" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>493</v>
       </c>
       <c r="AD22" s="1">
@@ -3471,31 +3455,31 @@
         <v>18</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H7:H70" si="9">AG25*Z23*AA23/10</f>
         <v>349320</v>
       </c>
       <c r="I23" s="1">
+        <f t="shared" ref="I6:I69" si="10">AB23*AG21*Z23/10</f>
+        <v>108120</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" ref="J7:J72" si="11">Y23*Z23*AC23</f>
+        <v>11923200</v>
+      </c>
+      <c r="K23" s="1">
         <f t="shared" si="0"/>
-        <v>108120</v>
-      </c>
-      <c r="J23" s="1">
-        <f t="shared" si="11"/>
-        <v>11923200</v>
-      </c>
-      <c r="K23" s="1">
+        <v>90</v>
+      </c>
+      <c r="L23" s="1">
         <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="L23" s="1">
+        <v>54</v>
+      </c>
+      <c r="M23" s="1">
         <f t="shared" si="2"/>
-        <v>54</v>
-      </c>
-      <c r="M23" s="1">
+        <v>36</v>
+      </c>
+      <c r="N23" s="1">
         <f t="shared" si="3"/>
-        <v>36</v>
-      </c>
-      <c r="N23" s="1">
-        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="O23" s="1">
@@ -3505,7 +3489,7 @@
         <v>18</v>
       </c>
       <c r="Q23" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>42</v>
       </c>
       <c r="R23" s="1">
@@ -3521,11 +3505,11 @@
         <v>0</v>
       </c>
       <c r="V23" s="1">
+        <f t="shared" si="4"/>
+        <v>180</v>
+      </c>
+      <c r="W23" s="1">
         <f t="shared" si="5"/>
-        <v>180</v>
-      </c>
-      <c r="W23" s="1">
-        <f t="shared" si="6"/>
         <v>180</v>
       </c>
       <c r="X23" s="1">
@@ -3545,7 +3529,7 @@
         <v>17</v>
       </c>
       <c r="AC23" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>552</v>
       </c>
       <c r="AD23" s="1">
@@ -3576,11 +3560,11 @@
         <v>19</v>
       </c>
       <c r="H24" s="1">
+        <f t="shared" si="9"/>
+        <v>439460</v>
+      </c>
+      <c r="I24" s="1">
         <f t="shared" si="10"/>
-        <v>439460</v>
-      </c>
-      <c r="I24" s="1">
-        <f t="shared" si="0"/>
         <v>148680</v>
       </c>
       <c r="J24" s="1">
@@ -3588,19 +3572,19 @@
         <v>16305800</v>
       </c>
       <c r="K24" s="1">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="L24" s="1">
         <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="L24" s="1">
+        <v>57</v>
+      </c>
+      <c r="M24" s="1">
         <f t="shared" si="2"/>
-        <v>57</v>
-      </c>
-      <c r="M24" s="1">
+        <v>38</v>
+      </c>
+      <c r="N24" s="1">
         <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-      <c r="N24" s="1">
-        <f t="shared" si="4"/>
         <v>76</v>
       </c>
       <c r="O24" s="1">
@@ -3610,7 +3594,7 @@
         <v>19</v>
       </c>
       <c r="Q24" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>44</v>
       </c>
       <c r="R24" s="1">
@@ -3626,11 +3610,11 @@
         <v>0</v>
       </c>
       <c r="V24" s="1">
+        <f t="shared" si="4"/>
+        <v>190</v>
+      </c>
+      <c r="W24" s="1">
         <f t="shared" si="5"/>
-        <v>190</v>
-      </c>
-      <c r="W24" s="1">
-        <f t="shared" si="6"/>
         <v>190</v>
       </c>
       <c r="X24" s="1">
@@ -3650,7 +3634,7 @@
         <v>18</v>
       </c>
       <c r="AC24" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>613</v>
       </c>
       <c r="AD24" s="1">
@@ -3681,11 +3665,11 @@
         <v>20</v>
       </c>
       <c r="H25" s="1">
+        <f t="shared" si="9"/>
+        <v>594080</v>
+      </c>
+      <c r="I25" s="1">
         <f t="shared" si="10"/>
-        <v>594080</v>
-      </c>
-      <c r="I25" s="1">
-        <f t="shared" si="0"/>
         <v>185440</v>
       </c>
       <c r="J25" s="1">
@@ -3693,19 +3677,19 @@
         <v>21760000</v>
       </c>
       <c r="K25" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
         <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="L25" s="1">
+        <v>60</v>
+      </c>
+      <c r="M25" s="1">
         <f t="shared" si="2"/>
-        <v>60</v>
-      </c>
-      <c r="M25" s="1">
+        <v>40</v>
+      </c>
+      <c r="N25" s="1">
         <f t="shared" si="3"/>
-        <v>40</v>
-      </c>
-      <c r="N25" s="1">
-        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="O25" s="1">
@@ -3715,7 +3699,7 @@
         <v>20</v>
       </c>
       <c r="Q25" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>46</v>
       </c>
       <c r="R25" s="1">
@@ -3731,11 +3715,11 @@
         <v>0</v>
       </c>
       <c r="V25" s="1">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="W25" s="1">
         <f t="shared" si="5"/>
-        <v>200</v>
-      </c>
-      <c r="W25" s="1">
-        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="X25" s="1">
@@ -3755,7 +3739,7 @@
         <v>19</v>
       </c>
       <c r="AC25" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>680</v>
       </c>
       <c r="AD25" s="1">
@@ -3786,11 +3770,11 @@
         <v>21</v>
       </c>
       <c r="H26" s="1">
+        <f t="shared" si="9"/>
+        <v>791820</v>
+      </c>
+      <c r="I26" s="1">
         <f t="shared" si="10"/>
-        <v>791820</v>
-      </c>
-      <c r="I26" s="1">
-        <f t="shared" si="0"/>
         <v>241200</v>
       </c>
       <c r="J26" s="1">
@@ -3798,19 +3782,19 @@
         <v>28387800</v>
       </c>
       <c r="K26" s="1">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="L26" s="1">
         <f t="shared" si="1"/>
-        <v>105</v>
-      </c>
-      <c r="L26" s="1">
+        <v>63</v>
+      </c>
+      <c r="M26" s="1">
         <f t="shared" si="2"/>
-        <v>63</v>
-      </c>
-      <c r="M26" s="1">
+        <v>42</v>
+      </c>
+      <c r="N26" s="1">
         <f t="shared" si="3"/>
-        <v>42</v>
-      </c>
-      <c r="N26" s="1">
-        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="O26" s="1">
@@ -3820,7 +3804,7 @@
         <v>21</v>
       </c>
       <c r="Q26" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>48</v>
       </c>
       <c r="R26" s="1">
@@ -3836,11 +3820,11 @@
         <v>0</v>
       </c>
       <c r="V26" s="1">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="W26" s="1">
         <f t="shared" si="5"/>
-        <v>210</v>
-      </c>
-      <c r="W26" s="1">
-        <f t="shared" si="6"/>
         <v>210</v>
       </c>
       <c r="X26" s="1">
@@ -3860,7 +3844,7 @@
         <v>20</v>
       </c>
       <c r="AC26" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>751</v>
       </c>
       <c r="AD26" s="1">
@@ -3891,11 +3875,11 @@
         <v>22</v>
       </c>
       <c r="H27" s="1">
+        <f t="shared" si="9"/>
+        <v>1050200</v>
+      </c>
+      <c r="I27" s="1">
         <f t="shared" si="10"/>
-        <v>1050200</v>
-      </c>
-      <c r="I27" s="1">
-        <f t="shared" si="0"/>
         <v>298200</v>
       </c>
       <c r="J27" s="1">
@@ -3903,19 +3887,19 @@
         <v>36256000</v>
       </c>
       <c r="K27" s="1">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>110</v>
-      </c>
-      <c r="L27" s="1">
+        <v>66</v>
+      </c>
+      <c r="M27" s="1">
         <f t="shared" si="2"/>
-        <v>66</v>
-      </c>
-      <c r="M27" s="1">
+        <v>44</v>
+      </c>
+      <c r="N27" s="1">
         <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="N27" s="1">
-        <f t="shared" si="4"/>
         <v>88</v>
       </c>
       <c r="O27" s="1">
@@ -3925,7 +3909,7 @@
         <v>22</v>
       </c>
       <c r="Q27" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="R27" s="1">
@@ -3941,11 +3925,11 @@
         <v>0</v>
       </c>
       <c r="V27" s="1">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="W27" s="1">
         <f t="shared" si="5"/>
-        <v>220</v>
-      </c>
-      <c r="W27" s="1">
-        <f t="shared" si="6"/>
         <v>220</v>
       </c>
       <c r="X27" s="1">
@@ -3965,7 +3949,7 @@
         <v>21</v>
       </c>
       <c r="AC27" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>824</v>
       </c>
       <c r="AD27" s="1">
@@ -3996,11 +3980,11 @@
         <v>23</v>
       </c>
       <c r="H28" s="1">
+        <f t="shared" si="9"/>
+        <v>1479250</v>
+      </c>
+      <c r="I28" s="1">
         <f t="shared" si="10"/>
-        <v>1479250</v>
-      </c>
-      <c r="I28" s="1">
-        <f t="shared" si="0"/>
         <v>401500</v>
       </c>
       <c r="J28" s="1">
@@ -4008,19 +3992,19 @@
         <v>51922500</v>
       </c>
       <c r="K28" s="1">
+        <f t="shared" si="0"/>
+        <v>115</v>
+      </c>
+      <c r="L28" s="1">
         <f t="shared" si="1"/>
-        <v>115</v>
-      </c>
-      <c r="L28" s="1">
+        <v>69</v>
+      </c>
+      <c r="M28" s="1">
         <f t="shared" si="2"/>
-        <v>69</v>
-      </c>
-      <c r="M28" s="1">
+        <v>46</v>
+      </c>
+      <c r="N28" s="1">
         <f t="shared" si="3"/>
-        <v>46</v>
-      </c>
-      <c r="N28" s="1">
-        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="O28" s="1">
@@ -4046,11 +4030,11 @@
         <v>0</v>
       </c>
       <c r="V28" s="1">
+        <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+      <c r="W28" s="1">
         <f t="shared" si="5"/>
-        <v>230</v>
-      </c>
-      <c r="W28" s="1">
-        <f t="shared" si="6"/>
         <v>230</v>
       </c>
       <c r="X28" s="1">
@@ -4070,7 +4054,7 @@
         <v>22</v>
       </c>
       <c r="AC28" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>903</v>
       </c>
       <c r="AD28" s="1">
@@ -4101,11 +4085,11 @@
         <v>24</v>
       </c>
       <c r="H29" s="1">
+        <f t="shared" si="9"/>
+        <v>2030100</v>
+      </c>
+      <c r="I29" s="1">
         <f t="shared" si="10"/>
-        <v>2030100</v>
-      </c>
-      <c r="I29" s="1">
-        <f t="shared" si="0"/>
         <v>545100</v>
       </c>
       <c r="J29" s="1">
@@ -4113,19 +4097,19 @@
         <v>70992000</v>
       </c>
       <c r="K29" s="1">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="L29" s="1">
         <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="L29" s="1">
+        <v>72</v>
+      </c>
+      <c r="M29" s="1">
         <f t="shared" si="2"/>
-        <v>72</v>
-      </c>
-      <c r="M29" s="1">
+        <v>48</v>
+      </c>
+      <c r="N29" s="1">
         <f t="shared" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="N29" s="1">
-        <f t="shared" si="4"/>
         <v>96</v>
       </c>
       <c r="O29" s="1">
@@ -4151,11 +4135,11 @@
         <v>0</v>
       </c>
       <c r="V29" s="1">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="W29" s="1">
         <f t="shared" si="5"/>
-        <v>240</v>
-      </c>
-      <c r="W29" s="1">
-        <f t="shared" si="6"/>
         <v>240</v>
       </c>
       <c r="X29" s="1">
@@ -4175,7 +4159,7 @@
         <v>23</v>
       </c>
       <c r="AC29" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>986</v>
       </c>
       <c r="AD29" s="1">
@@ -4206,11 +4190,11 @@
         <v>25</v>
       </c>
       <c r="H30" s="1">
+        <f t="shared" si="9"/>
+        <v>2559550</v>
+      </c>
+      <c r="I30" s="1">
         <f t="shared" si="10"/>
-        <v>2559550</v>
-      </c>
-      <c r="I30" s="1">
-        <f t="shared" si="0"/>
         <v>697200</v>
       </c>
       <c r="J30" s="1">
@@ -4218,19 +4202,19 @@
         <v>94062500</v>
       </c>
       <c r="K30" s="1">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="L30" s="1">
         <f t="shared" si="1"/>
-        <v>125</v>
-      </c>
-      <c r="L30" s="1">
+        <v>75</v>
+      </c>
+      <c r="M30" s="1">
         <f t="shared" si="2"/>
-        <v>75</v>
-      </c>
-      <c r="M30" s="1">
+        <v>50</v>
+      </c>
+      <c r="N30" s="1">
         <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="N30" s="1">
-        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="O30" s="1">
@@ -4256,11 +4240,11 @@
         <v>0</v>
       </c>
       <c r="V30" s="1">
+        <f t="shared" si="4"/>
+        <v>250</v>
+      </c>
+      <c r="W30" s="1">
         <f t="shared" si="5"/>
-        <v>250</v>
-      </c>
-      <c r="W30" s="1">
-        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="X30" s="1">
@@ -4280,7 +4264,7 @@
         <v>24</v>
       </c>
       <c r="AC30" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1075</v>
       </c>
       <c r="AD30" s="1">
@@ -4311,11 +4295,11 @@
         <v>26</v>
       </c>
       <c r="H31" s="1">
+        <f t="shared" si="9"/>
+        <v>3124400</v>
+      </c>
+      <c r="I31" s="1">
         <f t="shared" si="10"/>
-        <v>3124400</v>
-      </c>
-      <c r="I31" s="1">
-        <f t="shared" si="0"/>
         <v>890000</v>
       </c>
       <c r="J31" s="1">
@@ -4323,19 +4307,19 @@
         <v>121888000</v>
       </c>
       <c r="K31" s="1">
+        <f t="shared" si="0"/>
+        <v>130</v>
+      </c>
+      <c r="L31" s="1">
         <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-      <c r="L31" s="1">
+        <v>78</v>
+      </c>
+      <c r="M31" s="1">
         <f t="shared" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="M31" s="1">
+        <v>52</v>
+      </c>
+      <c r="N31" s="1">
         <f t="shared" si="3"/>
-        <v>52</v>
-      </c>
-      <c r="N31" s="1">
-        <f t="shared" si="4"/>
         <v>104</v>
       </c>
       <c r="O31" s="1">
@@ -4361,11 +4345,11 @@
         <v>0</v>
       </c>
       <c r="V31" s="1">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="W31" s="1">
         <f t="shared" si="5"/>
-        <v>260</v>
-      </c>
-      <c r="W31" s="1">
-        <f t="shared" si="6"/>
         <v>260</v>
       </c>
       <c r="X31" s="1">
@@ -4385,7 +4369,7 @@
         <v>25</v>
       </c>
       <c r="AC31" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1172</v>
       </c>
       <c r="AD31" s="1">
@@ -4416,11 +4400,11 @@
         <v>27</v>
       </c>
       <c r="H32" s="1">
+        <f t="shared" si="9"/>
+        <v>3874950</v>
+      </c>
+      <c r="I32" s="1">
         <f t="shared" si="10"/>
-        <v>3874950</v>
-      </c>
-      <c r="I32" s="1">
-        <f t="shared" si="0"/>
         <v>1134900</v>
       </c>
       <c r="J32" s="1">
@@ -4428,19 +4412,19 @@
         <v>154669500</v>
       </c>
       <c r="K32" s="1">
+        <f t="shared" si="0"/>
+        <v>135</v>
+      </c>
+      <c r="L32" s="1">
         <f t="shared" si="1"/>
-        <v>135</v>
-      </c>
-      <c r="L32" s="1">
+        <v>81</v>
+      </c>
+      <c r="M32" s="1">
         <f t="shared" si="2"/>
-        <v>81</v>
-      </c>
-      <c r="M32" s="1">
+        <v>54</v>
+      </c>
+      <c r="N32" s="1">
         <f t="shared" si="3"/>
-        <v>54</v>
-      </c>
-      <c r="N32" s="1">
-        <f t="shared" si="4"/>
         <v>108</v>
       </c>
       <c r="O32" s="1">
@@ -4466,11 +4450,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="1">
+        <f t="shared" si="4"/>
+        <v>270</v>
+      </c>
+      <c r="W32" s="1">
         <f t="shared" si="5"/>
-        <v>270</v>
-      </c>
-      <c r="W32" s="1">
-        <f t="shared" si="6"/>
         <v>270</v>
       </c>
       <c r="X32" s="1">
@@ -4490,7 +4474,7 @@
         <v>26</v>
       </c>
       <c r="AC32" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1273</v>
       </c>
       <c r="AD32" s="1">
@@ -4521,11 +4505,11 @@
         <v>28</v>
       </c>
       <c r="H33" s="1">
+        <f t="shared" si="9"/>
+        <v>4689500</v>
+      </c>
+      <c r="I33" s="1">
         <f t="shared" si="10"/>
-        <v>4689500</v>
-      </c>
-      <c r="I33" s="1">
-        <f t="shared" si="0"/>
         <v>1363500</v>
       </c>
       <c r="J33" s="1">
@@ -4533,19 +4517,19 @@
         <v>192640000</v>
       </c>
       <c r="K33" s="1">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="L33" s="1">
         <f t="shared" si="1"/>
-        <v>140</v>
-      </c>
-      <c r="L33" s="1">
+        <v>84</v>
+      </c>
+      <c r="M33" s="1">
         <f t="shared" si="2"/>
-        <v>84</v>
-      </c>
-      <c r="M33" s="1">
+        <v>56</v>
+      </c>
+      <c r="N33" s="1">
         <f t="shared" si="3"/>
-        <v>56</v>
-      </c>
-      <c r="N33" s="1">
-        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="O33" s="1">
@@ -4571,11 +4555,11 @@
         <v>0</v>
       </c>
       <c r="V33" s="1">
+        <f t="shared" si="4"/>
+        <v>280</v>
+      </c>
+      <c r="W33" s="1">
         <f t="shared" si="5"/>
-        <v>280</v>
-      </c>
-      <c r="W33" s="1">
-        <f t="shared" si="6"/>
         <v>280</v>
       </c>
       <c r="X33" s="1">
@@ -4595,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="AC33" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1376</v>
       </c>
       <c r="AD33" s="1">
@@ -4626,11 +4610,11 @@
         <v>29</v>
       </c>
       <c r="H34" s="1">
+        <f t="shared" si="9"/>
+        <v>6781800</v>
+      </c>
+      <c r="I34" s="1">
         <f t="shared" si="10"/>
-        <v>6781800</v>
-      </c>
-      <c r="I34" s="1">
-        <f t="shared" si="0"/>
         <v>1730400</v>
       </c>
       <c r="J34" s="1">
@@ -4638,19 +4622,19 @@
         <v>258042000</v>
       </c>
       <c r="K34" s="1">
+        <f t="shared" si="0"/>
+        <v>145</v>
+      </c>
+      <c r="L34" s="1">
         <f t="shared" si="1"/>
-        <v>145</v>
-      </c>
-      <c r="L34" s="1">
+        <v>87</v>
+      </c>
+      <c r="M34" s="1">
         <f t="shared" si="2"/>
-        <v>87</v>
-      </c>
-      <c r="M34" s="1">
+        <v>58</v>
+      </c>
+      <c r="N34" s="1">
         <f t="shared" si="3"/>
-        <v>58</v>
-      </c>
-      <c r="N34" s="1">
-        <f t="shared" si="4"/>
         <v>116</v>
       </c>
       <c r="O34" s="1">
@@ -4676,11 +4660,11 @@
         <v>0</v>
       </c>
       <c r="V34" s="1">
+        <f t="shared" si="4"/>
+        <v>290</v>
+      </c>
+      <c r="W34" s="1">
         <f t="shared" si="5"/>
-        <v>290</v>
-      </c>
-      <c r="W34" s="1">
-        <f t="shared" si="6"/>
         <v>290</v>
       </c>
       <c r="X34" s="1">
@@ -4700,7 +4684,7 @@
         <v>28</v>
       </c>
       <c r="AC34" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1483</v>
       </c>
       <c r="AD34" s="1">
@@ -4731,11 +4715,11 @@
         <v>30</v>
       </c>
       <c r="H35" s="1">
+        <f t="shared" si="9"/>
+        <v>8894900</v>
+      </c>
+      <c r="I35" s="1">
         <f t="shared" si="10"/>
-        <v>8894900</v>
-      </c>
-      <c r="I35" s="1">
-        <f t="shared" si="0"/>
         <v>2172100</v>
       </c>
       <c r="J35" s="1">
@@ -4743,19 +4727,19 @@
         <v>334320000</v>
       </c>
       <c r="K35" s="1">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="L35" s="1">
         <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-      <c r="L35" s="1">
+        <v>90</v>
+      </c>
+      <c r="M35" s="1">
         <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="M35" s="1">
+        <v>60</v>
+      </c>
+      <c r="N35" s="1">
         <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="N35" s="1">
-        <f t="shared" si="4"/>
         <v>120</v>
       </c>
       <c r="O35" s="1">
@@ -4781,11 +4765,11 @@
         <v>0</v>
       </c>
       <c r="V35" s="1">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="W35" s="1">
         <f t="shared" si="5"/>
-        <v>300</v>
-      </c>
-      <c r="W35" s="1">
-        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="X35" s="1">
@@ -4805,7 +4789,7 @@
         <v>29</v>
       </c>
       <c r="AC35" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1592</v>
       </c>
       <c r="AD35" s="1">
@@ -4836,11 +4820,11 @@
         <v>31</v>
       </c>
       <c r="H36" s="1">
+        <f t="shared" si="9"/>
+        <v>11069600</v>
+      </c>
+      <c r="I36" s="1">
         <f t="shared" si="10"/>
-        <v>11069600</v>
-      </c>
-      <c r="I36" s="1">
-        <f t="shared" si="0"/>
         <v>2616000</v>
       </c>
       <c r="J36" s="1">
@@ -4848,19 +4832,19 @@
         <v>422840000</v>
       </c>
       <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>155</v>
+      </c>
+      <c r="L36" s="1">
         <f t="shared" si="1"/>
-        <v>155</v>
-      </c>
-      <c r="L36" s="1">
+        <v>93</v>
+      </c>
+      <c r="M36" s="1">
         <f t="shared" si="2"/>
-        <v>93</v>
-      </c>
-      <c r="M36" s="1">
+        <v>62</v>
+      </c>
+      <c r="N36" s="1">
         <f t="shared" si="3"/>
-        <v>62</v>
-      </c>
-      <c r="N36" s="1">
-        <f t="shared" si="4"/>
         <v>124</v>
       </c>
       <c r="O36" s="1">
@@ -4886,11 +4870,11 @@
         <v>0</v>
       </c>
       <c r="V36" s="1">
+        <f t="shared" si="4"/>
+        <v>310</v>
+      </c>
+      <c r="W36" s="1">
         <f t="shared" si="5"/>
-        <v>310</v>
-      </c>
-      <c r="W36" s="1">
-        <f t="shared" si="6"/>
         <v>310</v>
       </c>
       <c r="X36" s="1">
@@ -4910,7 +4894,7 @@
         <v>30</v>
       </c>
       <c r="AC36" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1705</v>
       </c>
       <c r="AD36" s="1">
@@ -4941,11 +4925,11 @@
         <v>32</v>
       </c>
       <c r="H37" s="1">
+        <f t="shared" si="9"/>
+        <v>12885300</v>
+      </c>
+      <c r="I37" s="1">
         <f t="shared" si="10"/>
-        <v>12885300</v>
-      </c>
-      <c r="I37" s="1">
-        <f t="shared" si="0"/>
         <v>3152700</v>
       </c>
       <c r="J37" s="1">
@@ -4953,19 +4937,19 @@
         <v>527616000</v>
       </c>
       <c r="K37" s="1">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="L37" s="1">
         <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="L37" s="1">
+        <v>96</v>
+      </c>
+      <c r="M37" s="1">
         <f t="shared" si="2"/>
-        <v>96</v>
-      </c>
-      <c r="M37" s="1">
+        <v>64</v>
+      </c>
+      <c r="N37" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
-      </c>
-      <c r="N37" s="1">
-        <f t="shared" si="4"/>
         <v>128</v>
       </c>
       <c r="O37" s="1">
@@ -4991,11 +4975,11 @@
         <v>0</v>
       </c>
       <c r="V37" s="1">
+        <f t="shared" si="4"/>
+        <v>320</v>
+      </c>
+      <c r="W37" s="1">
         <f t="shared" si="5"/>
-        <v>320</v>
-      </c>
-      <c r="W37" s="1">
-        <f t="shared" si="6"/>
         <v>320</v>
       </c>
       <c r="X37" s="1">
@@ -5015,7 +4999,7 @@
         <v>31</v>
       </c>
       <c r="AC37" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1832</v>
       </c>
       <c r="AD37" s="1">
@@ -5046,11 +5030,11 @@
         <v>33</v>
       </c>
       <c r="H38" s="1">
+        <f t="shared" si="9"/>
+        <v>15943000</v>
+      </c>
+      <c r="I38" s="1">
         <f t="shared" si="10"/>
-        <v>15943000</v>
-      </c>
-      <c r="I38" s="1">
-        <f t="shared" si="0"/>
         <v>4064000</v>
       </c>
       <c r="J38" s="1">
@@ -5058,19 +5042,19 @@
         <v>647790000</v>
       </c>
       <c r="K38" s="1">
+        <f t="shared" si="0"/>
+        <v>165</v>
+      </c>
+      <c r="L38" s="1">
         <f t="shared" si="1"/>
-        <v>165</v>
-      </c>
-      <c r="L38" s="1">
+        <v>99</v>
+      </c>
+      <c r="M38" s="1">
         <f t="shared" si="2"/>
-        <v>99</v>
-      </c>
-      <c r="M38" s="1">
+        <v>66</v>
+      </c>
+      <c r="N38" s="1">
         <f t="shared" si="3"/>
-        <v>66</v>
-      </c>
-      <c r="N38" s="1">
-        <f t="shared" si="4"/>
         <v>132</v>
       </c>
       <c r="O38" s="1">
@@ -5096,11 +5080,11 @@
         <v>0</v>
       </c>
       <c r="V38" s="1">
+        <f t="shared" si="4"/>
+        <v>330</v>
+      </c>
+      <c r="W38" s="1">
         <f t="shared" si="5"/>
-        <v>330</v>
-      </c>
-      <c r="W38" s="1">
-        <f t="shared" si="6"/>
         <v>330</v>
       </c>
       <c r="X38" s="1">
@@ -5120,7 +5104,7 @@
         <v>32</v>
       </c>
       <c r="AC38" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1963</v>
       </c>
       <c r="AD38" s="1">
@@ -5151,11 +5135,11 @@
         <v>34</v>
       </c>
       <c r="H39" s="1">
+        <f t="shared" si="9"/>
+        <v>19750800</v>
+      </c>
+      <c r="I39" s="1">
         <f t="shared" si="10"/>
-        <v>19750800</v>
-      </c>
-      <c r="I39" s="1">
-        <f t="shared" si="0"/>
         <v>5187600</v>
       </c>
       <c r="J39" s="1">
@@ -5163,19 +5147,19 @@
         <v>856800000</v>
       </c>
       <c r="K39" s="1">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="L39" s="1">
         <f t="shared" si="1"/>
-        <v>170</v>
-      </c>
-      <c r="L39" s="1">
+        <v>102</v>
+      </c>
+      <c r="M39" s="1">
         <f t="shared" si="2"/>
-        <v>102</v>
-      </c>
-      <c r="M39" s="1">
+        <v>68</v>
+      </c>
+      <c r="N39" s="1">
         <f t="shared" si="3"/>
-        <v>68</v>
-      </c>
-      <c r="N39" s="1">
-        <f t="shared" si="4"/>
         <v>136</v>
       </c>
       <c r="O39" s="1">
@@ -5201,11 +5185,11 @@
         <v>0</v>
       </c>
       <c r="V39" s="1">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+      <c r="W39" s="1">
         <f t="shared" si="5"/>
-        <v>340</v>
-      </c>
-      <c r="W39" s="1">
-        <f t="shared" si="6"/>
         <v>340</v>
       </c>
       <c r="X39" s="1">
@@ -5225,7 +5209,7 @@
         <v>33</v>
       </c>
       <c r="AC39" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2100</v>
       </c>
       <c r="AD39" s="1">
@@ -5256,11 +5240,11 @@
         <v>35</v>
       </c>
       <c r="H40" s="1">
+        <f t="shared" si="9"/>
+        <v>24837400</v>
+      </c>
+      <c r="I40" s="1">
         <f t="shared" si="10"/>
-        <v>24837400</v>
-      </c>
-      <c r="I40" s="1">
-        <f t="shared" si="0"/>
         <v>6521200</v>
       </c>
       <c r="J40" s="1">
@@ -5268,19 +5252,19 @@
         <v>1097110000</v>
       </c>
       <c r="K40" s="1">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="L40" s="1">
         <f t="shared" si="1"/>
-        <v>175</v>
-      </c>
-      <c r="L40" s="1">
+        <v>105</v>
+      </c>
+      <c r="M40" s="1">
         <f t="shared" si="2"/>
-        <v>105</v>
-      </c>
-      <c r="M40" s="1">
+        <v>70</v>
+      </c>
+      <c r="N40" s="1">
         <f t="shared" si="3"/>
-        <v>70</v>
-      </c>
-      <c r="N40" s="1">
-        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="O40" s="1">
@@ -5306,11 +5290,11 @@
         <v>0</v>
       </c>
       <c r="V40" s="1">
+        <f t="shared" si="4"/>
+        <v>350</v>
+      </c>
+      <c r="W40" s="1">
         <f t="shared" si="5"/>
-        <v>350</v>
-      </c>
-      <c r="W40" s="1">
-        <f t="shared" si="6"/>
         <v>350</v>
       </c>
       <c r="X40" s="1">
@@ -5330,7 +5314,7 @@
         <v>34</v>
       </c>
       <c r="AC40" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2239</v>
       </c>
       <c r="AD40" s="1">
@@ -5362,11 +5346,11 @@
         <v>36</v>
       </c>
       <c r="H41" s="1">
+        <f t="shared" si="9"/>
+        <v>33121600</v>
+      </c>
+      <c r="I41" s="1">
         <f t="shared" si="10"/>
-        <v>33121600</v>
-      </c>
-      <c r="I41" s="1">
-        <f t="shared" si="0"/>
         <v>7784000</v>
       </c>
       <c r="J41" s="1">
@@ -5374,19 +5358,19 @@
         <v>1375488000</v>
       </c>
       <c r="K41" s="1">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="L41" s="1">
         <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="L41" s="1">
+        <v>108</v>
+      </c>
+      <c r="M41" s="1">
         <f t="shared" si="2"/>
-        <v>108</v>
-      </c>
-      <c r="M41" s="1">
+        <v>72</v>
+      </c>
+      <c r="N41" s="1">
         <f t="shared" si="3"/>
-        <v>72</v>
-      </c>
-      <c r="N41" s="1">
-        <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="O41" s="1">
@@ -5412,11 +5396,11 @@
         <v>0</v>
       </c>
       <c r="V41" s="1">
+        <f t="shared" si="4"/>
+        <v>360</v>
+      </c>
+      <c r="W41" s="1">
         <f t="shared" si="5"/>
-        <v>360</v>
-      </c>
-      <c r="W41" s="1">
-        <f t="shared" si="6"/>
         <v>360</v>
       </c>
       <c r="X41" s="1">
@@ -5436,7 +5420,7 @@
         <v>35</v>
       </c>
       <c r="AC41" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2388</v>
       </c>
       <c r="AD41" s="1">
@@ -5467,11 +5451,11 @@
         <v>37</v>
       </c>
       <c r="H42" s="1">
+        <f t="shared" si="9"/>
+        <v>39378600</v>
+      </c>
+      <c r="I42" s="1">
         <f t="shared" si="10"/>
-        <v>39378600</v>
-      </c>
-      <c r="I42" s="1">
-        <f t="shared" si="0"/>
         <v>9655200</v>
       </c>
       <c r="J42" s="1">
@@ -5479,19 +5463,19 @@
         <v>1690974000</v>
       </c>
       <c r="K42" s="1">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+      <c r="L42" s="1">
         <f t="shared" si="1"/>
-        <v>185</v>
-      </c>
-      <c r="L42" s="1">
+        <v>111</v>
+      </c>
+      <c r="M42" s="1">
         <f t="shared" si="2"/>
-        <v>111</v>
-      </c>
-      <c r="M42" s="1">
+        <v>74</v>
+      </c>
+      <c r="N42" s="1">
         <f t="shared" si="3"/>
-        <v>74</v>
-      </c>
-      <c r="N42" s="1">
-        <f t="shared" si="4"/>
         <v>148</v>
       </c>
       <c r="O42" s="1">
@@ -5517,11 +5501,11 @@
         <v>0</v>
       </c>
       <c r="V42" s="1">
+        <f t="shared" si="4"/>
+        <v>370</v>
+      </c>
+      <c r="W42" s="1">
         <f t="shared" si="5"/>
-        <v>370</v>
-      </c>
-      <c r="W42" s="1">
-        <f t="shared" si="6"/>
         <v>370</v>
       </c>
       <c r="X42" s="1">
@@ -5541,7 +5525,7 @@
         <v>36</v>
       </c>
       <c r="AC42" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2539</v>
       </c>
       <c r="AD42" s="1">
@@ -5572,11 +5556,11 @@
         <v>38</v>
       </c>
       <c r="H43" s="1">
+        <f t="shared" si="9"/>
+        <v>47402000</v>
+      </c>
+      <c r="I43" s="1">
         <f t="shared" si="10"/>
-        <v>47402000</v>
-      </c>
-      <c r="I43" s="1">
-        <f t="shared" si="0"/>
         <v>11174000</v>
       </c>
       <c r="J43" s="1">
@@ -5584,19 +5568,19 @@
         <v>2048960000</v>
       </c>
       <c r="K43" s="1">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="L43" s="1">
         <f t="shared" si="1"/>
-        <v>190</v>
-      </c>
-      <c r="L43" s="1">
+        <v>114</v>
+      </c>
+      <c r="M43" s="1">
         <f t="shared" si="2"/>
-        <v>114</v>
-      </c>
-      <c r="M43" s="1">
+        <v>76</v>
+      </c>
+      <c r="N43" s="1">
         <f t="shared" si="3"/>
-        <v>76</v>
-      </c>
-      <c r="N43" s="1">
-        <f t="shared" si="4"/>
         <v>152</v>
       </c>
       <c r="O43" s="1">
@@ -5622,11 +5606,11 @@
         <v>0</v>
       </c>
       <c r="V43" s="1">
+        <f t="shared" si="4"/>
+        <v>380</v>
+      </c>
+      <c r="W43" s="1">
         <f t="shared" si="5"/>
-        <v>380</v>
-      </c>
-      <c r="W43" s="1">
-        <f t="shared" si="6"/>
         <v>380</v>
       </c>
       <c r="X43" s="1">
@@ -5646,7 +5630,7 @@
         <v>37</v>
       </c>
       <c r="AC43" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2696</v>
       </c>
       <c r="AD43" s="1">
@@ -5677,11 +5661,11 @@
         <v>39</v>
       </c>
       <c r="H44" s="1">
+        <f t="shared" si="9"/>
+        <v>62202500</v>
+      </c>
+      <c r="I44" s="1">
         <f t="shared" si="10"/>
-        <v>62202500</v>
-      </c>
-      <c r="I44" s="1">
-        <f t="shared" si="0"/>
         <v>14915000</v>
       </c>
       <c r="J44" s="1">
@@ -5689,19 +5673,19 @@
         <v>2787525000</v>
       </c>
       <c r="K44" s="1">
+        <f t="shared" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="L44" s="1">
         <f t="shared" si="1"/>
-        <v>195</v>
-      </c>
-      <c r="L44" s="1">
+        <v>117</v>
+      </c>
+      <c r="M44" s="1">
         <f t="shared" si="2"/>
-        <v>117</v>
-      </c>
-      <c r="M44" s="1">
+        <v>78</v>
+      </c>
+      <c r="N44" s="1">
         <f t="shared" si="3"/>
-        <v>78</v>
-      </c>
-      <c r="N44" s="1">
-        <f t="shared" si="4"/>
         <v>156</v>
       </c>
       <c r="O44" s="1">
@@ -5727,11 +5711,11 @@
         <v>0</v>
       </c>
       <c r="V44" s="1">
+        <f t="shared" si="4"/>
+        <v>390</v>
+      </c>
+      <c r="W44" s="1">
         <f t="shared" si="5"/>
-        <v>390</v>
-      </c>
-      <c r="W44" s="1">
-        <f t="shared" si="6"/>
         <v>390</v>
       </c>
       <c r="X44" s="1">
@@ -5751,7 +5735,7 @@
         <v>38</v>
       </c>
       <c r="AC44" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2859</v>
       </c>
       <c r="AD44" s="1">
@@ -5782,11 +5766,11 @@
         <v>40</v>
       </c>
       <c r="H45" s="1">
+        <f t="shared" si="9"/>
+        <v>80907000</v>
+      </c>
+      <c r="I45" s="1">
         <f t="shared" si="10"/>
-        <v>80907000</v>
-      </c>
-      <c r="I45" s="1">
-        <f t="shared" si="0"/>
         <v>19071000</v>
       </c>
       <c r="J45" s="1">
@@ -5794,19 +5778,19 @@
         <v>3631200000</v>
       </c>
       <c r="K45" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L45" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L45" s="1">
+        <v>120</v>
+      </c>
+      <c r="M45" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M45" s="1">
+        <v>80</v>
+      </c>
+      <c r="N45" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N45" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O45" s="1">
@@ -5832,11 +5816,11 @@
         <v>0</v>
       </c>
       <c r="V45" s="1">
+        <f t="shared" si="4"/>
+        <v>400</v>
+      </c>
+      <c r="W45" s="1">
         <f t="shared" si="5"/>
-        <v>400</v>
-      </c>
-      <c r="W45" s="1">
-        <f t="shared" si="6"/>
         <v>400</v>
       </c>
       <c r="X45" s="1">
@@ -5856,7 +5840,7 @@
         <v>39</v>
       </c>
       <c r="AC45" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3026</v>
       </c>
       <c r="AD45" s="1">
@@ -5887,11 +5871,11 @@
         <v>41</v>
       </c>
       <c r="H46" s="1">
+        <f t="shared" si="9"/>
+        <v>100943500</v>
+      </c>
+      <c r="I46" s="1">
         <f t="shared" si="10"/>
-        <v>100943500</v>
-      </c>
-      <c r="I46" s="1">
-        <f t="shared" si="0"/>
         <v>22795500</v>
       </c>
       <c r="J46" s="1">
@@ -5899,19 +5883,19 @@
         <v>4478600000</v>
       </c>
       <c r="K46" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L46" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L46" s="1">
+        <v>120</v>
+      </c>
+      <c r="M46" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M46" s="1">
+        <v>80</v>
+      </c>
+      <c r="N46" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N46" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O46" s="1">
@@ -5937,11 +5921,11 @@
         <v>0</v>
       </c>
       <c r="V46" s="1">
+        <f t="shared" si="4"/>
+        <v>410</v>
+      </c>
+      <c r="W46" s="1">
         <f t="shared" si="5"/>
-        <v>410</v>
-      </c>
-      <c r="W46" s="1">
-        <f t="shared" si="6"/>
         <v>410</v>
       </c>
       <c r="X46" s="1">
@@ -5961,7 +5945,7 @@
         <v>39</v>
       </c>
       <c r="AC46" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3199</v>
       </c>
       <c r="AD46" s="1">
@@ -5991,11 +5975,11 @@
         <v>42</v>
       </c>
       <c r="H47" s="1">
+        <f t="shared" si="9"/>
+        <v>116572000</v>
+      </c>
+      <c r="I47" s="1">
         <f t="shared" si="10"/>
-        <v>116572000</v>
-      </c>
-      <c r="I47" s="1">
-        <f t="shared" si="0"/>
         <v>26988000</v>
       </c>
       <c r="J47" s="1">
@@ -6003,19 +5987,19 @@
         <v>5404800000</v>
       </c>
       <c r="K47" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L47" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L47" s="1">
+        <v>120</v>
+      </c>
+      <c r="M47" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M47" s="1">
+        <v>80</v>
+      </c>
+      <c r="N47" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N47" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O47" s="1">
@@ -6041,11 +6025,11 @@
         <v>0</v>
       </c>
       <c r="V47" s="1">
+        <f t="shared" si="4"/>
+        <v>420</v>
+      </c>
+      <c r="W47" s="1">
         <f t="shared" si="5"/>
-        <v>420</v>
-      </c>
-      <c r="W47" s="1">
-        <f t="shared" si="6"/>
         <v>420</v>
       </c>
       <c r="X47" s="1">
@@ -6065,7 +6049,7 @@
         <v>39</v>
       </c>
       <c r="AC47" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3378</v>
       </c>
       <c r="AD47" s="1">
@@ -6096,11 +6080,11 @@
         <v>43</v>
       </c>
       <c r="H48" s="1">
+        <f t="shared" si="9"/>
+        <v>139180500</v>
+      </c>
+      <c r="I48" s="1">
         <f t="shared" si="10"/>
-        <v>139180500</v>
-      </c>
-      <c r="I48" s="1">
-        <f t="shared" si="0"/>
         <v>31414500</v>
       </c>
       <c r="J48" s="1">
@@ -6108,19 +6092,19 @@
         <v>6406200000</v>
       </c>
       <c r="K48" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L48" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L48" s="1">
+        <v>120</v>
+      </c>
+      <c r="M48" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M48" s="1">
+        <v>80</v>
+      </c>
+      <c r="N48" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N48" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O48" s="1">
@@ -6146,11 +6130,11 @@
         <v>0</v>
       </c>
       <c r="V48" s="1">
+        <f t="shared" si="4"/>
+        <v>430</v>
+      </c>
+      <c r="W48" s="1">
         <f t="shared" si="5"/>
-        <v>430</v>
-      </c>
-      <c r="W48" s="1">
-        <f t="shared" si="6"/>
         <v>430</v>
       </c>
       <c r="X48" s="1">
@@ -6170,7 +6154,7 @@
         <v>39</v>
       </c>
       <c r="AC48" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3559</v>
       </c>
       <c r="AD48" s="1">
@@ -6201,11 +6185,11 @@
         <v>44</v>
       </c>
       <c r="H49" s="1">
+        <f t="shared" si="9"/>
+        <v>172135000</v>
+      </c>
+      <c r="I49" s="1">
         <f t="shared" si="10"/>
-        <v>172135000</v>
-      </c>
-      <c r="I49" s="1">
-        <f t="shared" si="0"/>
         <v>35295000</v>
       </c>
       <c r="J49" s="1">
@@ -6213,19 +6197,19 @@
         <v>7500000000</v>
       </c>
       <c r="K49" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L49" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L49" s="1">
+        <v>120</v>
+      </c>
+      <c r="M49" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M49" s="1">
+        <v>80</v>
+      </c>
+      <c r="N49" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N49" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O49" s="1">
@@ -6251,11 +6235,11 @@
         <v>0</v>
       </c>
       <c r="V49" s="1">
+        <f t="shared" si="4"/>
+        <v>440</v>
+      </c>
+      <c r="W49" s="1">
         <f t="shared" si="5"/>
-        <v>440</v>
-      </c>
-      <c r="W49" s="1">
-        <f t="shared" si="6"/>
         <v>440</v>
       </c>
       <c r="X49" s="1">
@@ -6275,7 +6259,7 @@
         <v>39</v>
       </c>
       <c r="AC49" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3750</v>
       </c>
       <c r="AD49" s="1">
@@ -6306,11 +6290,11 @@
         <v>45</v>
       </c>
       <c r="H50" s="1">
+        <f t="shared" si="9"/>
+        <v>200766500</v>
+      </c>
+      <c r="I50" s="1">
         <f t="shared" si="10"/>
-        <v>200766500</v>
-      </c>
-      <c r="I50" s="1">
-        <f t="shared" si="0"/>
         <v>40969500</v>
       </c>
       <c r="J50" s="1">
@@ -6318,19 +6302,19 @@
         <v>8674600000</v>
       </c>
       <c r="K50" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L50" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L50" s="1">
+        <v>120</v>
+      </c>
+      <c r="M50" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M50" s="1">
+        <v>80</v>
+      </c>
+      <c r="N50" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N50" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O50" s="1">
@@ -6356,11 +6340,11 @@
         <v>0</v>
       </c>
       <c r="V50" s="1">
+        <f t="shared" si="4"/>
+        <v>450</v>
+      </c>
+      <c r="W50" s="1">
         <f t="shared" si="5"/>
-        <v>450</v>
-      </c>
-      <c r="W50" s="1">
-        <f t="shared" si="6"/>
         <v>450</v>
       </c>
       <c r="X50" s="1">
@@ -6380,7 +6364,7 @@
         <v>39</v>
       </c>
       <c r="AC50" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3943</v>
       </c>
       <c r="AD50" s="1">
@@ -6411,11 +6395,11 @@
         <v>46</v>
       </c>
       <c r="H51" s="1">
+        <f t="shared" si="9"/>
+        <v>231474000</v>
+      </c>
+      <c r="I51" s="1">
         <f t="shared" si="10"/>
-        <v>231474000</v>
-      </c>
-      <c r="I51" s="1">
-        <f t="shared" si="0"/>
         <v>45162000</v>
       </c>
       <c r="J51" s="1">
@@ -6423,19 +6407,19 @@
         <v>9936000000</v>
       </c>
       <c r="K51" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L51" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L51" s="1">
+        <v>120</v>
+      </c>
+      <c r="M51" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M51" s="1">
+        <v>80</v>
+      </c>
+      <c r="N51" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N51" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O51" s="1">
@@ -6461,11 +6445,11 @@
         <v>0</v>
       </c>
       <c r="V51" s="1">
+        <f t="shared" si="4"/>
+        <v>460</v>
+      </c>
+      <c r="W51" s="1">
         <f t="shared" si="5"/>
-        <v>460</v>
-      </c>
-      <c r="W51" s="1">
-        <f t="shared" si="6"/>
         <v>460</v>
       </c>
       <c r="X51" s="1">
@@ -6485,7 +6469,7 @@
         <v>39</v>
       </c>
       <c r="AC51" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4140</v>
       </c>
       <c r="AD51" s="1">
@@ -6516,11 +6500,11 @@
         <v>47</v>
       </c>
       <c r="H52" s="1">
+        <f t="shared" si="9"/>
+        <v>255261500</v>
+      </c>
+      <c r="I52" s="1">
         <f t="shared" si="10"/>
-        <v>255261500</v>
-      </c>
-      <c r="I52" s="1">
-        <f t="shared" si="0"/>
         <v>49939500</v>
       </c>
       <c r="J52" s="1">
@@ -6528,19 +6512,19 @@
         <v>11281400000</v>
       </c>
       <c r="K52" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L52" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L52" s="1">
+        <v>120</v>
+      </c>
+      <c r="M52" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M52" s="1">
+        <v>80</v>
+      </c>
+      <c r="N52" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N52" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O52" s="1">
@@ -6566,11 +6550,11 @@
         <v>0</v>
       </c>
       <c r="V52" s="1">
+        <f t="shared" si="4"/>
+        <v>470</v>
+      </c>
+      <c r="W52" s="1">
         <f t="shared" si="5"/>
-        <v>470</v>
-      </c>
-      <c r="W52" s="1">
-        <f t="shared" si="6"/>
         <v>470</v>
       </c>
       <c r="X52" s="1">
@@ -6590,7 +6574,7 @@
         <v>39</v>
       </c>
       <c r="AC52" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4339</v>
       </c>
       <c r="AD52" s="1">
@@ -6621,11 +6605,11 @@
         <v>48</v>
       </c>
       <c r="H53" s="1">
+        <f t="shared" si="9"/>
+        <v>277319000</v>
+      </c>
+      <c r="I53" s="1">
         <f t="shared" si="10"/>
-        <v>277319000</v>
-      </c>
-      <c r="I53" s="1">
-        <f t="shared" si="0"/>
         <v>54327000</v>
       </c>
       <c r="J53" s="1">
@@ -6633,19 +6617,19 @@
         <v>12740000000</v>
       </c>
       <c r="K53" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L53" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L53" s="1">
+        <v>120</v>
+      </c>
+      <c r="M53" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M53" s="1">
+        <v>80</v>
+      </c>
+      <c r="N53" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N53" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O53" s="1">
@@ -6671,11 +6655,11 @@
         <v>0</v>
       </c>
       <c r="V53" s="1">
+        <f t="shared" si="4"/>
+        <v>480</v>
+      </c>
+      <c r="W53" s="1">
         <f t="shared" si="5"/>
-        <v>480</v>
-      </c>
-      <c r="W53" s="1">
-        <f t="shared" si="6"/>
         <v>480</v>
       </c>
       <c r="X53" s="1">
@@ -6695,7 +6679,7 @@
         <v>39</v>
       </c>
       <c r="AC53" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4550</v>
       </c>
       <c r="AD53" s="1">
@@ -6726,11 +6710,11 @@
         <v>49</v>
       </c>
       <c r="H54" s="1">
+        <f t="shared" si="9"/>
+        <v>302317500</v>
+      </c>
+      <c r="I54" s="1">
         <f t="shared" si="10"/>
-        <v>302317500</v>
-      </c>
-      <c r="I54" s="1">
-        <f t="shared" si="0"/>
         <v>61717500</v>
       </c>
       <c r="J54" s="1">
@@ -6738,19 +6722,19 @@
         <v>14319000000</v>
       </c>
       <c r="K54" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L54" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L54" s="1">
+        <v>120</v>
+      </c>
+      <c r="M54" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M54" s="1">
+        <v>80</v>
+      </c>
+      <c r="N54" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N54" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O54" s="1">
@@ -6776,11 +6760,11 @@
         <v>0</v>
       </c>
       <c r="V54" s="1">
+        <f t="shared" si="4"/>
+        <v>490</v>
+      </c>
+      <c r="W54" s="1">
         <f t="shared" si="5"/>
-        <v>490</v>
-      </c>
-      <c r="W54" s="1">
-        <f t="shared" si="6"/>
         <v>490</v>
       </c>
       <c r="X54" s="1">
@@ -6800,7 +6784,7 @@
         <v>39</v>
       </c>
       <c r="AC54" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4773</v>
       </c>
       <c r="AD54" s="1">
@@ -6831,11 +6815,11 @@
         <v>50</v>
       </c>
       <c r="H55" s="1">
+        <f t="shared" si="9"/>
+        <v>330776000</v>
+      </c>
+      <c r="I55" s="1">
         <f t="shared" si="10"/>
-        <v>330776000</v>
-      </c>
-      <c r="I55" s="1">
-        <f t="shared" si="0"/>
         <v>69576000</v>
       </c>
       <c r="J55" s="1">
@@ -6843,19 +6827,19 @@
         <v>16000000000</v>
       </c>
       <c r="K55" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L55" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L55" s="1">
+        <v>120</v>
+      </c>
+      <c r="M55" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M55" s="1">
+        <v>80</v>
+      </c>
+      <c r="N55" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N55" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O55" s="1">
@@ -6881,11 +6865,11 @@
         <v>0</v>
       </c>
       <c r="V55" s="1">
+        <f t="shared" si="4"/>
+        <v>500</v>
+      </c>
+      <c r="W55" s="1">
         <f t="shared" si="5"/>
-        <v>500</v>
-      </c>
-      <c r="W55" s="1">
-        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="X55" s="1">
@@ -6905,7 +6889,7 @@
         <v>39</v>
       </c>
       <c r="AC55" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5000</v>
       </c>
       <c r="AD55" s="1">
@@ -6936,11 +6920,11 @@
         <v>51</v>
       </c>
       <c r="H56" s="1">
+        <f t="shared" si="9"/>
+        <v>354390500</v>
+      </c>
+      <c r="I56" s="1">
         <f t="shared" si="10"/>
-        <v>354390500</v>
-      </c>
-      <c r="I56" s="1">
-        <f t="shared" si="0"/>
         <v>75250500</v>
       </c>
       <c r="J56" s="1">
@@ -6948,19 +6932,19 @@
         <v>17778600000</v>
       </c>
       <c r="K56" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L56" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L56" s="1">
+        <v>120</v>
+      </c>
+      <c r="M56" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M56" s="1">
+        <v>80</v>
+      </c>
+      <c r="N56" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N56" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O56" s="1">
@@ -6986,11 +6970,11 @@
         <v>0</v>
       </c>
       <c r="V56" s="1">
+        <f t="shared" si="4"/>
+        <v>510</v>
+      </c>
+      <c r="W56" s="1">
         <f t="shared" si="5"/>
-        <v>510</v>
-      </c>
-      <c r="W56" s="1">
-        <f t="shared" si="6"/>
         <v>510</v>
       </c>
       <c r="X56" s="1">
@@ -7010,7 +6994,7 @@
         <v>39</v>
       </c>
       <c r="AC56" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5229</v>
       </c>
       <c r="AD56" s="1">
@@ -7041,11 +7025,11 @@
         <v>52</v>
       </c>
       <c r="H57" s="1">
+        <f t="shared" si="9"/>
+        <v>390807000</v>
+      </c>
+      <c r="I57" s="1">
         <f t="shared" si="10"/>
-        <v>390807000</v>
-      </c>
-      <c r="I57" s="1">
-        <f t="shared" si="0"/>
         <v>80379000</v>
       </c>
       <c r="J57" s="1">
@@ -7053,19 +7037,19 @@
         <v>19663200000</v>
       </c>
       <c r="K57" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L57" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L57" s="1">
+        <v>120</v>
+      </c>
+      <c r="M57" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M57" s="1">
+        <v>80</v>
+      </c>
+      <c r="N57" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N57" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O57" s="1">
@@ -7091,11 +7075,11 @@
         <v>0</v>
       </c>
       <c r="V57" s="1">
+        <f t="shared" si="4"/>
+        <v>520</v>
+      </c>
+      <c r="W57" s="1">
         <f t="shared" si="5"/>
-        <v>520</v>
-      </c>
-      <c r="W57" s="1">
-        <f t="shared" si="6"/>
         <v>520</v>
       </c>
       <c r="X57" s="1">
@@ -7115,7 +7099,7 @@
         <v>39</v>
       </c>
       <c r="AC57" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5462</v>
       </c>
       <c r="AD57" s="1">
@@ -7146,11 +7130,11 @@
         <v>53</v>
       </c>
       <c r="H58" s="1">
+        <f t="shared" si="9"/>
+        <v>422379500</v>
+      </c>
+      <c r="I58" s="1">
         <f t="shared" si="10"/>
-        <v>422379500</v>
-      </c>
-      <c r="I58" s="1">
-        <f t="shared" si="0"/>
         <v>86326500</v>
       </c>
       <c r="J58" s="1">
@@ -7158,19 +7142,19 @@
         <v>21663800000</v>
       </c>
       <c r="K58" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L58" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L58" s="1">
+        <v>120</v>
+      </c>
+      <c r="M58" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M58" s="1">
+        <v>80</v>
+      </c>
+      <c r="N58" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N58" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O58" s="1">
@@ -7196,11 +7180,11 @@
         <v>0</v>
       </c>
       <c r="V58" s="1">
+        <f t="shared" si="4"/>
+        <v>530</v>
+      </c>
+      <c r="W58" s="1">
         <f t="shared" si="5"/>
-        <v>530</v>
-      </c>
-      <c r="W58" s="1">
-        <f t="shared" si="6"/>
         <v>530</v>
       </c>
       <c r="X58" s="1">
@@ -7220,7 +7204,7 @@
         <v>39</v>
       </c>
       <c r="AC58" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5701</v>
       </c>
       <c r="AD58" s="1">
@@ -7251,11 +7235,11 @@
         <v>54</v>
       </c>
       <c r="H59" s="1">
+        <f t="shared" si="9"/>
+        <v>454990000</v>
+      </c>
+      <c r="I59" s="1">
         <f t="shared" si="10"/>
-        <v>454990000</v>
-      </c>
-      <c r="I59" s="1">
-        <f t="shared" si="0"/>
         <v>93210000</v>
       </c>
       <c r="J59" s="1">
@@ -7263,19 +7247,19 @@
         <v>23768000000</v>
       </c>
       <c r="K59" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L59" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L59" s="1">
+        <v>120</v>
+      </c>
+      <c r="M59" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M59" s="1">
+        <v>80</v>
+      </c>
+      <c r="N59" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N59" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O59" s="1">
@@ -7301,11 +7285,11 @@
         <v>0</v>
       </c>
       <c r="V59" s="1">
+        <f t="shared" si="4"/>
+        <v>540</v>
+      </c>
+      <c r="W59" s="1">
         <f t="shared" si="5"/>
-        <v>540</v>
-      </c>
-      <c r="W59" s="1">
-        <f t="shared" si="6"/>
         <v>540</v>
       </c>
       <c r="X59" s="1">
@@ -7325,7 +7309,7 @@
         <v>39</v>
       </c>
       <c r="AC59" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5942</v>
       </c>
       <c r="AD59" s="1">
@@ -7356,11 +7340,11 @@
         <v>55</v>
       </c>
       <c r="H60" s="1">
+        <f t="shared" si="9"/>
+        <v>488638500</v>
+      </c>
+      <c r="I60" s="1">
         <f t="shared" si="10"/>
-        <v>488638500</v>
-      </c>
-      <c r="I60" s="1">
-        <f t="shared" si="0"/>
         <v>98689500</v>
       </c>
       <c r="J60" s="1">
@@ -7368,19 +7352,19 @@
         <v>26010600000</v>
       </c>
       <c r="K60" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L60" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L60" s="1">
+        <v>120</v>
+      </c>
+      <c r="M60" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M60" s="1">
+        <v>80</v>
+      </c>
+      <c r="N60" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N60" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O60" s="1">
@@ -7406,11 +7390,11 @@
         <v>0</v>
       </c>
       <c r="V60" s="1">
+        <f t="shared" si="4"/>
+        <v>550</v>
+      </c>
+      <c r="W60" s="1">
         <f t="shared" si="5"/>
-        <v>550</v>
-      </c>
-      <c r="W60" s="1">
-        <f t="shared" si="6"/>
         <v>550</v>
       </c>
       <c r="X60" s="1">
@@ -7430,7 +7414,7 @@
         <v>39</v>
       </c>
       <c r="AC60" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6193</v>
       </c>
       <c r="AD60" s="1">
@@ -7461,11 +7445,11 @@
         <v>56</v>
       </c>
       <c r="H61" s="1">
+        <f t="shared" si="9"/>
+        <v>515713000</v>
+      </c>
+      <c r="I61" s="1">
         <f t="shared" si="10"/>
-        <v>515713000</v>
-      </c>
-      <c r="I61" s="1">
-        <f t="shared" si="0"/>
         <v>107679000</v>
       </c>
       <c r="J61" s="1">
@@ -7473,19 +7457,19 @@
         <v>28380000000</v>
       </c>
       <c r="K61" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L61" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L61" s="1">
+        <v>120</v>
+      </c>
+      <c r="M61" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M61" s="1">
+        <v>80</v>
+      </c>
+      <c r="N61" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N61" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O61" s="1">
@@ -7511,11 +7495,11 @@
         <v>0</v>
       </c>
       <c r="V61" s="1">
+        <f t="shared" si="4"/>
+        <v>560</v>
+      </c>
+      <c r="W61" s="1">
         <f t="shared" si="5"/>
-        <v>560</v>
-      </c>
-      <c r="W61" s="1">
-        <f t="shared" si="6"/>
         <v>560</v>
       </c>
       <c r="X61" s="1">
@@ -7535,7 +7519,7 @@
         <v>39</v>
       </c>
       <c r="AC61" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6450</v>
       </c>
       <c r="AD61" s="1">
@@ -7566,11 +7550,11 @@
         <v>57</v>
       </c>
       <c r="H62" s="1">
+        <f t="shared" si="9"/>
+        <v>551091500</v>
+      </c>
+      <c r="I62" s="1">
         <f t="shared" si="10"/>
-        <v>551091500</v>
-      </c>
-      <c r="I62" s="1">
-        <f t="shared" si="0"/>
         <v>115264500</v>
       </c>
       <c r="J62" s="1">
@@ -7578,19 +7562,19 @@
         <v>30879800000</v>
       </c>
       <c r="K62" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L62" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L62" s="1">
+        <v>120</v>
+      </c>
+      <c r="M62" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M62" s="1">
+        <v>80</v>
+      </c>
+      <c r="N62" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N62" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O62" s="1">
@@ -7616,11 +7600,11 @@
         <v>0</v>
       </c>
       <c r="V62" s="1">
+        <f t="shared" si="4"/>
+        <v>570</v>
+      </c>
+      <c r="W62" s="1">
         <f t="shared" si="5"/>
-        <v>570</v>
-      </c>
-      <c r="W62" s="1">
-        <f t="shared" si="6"/>
         <v>570</v>
       </c>
       <c r="X62" s="1">
@@ -7640,7 +7624,7 @@
         <v>39</v>
       </c>
       <c r="AC62" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6713</v>
       </c>
       <c r="AD62" s="1">
@@ -7671,11 +7655,11 @@
         <v>58</v>
       </c>
       <c r="H63" s="1">
+        <f t="shared" si="9"/>
+        <v>583356000</v>
+      </c>
+      <c r="I63" s="1">
         <f t="shared" si="10"/>
-        <v>583356000</v>
-      </c>
-      <c r="I63" s="1">
-        <f t="shared" si="0"/>
         <v>123084000</v>
       </c>
       <c r="J63" s="1">
@@ -7683,19 +7667,19 @@
         <v>33513600000</v>
       </c>
       <c r="K63" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L63" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L63" s="1">
+        <v>120</v>
+      </c>
+      <c r="M63" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M63" s="1">
+        <v>80</v>
+      </c>
+      <c r="N63" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N63" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O63" s="1">
@@ -7721,11 +7705,11 @@
         <v>0</v>
       </c>
       <c r="V63" s="1">
+        <f t="shared" si="4"/>
+        <v>580</v>
+      </c>
+      <c r="W63" s="1">
         <f t="shared" si="5"/>
-        <v>580</v>
-      </c>
-      <c r="W63" s="1">
-        <f t="shared" si="6"/>
         <v>580</v>
       </c>
       <c r="X63" s="1">
@@ -7745,7 +7729,7 @@
         <v>39</v>
       </c>
       <c r="AC63" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6982</v>
       </c>
       <c r="AD63" s="1">
@@ -7776,11 +7760,11 @@
         <v>59</v>
       </c>
       <c r="H64" s="1">
+        <f t="shared" si="9"/>
+        <v>611987500</v>
+      </c>
+      <c r="I64" s="1">
         <f t="shared" si="10"/>
-        <v>611987500</v>
-      </c>
-      <c r="I64" s="1">
-        <f t="shared" si="0"/>
         <v>131137500</v>
       </c>
       <c r="J64" s="1">
@@ -7788,19 +7772,19 @@
         <v>36265000000</v>
       </c>
       <c r="K64" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L64" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L64" s="1">
+        <v>120</v>
+      </c>
+      <c r="M64" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M64" s="1">
+        <v>80</v>
+      </c>
+      <c r="N64" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N64" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O64" s="1">
@@ -7826,11 +7810,11 @@
         <v>0</v>
       </c>
       <c r="V64" s="1">
+        <f t="shared" si="4"/>
+        <v>590</v>
+      </c>
+      <c r="W64" s="1">
         <f t="shared" si="5"/>
-        <v>590</v>
-      </c>
-      <c r="W64" s="1">
-        <f t="shared" si="6"/>
         <v>590</v>
       </c>
       <c r="X64" s="1">
@@ -7850,7 +7834,7 @@
         <v>39</v>
       </c>
       <c r="AC64" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7253</v>
       </c>
       <c r="AD64" s="1">
@@ -7881,11 +7865,11 @@
         <v>60</v>
       </c>
       <c r="H65" s="1">
+        <f t="shared" si="9"/>
+        <v>658957000</v>
+      </c>
+      <c r="I65" s="1">
         <f t="shared" si="10"/>
-        <v>658957000</v>
-      </c>
-      <c r="I65" s="1">
-        <f t="shared" si="0"/>
         <v>137397000</v>
       </c>
       <c r="J65" s="1">
@@ -7893,19 +7877,19 @@
         <v>39156000000</v>
       </c>
       <c r="K65" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L65" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L65" s="1">
+        <v>120</v>
+      </c>
+      <c r="M65" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M65" s="1">
+        <v>80</v>
+      </c>
+      <c r="N65" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N65" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O65" s="1">
@@ -7931,11 +7915,11 @@
         <v>0</v>
       </c>
       <c r="V65" s="1">
+        <f t="shared" si="4"/>
+        <v>600</v>
+      </c>
+      <c r="W65" s="1">
         <f t="shared" si="5"/>
-        <v>600</v>
-      </c>
-      <c r="W65" s="1">
-        <f t="shared" si="6"/>
         <v>600</v>
       </c>
       <c r="X65" s="1">
@@ -7955,7 +7939,7 @@
         <v>39</v>
       </c>
       <c r="AC65" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7530</v>
       </c>
       <c r="AD65" s="1">
@@ -7986,11 +7970,11 @@
         <v>61</v>
       </c>
       <c r="H66" s="1">
+        <f t="shared" si="9"/>
+        <v>716998500</v>
+      </c>
+      <c r="I66" s="1">
         <f t="shared" si="10"/>
-        <v>716998500</v>
-      </c>
-      <c r="I66" s="1">
-        <f t="shared" si="0"/>
         <v>145840500</v>
       </c>
       <c r="J66" s="1">
@@ -7998,19 +7982,19 @@
         <v>42179400000</v>
       </c>
       <c r="K66" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L66" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L66" s="1">
+        <v>120</v>
+      </c>
+      <c r="M66" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M66" s="1">
+        <v>80</v>
+      </c>
+      <c r="N66" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N66" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O66" s="1">
@@ -8036,11 +8020,11 @@
         <v>0</v>
       </c>
       <c r="V66" s="1">
+        <f t="shared" si="4"/>
+        <v>610</v>
+      </c>
+      <c r="W66" s="1">
         <f t="shared" si="5"/>
-        <v>610</v>
-      </c>
-      <c r="W66" s="1">
-        <f t="shared" si="6"/>
         <v>610</v>
       </c>
       <c r="X66" s="1">
@@ -8060,7 +8044,7 @@
         <v>39</v>
       </c>
       <c r="AC66" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7811</v>
       </c>
       <c r="AD66" s="1">
@@ -8091,11 +8075,11 @@
         <v>62</v>
       </c>
       <c r="H67" s="1">
+        <f t="shared" si="9"/>
+        <v>753242000</v>
+      </c>
+      <c r="I67" s="1">
         <f t="shared" si="10"/>
-        <v>753242000</v>
-      </c>
-      <c r="I67" s="1">
-        <f t="shared" si="0"/>
         <v>153426000</v>
       </c>
       <c r="J67" s="1">
@@ -8103,19 +8087,19 @@
         <v>45326400000</v>
       </c>
       <c r="K67" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L67" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L67" s="1">
+        <v>120</v>
+      </c>
+      <c r="M67" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M67" s="1">
+        <v>80</v>
+      </c>
+      <c r="N67" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N67" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O67" s="1">
@@ -8141,11 +8125,11 @@
         <v>0</v>
       </c>
       <c r="V67" s="1">
+        <f t="shared" si="4"/>
+        <v>620</v>
+      </c>
+      <c r="W67" s="1">
         <f t="shared" si="5"/>
-        <v>620</v>
-      </c>
-      <c r="W67" s="1">
-        <f t="shared" si="6"/>
         <v>620</v>
       </c>
       <c r="X67" s="1">
@@ -8165,7 +8149,7 @@
         <v>39</v>
       </c>
       <c r="AC67" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8094</v>
       </c>
       <c r="AD67" s="1">
@@ -8196,11 +8180,11 @@
         <v>63</v>
       </c>
       <c r="H68" s="1">
+        <f t="shared" si="9"/>
+        <v>785160500</v>
+      </c>
+      <c r="I68" s="1">
         <f t="shared" si="10"/>
-        <v>785160500</v>
-      </c>
-      <c r="I68" s="1">
-        <f t="shared" si="0"/>
         <v>160036500</v>
       </c>
       <c r="J68" s="1">
@@ -8208,19 +8192,19 @@
         <v>48644600000</v>
       </c>
       <c r="K68" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L68" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L68" s="1">
+        <v>120</v>
+      </c>
+      <c r="M68" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M68" s="1">
+        <v>80</v>
+      </c>
+      <c r="N68" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N68" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O68" s="1">
@@ -8246,11 +8230,11 @@
         <v>0</v>
       </c>
       <c r="V68" s="1">
+        <f t="shared" si="4"/>
+        <v>630</v>
+      </c>
+      <c r="W68" s="1">
         <f t="shared" si="5"/>
-        <v>630</v>
-      </c>
-      <c r="W68" s="1">
-        <f t="shared" si="6"/>
         <v>630</v>
       </c>
       <c r="X68" s="1">
@@ -8270,7 +8254,7 @@
         <v>39</v>
       </c>
       <c r="AC68" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8387</v>
       </c>
       <c r="AD68" s="1">
@@ -8301,11 +8285,11 @@
         <v>64</v>
       </c>
       <c r="H69" s="1">
+        <f t="shared" si="9"/>
+        <v>822615000</v>
+      </c>
+      <c r="I69" s="1">
         <f t="shared" si="10"/>
-        <v>822615000</v>
-      </c>
-      <c r="I69" s="1">
-        <f t="shared" si="0"/>
         <v>171405000</v>
       </c>
       <c r="J69" s="1">
@@ -8313,19 +8297,19 @@
         <v>52164000000</v>
       </c>
       <c r="K69" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="L69" s="1">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="L69" s="1">
+        <v>120</v>
+      </c>
+      <c r="M69" s="1">
         <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="M69" s="1">
+        <v>80</v>
+      </c>
+      <c r="N69" s="1">
         <f t="shared" si="3"/>
-        <v>80</v>
-      </c>
-      <c r="N69" s="1">
-        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O69" s="1">
@@ -8351,11 +8335,11 @@
         <v>0</v>
       </c>
       <c r="V69" s="1">
+        <f t="shared" si="4"/>
+        <v>640</v>
+      </c>
+      <c r="W69" s="1">
         <f t="shared" si="5"/>
-        <v>640</v>
-      </c>
-      <c r="W69" s="1">
-        <f t="shared" si="6"/>
         <v>640</v>
       </c>
       <c r="X69" s="1">
@@ -8375,7 +8359,7 @@
         <v>39</v>
       </c>
       <c r="AC69" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8694</v>
       </c>
       <c r="AD69" s="1">
@@ -8406,7 +8390,7 @@
         <v>65</v>
       </c>
       <c r="H70" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>887576500</v>
       </c>
       <c r="I70" s="1">
@@ -8480,7 +8464,7 @@
         <v>39</v>
       </c>
       <c r="AC70" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9005</v>
       </c>
       <c r="AD70" s="1">
@@ -8585,7 +8569,7 @@
         <v>39</v>
       </c>
       <c r="AC71" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9318</v>
       </c>
       <c r="AD71" s="1">
@@ -8690,7 +8674,7 @@
         <v>39</v>
       </c>
       <c r="AC72" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9635</v>
       </c>
       <c r="AD72" s="1">
@@ -8795,7 +8779,7 @@
         <v>39</v>
       </c>
       <c r="AC73" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9966</v>
       </c>
       <c r="AD73" s="1">
@@ -8900,7 +8884,7 @@
         <v>39</v>
       </c>
       <c r="AC74" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>10303</v>
       </c>
       <c r="AD74" s="1">
@@ -9005,7 +8989,7 @@
         <v>39</v>
       </c>
       <c r="AC75" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>10650</v>
       </c>
       <c r="AD75" s="1">

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -526,12 +526,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -856,7 +862,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -880,16 +886,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -898,94 +904,95 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -995,6 +1002,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1320,82 +1328,82 @@
   <dimension ref="A1:AG103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
+    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="4" customWidth="1"/>
     <col min="7" max="7" width="9.58333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.0833333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.0833333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.4166666666667" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.3333333333333" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="14" max="15" width="8.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.16666666666667" style="2" customWidth="1"/>
-    <col min="18" max="19" width="8.75" style="2" customWidth="1"/>
-    <col min="20" max="20" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="21" max="21" width="8.33333333333333" style="2" customWidth="1"/>
-    <col min="22" max="22" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="23" max="23" width="10.3333333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.0833333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15.0833333333333" style="3" customWidth="1"/>
+    <col min="10" max="10" width="18.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.4166666666667" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.3333333333333" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.91666666666667" style="3" customWidth="1"/>
+    <col min="14" max="15" width="8.75" style="3" customWidth="1"/>
+    <col min="16" max="16" width="7.50833333333333" style="3" customWidth="1"/>
+    <col min="17" max="17" width="9.16666666666667" style="3" customWidth="1"/>
+    <col min="18" max="19" width="8.75" style="3" customWidth="1"/>
+    <col min="20" max="20" width="7.50833333333333" style="3" customWidth="1"/>
+    <col min="21" max="21" width="8.33333333333333" style="3" customWidth="1"/>
+    <col min="22" max="22" width="9.91666666666667" style="3" customWidth="1"/>
+    <col min="23" max="23" width="10.3333333333333" style="3" customWidth="1"/>
     <col min="24" max="24" width="8.33333333333333" style="1" customWidth="1"/>
     <col min="25" max="25" width="7.25" style="1" customWidth="1"/>
-    <col min="26" max="28" width="7.16666666666667" style="2" customWidth="1"/>
-    <col min="29" max="29" width="8.41666666666667" style="2" customWidth="1"/>
-    <col min="30" max="30" width="4.33333333333333" style="2" customWidth="1"/>
-    <col min="31" max="31" width="3.75" style="2" customWidth="1"/>
-    <col min="32" max="32" width="3" style="2" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="2"/>
+    <col min="26" max="28" width="7.16666666666667" style="3" customWidth="1"/>
+    <col min="29" max="29" width="8.41666666666667" style="3" customWidth="1"/>
+    <col min="30" max="30" width="4.33333333333333" style="3" customWidth="1"/>
+    <col min="31" max="31" width="3.75" style="3" customWidth="1"/>
+    <col min="32" max="32" width="3" style="3" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
       <c r="X1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Z1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="AG1" s="1" t="s">
@@ -1403,50 +1411,50 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
       <c r="X2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Y2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Z2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="2" t="s">
+      <c r="Z2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="AG2" s="1" t="s">
@@ -1454,69 +1462,69 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="X3" s="1" t="s">
@@ -1525,105 +1533,105 @@
       <c r="Y3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AD3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AE3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AF3" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="U4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="V4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="4" t="s">
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AE4" s="4" t="s">
+      <c r="AE4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AF4" s="4" t="s">
+      <c r="AF4" s="5" t="s">
         <v>30</v>
       </c>
       <c r="AG4" s="1">
@@ -1631,85 +1639,85 @@
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="V5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="4" t="s">
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AE5" s="4" t="s">
+      <c r="AE5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AF5" s="4" t="s">
+      <c r="AF5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AG5" s="2">
+      <c r="AG5" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1723,7 +1731,7 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="1">
@@ -1757,10 +1765,10 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
         <v>0</v>
       </c>
       <c r="R6" s="1">
@@ -1769,10 +1777,10 @@
       <c r="S6" s="1">
         <v>0</v>
       </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
+      <c r="T6" s="7">
+        <v>0</v>
+      </c>
+      <c r="U6" s="7">
         <v>0</v>
       </c>
       <c r="V6" s="1">
@@ -1789,16 +1797,16 @@
       <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6" s="3">
         <v>100</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AA6" s="3">
         <v>2</v>
       </c>
-      <c r="AB6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2">
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
         <v>10</v>
       </c>
       <c r="AD6" s="1">
@@ -1808,7 +1816,7 @@
       <c r="AF6" s="1">
         <v>0</v>
       </c>
-      <c r="AG6" s="2">
+      <c r="AG6" s="3">
         <v>2</v>
       </c>
     </row>
@@ -1822,7 +1830,7 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G7" s="1">
@@ -1856,10 +1864,10 @@
       <c r="O7" s="1">
         <v>1</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="7">
         <v>2</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q7" s="7">
         <v>10</v>
       </c>
       <c r="R7" s="1">
@@ -1868,10 +1876,10 @@
       <c r="S7" s="1">
         <v>0</v>
       </c>
-      <c r="T7" s="6">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6">
+      <c r="T7" s="7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7">
         <v>0</v>
       </c>
       <c r="V7" s="1">
@@ -1888,17 +1896,17 @@
       <c r="Y7" s="1">
         <v>2</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="Z7" s="3">
         <f>Z6+20</f>
         <v>120</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AA7" s="3">
         <v>3</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AB7" s="3">
         <v>1</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AC7" s="3">
         <v>20</v>
       </c>
       <c r="AD7" s="1">
@@ -1908,7 +1916,7 @@
       <c r="AF7" s="1">
         <v>0</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AG7" s="3">
         <v>3</v>
       </c>
     </row>
@@ -1922,7 +1930,7 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="1">
@@ -1956,10 +1964,10 @@
       <c r="O8" s="1">
         <v>2</v>
       </c>
-      <c r="P8" s="6">
+      <c r="P8" s="7">
         <v>3</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="3">
         <f t="shared" ref="Q8:Q45" si="6">Q7+2</f>
         <v>12</v>
       </c>
@@ -1969,10 +1977,10 @@
       <c r="S8" s="1">
         <v>0</v>
       </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
+      <c r="T8" s="7">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7">
         <v>0</v>
       </c>
       <c r="V8" s="1">
@@ -1989,17 +1997,17 @@
       <c r="Y8" s="1">
         <v>3</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="Z8" s="3">
         <f>Z7+20</f>
         <v>140</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AA8" s="3">
         <v>4</v>
       </c>
-      <c r="AB8" s="2">
+      <c r="AB8" s="3">
         <v>2</v>
       </c>
-      <c r="AC8" s="2">
+      <c r="AC8" s="3">
         <v>40</v>
       </c>
       <c r="AD8" s="1">
@@ -2009,7 +2017,7 @@
       <c r="AF8" s="1">
         <v>0</v>
       </c>
-      <c r="AG8" s="2">
+      <c r="AG8" s="3">
         <v>5</v>
       </c>
     </row>
@@ -2023,7 +2031,7 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="1">
@@ -2057,10 +2065,10 @@
       <c r="O9" s="1">
         <v>3</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="7">
         <v>4</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="3">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
@@ -2070,10 +2078,10 @@
       <c r="S9" s="1">
         <v>0</v>
       </c>
-      <c r="T9" s="6">
-        <v>0</v>
-      </c>
-      <c r="U9" s="6">
+      <c r="T9" s="7">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7">
         <v>0</v>
       </c>
       <c r="V9" s="1">
@@ -2090,17 +2098,17 @@
       <c r="Y9" s="1">
         <v>4</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="Z9" s="3">
         <f>Z8+20</f>
         <v>160</v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AA9" s="3">
         <v>5</v>
       </c>
-      <c r="AB9" s="2">
+      <c r="AB9" s="3">
         <v>3</v>
       </c>
-      <c r="AC9" s="2">
+      <c r="AC9" s="3">
         <v>60</v>
       </c>
       <c r="AD9" s="1">
@@ -2110,7 +2118,7 @@
       <c r="AF9" s="1">
         <v>0</v>
       </c>
-      <c r="AG9" s="2">
+      <c r="AG9" s="3">
         <v>7</v>
       </c>
     </row>
@@ -2124,7 +2132,7 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="1">
@@ -2158,10 +2166,10 @@
       <c r="O10" s="1">
         <v>4</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="7">
         <v>5</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="3">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
@@ -2171,10 +2179,10 @@
       <c r="S10" s="1">
         <v>0</v>
       </c>
-      <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6">
+      <c r="T10" s="7">
+        <v>0</v>
+      </c>
+      <c r="U10" s="7">
         <v>0</v>
       </c>
       <c r="V10" s="1">
@@ -2191,17 +2199,17 @@
       <c r="Y10" s="1">
         <v>5</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="Z10" s="3">
         <f>Z9+20</f>
         <v>180</v>
       </c>
-      <c r="AA10" s="2">
+      <c r="AA10" s="3">
         <v>6</v>
       </c>
-      <c r="AB10" s="2">
+      <c r="AB10" s="3">
         <v>4</v>
       </c>
-      <c r="AC10" s="2">
+      <c r="AC10" s="3">
         <v>100</v>
       </c>
       <c r="AD10" s="1">
@@ -2211,7 +2219,7 @@
       <c r="AF10" s="1">
         <v>0</v>
       </c>
-      <c r="AG10" s="2">
+      <c r="AG10" s="3">
         <v>11</v>
       </c>
     </row>
@@ -2225,7 +2233,7 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="1">
@@ -2259,10 +2267,10 @@
       <c r="O11" s="1">
         <v>5</v>
       </c>
-      <c r="P11" s="6">
+      <c r="P11" s="7">
         <v>6</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="3">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
@@ -2272,10 +2280,10 @@
       <c r="S11" s="1">
         <v>0</v>
       </c>
-      <c r="T11" s="6">
-        <v>0</v>
-      </c>
-      <c r="U11" s="6">
+      <c r="T11" s="7">
+        <v>0</v>
+      </c>
+      <c r="U11" s="7">
         <v>0</v>
       </c>
       <c r="V11" s="1">
@@ -2292,17 +2300,17 @@
       <c r="Y11" s="1">
         <v>6</v>
       </c>
-      <c r="Z11" s="2">
+      <c r="Z11" s="3">
         <f>Z10+20</f>
         <v>200</v>
       </c>
-      <c r="AA11" s="2">
+      <c r="AA11" s="3">
         <v>7</v>
       </c>
-      <c r="AB11" s="2">
+      <c r="AB11" s="3">
         <v>5</v>
       </c>
-      <c r="AC11" s="2">
+      <c r="AC11" s="3">
         <v>140</v>
       </c>
       <c r="AD11" s="1">
@@ -2312,7 +2320,7 @@
       <c r="AF11" s="1">
         <v>0</v>
       </c>
-      <c r="AG11" s="2">
+      <c r="AG11" s="3">
         <v>13</v>
       </c>
     </row>
@@ -2326,19 +2334,19 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="3">
         <v>3000</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="3">
         <v>490</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="3">
         <v>35000</v>
       </c>
       <c r="K12" s="1">
@@ -2360,10 +2368,10 @@
       <c r="O12" s="1">
         <v>6</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="7">
         <v>7</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="3">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
@@ -2373,10 +2381,10 @@
       <c r="S12" s="1">
         <v>0</v>
       </c>
-      <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6">
+      <c r="T12" s="7">
+        <v>0</v>
+      </c>
+      <c r="U12" s="7">
         <v>0</v>
       </c>
       <c r="V12" s="1">
@@ -2393,17 +2401,17 @@
       <c r="Y12" s="1">
         <v>7</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="Z12" s="3">
         <f>Z11+40</f>
         <v>240</v>
       </c>
-      <c r="AA12" s="2">
+      <c r="AA12" s="3">
         <v>8</v>
       </c>
-      <c r="AB12" s="2">
+      <c r="AB12" s="3">
         <v>6</v>
       </c>
-      <c r="AC12" s="2">
+      <c r="AC12" s="3">
         <f t="shared" ref="AC8:AC75" si="7">AC11+AG11</f>
         <v>153</v>
       </c>
@@ -2414,7 +2422,7 @@
       <c r="AF12" s="1">
         <v>0</v>
       </c>
-      <c r="AG12" s="2">
+      <c r="AG12" s="3">
         <v>17</v>
       </c>
     </row>
@@ -2428,7 +2436,7 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="1">
@@ -2462,10 +2470,10 @@
       <c r="O13" s="1">
         <v>7</v>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="7">
         <v>8</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="3">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
@@ -2475,10 +2483,10 @@
       <c r="S13" s="1">
         <v>0</v>
       </c>
-      <c r="T13" s="6">
-        <v>0</v>
-      </c>
-      <c r="U13" s="6">
+      <c r="T13" s="7">
+        <v>0</v>
+      </c>
+      <c r="U13" s="7">
         <v>0</v>
       </c>
       <c r="V13" s="1">
@@ -2495,17 +2503,17 @@
       <c r="Y13" s="1">
         <v>8</v>
       </c>
-      <c r="Z13" s="2">
+      <c r="Z13" s="3">
         <f>Z12+40</f>
         <v>280</v>
       </c>
-      <c r="AA13" s="2">
+      <c r="AA13" s="3">
         <v>9</v>
       </c>
-      <c r="AB13" s="2">
+      <c r="AB13" s="3">
         <v>7</v>
       </c>
-      <c r="AC13" s="2">
+      <c r="AC13" s="3">
         <f t="shared" si="7"/>
         <v>170</v>
       </c>
@@ -2516,7 +2524,7 @@
       <c r="AF13" s="1">
         <v>0</v>
       </c>
-      <c r="AG13" s="2">
+      <c r="AG13" s="3">
         <v>19</v>
       </c>
     </row>
@@ -2530,7 +2538,7 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G14" s="1">
@@ -2564,10 +2572,10 @@
       <c r="O14" s="1">
         <v>8</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P14" s="7">
         <v>9</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="3">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
@@ -2577,10 +2585,10 @@
       <c r="S14" s="1">
         <v>0</v>
       </c>
-      <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="6">
+      <c r="T14" s="7">
+        <v>0</v>
+      </c>
+      <c r="U14" s="7">
         <v>0</v>
       </c>
       <c r="V14" s="1">
@@ -2597,17 +2605,17 @@
       <c r="Y14" s="1">
         <v>9</v>
       </c>
-      <c r="Z14" s="2">
+      <c r="Z14" s="3">
         <f>Z13+40</f>
         <v>320</v>
       </c>
-      <c r="AA14" s="2">
+      <c r="AA14" s="3">
         <v>10</v>
       </c>
-      <c r="AB14" s="2">
+      <c r="AB14" s="3">
         <v>8</v>
       </c>
-      <c r="AC14" s="2">
+      <c r="AC14" s="3">
         <f t="shared" si="7"/>
         <v>189</v>
       </c>
@@ -2618,7 +2626,7 @@
       <c r="AF14" s="1">
         <v>0</v>
       </c>
-      <c r="AG14" s="2">
+      <c r="AG14" s="3">
         <v>23</v>
       </c>
     </row>
@@ -2632,7 +2640,7 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G15" s="1">
@@ -2666,10 +2674,10 @@
       <c r="O15" s="1">
         <v>9</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="7">
         <v>10</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="3">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
@@ -2679,10 +2687,10 @@
       <c r="S15" s="1">
         <v>0</v>
       </c>
-      <c r="T15" s="6">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6">
+      <c r="T15" s="7">
+        <v>0</v>
+      </c>
+      <c r="U15" s="7">
         <v>0</v>
       </c>
       <c r="V15" s="1">
@@ -2699,17 +2707,17 @@
       <c r="Y15" s="1">
         <v>10</v>
       </c>
-      <c r="Z15" s="2">
+      <c r="Z15" s="3">
         <f>Z14+40</f>
         <v>360</v>
       </c>
-      <c r="AA15" s="2">
+      <c r="AA15" s="3">
         <v>11</v>
       </c>
-      <c r="AB15" s="2">
+      <c r="AB15" s="3">
         <v>9</v>
       </c>
-      <c r="AC15" s="2">
+      <c r="AC15" s="3">
         <f t="shared" si="7"/>
         <v>212</v>
       </c>
@@ -2720,7 +2728,7 @@
       <c r="AF15" s="1">
         <v>0</v>
       </c>
-      <c r="AG15" s="2">
+      <c r="AG15" s="3">
         <v>29</v>
       </c>
     </row>
@@ -2734,7 +2742,7 @@
       <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G16" s="1">
@@ -2768,10 +2776,10 @@
       <c r="O16" s="1">
         <v>10</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P16" s="7">
         <v>11</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="3">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
@@ -2781,10 +2789,10 @@
       <c r="S16" s="1">
         <v>0</v>
       </c>
-      <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="6">
+      <c r="T16" s="7">
+        <v>0</v>
+      </c>
+      <c r="U16" s="7">
         <v>0</v>
       </c>
       <c r="V16" s="1">
@@ -2801,17 +2809,17 @@
       <c r="Y16" s="1">
         <v>11</v>
       </c>
-      <c r="Z16" s="2">
+      <c r="Z16" s="3">
         <f>Z15+40</f>
         <v>400</v>
       </c>
-      <c r="AA16" s="2">
+      <c r="AA16" s="3">
         <v>13</v>
       </c>
-      <c r="AB16" s="2">
+      <c r="AB16" s="3">
         <v>10</v>
       </c>
-      <c r="AC16" s="2">
+      <c r="AC16" s="3">
         <f t="shared" si="7"/>
         <v>241</v>
       </c>
@@ -2822,7 +2830,7 @@
       <c r="AF16" s="1">
         <v>0</v>
       </c>
-      <c r="AG16" s="2">
+      <c r="AG16" s="3">
         <v>31</v>
       </c>
     </row>
@@ -2836,7 +2844,7 @@
       <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G17" s="1">
@@ -2870,10 +2878,10 @@
       <c r="O17" s="1">
         <v>11</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P17" s="7">
         <v>12</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="3">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
@@ -2883,10 +2891,10 @@
       <c r="S17" s="1">
         <v>0</v>
       </c>
-      <c r="T17" s="6">
-        <v>0</v>
-      </c>
-      <c r="U17" s="6">
+      <c r="T17" s="7">
+        <v>0</v>
+      </c>
+      <c r="U17" s="7">
         <v>0</v>
       </c>
       <c r="V17" s="1">
@@ -2903,17 +2911,17 @@
       <c r="Y17" s="1">
         <v>12</v>
       </c>
-      <c r="Z17" s="2">
+      <c r="Z17" s="3">
         <f t="shared" ref="Z17:Z22" si="8">Z16+100</f>
         <v>500</v>
       </c>
-      <c r="AA17" s="2">
+      <c r="AA17" s="3">
         <v>17</v>
       </c>
-      <c r="AB17" s="2">
+      <c r="AB17" s="3">
         <v>11</v>
       </c>
-      <c r="AC17" s="2">
+      <c r="AC17" s="3">
         <f t="shared" si="7"/>
         <v>272</v>
       </c>
@@ -2924,7 +2932,7 @@
       <c r="AF17" s="1">
         <v>0</v>
       </c>
-      <c r="AG17" s="2">
+      <c r="AG17" s="3">
         <v>37</v>
       </c>
     </row>
@@ -2938,7 +2946,7 @@
       <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="8" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="1">
@@ -2972,10 +2980,10 @@
       <c r="O18" s="1">
         <v>12</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P18" s="7">
         <v>13</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="3">
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
@@ -2985,10 +2993,10 @@
       <c r="S18" s="1">
         <v>0</v>
       </c>
-      <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="6">
+      <c r="T18" s="7">
+        <v>0</v>
+      </c>
+      <c r="U18" s="7">
         <v>0</v>
       </c>
       <c r="V18" s="1">
@@ -3005,17 +3013,17 @@
       <c r="Y18" s="1">
         <v>13</v>
       </c>
-      <c r="Z18" s="2">
+      <c r="Z18" s="3">
         <f t="shared" si="8"/>
         <v>600</v>
       </c>
-      <c r="AA18" s="2">
+      <c r="AA18" s="3">
         <v>19</v>
       </c>
-      <c r="AB18" s="2">
+      <c r="AB18" s="3">
         <v>12</v>
       </c>
-      <c r="AC18" s="2">
+      <c r="AC18" s="3">
         <f t="shared" si="7"/>
         <v>309</v>
       </c>
@@ -3026,7 +3034,7 @@
       <c r="AF18" s="1">
         <v>0</v>
       </c>
-      <c r="AG18" s="2">
+      <c r="AG18" s="3">
         <v>41</v>
       </c>
     </row>
@@ -3040,7 +3048,7 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="6" t="s">
         <v>48</v>
       </c>
       <c r="G19" s="1">
@@ -3074,10 +3082,10 @@
       <c r="O19" s="1">
         <v>13</v>
       </c>
-      <c r="P19" s="6">
+      <c r="P19" s="7">
         <v>14</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="3">
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
@@ -3087,10 +3095,10 @@
       <c r="S19" s="1">
         <v>0</v>
       </c>
-      <c r="T19" s="6">
-        <v>0</v>
-      </c>
-      <c r="U19" s="6">
+      <c r="T19" s="7">
+        <v>0</v>
+      </c>
+      <c r="U19" s="7">
         <v>0</v>
       </c>
       <c r="V19" s="1">
@@ -3107,17 +3115,17 @@
       <c r="Y19" s="1">
         <v>14</v>
       </c>
-      <c r="Z19" s="2">
+      <c r="Z19" s="3">
         <f t="shared" si="8"/>
         <v>700</v>
       </c>
-      <c r="AA19" s="2">
+      <c r="AA19" s="3">
         <v>23</v>
       </c>
-      <c r="AB19" s="2">
+      <c r="AB19" s="3">
         <v>13</v>
       </c>
-      <c r="AC19" s="2">
+      <c r="AC19" s="3">
         <f t="shared" si="7"/>
         <v>350</v>
       </c>
@@ -3128,7 +3136,7 @@
       <c r="AF19" s="1">
         <v>0</v>
       </c>
-      <c r="AG19" s="2">
+      <c r="AG19" s="3">
         <v>43</v>
       </c>
     </row>
@@ -3142,7 +3150,7 @@
       <c r="E20" s="1">
         <v>1</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="6" t="s">
         <v>49</v>
       </c>
       <c r="G20" s="1">
@@ -3176,10 +3184,10 @@
       <c r="O20" s="1">
         <v>14</v>
       </c>
-      <c r="P20" s="6">
+      <c r="P20" s="7">
         <v>15</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="3">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
@@ -3189,10 +3197,10 @@
       <c r="S20" s="1">
         <v>0</v>
       </c>
-      <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="6">
+      <c r="T20" s="7">
+        <v>0</v>
+      </c>
+      <c r="U20" s="7">
         <v>0</v>
       </c>
       <c r="V20" s="1">
@@ -3209,17 +3217,17 @@
       <c r="Y20" s="1">
         <v>15</v>
       </c>
-      <c r="Z20" s="2">
+      <c r="Z20" s="3">
         <f t="shared" si="8"/>
         <v>800</v>
       </c>
-      <c r="AA20" s="2">
+      <c r="AA20" s="3">
         <v>29</v>
       </c>
-      <c r="AB20" s="2">
+      <c r="AB20" s="3">
         <v>14</v>
       </c>
-      <c r="AC20" s="2">
+      <c r="AC20" s="3">
         <f t="shared" si="7"/>
         <v>393</v>
       </c>
@@ -3230,7 +3238,7 @@
       <c r="AF20" s="1">
         <v>0</v>
       </c>
-      <c r="AG20" s="2">
+      <c r="AG20" s="3">
         <v>47</v>
       </c>
     </row>
@@ -3244,7 +3252,7 @@
       <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="6" t="s">
         <v>50</v>
       </c>
       <c r="G21" s="1">
@@ -3278,10 +3286,10 @@
       <c r="O21" s="1">
         <v>15</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="7">
         <v>16</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="3">
         <f t="shared" si="6"/>
         <v>38</v>
       </c>
@@ -3291,10 +3299,10 @@
       <c r="S21" s="1">
         <v>0</v>
       </c>
-      <c r="T21" s="6">
-        <v>0</v>
-      </c>
-      <c r="U21" s="6">
+      <c r="T21" s="7">
+        <v>0</v>
+      </c>
+      <c r="U21" s="7">
         <v>0</v>
       </c>
       <c r="V21" s="1">
@@ -3311,17 +3319,17 @@
       <c r="Y21" s="1">
         <v>16</v>
       </c>
-      <c r="Z21" s="2">
+      <c r="Z21" s="3">
         <f t="shared" si="8"/>
         <v>900</v>
       </c>
-      <c r="AA21" s="2">
+      <c r="AA21" s="3">
         <v>31</v>
       </c>
-      <c r="AB21" s="2">
+      <c r="AB21" s="3">
         <v>15</v>
       </c>
-      <c r="AC21" s="2">
+      <c r="AC21" s="3">
         <f t="shared" si="7"/>
         <v>440</v>
       </c>
@@ -3332,7 +3340,7 @@
       <c r="AF21" s="1">
         <v>0</v>
       </c>
-      <c r="AG21" s="2">
+      <c r="AG21" s="3">
         <v>53</v>
       </c>
     </row>
@@ -3346,7 +3354,7 @@
       <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="6" t="s">
         <v>51</v>
       </c>
       <c r="G22" s="1">
@@ -3380,10 +3388,10 @@
       <c r="O22" s="1">
         <v>16</v>
       </c>
-      <c r="P22" s="6">
+      <c r="P22" s="7">
         <v>17</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="3">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
@@ -3393,10 +3401,10 @@
       <c r="S22" s="1">
         <v>0</v>
       </c>
-      <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="6">
+      <c r="T22" s="7">
+        <v>0</v>
+      </c>
+      <c r="U22" s="7">
         <v>0</v>
       </c>
       <c r="V22" s="1">
@@ -3413,17 +3421,17 @@
       <c r="Y22" s="1">
         <v>17</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="Z22" s="3">
         <f t="shared" si="8"/>
         <v>1000</v>
       </c>
-      <c r="AA22" s="2">
+      <c r="AA22" s="3">
         <v>37</v>
       </c>
-      <c r="AB22" s="2">
+      <c r="AB22" s="3">
         <v>16</v>
       </c>
-      <c r="AC22" s="2">
+      <c r="AC22" s="3">
         <f t="shared" si="7"/>
         <v>493</v>
       </c>
@@ -3434,7 +3442,7 @@
       <c r="AF22" s="1">
         <v>0</v>
       </c>
-      <c r="AG22" s="2">
+      <c r="AG22" s="3">
         <v>59</v>
       </c>
     </row>
@@ -3448,23 +3456,20 @@
       <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="1">
         <v>18</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" ref="H7:H70" si="9">AG25*Z23*AA23/10</f>
-        <v>349320</v>
+        <v>72000</v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" ref="I6:I69" si="10">AB23*AG21*Z23/10</f>
-        <v>108120</v>
+        <v>36000</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" ref="J7:J72" si="11">Y23*Z23*AC23</f>
-        <v>11923200</v>
+        <v>2550000</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" si="0"/>
@@ -3485,10 +3490,10 @@
       <c r="O23" s="1">
         <v>17</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P23" s="7">
         <v>18</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="3">
         <f t="shared" si="6"/>
         <v>42</v>
       </c>
@@ -3498,10 +3503,10 @@
       <c r="S23" s="1">
         <v>0</v>
       </c>
-      <c r="T23" s="6">
-        <v>0</v>
-      </c>
-      <c r="U23" s="6">
+      <c r="T23" s="7">
+        <v>0</v>
+      </c>
+      <c r="U23" s="7">
         <v>0</v>
       </c>
       <c r="V23" s="1">
@@ -3518,17 +3523,17 @@
       <c r="Y23" s="1">
         <v>18</v>
       </c>
-      <c r="Z23" s="2">
+      <c r="Z23" s="3">
         <f>Z22+200</f>
         <v>1200</v>
       </c>
-      <c r="AA23" s="2">
+      <c r="AA23" s="3">
         <v>41</v>
       </c>
-      <c r="AB23" s="2">
+      <c r="AB23" s="3">
         <v>17</v>
       </c>
-      <c r="AC23" s="2">
+      <c r="AC23" s="3">
         <f t="shared" si="7"/>
         <v>552</v>
       </c>
@@ -3539,7 +3544,7 @@
       <c r="AF23" s="1">
         <v>0</v>
       </c>
-      <c r="AG23" s="2">
+      <c r="AG23" s="3">
         <v>61</v>
       </c>
     </row>
@@ -3553,23 +3558,20 @@
       <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="6" t="s">
         <v>53</v>
       </c>
       <c r="G24" s="1">
         <v>19</v>
       </c>
       <c r="H24" s="1">
-        <f t="shared" si="9"/>
-        <v>439460</v>
+        <v>85000</v>
       </c>
       <c r="I24" s="1">
-        <f t="shared" si="10"/>
-        <v>148680</v>
+        <v>48000</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="11"/>
-        <v>16305800</v>
+        <v>3400000</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" si="0"/>
@@ -3590,10 +3592,10 @@
       <c r="O24" s="1">
         <v>18</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P24" s="7">
         <v>19</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="3">
         <f t="shared" si="6"/>
         <v>44</v>
       </c>
@@ -3603,10 +3605,10 @@
       <c r="S24" s="1">
         <v>0</v>
       </c>
-      <c r="T24" s="6">
-        <v>0</v>
-      </c>
-      <c r="U24" s="6">
+      <c r="T24" s="7">
+        <v>0</v>
+      </c>
+      <c r="U24" s="7">
         <v>0</v>
       </c>
       <c r="V24" s="1">
@@ -3623,17 +3625,17 @@
       <c r="Y24" s="1">
         <v>19</v>
       </c>
-      <c r="Z24" s="2">
+      <c r="Z24" s="3">
         <f>Z23+200</f>
         <v>1400</v>
       </c>
-      <c r="AA24" s="2">
+      <c r="AA24" s="3">
         <v>43</v>
       </c>
-      <c r="AB24" s="2">
+      <c r="AB24" s="3">
         <v>18</v>
       </c>
-      <c r="AC24" s="2">
+      <c r="AC24" s="3">
         <f t="shared" si="7"/>
         <v>613</v>
       </c>
@@ -3644,7 +3646,7 @@
       <c r="AF24" s="1">
         <v>0</v>
       </c>
-      <c r="AG24" s="2">
+      <c r="AG24" s="3">
         <v>67</v>
       </c>
     </row>
@@ -3658,23 +3660,20 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="6" t="s">
         <v>54</v>
       </c>
       <c r="G25" s="1">
         <v>20</v>
       </c>
       <c r="H25" s="1">
-        <f t="shared" si="9"/>
-        <v>594080</v>
+        <v>100000</v>
       </c>
       <c r="I25" s="1">
-        <f t="shared" si="10"/>
-        <v>185440</v>
+        <v>63000</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="11"/>
-        <v>21760000</v>
+        <v>4500000</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" si="0"/>
@@ -3695,10 +3694,10 @@
       <c r="O25" s="1">
         <v>19</v>
       </c>
-      <c r="P25" s="6">
+      <c r="P25" s="7">
         <v>20</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="3">
         <f t="shared" si="6"/>
         <v>46</v>
       </c>
@@ -3708,10 +3707,10 @@
       <c r="S25" s="1">
         <v>0</v>
       </c>
-      <c r="T25" s="6">
-        <v>0</v>
-      </c>
-      <c r="U25" s="6">
+      <c r="T25" s="7">
+        <v>0</v>
+      </c>
+      <c r="U25" s="7">
         <v>0</v>
       </c>
       <c r="V25" s="1">
@@ -3728,17 +3727,17 @@
       <c r="Y25" s="1">
         <v>20</v>
       </c>
-      <c r="Z25" s="2">
+      <c r="Z25" s="3">
         <f>Z24+200</f>
         <v>1600</v>
       </c>
-      <c r="AA25" s="2">
+      <c r="AA25" s="3">
         <v>47</v>
       </c>
-      <c r="AB25" s="2">
+      <c r="AB25" s="3">
         <v>19</v>
       </c>
-      <c r="AC25" s="2">
+      <c r="AC25" s="3">
         <f t="shared" si="7"/>
         <v>680</v>
       </c>
@@ -3749,7 +3748,7 @@
       <c r="AF25" s="1">
         <v>0</v>
       </c>
-      <c r="AG25" s="2">
+      <c r="AG25" s="3">
         <v>71</v>
       </c>
     </row>
@@ -3763,23 +3762,20 @@
       <c r="E26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G26" s="1">
         <v>21</v>
       </c>
       <c r="H26" s="1">
-        <f t="shared" si="9"/>
-        <v>791820</v>
+        <v>120000</v>
       </c>
       <c r="I26" s="1">
-        <f t="shared" si="10"/>
-        <v>241200</v>
+        <v>80000</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="11"/>
-        <v>28387800</v>
+        <v>6000000</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" si="0"/>
@@ -3800,10 +3796,10 @@
       <c r="O26" s="1">
         <v>20</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="7">
         <v>21</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="3">
         <f t="shared" si="6"/>
         <v>48</v>
       </c>
@@ -3813,10 +3809,10 @@
       <c r="S26" s="1">
         <v>0</v>
       </c>
-      <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="6">
+      <c r="T26" s="7">
+        <v>0</v>
+      </c>
+      <c r="U26" s="7">
         <v>0</v>
       </c>
       <c r="V26" s="1">
@@ -3833,17 +3829,17 @@
       <c r="Y26" s="1">
         <v>21</v>
       </c>
-      <c r="Z26" s="2">
+      <c r="Z26" s="3">
         <f>Z25+200</f>
         <v>1800</v>
       </c>
-      <c r="AA26" s="2">
+      <c r="AA26" s="3">
         <v>53</v>
       </c>
-      <c r="AB26" s="2">
+      <c r="AB26" s="3">
         <v>20</v>
       </c>
-      <c r="AC26" s="2">
+      <c r="AC26" s="3">
         <f t="shared" si="7"/>
         <v>751</v>
       </c>
@@ -3854,7 +3850,7 @@
       <c r="AF26" s="1">
         <v>0</v>
       </c>
-      <c r="AG26" s="2">
+      <c r="AG26" s="3">
         <v>73</v>
       </c>
     </row>
@@ -3868,23 +3864,20 @@
       <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="6" t="s">
         <v>56</v>
       </c>
       <c r="G27" s="1">
         <v>22</v>
       </c>
       <c r="H27" s="1">
-        <f t="shared" si="9"/>
-        <v>1050200</v>
+        <v>150000</v>
       </c>
       <c r="I27" s="1">
-        <f t="shared" si="10"/>
-        <v>298200</v>
+        <v>100000</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="11"/>
-        <v>36256000</v>
+        <v>8000000</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" si="0"/>
@@ -3905,10 +3898,10 @@
       <c r="O27" s="1">
         <v>21</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="7">
         <v>22</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="3">
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
@@ -3918,10 +3911,10 @@
       <c r="S27" s="1">
         <v>0</v>
       </c>
-      <c r="T27" s="6">
-        <v>0</v>
-      </c>
-      <c r="U27" s="6">
+      <c r="T27" s="7">
+        <v>0</v>
+      </c>
+      <c r="U27" s="7">
         <v>0</v>
       </c>
       <c r="V27" s="1">
@@ -3938,17 +3931,17 @@
       <c r="Y27" s="1">
         <v>22</v>
       </c>
-      <c r="Z27" s="2">
+      <c r="Z27" s="3">
         <f>Z26+200</f>
         <v>2000</v>
       </c>
-      <c r="AA27" s="2">
+      <c r="AA27" s="3">
         <v>59</v>
       </c>
-      <c r="AB27" s="2">
+      <c r="AB27" s="3">
         <v>21</v>
       </c>
-      <c r="AC27" s="2">
+      <c r="AC27" s="3">
         <f t="shared" si="7"/>
         <v>824</v>
       </c>
@@ -3959,7 +3952,7 @@
       <c r="AF27" s="1">
         <v>0</v>
       </c>
-      <c r="AG27" s="2">
+      <c r="AG27" s="3">
         <v>79</v>
       </c>
     </row>
@@ -3973,23 +3966,20 @@
       <c r="E28" s="1">
         <v>1</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="8" t="s">
         <v>57</v>
       </c>
       <c r="G28" s="1">
         <v>23</v>
       </c>
       <c r="H28" s="1">
-        <f t="shared" si="9"/>
-        <v>1479250</v>
+        <v>190000</v>
       </c>
       <c r="I28" s="1">
-        <f t="shared" si="10"/>
-        <v>401500</v>
+        <v>130000</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="11"/>
-        <v>51922500</v>
+        <v>10000000</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="0"/>
@@ -4010,11 +4000,11 @@
       <c r="O28" s="1">
         <v>22</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="7">
         <v>23</v>
       </c>
-      <c r="Q28" s="2">
-        <f t="shared" ref="Q28:Q77" si="12">Q27+3</f>
+      <c r="Q28" s="3">
+        <f t="shared" ref="Q28:Q77" si="9">Q27+3</f>
         <v>53</v>
       </c>
       <c r="R28" s="1">
@@ -4023,10 +4013,10 @@
       <c r="S28" s="1">
         <v>0</v>
       </c>
-      <c r="T28" s="6">
-        <v>0</v>
-      </c>
-      <c r="U28" s="6">
+      <c r="T28" s="7">
+        <v>0</v>
+      </c>
+      <c r="U28" s="7">
         <v>0</v>
       </c>
       <c r="V28" s="1">
@@ -4043,17 +4033,17 @@
       <c r="Y28" s="1">
         <v>23</v>
       </c>
-      <c r="Z28" s="2">
-        <f t="shared" ref="Z28:Z33" si="13">Z27+500</f>
+      <c r="Z28" s="3">
+        <f t="shared" ref="Z28:Z33" si="10">Z27+500</f>
         <v>2500</v>
       </c>
-      <c r="AA28" s="2">
+      <c r="AA28" s="3">
         <v>61</v>
       </c>
-      <c r="AB28" s="2">
+      <c r="AB28" s="3">
         <v>22</v>
       </c>
-      <c r="AC28" s="2">
+      <c r="AC28" s="3">
         <f t="shared" si="7"/>
         <v>903</v>
       </c>
@@ -4064,92 +4054,89 @@
       <c r="AF28" s="1">
         <v>0</v>
       </c>
-      <c r="AG28" s="2">
+      <c r="AG28" s="3">
         <v>83</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:33">
-      <c r="C29" s="1">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="C29" s="9">
         <v>24</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="9">
         <v>24</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="9">
         <v>1</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="9">
         <v>24</v>
       </c>
-      <c r="H29" s="1">
-        <f t="shared" si="9"/>
-        <v>2030100</v>
-      </c>
-      <c r="I29" s="1">
-        <f t="shared" si="10"/>
-        <v>545100</v>
-      </c>
-      <c r="J29" s="1">
-        <f t="shared" si="11"/>
-        <v>70992000</v>
-      </c>
-      <c r="K29" s="1">
+      <c r="H29" s="9">
+        <v>250000</v>
+      </c>
+      <c r="I29" s="9">
+        <v>170000</v>
+      </c>
+      <c r="J29" s="9">
+        <v>12000000</v>
+      </c>
+      <c r="K29" s="9">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L29" s="9">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M29" s="9">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="N29" s="1">
+      <c r="N29" s="9">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="O29" s="1">
+      <c r="O29" s="9">
         <v>23</v>
       </c>
-      <c r="P29" s="6">
+      <c r="P29" s="2">
         <v>24</v>
       </c>
       <c r="Q29" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>56</v>
       </c>
-      <c r="R29" s="1">
-        <v>0</v>
-      </c>
-      <c r="S29" s="1">
-        <v>0</v>
-      </c>
-      <c r="T29" s="6">
-        <v>0</v>
-      </c>
-      <c r="U29" s="6">
-        <v>0</v>
-      </c>
-      <c r="V29" s="1">
+      <c r="R29" s="9">
+        <v>0</v>
+      </c>
+      <c r="S29" s="9">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2">
+        <v>0</v>
+      </c>
+      <c r="V29" s="9">
         <f t="shared" si="4"/>
         <v>240</v>
       </c>
-      <c r="W29" s="1">
+      <c r="W29" s="9">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
-      <c r="X29" s="1">
+      <c r="X29" s="9">
         <v>24</v>
       </c>
-      <c r="Y29" s="1">
+      <c r="Y29" s="9">
         <v>24</v>
       </c>
       <c r="Z29" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>3000</v>
       </c>
       <c r="AA29" s="2">
@@ -4162,11 +4149,11 @@
         <f t="shared" si="7"/>
         <v>986</v>
       </c>
-      <c r="AD29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="1"/>
-      <c r="AF29" s="1">
+      <c r="AD29" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="9"/>
+      <c r="AF29" s="9">
         <v>0</v>
       </c>
       <c r="AG29" s="2">
@@ -4183,22 +4170,22 @@
       <c r="E30" s="1">
         <v>1</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="6" t="s">
         <v>59</v>
       </c>
       <c r="G30" s="1">
         <v>25</v>
       </c>
       <c r="H30" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="H7:H70" si="11">AG32*Z30*AA30/10</f>
         <v>2559550</v>
       </c>
       <c r="I30" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I6:I69" si="12">AB30*AG28*Z30/10</f>
         <v>697200</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J7:J72" si="13">Y30*Z30*AC30</f>
         <v>94062500</v>
       </c>
       <c r="K30" s="1">
@@ -4220,11 +4207,11 @@
       <c r="O30" s="1">
         <v>24</v>
       </c>
-      <c r="P30" s="6">
+      <c r="P30" s="7">
         <v>25</v>
       </c>
-      <c r="Q30" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q30" s="3">
+        <f t="shared" si="9"/>
         <v>59</v>
       </c>
       <c r="R30" s="1">
@@ -4233,10 +4220,10 @@
       <c r="S30" s="1">
         <v>0</v>
       </c>
-      <c r="T30" s="6">
-        <v>0</v>
-      </c>
-      <c r="U30" s="6">
+      <c r="T30" s="7">
+        <v>0</v>
+      </c>
+      <c r="U30" s="7">
         <v>0</v>
       </c>
       <c r="V30" s="1">
@@ -4253,17 +4240,17 @@
       <c r="Y30" s="1">
         <v>25</v>
       </c>
-      <c r="Z30" s="2">
-        <f t="shared" si="13"/>
+      <c r="Z30" s="3">
+        <f t="shared" si="10"/>
         <v>3500</v>
       </c>
-      <c r="AA30" s="2">
+      <c r="AA30" s="3">
         <v>71</v>
       </c>
-      <c r="AB30" s="2">
+      <c r="AB30" s="3">
         <v>24</v>
       </c>
-      <c r="AC30" s="2">
+      <c r="AC30" s="3">
         <f t="shared" si="7"/>
         <v>1075</v>
       </c>
@@ -4274,7 +4261,7 @@
       <c r="AF30" s="1">
         <v>0</v>
       </c>
-      <c r="AG30" s="2">
+      <c r="AG30" s="3">
         <v>97</v>
       </c>
     </row>
@@ -4288,22 +4275,22 @@
       <c r="E31" s="1">
         <v>1</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G31" s="1">
         <v>26</v>
       </c>
       <c r="H31" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>3124400</v>
       </c>
       <c r="I31" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>890000</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>121888000</v>
       </c>
       <c r="K31" s="1">
@@ -4325,11 +4312,11 @@
       <c r="O31" s="1">
         <v>25</v>
       </c>
-      <c r="P31" s="6">
+      <c r="P31" s="7">
         <v>26</v>
       </c>
-      <c r="Q31" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q31" s="3">
+        <f t="shared" si="9"/>
         <v>62</v>
       </c>
       <c r="R31" s="1">
@@ -4338,10 +4325,10 @@
       <c r="S31" s="1">
         <v>0</v>
       </c>
-      <c r="T31" s="6">
-        <v>0</v>
-      </c>
-      <c r="U31" s="6">
+      <c r="T31" s="7">
+        <v>0</v>
+      </c>
+      <c r="U31" s="7">
         <v>0</v>
       </c>
       <c r="V31" s="1">
@@ -4358,17 +4345,17 @@
       <c r="Y31" s="1">
         <v>26</v>
       </c>
-      <c r="Z31" s="2">
-        <f t="shared" si="13"/>
+      <c r="Z31" s="3">
+        <f t="shared" si="10"/>
         <v>4000</v>
       </c>
-      <c r="AA31" s="2">
+      <c r="AA31" s="3">
         <v>73</v>
       </c>
-      <c r="AB31" s="2">
+      <c r="AB31" s="3">
         <v>25</v>
       </c>
-      <c r="AC31" s="2">
+      <c r="AC31" s="3">
         <f t="shared" si="7"/>
         <v>1172</v>
       </c>
@@ -4379,7 +4366,7 @@
       <c r="AF31" s="1">
         <v>0</v>
       </c>
-      <c r="AG31" s="2">
+      <c r="AG31" s="3">
         <v>101</v>
       </c>
     </row>
@@ -4393,22 +4380,22 @@
       <c r="E32" s="1">
         <v>1</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="10" t="s">
         <v>61</v>
       </c>
       <c r="G32" s="1">
         <v>27</v>
       </c>
       <c r="H32" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>3874950</v>
       </c>
       <c r="I32" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1134900</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>154669500</v>
       </c>
       <c r="K32" s="1">
@@ -4430,11 +4417,11 @@
       <c r="O32" s="1">
         <v>26</v>
       </c>
-      <c r="P32" s="6">
+      <c r="P32" s="7">
         <v>27</v>
       </c>
-      <c r="Q32" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q32" s="3">
+        <f t="shared" si="9"/>
         <v>65</v>
       </c>
       <c r="R32" s="1">
@@ -4443,10 +4430,10 @@
       <c r="S32" s="1">
         <v>0</v>
       </c>
-      <c r="T32" s="6">
-        <v>0</v>
-      </c>
-      <c r="U32" s="6">
+      <c r="T32" s="7">
+        <v>0</v>
+      </c>
+      <c r="U32" s="7">
         <v>0</v>
       </c>
       <c r="V32" s="1">
@@ -4463,17 +4450,17 @@
       <c r="Y32" s="1">
         <v>27</v>
       </c>
-      <c r="Z32" s="2">
-        <f t="shared" si="13"/>
+      <c r="Z32" s="3">
+        <f t="shared" si="10"/>
         <v>4500</v>
       </c>
-      <c r="AA32" s="2">
+      <c r="AA32" s="3">
         <v>79</v>
       </c>
-      <c r="AB32" s="2">
+      <c r="AB32" s="3">
         <v>26</v>
       </c>
-      <c r="AC32" s="2">
+      <c r="AC32" s="3">
         <f t="shared" si="7"/>
         <v>1273</v>
       </c>
@@ -4484,7 +4471,7 @@
       <c r="AF32" s="1">
         <v>0</v>
       </c>
-      <c r="AG32" s="2">
+      <c r="AG32" s="3">
         <v>103</v>
       </c>
     </row>
@@ -4498,22 +4485,22 @@
       <c r="E33" s="1">
         <v>1</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G33" s="1">
         <v>28</v>
       </c>
       <c r="H33" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>4689500</v>
       </c>
       <c r="I33" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1363500</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>192640000</v>
       </c>
       <c r="K33" s="1">
@@ -4535,11 +4522,11 @@
       <c r="O33" s="1">
         <v>27</v>
       </c>
-      <c r="P33" s="6">
+      <c r="P33" s="7">
         <v>28</v>
       </c>
-      <c r="Q33" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q33" s="3">
+        <f t="shared" si="9"/>
         <v>68</v>
       </c>
       <c r="R33" s="1">
@@ -4548,10 +4535,10 @@
       <c r="S33" s="1">
         <v>0</v>
       </c>
-      <c r="T33" s="6">
-        <v>0</v>
-      </c>
-      <c r="U33" s="6">
+      <c r="T33" s="7">
+        <v>0</v>
+      </c>
+      <c r="U33" s="7">
         <v>0</v>
       </c>
       <c r="V33" s="1">
@@ -4568,17 +4555,17 @@
       <c r="Y33" s="1">
         <v>28</v>
       </c>
-      <c r="Z33" s="2">
-        <f t="shared" si="13"/>
+      <c r="Z33" s="3">
+        <f t="shared" si="10"/>
         <v>5000</v>
       </c>
-      <c r="AA33" s="2">
+      <c r="AA33" s="3">
         <v>83</v>
       </c>
-      <c r="AB33" s="2">
+      <c r="AB33" s="3">
         <v>27</v>
       </c>
-      <c r="AC33" s="2">
+      <c r="AC33" s="3">
         <f t="shared" si="7"/>
         <v>1376</v>
       </c>
@@ -4589,7 +4576,7 @@
       <c r="AF33" s="1">
         <v>0</v>
       </c>
-      <c r="AG33" s="2">
+      <c r="AG33" s="3">
         <v>107</v>
       </c>
     </row>
@@ -4603,22 +4590,22 @@
       <c r="E34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="10" t="s">
         <v>63</v>
       </c>
       <c r="G34" s="1">
         <v>29</v>
       </c>
       <c r="H34" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>6781800</v>
       </c>
       <c r="I34" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1730400</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>258042000</v>
       </c>
       <c r="K34" s="1">
@@ -4640,11 +4627,11 @@
       <c r="O34" s="1">
         <v>28</v>
       </c>
-      <c r="P34" s="6">
+      <c r="P34" s="7">
         <v>29</v>
       </c>
-      <c r="Q34" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q34" s="3">
+        <f t="shared" si="9"/>
         <v>71</v>
       </c>
       <c r="R34" s="1">
@@ -4653,10 +4640,10 @@
       <c r="S34" s="1">
         <v>0</v>
       </c>
-      <c r="T34" s="6">
-        <v>0</v>
-      </c>
-      <c r="U34" s="6">
+      <c r="T34" s="7">
+        <v>0</v>
+      </c>
+      <c r="U34" s="7">
         <v>0</v>
       </c>
       <c r="V34" s="1">
@@ -4673,17 +4660,17 @@
       <c r="Y34" s="1">
         <v>29</v>
       </c>
-      <c r="Z34" s="2">
+      <c r="Z34" s="3">
         <f>Z33+1000</f>
         <v>6000</v>
       </c>
-      <c r="AA34" s="2">
+      <c r="AA34" s="3">
         <v>89</v>
       </c>
-      <c r="AB34" s="2">
+      <c r="AB34" s="3">
         <v>28</v>
       </c>
-      <c r="AC34" s="2">
+      <c r="AC34" s="3">
         <f t="shared" si="7"/>
         <v>1483</v>
       </c>
@@ -4694,7 +4681,7 @@
       <c r="AF34" s="1">
         <v>0</v>
       </c>
-      <c r="AG34" s="2">
+      <c r="AG34" s="3">
         <v>109</v>
       </c>
     </row>
@@ -4708,22 +4695,22 @@
       <c r="E35" s="1">
         <v>1</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G35" s="1">
         <v>30</v>
       </c>
       <c r="H35" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>8894900</v>
       </c>
       <c r="I35" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>2172100</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>334320000</v>
       </c>
       <c r="K35" s="1">
@@ -4745,11 +4732,11 @@
       <c r="O35" s="1">
         <v>29</v>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="7">
         <v>30</v>
       </c>
-      <c r="Q35" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q35" s="3">
+        <f t="shared" si="9"/>
         <v>74</v>
       </c>
       <c r="R35" s="1">
@@ -4758,10 +4745,10 @@
       <c r="S35" s="1">
         <v>0</v>
       </c>
-      <c r="T35" s="6">
-        <v>0</v>
-      </c>
-      <c r="U35" s="6">
+      <c r="T35" s="7">
+        <v>0</v>
+      </c>
+      <c r="U35" s="7">
         <v>0</v>
       </c>
       <c r="V35" s="1">
@@ -4778,17 +4765,17 @@
       <c r="Y35" s="1">
         <v>30</v>
       </c>
-      <c r="Z35" s="2">
+      <c r="Z35" s="3">
         <f>Z34+1000</f>
         <v>7000</v>
       </c>
-      <c r="AA35" s="2">
+      <c r="AA35" s="3">
         <v>97</v>
       </c>
-      <c r="AB35" s="2">
+      <c r="AB35" s="3">
         <v>29</v>
       </c>
-      <c r="AC35" s="2">
+      <c r="AC35" s="3">
         <f t="shared" si="7"/>
         <v>1592</v>
       </c>
@@ -4799,7 +4786,7 @@
       <c r="AF35" s="1">
         <v>0</v>
       </c>
-      <c r="AG35" s="2">
+      <c r="AG35" s="3">
         <v>113</v>
       </c>
     </row>
@@ -4813,22 +4800,22 @@
       <c r="E36" s="1">
         <v>1</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G36" s="1">
         <v>31</v>
       </c>
       <c r="H36" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>11069600</v>
       </c>
       <c r="I36" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>2616000</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>422840000</v>
       </c>
       <c r="K36" s="1">
@@ -4850,11 +4837,11 @@
       <c r="O36" s="1">
         <v>30</v>
       </c>
-      <c r="P36" s="6">
+      <c r="P36" s="7">
         <v>31</v>
       </c>
-      <c r="Q36" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q36" s="3">
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="R36" s="1">
@@ -4863,10 +4850,10 @@
       <c r="S36" s="1">
         <v>0</v>
       </c>
-      <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="6">
+      <c r="T36" s="7">
+        <v>0</v>
+      </c>
+      <c r="U36" s="7">
         <v>0</v>
       </c>
       <c r="V36" s="1">
@@ -4883,17 +4870,17 @@
       <c r="Y36" s="1">
         <v>31</v>
       </c>
-      <c r="Z36" s="2">
+      <c r="Z36" s="3">
         <f>Z35+1000</f>
         <v>8000</v>
       </c>
-      <c r="AA36" s="2">
+      <c r="AA36" s="3">
         <v>101</v>
       </c>
-      <c r="AB36" s="2">
+      <c r="AB36" s="3">
         <v>30</v>
       </c>
-      <c r="AC36" s="2">
+      <c r="AC36" s="3">
         <f t="shared" si="7"/>
         <v>1705</v>
       </c>
@@ -4904,7 +4891,7 @@
       <c r="AF36" s="1">
         <v>0</v>
       </c>
-      <c r="AG36" s="2">
+      <c r="AG36" s="3">
         <v>127</v>
       </c>
     </row>
@@ -4918,22 +4905,22 @@
       <c r="E37" s="1">
         <v>1</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="6" t="s">
         <v>66</v>
       </c>
       <c r="G37" s="1">
         <v>32</v>
       </c>
       <c r="H37" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>12885300</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>3152700</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>527616000</v>
       </c>
       <c r="K37" s="1">
@@ -4955,11 +4942,11 @@
       <c r="O37" s="1">
         <v>31</v>
       </c>
-      <c r="P37" s="6">
+      <c r="P37" s="7">
         <v>32</v>
       </c>
-      <c r="Q37" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q37" s="3">
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="R37" s="1">
@@ -4968,10 +4955,10 @@
       <c r="S37" s="1">
         <v>0</v>
       </c>
-      <c r="T37" s="6">
-        <v>0</v>
-      </c>
-      <c r="U37" s="6">
+      <c r="T37" s="7">
+        <v>0</v>
+      </c>
+      <c r="U37" s="7">
         <v>0</v>
       </c>
       <c r="V37" s="1">
@@ -4988,17 +4975,17 @@
       <c r="Y37" s="1">
         <v>32</v>
       </c>
-      <c r="Z37" s="2">
+      <c r="Z37" s="3">
         <f>Z36+1000</f>
         <v>9000</v>
       </c>
-      <c r="AA37" s="2">
+      <c r="AA37" s="3">
         <v>103</v>
       </c>
-      <c r="AB37" s="2">
+      <c r="AB37" s="3">
         <v>31</v>
       </c>
-      <c r="AC37" s="2">
+      <c r="AC37" s="3">
         <f t="shared" si="7"/>
         <v>1832</v>
       </c>
@@ -5009,7 +4996,7 @@
       <c r="AF37" s="1">
         <v>0</v>
       </c>
-      <c r="AG37" s="2">
+      <c r="AG37" s="3">
         <v>131</v>
       </c>
     </row>
@@ -5023,22 +5010,22 @@
       <c r="E38" s="1">
         <v>1</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="6" t="s">
         <v>67</v>
       </c>
       <c r="G38" s="1">
         <v>33</v>
       </c>
       <c r="H38" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>15943000</v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4064000</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>647790000</v>
       </c>
       <c r="K38" s="1">
@@ -5060,11 +5047,11 @@
       <c r="O38" s="1">
         <v>32</v>
       </c>
-      <c r="P38" s="6">
+      <c r="P38" s="7">
         <v>33</v>
       </c>
-      <c r="Q38" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q38" s="3">
+        <f t="shared" si="9"/>
         <v>83</v>
       </c>
       <c r="R38" s="1">
@@ -5073,10 +5060,10 @@
       <c r="S38" s="1">
         <v>0</v>
       </c>
-      <c r="T38" s="6">
-        <v>0</v>
-      </c>
-      <c r="U38" s="6">
+      <c r="T38" s="7">
+        <v>0</v>
+      </c>
+      <c r="U38" s="7">
         <v>0</v>
       </c>
       <c r="V38" s="1">
@@ -5093,17 +5080,17 @@
       <c r="Y38" s="1">
         <v>33</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="Z38" s="3">
         <f>Z37+1000</f>
         <v>10000</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AA38" s="3">
         <v>107</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AB38" s="3">
         <v>32</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AC38" s="3">
         <f t="shared" si="7"/>
         <v>1963</v>
       </c>
@@ -5114,7 +5101,7 @@
       <c r="AF38" s="1">
         <v>0</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AG38" s="3">
         <v>137</v>
       </c>
     </row>
@@ -5128,22 +5115,22 @@
       <c r="E39" s="1">
         <v>1</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="6" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="1">
         <v>34</v>
       </c>
       <c r="H39" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>19750800</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>5187600</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>856800000</v>
       </c>
       <c r="K39" s="1">
@@ -5165,11 +5152,11 @@
       <c r="O39" s="1">
         <v>33</v>
       </c>
-      <c r="P39" s="6">
+      <c r="P39" s="7">
         <v>34</v>
       </c>
-      <c r="Q39" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q39" s="3">
+        <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="R39" s="1">
@@ -5178,10 +5165,10 @@
       <c r="S39" s="1">
         <v>0</v>
       </c>
-      <c r="T39" s="6">
-        <v>0</v>
-      </c>
-      <c r="U39" s="6">
+      <c r="T39" s="7">
+        <v>0</v>
+      </c>
+      <c r="U39" s="7">
         <v>0</v>
       </c>
       <c r="V39" s="1">
@@ -5198,17 +5185,17 @@
       <c r="Y39" s="1">
         <v>34</v>
       </c>
-      <c r="Z39" s="2">
+      <c r="Z39" s="3">
         <f t="shared" ref="Z39:Z45" si="14">Z38+2000</f>
         <v>12000</v>
       </c>
-      <c r="AA39" s="2">
+      <c r="AA39" s="3">
         <v>109</v>
       </c>
-      <c r="AB39" s="2">
+      <c r="AB39" s="3">
         <v>33</v>
       </c>
-      <c r="AC39" s="2">
+      <c r="AC39" s="3">
         <f t="shared" si="7"/>
         <v>2100</v>
       </c>
@@ -5219,7 +5206,7 @@
       <c r="AF39" s="1">
         <v>0</v>
       </c>
-      <c r="AG39" s="2">
+      <c r="AG39" s="3">
         <v>139</v>
       </c>
     </row>
@@ -5233,22 +5220,22 @@
       <c r="E40" s="1">
         <v>1</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="6" t="s">
         <v>69</v>
       </c>
       <c r="G40" s="1">
         <v>35</v>
       </c>
       <c r="H40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>24837400</v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>6521200</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1097110000</v>
       </c>
       <c r="K40" s="1">
@@ -5270,11 +5257,11 @@
       <c r="O40" s="1">
         <v>34</v>
       </c>
-      <c r="P40" s="6">
+      <c r="P40" s="7">
         <v>35</v>
       </c>
-      <c r="Q40" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q40" s="3">
+        <f t="shared" si="9"/>
         <v>89</v>
       </c>
       <c r="R40" s="1">
@@ -5283,10 +5270,10 @@
       <c r="S40" s="1">
         <v>0</v>
       </c>
-      <c r="T40" s="6">
-        <v>0</v>
-      </c>
-      <c r="U40" s="6">
+      <c r="T40" s="7">
+        <v>0</v>
+      </c>
+      <c r="U40" s="7">
         <v>0</v>
       </c>
       <c r="V40" s="1">
@@ -5303,17 +5290,17 @@
       <c r="Y40" s="1">
         <v>35</v>
       </c>
-      <c r="Z40" s="2">
+      <c r="Z40" s="3">
         <f t="shared" si="14"/>
         <v>14000</v>
       </c>
-      <c r="AA40" s="2">
+      <c r="AA40" s="3">
         <v>113</v>
       </c>
-      <c r="AB40" s="2">
+      <c r="AB40" s="3">
         <v>34</v>
       </c>
-      <c r="AC40" s="2">
+      <c r="AC40" s="3">
         <f t="shared" si="7"/>
         <v>2239</v>
       </c>
@@ -5329,7 +5316,7 @@
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A41" s="2"/>
+      <c r="A41" s="3"/>
       <c r="C41" s="1">
         <v>36</v>
       </c>
@@ -5339,22 +5326,22 @@
       <c r="E41" s="1">
         <v>1</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G41" s="1">
         <v>36</v>
       </c>
       <c r="H41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>33121600</v>
       </c>
       <c r="I41" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7784000</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1375488000</v>
       </c>
       <c r="K41" s="1">
@@ -5376,11 +5363,11 @@
       <c r="O41" s="1">
         <v>35</v>
       </c>
-      <c r="P41" s="6">
+      <c r="P41" s="7">
         <v>36</v>
       </c>
-      <c r="Q41" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q41" s="3">
+        <f t="shared" si="9"/>
         <v>92</v>
       </c>
       <c r="R41" s="1">
@@ -5389,10 +5376,10 @@
       <c r="S41" s="1">
         <v>0</v>
       </c>
-      <c r="T41" s="6">
-        <v>0</v>
-      </c>
-      <c r="U41" s="6">
+      <c r="T41" s="7">
+        <v>0</v>
+      </c>
+      <c r="U41" s="7">
         <v>0</v>
       </c>
       <c r="V41" s="1">
@@ -5409,17 +5396,17 @@
       <c r="Y41" s="1">
         <v>36</v>
       </c>
-      <c r="Z41" s="2">
+      <c r="Z41" s="3">
         <f t="shared" si="14"/>
         <v>16000</v>
       </c>
-      <c r="AA41" s="2">
+      <c r="AA41" s="3">
         <v>127</v>
       </c>
-      <c r="AB41" s="2">
+      <c r="AB41" s="3">
         <v>35</v>
       </c>
-      <c r="AC41" s="2">
+      <c r="AC41" s="3">
         <f t="shared" si="7"/>
         <v>2388</v>
       </c>
@@ -5434,7 +5421,7 @@
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A42" s="2"/>
+      <c r="A42" s="3"/>
       <c r="C42" s="1">
         <v>37</v>
       </c>
@@ -5444,22 +5431,22 @@
       <c r="E42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="8" t="s">
         <v>71</v>
       </c>
       <c r="G42" s="1">
         <v>37</v>
       </c>
       <c r="H42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>39378600</v>
       </c>
       <c r="I42" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>9655200</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1690974000</v>
       </c>
       <c r="K42" s="1">
@@ -5481,11 +5468,11 @@
       <c r="O42" s="1">
         <v>36</v>
       </c>
-      <c r="P42" s="6">
+      <c r="P42" s="7">
         <v>37</v>
       </c>
-      <c r="Q42" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q42" s="3">
+        <f t="shared" si="9"/>
         <v>95</v>
       </c>
       <c r="R42" s="1">
@@ -5494,10 +5481,10 @@
       <c r="S42" s="1">
         <v>0</v>
       </c>
-      <c r="T42" s="6">
-        <v>0</v>
-      </c>
-      <c r="U42" s="6">
+      <c r="T42" s="7">
+        <v>0</v>
+      </c>
+      <c r="U42" s="7">
         <v>0</v>
       </c>
       <c r="V42" s="1">
@@ -5514,17 +5501,17 @@
       <c r="Y42" s="1">
         <v>37</v>
       </c>
-      <c r="Z42" s="2">
+      <c r="Z42" s="3">
         <f t="shared" si="14"/>
         <v>18000</v>
       </c>
-      <c r="AA42" s="2">
+      <c r="AA42" s="3">
         <v>131</v>
       </c>
-      <c r="AB42" s="2">
+      <c r="AB42" s="3">
         <v>36</v>
       </c>
-      <c r="AC42" s="2">
+      <c r="AC42" s="3">
         <f t="shared" si="7"/>
         <v>2539</v>
       </c>
@@ -5539,7 +5526,7 @@
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A43" s="2"/>
+      <c r="A43" s="3"/>
       <c r="C43" s="1">
         <v>38</v>
       </c>
@@ -5549,22 +5536,22 @@
       <c r="E43" s="1">
         <v>1</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="6" t="s">
         <v>72</v>
       </c>
       <c r="G43" s="1">
         <v>38</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>47402000</v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>11174000</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2048960000</v>
       </c>
       <c r="K43" s="1">
@@ -5586,11 +5573,11 @@
       <c r="O43" s="1">
         <v>37</v>
       </c>
-      <c r="P43" s="6">
+      <c r="P43" s="7">
         <v>38</v>
       </c>
-      <c r="Q43" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q43" s="3">
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="R43" s="1">
@@ -5599,10 +5586,10 @@
       <c r="S43" s="1">
         <v>0</v>
       </c>
-      <c r="T43" s="6">
-        <v>0</v>
-      </c>
-      <c r="U43" s="6">
+      <c r="T43" s="7">
+        <v>0</v>
+      </c>
+      <c r="U43" s="7">
         <v>0</v>
       </c>
       <c r="V43" s="1">
@@ -5619,17 +5606,17 @@
       <c r="Y43" s="1">
         <v>38</v>
       </c>
-      <c r="Z43" s="2">
+      <c r="Z43" s="3">
         <f t="shared" si="14"/>
         <v>20000</v>
       </c>
-      <c r="AA43" s="2">
+      <c r="AA43" s="3">
         <v>137</v>
       </c>
-      <c r="AB43" s="2">
+      <c r="AB43" s="3">
         <v>37</v>
       </c>
-      <c r="AC43" s="2">
+      <c r="AC43" s="3">
         <f t="shared" si="7"/>
         <v>2696</v>
       </c>
@@ -5644,7 +5631,7 @@
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A44" s="2"/>
+      <c r="A44" s="3"/>
       <c r="C44" s="1">
         <v>39</v>
       </c>
@@ -5654,22 +5641,22 @@
       <c r="E44" s="1">
         <v>1</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="8" t="s">
         <v>73</v>
       </c>
       <c r="G44" s="1">
         <v>39</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>62202500</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>14915000</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2787525000</v>
       </c>
       <c r="K44" s="1">
@@ -5691,11 +5678,11 @@
       <c r="O44" s="1">
         <v>38</v>
       </c>
-      <c r="P44" s="6">
+      <c r="P44" s="7">
         <v>39</v>
       </c>
-      <c r="Q44" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q44" s="3">
+        <f t="shared" si="9"/>
         <v>101</v>
       </c>
       <c r="R44" s="1">
@@ -5704,10 +5691,10 @@
       <c r="S44" s="1">
         <v>0</v>
       </c>
-      <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="6">
+      <c r="T44" s="7">
+        <v>0</v>
+      </c>
+      <c r="U44" s="7">
         <v>0</v>
       </c>
       <c r="V44" s="1">
@@ -5724,17 +5711,17 @@
       <c r="Y44" s="1">
         <v>39</v>
       </c>
-      <c r="Z44" s="2">
+      <c r="Z44" s="3">
         <f t="shared" ref="Z44:Z77" si="15">Z43+5000</f>
         <v>25000</v>
       </c>
-      <c r="AA44" s="2">
+      <c r="AA44" s="3">
         <v>139</v>
       </c>
-      <c r="AB44" s="2">
+      <c r="AB44" s="3">
         <v>38</v>
       </c>
-      <c r="AC44" s="2">
+      <c r="AC44" s="3">
         <f t="shared" si="7"/>
         <v>2859</v>
       </c>
@@ -5749,7 +5736,7 @@
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A45" s="2"/>
+      <c r="A45" s="3"/>
       <c r="C45" s="1">
         <v>40</v>
       </c>
@@ -5759,22 +5746,22 @@
       <c r="E45" s="1">
         <v>1</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="6" t="s">
         <v>74</v>
       </c>
       <c r="G45" s="1">
         <v>40</v>
       </c>
       <c r="H45" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>80907000</v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>19071000</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3631200000</v>
       </c>
       <c r="K45" s="1">
@@ -5796,11 +5783,11 @@
       <c r="O45" s="1">
         <v>39</v>
       </c>
-      <c r="P45" s="6">
+      <c r="P45" s="7">
         <v>40</v>
       </c>
-      <c r="Q45" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q45" s="3">
+        <f t="shared" si="9"/>
         <v>104</v>
       </c>
       <c r="R45" s="1">
@@ -5809,10 +5796,10 @@
       <c r="S45" s="1">
         <v>0</v>
       </c>
-      <c r="T45" s="6">
-        <v>0</v>
-      </c>
-      <c r="U45" s="6">
+      <c r="T45" s="7">
+        <v>0</v>
+      </c>
+      <c r="U45" s="7">
         <v>0</v>
       </c>
       <c r="V45" s="1">
@@ -5829,17 +5816,17 @@
       <c r="Y45" s="1">
         <v>40</v>
       </c>
-      <c r="Z45" s="2">
+      <c r="Z45" s="3">
         <f t="shared" si="15"/>
         <v>30000</v>
       </c>
       <c r="AA45" s="1">
         <v>149</v>
       </c>
-      <c r="AB45" s="2">
+      <c r="AB45" s="3">
         <v>39</v>
       </c>
-      <c r="AC45" s="2">
+      <c r="AC45" s="3">
         <f t="shared" si="7"/>
         <v>3026</v>
       </c>
@@ -5854,7 +5841,7 @@
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A46" s="2"/>
+      <c r="A46" s="3"/>
       <c r="C46" s="1">
         <v>41</v>
       </c>
@@ -5864,22 +5851,22 @@
       <c r="E46" s="1">
         <v>1</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="10" t="s">
         <v>75</v>
       </c>
       <c r="G46" s="1">
         <v>41</v>
       </c>
       <c r="H46" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>100943500</v>
       </c>
       <c r="I46" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>22795500</v>
       </c>
       <c r="J46" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4478600000</v>
       </c>
       <c r="K46" s="1">
@@ -5901,11 +5888,11 @@
       <c r="O46" s="1">
         <v>40</v>
       </c>
-      <c r="P46" s="6">
+      <c r="P46" s="7">
         <v>41</v>
       </c>
-      <c r="Q46" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q46" s="3">
+        <f t="shared" si="9"/>
         <v>107</v>
       </c>
       <c r="R46" s="1">
@@ -5914,10 +5901,10 @@
       <c r="S46" s="1">
         <v>0</v>
       </c>
-      <c r="T46" s="6">
-        <v>0</v>
-      </c>
-      <c r="U46" s="6">
+      <c r="T46" s="7">
+        <v>0</v>
+      </c>
+      <c r="U46" s="7">
         <v>0</v>
       </c>
       <c r="V46" s="1">
@@ -5934,17 +5921,17 @@
       <c r="Y46" s="1">
         <v>40</v>
       </c>
-      <c r="Z46" s="2">
+      <c r="Z46" s="3">
         <f t="shared" si="15"/>
         <v>35000</v>
       </c>
       <c r="AA46" s="1">
         <v>151</v>
       </c>
-      <c r="AB46" s="2">
+      <c r="AB46" s="3">
         <v>39</v>
       </c>
-      <c r="AC46" s="2">
+      <c r="AC46" s="3">
         <f t="shared" si="7"/>
         <v>3199</v>
       </c>
@@ -5954,7 +5941,7 @@
       <c r="AF46" s="1">
         <v>0</v>
       </c>
-      <c r="AG46" s="2">
+      <c r="AG46" s="3">
         <v>179</v>
       </c>
     </row>
@@ -5968,22 +5955,22 @@
       <c r="E47" s="1">
         <v>1</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="8" t="s">
         <v>76</v>
       </c>
       <c r="G47" s="1">
         <v>42</v>
       </c>
       <c r="H47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>116572000</v>
       </c>
       <c r="I47" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>26988000</v>
       </c>
       <c r="J47" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5404800000</v>
       </c>
       <c r="K47" s="1">
@@ -6005,11 +5992,11 @@
       <c r="O47" s="1">
         <v>41</v>
       </c>
-      <c r="P47" s="6">
+      <c r="P47" s="7">
         <v>42</v>
       </c>
-      <c r="Q47" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q47" s="3">
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="R47" s="1">
@@ -6018,10 +6005,10 @@
       <c r="S47" s="1">
         <v>0</v>
       </c>
-      <c r="T47" s="6">
-        <v>0</v>
-      </c>
-      <c r="U47" s="6">
+      <c r="T47" s="7">
+        <v>0</v>
+      </c>
+      <c r="U47" s="7">
         <v>0</v>
       </c>
       <c r="V47" s="1">
@@ -6038,17 +6025,17 @@
       <c r="Y47" s="1">
         <v>40</v>
       </c>
-      <c r="Z47" s="2">
+      <c r="Z47" s="3">
         <f t="shared" si="15"/>
         <v>40000</v>
       </c>
       <c r="AA47" s="1">
         <v>151</v>
       </c>
-      <c r="AB47" s="2">
+      <c r="AB47" s="3">
         <v>39</v>
       </c>
-      <c r="AC47" s="2">
+      <c r="AC47" s="3">
         <f t="shared" si="7"/>
         <v>3378</v>
       </c>
@@ -6059,7 +6046,7 @@
       <c r="AF47" s="1">
         <v>0</v>
       </c>
-      <c r="AG47" s="2">
+      <c r="AG47" s="3">
         <v>181</v>
       </c>
     </row>
@@ -6073,22 +6060,22 @@
       <c r="E48" s="1">
         <v>1</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G48" s="1">
         <v>43</v>
       </c>
       <c r="H48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>139180500</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>31414500</v>
       </c>
       <c r="J48" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6406200000</v>
       </c>
       <c r="K48" s="1">
@@ -6110,11 +6097,11 @@
       <c r="O48" s="1">
         <v>42</v>
       </c>
-      <c r="P48" s="6">
+      <c r="P48" s="7">
         <v>43</v>
       </c>
-      <c r="Q48" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q48" s="3">
+        <f t="shared" si="9"/>
         <v>113</v>
       </c>
       <c r="R48" s="1">
@@ -6123,10 +6110,10 @@
       <c r="S48" s="1">
         <v>0</v>
       </c>
-      <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="6">
+      <c r="T48" s="7">
+        <v>0</v>
+      </c>
+      <c r="U48" s="7">
         <v>0</v>
       </c>
       <c r="V48" s="1">
@@ -6143,17 +6130,17 @@
       <c r="Y48" s="1">
         <v>40</v>
       </c>
-      <c r="Z48" s="2">
+      <c r="Z48" s="3">
         <f t="shared" si="15"/>
         <v>45000</v>
       </c>
       <c r="AA48" s="1">
         <v>157</v>
       </c>
-      <c r="AB48" s="2">
+      <c r="AB48" s="3">
         <v>39</v>
       </c>
-      <c r="AC48" s="2">
+      <c r="AC48" s="3">
         <f t="shared" si="7"/>
         <v>3559</v>
       </c>
@@ -6164,7 +6151,7 @@
       <c r="AF48" s="1">
         <v>0</v>
       </c>
-      <c r="AG48" s="2">
+      <c r="AG48" s="3">
         <v>191</v>
       </c>
     </row>
@@ -6178,22 +6165,22 @@
       <c r="E49" s="1">
         <v>1</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="6" t="s">
         <v>78</v>
       </c>
       <c r="G49" s="1">
         <v>44</v>
       </c>
       <c r="H49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>172135000</v>
       </c>
       <c r="I49" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>35295000</v>
       </c>
       <c r="J49" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>7500000000</v>
       </c>
       <c r="K49" s="1">
@@ -6215,11 +6202,11 @@
       <c r="O49" s="1">
         <v>43</v>
       </c>
-      <c r="P49" s="6">
+      <c r="P49" s="7">
         <v>44</v>
       </c>
-      <c r="Q49" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q49" s="3">
+        <f t="shared" si="9"/>
         <v>116</v>
       </c>
       <c r="R49" s="1">
@@ -6228,10 +6215,10 @@
       <c r="S49" s="1">
         <v>0</v>
       </c>
-      <c r="T49" s="6">
-        <v>0</v>
-      </c>
-      <c r="U49" s="6">
+      <c r="T49" s="7">
+        <v>0</v>
+      </c>
+      <c r="U49" s="7">
         <v>0</v>
       </c>
       <c r="V49" s="1">
@@ -6248,17 +6235,17 @@
       <c r="Y49" s="1">
         <v>40</v>
       </c>
-      <c r="Z49" s="2">
+      <c r="Z49" s="3">
         <f t="shared" si="15"/>
         <v>50000</v>
       </c>
       <c r="AA49" s="1">
         <v>173</v>
       </c>
-      <c r="AB49" s="2">
+      <c r="AB49" s="3">
         <v>39</v>
       </c>
-      <c r="AC49" s="2">
+      <c r="AC49" s="3">
         <f t="shared" si="7"/>
         <v>3750</v>
       </c>
@@ -6269,7 +6256,7 @@
       <c r="AF49" s="1">
         <v>0</v>
       </c>
-      <c r="AG49" s="2">
+      <c r="AG49" s="3">
         <v>193</v>
       </c>
     </row>
@@ -6283,22 +6270,22 @@
       <c r="E50" s="1">
         <v>1</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="6" t="s">
         <v>79</v>
       </c>
       <c r="G50" s="1">
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>200766500</v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>40969500</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8674600000</v>
       </c>
       <c r="K50" s="1">
@@ -6320,11 +6307,11 @@
       <c r="O50" s="1">
         <v>44</v>
       </c>
-      <c r="P50" s="6">
+      <c r="P50" s="7">
         <v>45</v>
       </c>
-      <c r="Q50" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q50" s="3">
+        <f t="shared" si="9"/>
         <v>119</v>
       </c>
       <c r="R50" s="1">
@@ -6333,10 +6320,10 @@
       <c r="S50" s="1">
         <v>0</v>
       </c>
-      <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="6">
+      <c r="T50" s="7">
+        <v>0</v>
+      </c>
+      <c r="U50" s="7">
         <v>0</v>
       </c>
       <c r="V50" s="1">
@@ -6353,17 +6340,17 @@
       <c r="Y50" s="1">
         <v>40</v>
       </c>
-      <c r="Z50" s="2">
+      <c r="Z50" s="3">
         <f t="shared" si="15"/>
         <v>55000</v>
       </c>
       <c r="AA50" s="1">
         <v>173</v>
       </c>
-      <c r="AB50" s="2">
+      <c r="AB50" s="3">
         <v>39</v>
       </c>
-      <c r="AC50" s="2">
+      <c r="AC50" s="3">
         <f t="shared" si="7"/>
         <v>3943</v>
       </c>
@@ -6374,7 +6361,7 @@
       <c r="AF50" s="1">
         <v>0</v>
       </c>
-      <c r="AG50" s="2">
+      <c r="AG50" s="3">
         <v>197</v>
       </c>
     </row>
@@ -6388,22 +6375,22 @@
       <c r="E51" s="1">
         <v>1</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" s="10" t="s">
         <v>80</v>
       </c>
       <c r="G51" s="1">
         <v>46</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>231474000</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>45162000</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>9936000000</v>
       </c>
       <c r="K51" s="1">
@@ -6425,11 +6412,11 @@
       <c r="O51" s="1">
         <v>45</v>
       </c>
-      <c r="P51" s="6">
+      <c r="P51" s="7">
         <v>46</v>
       </c>
-      <c r="Q51" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q51" s="3">
+        <f t="shared" si="9"/>
         <v>122</v>
       </c>
       <c r="R51" s="1">
@@ -6438,10 +6425,10 @@
       <c r="S51" s="1">
         <v>0</v>
       </c>
-      <c r="T51" s="6">
-        <v>0</v>
-      </c>
-      <c r="U51" s="6">
+      <c r="T51" s="7">
+        <v>0</v>
+      </c>
+      <c r="U51" s="7">
         <v>0</v>
       </c>
       <c r="V51" s="1">
@@ -6458,17 +6445,17 @@
       <c r="Y51" s="1">
         <v>40</v>
       </c>
-      <c r="Z51" s="2">
+      <c r="Z51" s="3">
         <f t="shared" si="15"/>
         <v>60000</v>
       </c>
       <c r="AA51" s="1">
         <v>173</v>
       </c>
-      <c r="AB51" s="2">
+      <c r="AB51" s="3">
         <v>39</v>
       </c>
-      <c r="AC51" s="2">
+      <c r="AC51" s="3">
         <f t="shared" si="7"/>
         <v>4140</v>
       </c>
@@ -6479,7 +6466,7 @@
       <c r="AF51" s="1">
         <v>0</v>
       </c>
-      <c r="AG51" s="2">
+      <c r="AG51" s="3">
         <v>199</v>
       </c>
     </row>
@@ -6493,22 +6480,22 @@
       <c r="E52" s="1">
         <v>1</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="6" t="s">
         <v>81</v>
       </c>
       <c r="G52" s="1">
         <v>47</v>
       </c>
       <c r="H52" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>255261500</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>49939500</v>
       </c>
       <c r="J52" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>11281400000</v>
       </c>
       <c r="K52" s="1">
@@ -6530,11 +6517,11 @@
       <c r="O52" s="1">
         <v>46</v>
       </c>
-      <c r="P52" s="6">
+      <c r="P52" s="7">
         <v>47</v>
       </c>
-      <c r="Q52" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q52" s="3">
+        <f t="shared" si="9"/>
         <v>125</v>
       </c>
       <c r="R52" s="1">
@@ -6543,10 +6530,10 @@
       <c r="S52" s="1">
         <v>0</v>
       </c>
-      <c r="T52" s="6">
-        <v>0</v>
-      </c>
-      <c r="U52" s="6">
+      <c r="T52" s="7">
+        <v>0</v>
+      </c>
+      <c r="U52" s="7">
         <v>0</v>
       </c>
       <c r="V52" s="1">
@@ -6563,17 +6550,17 @@
       <c r="Y52" s="1">
         <v>40</v>
       </c>
-      <c r="Z52" s="2">
+      <c r="Z52" s="3">
         <f t="shared" si="15"/>
         <v>65000</v>
       </c>
       <c r="AA52" s="1">
         <v>173</v>
       </c>
-      <c r="AB52" s="2">
+      <c r="AB52" s="3">
         <v>39</v>
       </c>
-      <c r="AC52" s="2">
+      <c r="AC52" s="3">
         <f t="shared" si="7"/>
         <v>4339</v>
       </c>
@@ -6584,7 +6571,7 @@
       <c r="AF52" s="1">
         <v>0</v>
       </c>
-      <c r="AG52" s="2">
+      <c r="AG52" s="3">
         <v>211</v>
       </c>
     </row>
@@ -6598,22 +6585,22 @@
       <c r="E53" s="1">
         <v>1</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="4" t="s">
         <v>82</v>
       </c>
       <c r="G53" s="1">
         <v>48</v>
       </c>
       <c r="H53" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>277319000</v>
       </c>
       <c r="I53" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>54327000</v>
       </c>
       <c r="J53" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>12740000000</v>
       </c>
       <c r="K53" s="1">
@@ -6635,11 +6622,11 @@
       <c r="O53" s="1">
         <v>47</v>
       </c>
-      <c r="P53" s="6">
+      <c r="P53" s="7">
         <v>48</v>
       </c>
-      <c r="Q53" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q53" s="3">
+        <f t="shared" si="9"/>
         <v>128</v>
       </c>
       <c r="R53" s="1">
@@ -6648,10 +6635,10 @@
       <c r="S53" s="1">
         <v>0</v>
       </c>
-      <c r="T53" s="6">
-        <v>0</v>
-      </c>
-      <c r="U53" s="6">
+      <c r="T53" s="7">
+        <v>0</v>
+      </c>
+      <c r="U53" s="7">
         <v>0</v>
       </c>
       <c r="V53" s="1">
@@ -6668,17 +6655,17 @@
       <c r="Y53" s="1">
         <v>40</v>
       </c>
-      <c r="Z53" s="2">
+      <c r="Z53" s="3">
         <f t="shared" si="15"/>
         <v>70000</v>
       </c>
       <c r="AA53" s="1">
         <v>173</v>
       </c>
-      <c r="AB53" s="2">
+      <c r="AB53" s="3">
         <v>39</v>
       </c>
-      <c r="AC53" s="2">
+      <c r="AC53" s="3">
         <f t="shared" si="7"/>
         <v>4550</v>
       </c>
@@ -6689,7 +6676,7 @@
       <c r="AF53" s="1">
         <v>0</v>
       </c>
-      <c r="AG53" s="2">
+      <c r="AG53" s="3">
         <v>223</v>
       </c>
     </row>
@@ -6703,22 +6690,22 @@
       <c r="E54" s="1">
         <v>1</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" s="6" t="s">
         <v>83</v>
       </c>
       <c r="G54" s="1">
         <v>49</v>
       </c>
       <c r="H54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>302317500</v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>61717500</v>
       </c>
       <c r="J54" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>14319000000</v>
       </c>
       <c r="K54" s="1">
@@ -6740,11 +6727,11 @@
       <c r="O54" s="1">
         <v>48</v>
       </c>
-      <c r="P54" s="6">
+      <c r="P54" s="7">
         <v>49</v>
       </c>
-      <c r="Q54" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q54" s="3">
+        <f t="shared" si="9"/>
         <v>131</v>
       </c>
       <c r="R54" s="1">
@@ -6753,10 +6740,10 @@
       <c r="S54" s="1">
         <v>0</v>
       </c>
-      <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="6">
+      <c r="T54" s="7">
+        <v>0</v>
+      </c>
+      <c r="U54" s="7">
         <v>0</v>
       </c>
       <c r="V54" s="1">
@@ -6773,17 +6760,17 @@
       <c r="Y54" s="1">
         <v>40</v>
       </c>
-      <c r="Z54" s="2">
+      <c r="Z54" s="3">
         <f t="shared" si="15"/>
         <v>75000</v>
       </c>
       <c r="AA54" s="1">
         <v>173</v>
       </c>
-      <c r="AB54" s="2">
+      <c r="AB54" s="3">
         <v>39</v>
       </c>
-      <c r="AC54" s="2">
+      <c r="AC54" s="3">
         <f t="shared" si="7"/>
         <v>4773</v>
       </c>
@@ -6794,7 +6781,7 @@
       <c r="AF54" s="1">
         <v>0</v>
       </c>
-      <c r="AG54" s="2">
+      <c r="AG54" s="3">
         <v>227</v>
       </c>
     </row>
@@ -6808,22 +6795,22 @@
       <c r="E55" s="1">
         <v>1</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" s="6" t="s">
         <v>84</v>
       </c>
       <c r="G55" s="1">
         <v>50</v>
       </c>
       <c r="H55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>330776000</v>
       </c>
       <c r="I55" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>69576000</v>
       </c>
       <c r="J55" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>16000000000</v>
       </c>
       <c r="K55" s="1">
@@ -6845,11 +6832,11 @@
       <c r="O55" s="1">
         <v>49</v>
       </c>
-      <c r="P55" s="6">
+      <c r="P55" s="7">
         <v>50</v>
       </c>
-      <c r="Q55" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q55" s="3">
+        <f t="shared" si="9"/>
         <v>134</v>
       </c>
       <c r="R55" s="1">
@@ -6858,10 +6845,10 @@
       <c r="S55" s="1">
         <v>0</v>
       </c>
-      <c r="T55" s="6">
-        <v>0</v>
-      </c>
-      <c r="U55" s="6">
+      <c r="T55" s="7">
+        <v>0</v>
+      </c>
+      <c r="U55" s="7">
         <v>0</v>
       </c>
       <c r="V55" s="1">
@@ -6878,17 +6865,17 @@
       <c r="Y55" s="1">
         <v>40</v>
       </c>
-      <c r="Z55" s="2">
+      <c r="Z55" s="3">
         <f t="shared" si="15"/>
         <v>80000</v>
       </c>
       <c r="AA55" s="1">
         <v>173</v>
       </c>
-      <c r="AB55" s="2">
+      <c r="AB55" s="3">
         <v>39</v>
       </c>
-      <c r="AC55" s="2">
+      <c r="AC55" s="3">
         <f t="shared" si="7"/>
         <v>5000</v>
       </c>
@@ -6899,7 +6886,7 @@
       <c r="AF55" s="1">
         <v>0</v>
       </c>
-      <c r="AG55" s="2">
+      <c r="AG55" s="3">
         <v>229</v>
       </c>
     </row>
@@ -6913,22 +6900,22 @@
       <c r="E56" s="1">
         <v>1</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="6" t="s">
         <v>85</v>
       </c>
       <c r="G56" s="1">
         <v>51</v>
       </c>
       <c r="H56" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>354390500</v>
       </c>
       <c r="I56" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>75250500</v>
       </c>
       <c r="J56" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>17778600000</v>
       </c>
       <c r="K56" s="1">
@@ -6950,11 +6937,11 @@
       <c r="O56" s="1">
         <v>50</v>
       </c>
-      <c r="P56" s="6">
+      <c r="P56" s="7">
         <v>51</v>
       </c>
-      <c r="Q56" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q56" s="3">
+        <f t="shared" si="9"/>
         <v>137</v>
       </c>
       <c r="R56" s="1">
@@ -6963,10 +6950,10 @@
       <c r="S56" s="1">
         <v>0</v>
       </c>
-      <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="6">
+      <c r="T56" s="7">
+        <v>0</v>
+      </c>
+      <c r="U56" s="7">
         <v>0</v>
       </c>
       <c r="V56" s="1">
@@ -6983,17 +6970,17 @@
       <c r="Y56" s="1">
         <v>40</v>
       </c>
-      <c r="Z56" s="2">
+      <c r="Z56" s="3">
         <f t="shared" si="15"/>
         <v>85000</v>
       </c>
       <c r="AA56" s="1">
         <v>173</v>
       </c>
-      <c r="AB56" s="2">
+      <c r="AB56" s="3">
         <v>39</v>
       </c>
-      <c r="AC56" s="2">
+      <c r="AC56" s="3">
         <f t="shared" si="7"/>
         <v>5229</v>
       </c>
@@ -7004,7 +6991,7 @@
       <c r="AF56" s="1">
         <v>0</v>
       </c>
-      <c r="AG56" s="2">
+      <c r="AG56" s="3">
         <v>233</v>
       </c>
     </row>
@@ -7018,22 +7005,22 @@
       <c r="E57" s="1">
         <v>1</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="6" t="s">
         <v>86</v>
       </c>
       <c r="G57" s="1">
         <v>52</v>
       </c>
       <c r="H57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>390807000</v>
       </c>
       <c r="I57" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>80379000</v>
       </c>
       <c r="J57" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>19663200000</v>
       </c>
       <c r="K57" s="1">
@@ -7055,11 +7042,11 @@
       <c r="O57" s="1">
         <v>51</v>
       </c>
-      <c r="P57" s="6">
+      <c r="P57" s="7">
         <v>52</v>
       </c>
-      <c r="Q57" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q57" s="3">
+        <f t="shared" si="9"/>
         <v>140</v>
       </c>
       <c r="R57" s="1">
@@ -7068,10 +7055,10 @@
       <c r="S57" s="1">
         <v>0</v>
       </c>
-      <c r="T57" s="6">
-        <v>0</v>
-      </c>
-      <c r="U57" s="6">
+      <c r="T57" s="7">
+        <v>0</v>
+      </c>
+      <c r="U57" s="7">
         <v>0</v>
       </c>
       <c r="V57" s="1">
@@ -7088,17 +7075,17 @@
       <c r="Y57" s="1">
         <v>40</v>
       </c>
-      <c r="Z57" s="2">
+      <c r="Z57" s="3">
         <f t="shared" si="15"/>
         <v>90000</v>
       </c>
       <c r="AA57" s="1">
         <v>173</v>
       </c>
-      <c r="AB57" s="2">
+      <c r="AB57" s="3">
         <v>39</v>
       </c>
-      <c r="AC57" s="2">
+      <c r="AC57" s="3">
         <f t="shared" si="7"/>
         <v>5462</v>
       </c>
@@ -7109,7 +7096,7 @@
       <c r="AF57" s="1">
         <v>0</v>
       </c>
-      <c r="AG57" s="2">
+      <c r="AG57" s="3">
         <v>239</v>
       </c>
     </row>
@@ -7123,22 +7110,22 @@
       <c r="E58" s="1">
         <v>1</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="6" t="s">
         <v>87</v>
       </c>
       <c r="G58" s="1">
         <v>53</v>
       </c>
       <c r="H58" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>422379500</v>
       </c>
       <c r="I58" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>86326500</v>
       </c>
       <c r="J58" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>21663800000</v>
       </c>
       <c r="K58" s="1">
@@ -7160,11 +7147,11 @@
       <c r="O58" s="1">
         <v>52</v>
       </c>
-      <c r="P58" s="6">
+      <c r="P58" s="7">
         <v>53</v>
       </c>
-      <c r="Q58" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q58" s="3">
+        <f t="shared" si="9"/>
         <v>143</v>
       </c>
       <c r="R58" s="1">
@@ -7173,10 +7160,10 @@
       <c r="S58" s="1">
         <v>0</v>
       </c>
-      <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="6">
+      <c r="T58" s="7">
+        <v>0</v>
+      </c>
+      <c r="U58" s="7">
         <v>0</v>
       </c>
       <c r="V58" s="1">
@@ -7193,17 +7180,17 @@
       <c r="Y58" s="1">
         <v>40</v>
       </c>
-      <c r="Z58" s="2">
+      <c r="Z58" s="3">
         <f t="shared" si="15"/>
         <v>95000</v>
       </c>
       <c r="AA58" s="1">
         <v>173</v>
       </c>
-      <c r="AB58" s="2">
+      <c r="AB58" s="3">
         <v>39</v>
       </c>
-      <c r="AC58" s="2">
+      <c r="AC58" s="3">
         <f t="shared" si="7"/>
         <v>5701</v>
       </c>
@@ -7214,7 +7201,7 @@
       <c r="AF58" s="1">
         <v>0</v>
       </c>
-      <c r="AG58" s="2">
+      <c r="AG58" s="3">
         <v>241</v>
       </c>
     </row>
@@ -7228,22 +7215,22 @@
       <c r="E59" s="1">
         <v>1</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="4" t="s">
         <v>88</v>
       </c>
       <c r="G59" s="1">
         <v>54</v>
       </c>
       <c r="H59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>454990000</v>
       </c>
       <c r="I59" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>93210000</v>
       </c>
       <c r="J59" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>23768000000</v>
       </c>
       <c r="K59" s="1">
@@ -7265,11 +7252,11 @@
       <c r="O59" s="1">
         <v>53</v>
       </c>
-      <c r="P59" s="6">
+      <c r="P59" s="7">
         <v>54</v>
       </c>
-      <c r="Q59" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q59" s="3">
+        <f t="shared" si="9"/>
         <v>146</v>
       </c>
       <c r="R59" s="1">
@@ -7278,10 +7265,10 @@
       <c r="S59" s="1">
         <v>0</v>
       </c>
-      <c r="T59" s="6">
-        <v>0</v>
-      </c>
-      <c r="U59" s="6">
+      <c r="T59" s="7">
+        <v>0</v>
+      </c>
+      <c r="U59" s="7">
         <v>0</v>
       </c>
       <c r="V59" s="1">
@@ -7298,17 +7285,17 @@
       <c r="Y59" s="1">
         <v>40</v>
       </c>
-      <c r="Z59" s="2">
+      <c r="Z59" s="3">
         <f t="shared" si="15"/>
         <v>100000</v>
       </c>
       <c r="AA59" s="1">
         <v>173</v>
       </c>
-      <c r="AB59" s="2">
+      <c r="AB59" s="3">
         <v>39</v>
       </c>
-      <c r="AC59" s="2">
+      <c r="AC59" s="3">
         <f t="shared" si="7"/>
         <v>5942</v>
       </c>
@@ -7319,7 +7306,7 @@
       <c r="AF59" s="1">
         <v>0</v>
       </c>
-      <c r="AG59" s="2">
+      <c r="AG59" s="3">
         <v>251</v>
       </c>
     </row>
@@ -7333,22 +7320,22 @@
       <c r="E60" s="1">
         <v>1</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="6" t="s">
         <v>89</v>
       </c>
       <c r="G60" s="1">
         <v>55</v>
       </c>
       <c r="H60" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>488638500</v>
       </c>
       <c r="I60" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>98689500</v>
       </c>
       <c r="J60" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>26010600000</v>
       </c>
       <c r="K60" s="1">
@@ -7370,11 +7357,11 @@
       <c r="O60" s="1">
         <v>54</v>
       </c>
-      <c r="P60" s="6">
+      <c r="P60" s="7">
         <v>55</v>
       </c>
-      <c r="Q60" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q60" s="3">
+        <f t="shared" si="9"/>
         <v>149</v>
       </c>
       <c r="R60" s="1">
@@ -7383,10 +7370,10 @@
       <c r="S60" s="1">
         <v>0</v>
       </c>
-      <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="6">
+      <c r="T60" s="7">
+        <v>0</v>
+      </c>
+      <c r="U60" s="7">
         <v>0</v>
       </c>
       <c r="V60" s="1">
@@ -7403,17 +7390,17 @@
       <c r="Y60" s="1">
         <v>40</v>
       </c>
-      <c r="Z60" s="2">
+      <c r="Z60" s="3">
         <f t="shared" si="15"/>
         <v>105000</v>
       </c>
       <c r="AA60" s="1">
         <v>173</v>
       </c>
-      <c r="AB60" s="2">
+      <c r="AB60" s="3">
         <v>39</v>
       </c>
-      <c r="AC60" s="2">
+      <c r="AC60" s="3">
         <f t="shared" si="7"/>
         <v>6193</v>
       </c>
@@ -7424,7 +7411,7 @@
       <c r="AF60" s="1">
         <v>0</v>
       </c>
-      <c r="AG60" s="2">
+      <c r="AG60" s="3">
         <v>257</v>
       </c>
     </row>
@@ -7438,22 +7425,22 @@
       <c r="E61" s="1">
         <v>1</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" s="6" t="s">
         <v>90</v>
       </c>
       <c r="G61" s="1">
         <v>56</v>
       </c>
       <c r="H61" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>515713000</v>
       </c>
       <c r="I61" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>107679000</v>
       </c>
       <c r="J61" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>28380000000</v>
       </c>
       <c r="K61" s="1">
@@ -7475,11 +7462,11 @@
       <c r="O61" s="1">
         <v>55</v>
       </c>
-      <c r="P61" s="6">
+      <c r="P61" s="7">
         <v>56</v>
       </c>
-      <c r="Q61" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q61" s="3">
+        <f t="shared" si="9"/>
         <v>152</v>
       </c>
       <c r="R61" s="1">
@@ -7488,10 +7475,10 @@
       <c r="S61" s="1">
         <v>0</v>
       </c>
-      <c r="T61" s="6">
-        <v>0</v>
-      </c>
-      <c r="U61" s="6">
+      <c r="T61" s="7">
+        <v>0</v>
+      </c>
+      <c r="U61" s="7">
         <v>0</v>
       </c>
       <c r="V61" s="1">
@@ -7508,17 +7495,17 @@
       <c r="Y61" s="1">
         <v>40</v>
       </c>
-      <c r="Z61" s="2">
+      <c r="Z61" s="3">
         <f t="shared" si="15"/>
         <v>110000</v>
       </c>
       <c r="AA61" s="1">
         <v>173</v>
       </c>
-      <c r="AB61" s="2">
+      <c r="AB61" s="3">
         <v>39</v>
       </c>
-      <c r="AC61" s="2">
+      <c r="AC61" s="3">
         <f t="shared" si="7"/>
         <v>6450</v>
       </c>
@@ -7529,7 +7516,7 @@
       <c r="AF61" s="1">
         <v>0</v>
       </c>
-      <c r="AG61" s="2">
+      <c r="AG61" s="3">
         <v>263</v>
       </c>
     </row>
@@ -7543,22 +7530,22 @@
       <c r="E62" s="1">
         <v>1</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="6" t="s">
         <v>91</v>
       </c>
       <c r="G62" s="1">
         <v>57</v>
       </c>
       <c r="H62" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>551091500</v>
       </c>
       <c r="I62" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>115264500</v>
       </c>
       <c r="J62" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>30879800000</v>
       </c>
       <c r="K62" s="1">
@@ -7580,11 +7567,11 @@
       <c r="O62" s="1">
         <v>56</v>
       </c>
-      <c r="P62" s="6">
+      <c r="P62" s="7">
         <v>57</v>
       </c>
-      <c r="Q62" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q62" s="3">
+        <f t="shared" si="9"/>
         <v>155</v>
       </c>
       <c r="R62" s="1">
@@ -7593,10 +7580,10 @@
       <c r="S62" s="1">
         <v>0</v>
       </c>
-      <c r="T62" s="6">
-        <v>0</v>
-      </c>
-      <c r="U62" s="6">
+      <c r="T62" s="7">
+        <v>0</v>
+      </c>
+      <c r="U62" s="7">
         <v>0</v>
       </c>
       <c r="V62" s="1">
@@ -7613,17 +7600,17 @@
       <c r="Y62" s="1">
         <v>40</v>
       </c>
-      <c r="Z62" s="2">
+      <c r="Z62" s="3">
         <f t="shared" si="15"/>
         <v>115000</v>
       </c>
       <c r="AA62" s="1">
         <v>173</v>
       </c>
-      <c r="AB62" s="2">
+      <c r="AB62" s="3">
         <v>39</v>
       </c>
-      <c r="AC62" s="2">
+      <c r="AC62" s="3">
         <f t="shared" si="7"/>
         <v>6713</v>
       </c>
@@ -7634,7 +7621,7 @@
       <c r="AF62" s="1">
         <v>0</v>
       </c>
-      <c r="AG62" s="2">
+      <c r="AG62" s="3">
         <v>269</v>
       </c>
     </row>
@@ -7648,22 +7635,22 @@
       <c r="E63" s="1">
         <v>1</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="8" t="s">
         <v>92</v>
       </c>
       <c r="G63" s="1">
         <v>58</v>
       </c>
       <c r="H63" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>583356000</v>
       </c>
       <c r="I63" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>123084000</v>
       </c>
       <c r="J63" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>33513600000</v>
       </c>
       <c r="K63" s="1">
@@ -7685,11 +7672,11 @@
       <c r="O63" s="1">
         <v>57</v>
       </c>
-      <c r="P63" s="6">
+      <c r="P63" s="7">
         <v>58</v>
       </c>
-      <c r="Q63" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q63" s="3">
+        <f t="shared" si="9"/>
         <v>158</v>
       </c>
       <c r="R63" s="1">
@@ -7698,10 +7685,10 @@
       <c r="S63" s="1">
         <v>0</v>
       </c>
-      <c r="T63" s="6">
-        <v>0</v>
-      </c>
-      <c r="U63" s="6">
+      <c r="T63" s="7">
+        <v>0</v>
+      </c>
+      <c r="U63" s="7">
         <v>0</v>
       </c>
       <c r="V63" s="1">
@@ -7718,17 +7705,17 @@
       <c r="Y63" s="1">
         <v>40</v>
       </c>
-      <c r="Z63" s="2">
+      <c r="Z63" s="3">
         <f t="shared" si="15"/>
         <v>120000</v>
       </c>
       <c r="AA63" s="1">
         <v>173</v>
       </c>
-      <c r="AB63" s="2">
+      <c r="AB63" s="3">
         <v>39</v>
       </c>
-      <c r="AC63" s="2">
+      <c r="AC63" s="3">
         <f t="shared" si="7"/>
         <v>6982</v>
       </c>
@@ -7739,7 +7726,7 @@
       <c r="AF63" s="1">
         <v>0</v>
       </c>
-      <c r="AG63" s="2">
+      <c r="AG63" s="3">
         <v>271</v>
       </c>
     </row>
@@ -7753,22 +7740,22 @@
       <c r="E64" s="1">
         <v>1</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" s="6" t="s">
         <v>93</v>
       </c>
       <c r="G64" s="1">
         <v>59</v>
       </c>
       <c r="H64" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>611987500</v>
       </c>
       <c r="I64" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>131137500</v>
       </c>
       <c r="J64" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>36265000000</v>
       </c>
       <c r="K64" s="1">
@@ -7790,11 +7777,11 @@
       <c r="O64" s="1">
         <v>58</v>
       </c>
-      <c r="P64" s="6">
+      <c r="P64" s="7">
         <v>59</v>
       </c>
-      <c r="Q64" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q64" s="3">
+        <f t="shared" si="9"/>
         <v>161</v>
       </c>
       <c r="R64" s="1">
@@ -7803,10 +7790,10 @@
       <c r="S64" s="1">
         <v>0</v>
       </c>
-      <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="6">
+      <c r="T64" s="7">
+        <v>0</v>
+      </c>
+      <c r="U64" s="7">
         <v>0</v>
       </c>
       <c r="V64" s="1">
@@ -7823,17 +7810,17 @@
       <c r="Y64" s="1">
         <v>40</v>
       </c>
-      <c r="Z64" s="2">
+      <c r="Z64" s="3">
         <f t="shared" si="15"/>
         <v>125000</v>
       </c>
       <c r="AA64" s="1">
         <v>173</v>
       </c>
-      <c r="AB64" s="2">
+      <c r="AB64" s="3">
         <v>39</v>
       </c>
-      <c r="AC64" s="2">
+      <c r="AC64" s="3">
         <f t="shared" si="7"/>
         <v>7253</v>
       </c>
@@ -7844,7 +7831,7 @@
       <c r="AF64" s="1">
         <v>0</v>
       </c>
-      <c r="AG64" s="2">
+      <c r="AG64" s="3">
         <v>277</v>
       </c>
     </row>
@@ -7858,22 +7845,22 @@
       <c r="E65" s="1">
         <v>1</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="4" t="s">
         <v>94</v>
       </c>
       <c r="G65" s="1">
         <v>60</v>
       </c>
       <c r="H65" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>658957000</v>
       </c>
       <c r="I65" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>137397000</v>
       </c>
       <c r="J65" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>39156000000</v>
       </c>
       <c r="K65" s="1">
@@ -7895,11 +7882,11 @@
       <c r="O65" s="1">
         <v>59</v>
       </c>
-      <c r="P65" s="6">
+      <c r="P65" s="7">
         <v>60</v>
       </c>
-      <c r="Q65" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q65" s="3">
+        <f t="shared" si="9"/>
         <v>164</v>
       </c>
       <c r="R65" s="1">
@@ -7908,10 +7895,10 @@
       <c r="S65" s="1">
         <v>0</v>
       </c>
-      <c r="T65" s="6">
-        <v>0</v>
-      </c>
-      <c r="U65" s="6">
+      <c r="T65" s="7">
+        <v>0</v>
+      </c>
+      <c r="U65" s="7">
         <v>0</v>
       </c>
       <c r="V65" s="1">
@@ -7928,17 +7915,17 @@
       <c r="Y65" s="1">
         <v>40</v>
       </c>
-      <c r="Z65" s="2">
+      <c r="Z65" s="3">
         <f t="shared" si="15"/>
         <v>130000</v>
       </c>
       <c r="AA65" s="1">
         <v>173</v>
       </c>
-      <c r="AB65" s="2">
+      <c r="AB65" s="3">
         <v>39</v>
       </c>
-      <c r="AC65" s="2">
+      <c r="AC65" s="3">
         <f t="shared" si="7"/>
         <v>7530</v>
       </c>
@@ -7949,7 +7936,7 @@
       <c r="AF65" s="1">
         <v>0</v>
       </c>
-      <c r="AG65" s="2">
+      <c r="AG65" s="3">
         <v>281</v>
       </c>
     </row>
@@ -7963,22 +7950,22 @@
       <c r="E66" s="1">
         <v>1</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" s="6" t="s">
         <v>95</v>
       </c>
       <c r="G66" s="1">
         <v>61</v>
       </c>
       <c r="H66" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>716998500</v>
       </c>
       <c r="I66" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>145840500</v>
       </c>
       <c r="J66" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>42179400000</v>
       </c>
       <c r="K66" s="1">
@@ -8000,11 +7987,11 @@
       <c r="O66" s="1">
         <v>60</v>
       </c>
-      <c r="P66" s="6">
+      <c r="P66" s="7">
         <v>61</v>
       </c>
-      <c r="Q66" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q66" s="3">
+        <f t="shared" si="9"/>
         <v>167</v>
       </c>
       <c r="R66" s="1">
@@ -8013,10 +8000,10 @@
       <c r="S66" s="1">
         <v>0</v>
       </c>
-      <c r="T66" s="6">
-        <v>0</v>
-      </c>
-      <c r="U66" s="6">
+      <c r="T66" s="7">
+        <v>0</v>
+      </c>
+      <c r="U66" s="7">
         <v>0</v>
       </c>
       <c r="V66" s="1">
@@ -8033,17 +8020,17 @@
       <c r="Y66" s="1">
         <v>40</v>
       </c>
-      <c r="Z66" s="2">
+      <c r="Z66" s="3">
         <f t="shared" si="15"/>
         <v>135000</v>
       </c>
       <c r="AA66" s="1">
         <v>173</v>
       </c>
-      <c r="AB66" s="2">
+      <c r="AB66" s="3">
         <v>39</v>
       </c>
-      <c r="AC66" s="2">
+      <c r="AC66" s="3">
         <f t="shared" si="7"/>
         <v>7811</v>
       </c>
@@ -8054,7 +8041,7 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-      <c r="AG66" s="2">
+      <c r="AG66" s="3">
         <v>283</v>
       </c>
     </row>
@@ -8068,22 +8055,22 @@
       <c r="E67" s="1">
         <v>1</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="10" t="s">
         <v>96</v>
       </c>
       <c r="G67" s="1">
         <v>62</v>
       </c>
       <c r="H67" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>753242000</v>
       </c>
       <c r="I67" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>153426000</v>
       </c>
       <c r="J67" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>45326400000</v>
       </c>
       <c r="K67" s="1">
@@ -8105,11 +8092,11 @@
       <c r="O67" s="1">
         <v>61</v>
       </c>
-      <c r="P67" s="6">
+      <c r="P67" s="7">
         <v>62</v>
       </c>
-      <c r="Q67" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q67" s="3">
+        <f t="shared" si="9"/>
         <v>170</v>
       </c>
       <c r="R67" s="1">
@@ -8118,10 +8105,10 @@
       <c r="S67" s="1">
         <v>0</v>
       </c>
-      <c r="T67" s="6">
-        <v>0</v>
-      </c>
-      <c r="U67" s="6">
+      <c r="T67" s="7">
+        <v>0</v>
+      </c>
+      <c r="U67" s="7">
         <v>0</v>
       </c>
       <c r="V67" s="1">
@@ -8138,17 +8125,17 @@
       <c r="Y67" s="1">
         <v>40</v>
       </c>
-      <c r="Z67" s="2">
+      <c r="Z67" s="3">
         <f t="shared" si="15"/>
         <v>140000</v>
       </c>
       <c r="AA67" s="1">
         <v>173</v>
       </c>
-      <c r="AB67" s="2">
+      <c r="AB67" s="3">
         <v>39</v>
       </c>
-      <c r="AC67" s="2">
+      <c r="AC67" s="3">
         <f t="shared" si="7"/>
         <v>8094</v>
       </c>
@@ -8159,7 +8146,7 @@
       <c r="AF67" s="1">
         <v>0</v>
       </c>
-      <c r="AG67" s="2">
+      <c r="AG67" s="3">
         <v>293</v>
       </c>
     </row>
@@ -8173,22 +8160,22 @@
       <c r="E68" s="1">
         <v>1</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F68" s="6" t="s">
         <v>97</v>
       </c>
       <c r="G68" s="1">
         <v>63</v>
       </c>
       <c r="H68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>785160500</v>
       </c>
       <c r="I68" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>160036500</v>
       </c>
       <c r="J68" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>48644600000</v>
       </c>
       <c r="K68" s="1">
@@ -8210,11 +8197,11 @@
       <c r="O68" s="1">
         <v>62</v>
       </c>
-      <c r="P68" s="6">
+      <c r="P68" s="7">
         <v>63</v>
       </c>
-      <c r="Q68" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q68" s="3">
+        <f t="shared" si="9"/>
         <v>173</v>
       </c>
       <c r="R68" s="1">
@@ -8223,10 +8210,10 @@
       <c r="S68" s="1">
         <v>0</v>
       </c>
-      <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="6">
+      <c r="T68" s="7">
+        <v>0</v>
+      </c>
+      <c r="U68" s="7">
         <v>0</v>
       </c>
       <c r="V68" s="1">
@@ -8243,17 +8230,17 @@
       <c r="Y68" s="1">
         <v>40</v>
       </c>
-      <c r="Z68" s="2">
+      <c r="Z68" s="3">
         <f t="shared" si="15"/>
         <v>145000</v>
       </c>
       <c r="AA68" s="1">
         <v>173</v>
       </c>
-      <c r="AB68" s="2">
+      <c r="AB68" s="3">
         <v>39</v>
       </c>
-      <c r="AC68" s="2">
+      <c r="AC68" s="3">
         <f t="shared" si="7"/>
         <v>8387</v>
       </c>
@@ -8264,7 +8251,7 @@
       <c r="AF68" s="1">
         <v>0</v>
       </c>
-      <c r="AG68" s="2">
+      <c r="AG68" s="3">
         <v>307</v>
       </c>
     </row>
@@ -8278,22 +8265,22 @@
       <c r="E69" s="1">
         <v>1</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F69" s="6" t="s">
         <v>98</v>
       </c>
       <c r="G69" s="1">
         <v>64</v>
       </c>
       <c r="H69" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>822615000</v>
       </c>
       <c r="I69" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>171405000</v>
       </c>
       <c r="J69" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>52164000000</v>
       </c>
       <c r="K69" s="1">
@@ -8315,11 +8302,11 @@
       <c r="O69" s="1">
         <v>63</v>
       </c>
-      <c r="P69" s="6">
+      <c r="P69" s="7">
         <v>64</v>
       </c>
-      <c r="Q69" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q69" s="3">
+        <f t="shared" si="9"/>
         <v>176</v>
       </c>
       <c r="R69" s="1">
@@ -8328,10 +8315,10 @@
       <c r="S69" s="1">
         <v>0</v>
       </c>
-      <c r="T69" s="6">
-        <v>0</v>
-      </c>
-      <c r="U69" s="6">
+      <c r="T69" s="7">
+        <v>0</v>
+      </c>
+      <c r="U69" s="7">
         <v>0</v>
       </c>
       <c r="V69" s="1">
@@ -8348,17 +8335,17 @@
       <c r="Y69" s="1">
         <v>40</v>
       </c>
-      <c r="Z69" s="2">
+      <c r="Z69" s="3">
         <f t="shared" si="15"/>
         <v>150000</v>
       </c>
       <c r="AA69" s="1">
         <v>173</v>
       </c>
-      <c r="AB69" s="2">
+      <c r="AB69" s="3">
         <v>39</v>
       </c>
-      <c r="AC69" s="2">
+      <c r="AC69" s="3">
         <f t="shared" si="7"/>
         <v>8694</v>
       </c>
@@ -8369,7 +8356,7 @@
       <c r="AF69" s="1">
         <v>0</v>
       </c>
-      <c r="AG69" s="2">
+      <c r="AG69" s="3">
         <v>311</v>
       </c>
     </row>
@@ -8383,14 +8370,14 @@
       <c r="E70" s="1">
         <v>1</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="F70" s="6" t="s">
         <v>99</v>
       </c>
       <c r="G70" s="1">
         <v>65</v>
       </c>
       <c r="H70" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>887576500</v>
       </c>
       <c r="I70" s="1">
@@ -8398,7 +8385,7 @@
         <v>185581500</v>
       </c>
       <c r="J70" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>55831000000</v>
       </c>
       <c r="K70" s="1">
@@ -8420,11 +8407,11 @@
       <c r="O70" s="1">
         <v>64</v>
       </c>
-      <c r="P70" s="6">
+      <c r="P70" s="7">
         <v>65</v>
       </c>
-      <c r="Q70" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q70" s="3">
+        <f t="shared" si="9"/>
         <v>179</v>
       </c>
       <c r="R70" s="1">
@@ -8433,10 +8420,10 @@
       <c r="S70" s="1">
         <v>0</v>
       </c>
-      <c r="T70" s="6">
-        <v>0</v>
-      </c>
-      <c r="U70" s="6">
+      <c r="T70" s="7">
+        <v>0</v>
+      </c>
+      <c r="U70" s="7">
         <v>0</v>
       </c>
       <c r="V70" s="1">
@@ -8453,17 +8440,17 @@
       <c r="Y70" s="1">
         <v>40</v>
       </c>
-      <c r="Z70" s="2">
+      <c r="Z70" s="3">
         <f t="shared" si="15"/>
         <v>155000</v>
       </c>
       <c r="AA70" s="1">
         <v>173</v>
       </c>
-      <c r="AB70" s="2">
+      <c r="AB70" s="3">
         <v>39</v>
       </c>
-      <c r="AC70" s="2">
+      <c r="AC70" s="3">
         <f t="shared" si="7"/>
         <v>9005</v>
       </c>
@@ -8474,7 +8461,7 @@
       <c r="AF70" s="1">
         <v>0</v>
       </c>
-      <c r="AG70" s="2">
+      <c r="AG70" s="3">
         <v>313</v>
       </c>
     </row>
@@ -8488,7 +8475,7 @@
       <c r="E71" s="1">
         <v>1</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="4" t="s">
         <v>100</v>
       </c>
       <c r="G71" s="1">
@@ -8503,7 +8490,7 @@
         <v>194064000</v>
       </c>
       <c r="J71" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>59635200000</v>
       </c>
       <c r="K71" s="1">
@@ -8525,11 +8512,11 @@
       <c r="O71" s="1">
         <v>65</v>
       </c>
-      <c r="P71" s="6">
+      <c r="P71" s="7">
         <v>66</v>
       </c>
-      <c r="Q71" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q71" s="3">
+        <f t="shared" si="9"/>
         <v>182</v>
       </c>
       <c r="R71" s="1">
@@ -8538,10 +8525,10 @@
       <c r="S71" s="1">
         <v>0</v>
       </c>
-      <c r="T71" s="6">
-        <v>0</v>
-      </c>
-      <c r="U71" s="6">
+      <c r="T71" s="7">
+        <v>0</v>
+      </c>
+      <c r="U71" s="7">
         <v>0</v>
       </c>
       <c r="V71" s="1">
@@ -8558,17 +8545,17 @@
       <c r="Y71" s="1">
         <v>40</v>
       </c>
-      <c r="Z71" s="2">
+      <c r="Z71" s="3">
         <f t="shared" si="15"/>
         <v>160000</v>
       </c>
       <c r="AA71" s="1">
         <v>173</v>
       </c>
-      <c r="AB71" s="2">
+      <c r="AB71" s="3">
         <v>39</v>
       </c>
-      <c r="AC71" s="2">
+      <c r="AC71" s="3">
         <f t="shared" si="7"/>
         <v>9318</v>
       </c>
@@ -8579,7 +8566,7 @@
       <c r="AF71" s="1">
         <v>0</v>
       </c>
-      <c r="AG71" s="2">
+      <c r="AG71" s="3">
         <v>317</v>
       </c>
     </row>
@@ -8593,7 +8580,7 @@
       <c r="E72" s="1">
         <v>1</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="6" t="s">
         <v>101</v>
       </c>
       <c r="G72" s="1">
@@ -8608,7 +8595,7 @@
         <v>201415500</v>
       </c>
       <c r="J72" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>63591000000</v>
       </c>
       <c r="K72" s="1">
@@ -8630,11 +8617,11 @@
       <c r="O72" s="1">
         <v>66</v>
       </c>
-      <c r="P72" s="6">
+      <c r="P72" s="7">
         <v>67</v>
       </c>
-      <c r="Q72" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q72" s="3">
+        <f t="shared" si="9"/>
         <v>185</v>
       </c>
       <c r="R72" s="1">
@@ -8643,10 +8630,10 @@
       <c r="S72" s="1">
         <v>0</v>
       </c>
-      <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="6">
+      <c r="T72" s="7">
+        <v>0</v>
+      </c>
+      <c r="U72" s="7">
         <v>0</v>
       </c>
       <c r="V72" s="1">
@@ -8663,17 +8650,17 @@
       <c r="Y72" s="1">
         <v>40</v>
       </c>
-      <c r="Z72" s="2">
+      <c r="Z72" s="3">
         <f t="shared" si="15"/>
         <v>165000</v>
       </c>
       <c r="AA72" s="1">
         <v>173</v>
       </c>
-      <c r="AB72" s="2">
+      <c r="AB72" s="3">
         <v>39</v>
       </c>
-      <c r="AC72" s="2">
+      <c r="AC72" s="3">
         <f t="shared" si="7"/>
         <v>9635</v>
       </c>
@@ -8684,7 +8671,7 @@
       <c r="AF72" s="1">
         <v>0</v>
       </c>
-      <c r="AG72" s="2">
+      <c r="AG72" s="3">
         <v>331</v>
       </c>
     </row>
@@ -8698,7 +8685,7 @@
       <c r="E73" s="1">
         <v>1</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G73" s="1">
@@ -8735,11 +8722,11 @@
       <c r="O73" s="1">
         <v>67</v>
       </c>
-      <c r="P73" s="6">
+      <c r="P73" s="7">
         <v>68</v>
       </c>
-      <c r="Q73" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q73" s="3">
+        <f t="shared" si="9"/>
         <v>188</v>
       </c>
       <c r="R73" s="1">
@@ -8748,10 +8735,10 @@
       <c r="S73" s="1">
         <v>0</v>
       </c>
-      <c r="T73" s="6">
-        <v>0</v>
-      </c>
-      <c r="U73" s="6">
+      <c r="T73" s="7">
+        <v>0</v>
+      </c>
+      <c r="U73" s="7">
         <v>0</v>
       </c>
       <c r="V73" s="1">
@@ -8768,17 +8755,17 @@
       <c r="Y73" s="1">
         <v>40</v>
       </c>
-      <c r="Z73" s="2">
+      <c r="Z73" s="3">
         <f t="shared" si="15"/>
         <v>170000</v>
       </c>
       <c r="AA73" s="1">
         <v>173</v>
       </c>
-      <c r="AB73" s="2">
+      <c r="AB73" s="3">
         <v>39</v>
       </c>
-      <c r="AC73" s="2">
+      <c r="AC73" s="3">
         <f t="shared" si="7"/>
         <v>9966</v>
       </c>
@@ -8789,7 +8776,7 @@
       <c r="AF73" s="1">
         <v>0</v>
       </c>
-      <c r="AG73" s="2">
+      <c r="AG73" s="3">
         <v>337</v>
       </c>
     </row>
@@ -8803,7 +8790,7 @@
       <c r="E74" s="1">
         <v>1</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="6" t="s">
         <v>103</v>
       </c>
       <c r="G74" s="1">
@@ -8840,11 +8827,11 @@
       <c r="O74" s="1">
         <v>68</v>
       </c>
-      <c r="P74" s="6">
+      <c r="P74" s="7">
         <v>69</v>
       </c>
-      <c r="Q74" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q74" s="3">
+        <f t="shared" si="9"/>
         <v>191</v>
       </c>
       <c r="R74" s="1">
@@ -8853,10 +8840,10 @@
       <c r="S74" s="1">
         <v>0</v>
       </c>
-      <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="6">
+      <c r="T74" s="7">
+        <v>0</v>
+      </c>
+      <c r="U74" s="7">
         <v>0</v>
       </c>
       <c r="V74" s="1">
@@ -8873,17 +8860,17 @@
       <c r="Y74" s="1">
         <v>40</v>
       </c>
-      <c r="Z74" s="2">
+      <c r="Z74" s="3">
         <f t="shared" si="15"/>
         <v>175000</v>
       </c>
       <c r="AA74" s="1">
         <v>173</v>
       </c>
-      <c r="AB74" s="2">
+      <c r="AB74" s="3">
         <v>39</v>
       </c>
-      <c r="AC74" s="2">
+      <c r="AC74" s="3">
         <f t="shared" si="7"/>
         <v>10303</v>
       </c>
@@ -8894,7 +8881,7 @@
       <c r="AF74" s="1">
         <v>0</v>
       </c>
-      <c r="AG74" s="2">
+      <c r="AG74" s="3">
         <v>347</v>
       </c>
     </row>
@@ -8908,7 +8895,7 @@
       <c r="E75" s="1">
         <v>1</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="6" t="s">
         <v>104</v>
       </c>
       <c r="G75" s="1">
@@ -8945,11 +8932,11 @@
       <c r="O75" s="1">
         <v>69</v>
       </c>
-      <c r="P75" s="6">
+      <c r="P75" s="7">
         <v>70</v>
       </c>
-      <c r="Q75" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q75" s="3">
+        <f t="shared" si="9"/>
         <v>194</v>
       </c>
       <c r="R75" s="1">
@@ -8958,10 +8945,10 @@
       <c r="S75" s="1">
         <v>0</v>
       </c>
-      <c r="T75" s="6">
-        <v>0</v>
-      </c>
-      <c r="U75" s="6">
+      <c r="T75" s="7">
+        <v>0</v>
+      </c>
+      <c r="U75" s="7">
         <v>0</v>
       </c>
       <c r="V75" s="1">
@@ -8978,17 +8965,17 @@
       <c r="Y75" s="1">
         <v>40</v>
       </c>
-      <c r="Z75" s="2">
+      <c r="Z75" s="3">
         <f t="shared" si="15"/>
         <v>180000</v>
       </c>
       <c r="AA75" s="1">
         <v>173</v>
       </c>
-      <c r="AB75" s="2">
+      <c r="AB75" s="3">
         <v>39</v>
       </c>
-      <c r="AC75" s="2">
+      <c r="AC75" s="3">
         <f t="shared" si="7"/>
         <v>10650</v>
       </c>
@@ -8999,7 +8986,7 @@
       <c r="AF75" s="1">
         <v>0</v>
       </c>
-      <c r="AG75" s="2">
+      <c r="AG75" s="3">
         <v>349</v>
       </c>
     </row>
@@ -9013,7 +9000,7 @@
       <c r="E76" s="1">
         <v>1</v>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F76" s="8" t="s">
         <v>105</v>
       </c>
       <c r="G76" s="1">
@@ -9050,11 +9037,11 @@
       <c r="O76" s="1">
         <v>70</v>
       </c>
-      <c r="P76" s="6">
+      <c r="P76" s="7">
         <v>71</v>
       </c>
-      <c r="Q76" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q76" s="3">
+        <f t="shared" si="9"/>
         <v>197</v>
       </c>
       <c r="R76" s="1">
@@ -9063,10 +9050,10 @@
       <c r="S76" s="1">
         <v>0</v>
       </c>
-      <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="6">
+      <c r="T76" s="7">
+        <v>0</v>
+      </c>
+      <c r="U76" s="7">
         <v>0</v>
       </c>
       <c r="V76" s="1">
@@ -9083,17 +9070,17 @@
       <c r="Y76" s="1">
         <v>40</v>
       </c>
-      <c r="Z76" s="2">
+      <c r="Z76" s="3">
         <f t="shared" si="15"/>
         <v>185000</v>
       </c>
       <c r="AA76" s="1">
         <v>173</v>
       </c>
-      <c r="AB76" s="2">
+      <c r="AB76" s="3">
         <v>39</v>
       </c>
-      <c r="AC76" s="2">
+      <c r="AC76" s="3">
         <f>AC75+AG75</f>
         <v>10999</v>
       </c>
@@ -9104,7 +9091,7 @@
       <c r="AF76" s="1">
         <v>0</v>
       </c>
-      <c r="AG76" s="2">
+      <c r="AG76" s="3">
         <v>353</v>
       </c>
     </row>
@@ -9118,7 +9105,7 @@
       <c r="E77" s="1">
         <v>1</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="4" t="s">
         <v>106</v>
       </c>
       <c r="G77" s="1">
@@ -9155,11 +9142,11 @@
       <c r="O77" s="1">
         <v>71</v>
       </c>
-      <c r="P77" s="6">
+      <c r="P77" s="7">
         <v>72</v>
       </c>
-      <c r="Q77" s="2">
-        <f t="shared" si="12"/>
+      <c r="Q77" s="3">
+        <f t="shared" si="9"/>
         <v>200</v>
       </c>
       <c r="R77" s="1">
@@ -9168,10 +9155,10 @@
       <c r="S77" s="1">
         <v>0</v>
       </c>
-      <c r="T77" s="6">
-        <v>0</v>
-      </c>
-      <c r="U77" s="6">
+      <c r="T77" s="7">
+        <v>0</v>
+      </c>
+      <c r="U77" s="7">
         <v>0</v>
       </c>
       <c r="V77" s="1">
@@ -9188,17 +9175,17 @@
       <c r="Y77" s="1">
         <v>40</v>
       </c>
-      <c r="Z77" s="2">
+      <c r="Z77" s="3">
         <f t="shared" si="15"/>
         <v>190000</v>
       </c>
       <c r="AA77" s="1">
         <v>173</v>
       </c>
-      <c r="AB77" s="2">
+      <c r="AB77" s="3">
         <v>39</v>
       </c>
-      <c r="AC77" s="2">
+      <c r="AC77" s="3">
         <f>AC76+AG76</f>
         <v>11352</v>
       </c>
@@ -9209,137 +9196,137 @@
       <c r="AF77" s="1">
         <v>0</v>
       </c>
-      <c r="AG77" s="2">
+      <c r="AG77" s="3">
         <v>359</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:33">
-      <c r="AG78" s="2">
+      <c r="AG78" s="3">
         <v>367</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:33">
-      <c r="AG79" s="2">
+      <c r="AG79" s="3">
         <v>373</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:33">
-      <c r="AG80" s="2">
+      <c r="AG80" s="3">
         <v>379</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="33:33">
-      <c r="AG81" s="2">
+      <c r="AG81" s="3">
         <v>383</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="33:33">
-      <c r="AG82" s="2">
+      <c r="AG82" s="3">
         <v>389</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="33:33">
-      <c r="AG83" s="2">
+      <c r="AG83" s="3">
         <v>397</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="33:33">
-      <c r="AG84" s="2">
+      <c r="AG84" s="3">
         <v>401</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="33:33">
-      <c r="AG85" s="2">
+      <c r="AG85" s="3">
         <v>409</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="33:33">
-      <c r="AG86" s="2">
+      <c r="AG86" s="3">
         <v>419</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="33:33">
-      <c r="AG87" s="2">
+      <c r="AG87" s="3">
         <v>421</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="33:33">
-      <c r="AG88" s="2">
+      <c r="AG88" s="3">
         <v>431</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="33:33">
-      <c r="AG89" s="2">
+      <c r="AG89" s="3">
         <v>433</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="33:33">
-      <c r="AG90" s="2">
+      <c r="AG90" s="3">
         <v>439</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="33:33">
-      <c r="AG91" s="2">
+      <c r="AG91" s="3">
         <v>443</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="33:33">
-      <c r="AG92" s="2">
+      <c r="AG92" s="3">
         <v>449</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="33:33">
-      <c r="AG93" s="2">
+      <c r="AG93" s="3">
         <v>457</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="33:33">
-      <c r="AG94" s="2">
+      <c r="AG94" s="3">
         <v>461</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="33:33">
-      <c r="AG95" s="2">
+      <c r="AG95" s="3">
         <v>463</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="33:33">
-      <c r="AG96" s="2">
+      <c r="AG96" s="3">
         <v>467</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="33:33">
-      <c r="AG97" s="2">
+      <c r="AG97" s="3">
         <v>479</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="33:33">
-      <c r="AG98" s="2">
+      <c r="AG98" s="3">
         <v>487</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="33:33">
-      <c r="AG99" s="2">
+      <c r="AG99" s="3">
         <v>491</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="33:33">
-      <c r="AG100" s="2">
+      <c r="AG100" s="3">
         <v>499</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="33:33">
-      <c r="AG101" s="2">
+      <c r="AG101" s="3">
         <v>503</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="33:33">
-      <c r="AG102" s="2">
+      <c r="AG102" s="3">
         <v>509</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="33:33">
-      <c r="AG103" s="2">
+      <c r="AG103" s="3">
         <v>509</v>
       </c>
     </row>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -2038,7 +2038,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="I9" s="1">
         <v>120</v>
@@ -2139,7 +2139,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="1">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="I10" s="1">
         <v>200</v>
@@ -2240,7 +2240,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="1">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="I11" s="1">
         <v>300</v>
@@ -2341,7 +2341,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="3">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="I12" s="3">
         <v>490</v>
@@ -2443,7 +2443,7 @@
         <v>8</v>
       </c>
       <c r="H13" s="1">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="I13" s="1">
         <v>700</v>
@@ -2545,7 +2545,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="1">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="I14" s="1">
         <v>1000</v>
@@ -2647,7 +2647,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="1">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="I15" s="1">
         <v>1500</v>
@@ -2749,7 +2749,7 @@
         <v>11</v>
       </c>
       <c r="H16" s="1">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="I16" s="1">
         <v>2400</v>
@@ -2851,7 +2851,7 @@
         <v>12</v>
       </c>
       <c r="H17" s="1">
-        <v>19000</v>
+        <v>25000</v>
       </c>
       <c r="I17" s="1">
         <v>3600</v>
@@ -2953,7 +2953,7 @@
         <v>13</v>
       </c>
       <c r="H18" s="1">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I18" s="1">
         <v>6000</v>
@@ -3055,7 +3055,7 @@
         <v>14</v>
       </c>
       <c r="H19" s="1">
-        <v>34000</v>
+        <v>50000</v>
       </c>
       <c r="I19" s="1">
         <v>9600</v>
@@ -3157,7 +3157,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="1">
-        <v>42000</v>
+        <v>65000</v>
       </c>
       <c r="I20" s="1">
         <v>14000</v>
@@ -3259,7 +3259,7 @@
         <v>16</v>
       </c>
       <c r="H21" s="1">
-        <v>51000</v>
+        <v>80000</v>
       </c>
       <c r="I21" s="1">
         <v>20000</v>
@@ -3361,7 +3361,7 @@
         <v>17</v>
       </c>
       <c r="H22" s="1">
-        <v>61000</v>
+        <v>100000</v>
       </c>
       <c r="I22" s="1">
         <v>27000</v>
@@ -3463,7 +3463,7 @@
         <v>18</v>
       </c>
       <c r="H23" s="1">
-        <v>72000</v>
+        <v>120000</v>
       </c>
       <c r="I23" s="1">
         <v>36000</v>
@@ -3565,7 +3565,7 @@
         <v>19</v>
       </c>
       <c r="H24" s="1">
-        <v>85000</v>
+        <v>150000</v>
       </c>
       <c r="I24" s="1">
         <v>48000</v>
@@ -3667,7 +3667,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="1">
-        <v>100000</v>
+        <v>190000</v>
       </c>
       <c r="I25" s="1">
         <v>63000</v>
@@ -3769,7 +3769,7 @@
         <v>21</v>
       </c>
       <c r="H26" s="1">
-        <v>120000</v>
+        <v>240000</v>
       </c>
       <c r="I26" s="1">
         <v>80000</v>
@@ -3871,7 +3871,7 @@
         <v>22</v>
       </c>
       <c r="H27" s="1">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="I27" s="1">
         <v>100000</v>
@@ -3973,7 +3973,7 @@
         <v>23</v>
       </c>
       <c r="H28" s="1">
-        <v>190000</v>
+        <v>380000</v>
       </c>
       <c r="I28" s="1">
         <v>130000</v>
@@ -4075,7 +4075,7 @@
         <v>24</v>
       </c>
       <c r="H29" s="9">
-        <v>250000</v>
+        <v>500000</v>
       </c>
       <c r="I29" s="9">
         <v>170000</v>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -4177,16 +4177,13 @@
         <v>25</v>
       </c>
       <c r="H30" s="1">
-        <f t="shared" ref="H7:H70" si="11">AG32*Z30*AA30/10</f>
-        <v>2559550</v>
+        <v>650000</v>
       </c>
       <c r="I30" s="1">
-        <f t="shared" ref="I6:I69" si="12">AB30*AG28*Z30/10</f>
-        <v>697200</v>
+        <v>270000</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" ref="J7:J72" si="13">Y30*Z30*AC30</f>
-        <v>94062500</v>
+        <v>15000000</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="0"/>
@@ -4282,16 +4279,13 @@
         <v>26</v>
       </c>
       <c r="H31" s="1">
-        <f t="shared" si="11"/>
-        <v>3124400</v>
+        <v>800000</v>
       </c>
       <c r="I31" s="1">
-        <f t="shared" si="12"/>
-        <v>890000</v>
+        <v>390000</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="13"/>
-        <v>121888000</v>
+        <v>18000000</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" si="0"/>
@@ -4387,16 +4381,13 @@
         <v>27</v>
       </c>
       <c r="H32" s="1">
-        <f t="shared" si="11"/>
-        <v>3874950</v>
+        <v>1000000</v>
       </c>
       <c r="I32" s="1">
-        <f t="shared" si="12"/>
-        <v>1134900</v>
+        <v>500000</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="13"/>
-        <v>154669500</v>
+        <v>22000000</v>
       </c>
       <c r="K32" s="1">
         <f t="shared" si="0"/>
@@ -4492,16 +4483,13 @@
         <v>28</v>
       </c>
       <c r="H33" s="1">
-        <f t="shared" si="11"/>
-        <v>4689500</v>
+        <v>1200000</v>
       </c>
       <c r="I33" s="1">
-        <f t="shared" si="12"/>
-        <v>1363500</v>
+        <v>630000</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" si="13"/>
-        <v>192640000</v>
+        <v>24000000</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" si="0"/>
@@ -4597,16 +4585,13 @@
         <v>29</v>
       </c>
       <c r="H34" s="1">
-        <f t="shared" si="11"/>
-        <v>6781800</v>
+        <v>1500000</v>
       </c>
       <c r="I34" s="1">
-        <f t="shared" si="12"/>
-        <v>1730400</v>
+        <v>800000</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="13"/>
-        <v>258042000</v>
+        <v>27000000</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" si="0"/>
@@ -4702,16 +4687,13 @@
         <v>30</v>
       </c>
       <c r="H35" s="1">
-        <f t="shared" si="11"/>
-        <v>8894900</v>
+        <v>1800000</v>
       </c>
       <c r="I35" s="1">
-        <f t="shared" si="12"/>
-        <v>2172100</v>
+        <v>1000000</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="13"/>
-        <v>334320000</v>
+        <v>30000000</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" si="0"/>
@@ -4807,15 +4789,15 @@
         <v>31</v>
       </c>
       <c r="H36" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="H7:H70" si="11">AG38*Z36*AA36/10</f>
         <v>11069600</v>
       </c>
       <c r="I36" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I6:I69" si="12">AB36*AG34*Z36/10</f>
         <v>2616000</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J7:J72" si="13">Y36*Z36*AC36</f>
         <v>422840000</v>
       </c>
       <c r="K36" s="1">

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -999,10 +999,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1865,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="7">
         <v>10</v>
@@ -1964,12 +1964,13 @@
       <c r="O8" s="1">
         <v>2</v>
       </c>
-      <c r="P8" s="7">
-        <v>3</v>
+      <c r="P8" s="3">
+        <f t="shared" ref="P8:P71" si="6">P7+1</f>
+        <v>2</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" ref="Q8:Q45" si="6">Q7+2</f>
-        <v>12</v>
+        <f t="shared" ref="Q8:Q71" si="7">Q7+1</f>
+        <v>11</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
@@ -2065,12 +2066,13 @@
       <c r="O9" s="1">
         <v>3</v>
       </c>
-      <c r="P9" s="7">
-        <v>4</v>
+      <c r="P9" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="Q9" s="3">
-        <f t="shared" si="6"/>
-        <v>14</v>
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="R9" s="1">
         <v>0</v>
@@ -2166,12 +2168,13 @@
       <c r="O10" s="1">
         <v>4</v>
       </c>
-      <c r="P10" s="7">
-        <v>5</v>
+      <c r="P10" s="3">
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="Q10" s="3">
-        <f t="shared" si="6"/>
-        <v>16</v>
+        <f t="shared" si="7"/>
+        <v>13</v>
       </c>
       <c r="R10" s="1">
         <v>0</v>
@@ -2223,104 +2226,105 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:33">
-      <c r="C11" s="1">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:33">
+      <c r="C11" s="8">
         <v>6</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="8">
         <v>6</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="8">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="8">
         <v>6</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="8">
         <v>2500</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="8">
         <v>300</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="8">
         <v>20000</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="8">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="8">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M11" s="8">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="8">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O11" s="8">
         <v>5</v>
       </c>
-      <c r="P11" s="7">
-        <v>6</v>
-      </c>
-      <c r="Q11" s="3">
+      <c r="P11" s="2">
         <f t="shared" si="6"/>
-        <v>18</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="7">
-        <v>0</v>
-      </c>
-      <c r="U11" s="7">
-        <v>0</v>
-      </c>
-      <c r="V11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="2">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
+      </c>
+      <c r="S11" s="8">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0</v>
+      </c>
+      <c r="V11" s="8">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="W11" s="1">
+      <c r="W11" s="8">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="X11" s="1">
+      <c r="X11" s="8">
         <v>6</v>
       </c>
-      <c r="Y11" s="1">
+      <c r="Y11" s="8">
         <v>6</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="Z11" s="2">
         <f>Z10+20</f>
         <v>200</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="2">
         <v>7</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AB11" s="2">
         <v>5</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AC11" s="2">
         <v>140</v>
       </c>
-      <c r="AD11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="3">
+      <c r="AD11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="8"/>
+      <c r="AF11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="2">
         <v>13</v>
       </c>
     </row>
@@ -2368,12 +2372,13 @@
       <c r="O12" s="1">
         <v>6</v>
       </c>
-      <c r="P12" s="7">
-        <v>7</v>
+      <c r="P12" s="3">
+        <f t="shared" si="6"/>
+        <v>6</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" si="6"/>
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>15</v>
       </c>
       <c r="R12" s="1">
         <v>0</v>
@@ -2412,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="AC12" s="3">
-        <f t="shared" ref="AC8:AC75" si="7">AC11+AG11</f>
+        <f t="shared" ref="AC8:AC75" si="8">AC11+AG11</f>
         <v>153</v>
       </c>
       <c r="AD12" s="1">
@@ -2436,7 +2441,7 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="9" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="1">
@@ -2470,12 +2475,13 @@
       <c r="O13" s="1">
         <v>7</v>
       </c>
-      <c r="P13" s="7">
-        <v>8</v>
+      <c r="P13" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
       </c>
       <c r="Q13" s="3">
-        <f t="shared" si="6"/>
-        <v>22</v>
+        <f t="shared" si="7"/>
+        <v>16</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
@@ -2514,7 +2520,7 @@
         <v>7</v>
       </c>
       <c r="AC13" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>170</v>
       </c>
       <c r="AD13" s="1">
@@ -2572,12 +2578,13 @@
       <c r="O14" s="1">
         <v>8</v>
       </c>
-      <c r="P14" s="7">
-        <v>9</v>
+      <c r="P14" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
-        <f t="shared" si="6"/>
-        <v>24</v>
+        <f t="shared" si="7"/>
+        <v>17</v>
       </c>
       <c r="R14" s="1">
         <v>0</v>
@@ -2616,7 +2623,7 @@
         <v>8</v>
       </c>
       <c r="AC14" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>189</v>
       </c>
       <c r="AD14" s="1">
@@ -2640,7 +2647,7 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G15" s="1">
@@ -2674,12 +2681,13 @@
       <c r="O15" s="1">
         <v>9</v>
       </c>
-      <c r="P15" s="7">
-        <v>10</v>
+      <c r="P15" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
       </c>
       <c r="Q15" s="3">
-        <f t="shared" si="6"/>
-        <v>26</v>
+        <f t="shared" si="7"/>
+        <v>18</v>
       </c>
       <c r="R15" s="1">
         <v>0</v>
@@ -2718,7 +2726,7 @@
         <v>9</v>
       </c>
       <c r="AC15" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>212</v>
       </c>
       <c r="AD15" s="1">
@@ -2776,12 +2784,13 @@
       <c r="O16" s="1">
         <v>10</v>
       </c>
-      <c r="P16" s="7">
-        <v>11</v>
+      <c r="P16" s="3">
+        <f t="shared" si="6"/>
+        <v>10</v>
       </c>
       <c r="Q16" s="3">
-        <f t="shared" si="6"/>
-        <v>28</v>
+        <f t="shared" si="7"/>
+        <v>19</v>
       </c>
       <c r="R16" s="1">
         <v>0</v>
@@ -2820,7 +2829,7 @@
         <v>10</v>
       </c>
       <c r="AC16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>241</v>
       </c>
       <c r="AD16" s="1">
@@ -2834,105 +2843,106 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:33">
-      <c r="C17" s="1">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="C17" s="8">
         <v>12</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="8">
         <v>12</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="8">
         <v>1</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="8">
         <v>12</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="8">
         <v>25000</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="8">
         <v>3600</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="8">
         <v>300000</v>
       </c>
-      <c r="K17" s="1">
+      <c r="K17" s="8">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17" s="8">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M17" s="8">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="8">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O17" s="8">
         <v>11</v>
       </c>
-      <c r="P17" s="7">
-        <v>12</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="P17" s="2">
         <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="7">
-        <v>0</v>
-      </c>
-      <c r="U17" s="7">
-        <v>0</v>
-      </c>
-      <c r="V17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="2">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
+      </c>
+      <c r="S17" s="8">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0</v>
+      </c>
+      <c r="V17" s="8">
         <f t="shared" si="4"/>
         <v>120</v>
       </c>
-      <c r="W17" s="1">
+      <c r="W17" s="8">
         <f t="shared" si="5"/>
         <v>120</v>
       </c>
-      <c r="X17" s="1">
+      <c r="X17" s="8">
         <v>12</v>
       </c>
-      <c r="Y17" s="1">
+      <c r="Y17" s="8">
         <v>12</v>
       </c>
-      <c r="Z17" s="3">
-        <f t="shared" ref="Z17:Z22" si="8">Z16+100</f>
+      <c r="Z17" s="2">
+        <f t="shared" ref="Z17:Z22" si="9">Z16+100</f>
         <v>500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="2">
         <v>17</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AB17" s="2">
         <v>11</v>
       </c>
-      <c r="AC17" s="3">
-        <f t="shared" si="7"/>
+      <c r="AC17" s="2">
+        <f t="shared" si="8"/>
         <v>272</v>
       </c>
-      <c r="AD17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AD17" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="8"/>
+      <c r="AF17" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="2">
         <v>37</v>
       </c>
     </row>
@@ -2946,7 +2956,7 @@
       <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="9" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="1">
@@ -2980,12 +2990,13 @@
       <c r="O18" s="1">
         <v>12</v>
       </c>
-      <c r="P18" s="7">
-        <v>13</v>
+      <c r="P18" s="3">
+        <f t="shared" si="6"/>
+        <v>12</v>
       </c>
       <c r="Q18" s="3">
-        <f t="shared" si="6"/>
-        <v>32</v>
+        <f t="shared" si="7"/>
+        <v>21</v>
       </c>
       <c r="R18" s="1">
         <v>0</v>
@@ -3014,7 +3025,7 @@
         <v>13</v>
       </c>
       <c r="Z18" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>600</v>
       </c>
       <c r="AA18" s="3">
@@ -3024,7 +3035,7 @@
         <v>12</v>
       </c>
       <c r="AC18" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>309</v>
       </c>
       <c r="AD18" s="1">
@@ -3082,12 +3093,13 @@
       <c r="O19" s="1">
         <v>13</v>
       </c>
-      <c r="P19" s="7">
-        <v>14</v>
+      <c r="P19" s="3">
+        <f t="shared" si="6"/>
+        <v>13</v>
       </c>
       <c r="Q19" s="3">
-        <f t="shared" si="6"/>
-        <v>34</v>
+        <f t="shared" si="7"/>
+        <v>22</v>
       </c>
       <c r="R19" s="1">
         <v>0</v>
@@ -3116,7 +3128,7 @@
         <v>14</v>
       </c>
       <c r="Z19" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>700</v>
       </c>
       <c r="AA19" s="3">
@@ -3126,7 +3138,7 @@
         <v>13</v>
       </c>
       <c r="AC19" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>350</v>
       </c>
       <c r="AD19" s="1">
@@ -3184,12 +3196,13 @@
       <c r="O20" s="1">
         <v>14</v>
       </c>
-      <c r="P20" s="7">
-        <v>15</v>
+      <c r="P20" s="3">
+        <f t="shared" si="6"/>
+        <v>14</v>
       </c>
       <c r="Q20" s="3">
-        <f t="shared" si="6"/>
-        <v>36</v>
+        <f t="shared" si="7"/>
+        <v>23</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -3218,7 +3231,7 @@
         <v>15</v>
       </c>
       <c r="Z20" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>800</v>
       </c>
       <c r="AA20" s="3">
@@ -3228,7 +3241,7 @@
         <v>14</v>
       </c>
       <c r="AC20" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>393</v>
       </c>
       <c r="AD20" s="1">
@@ -3286,12 +3299,13 @@
       <c r="O21" s="1">
         <v>15</v>
       </c>
-      <c r="P21" s="7">
-        <v>16</v>
+      <c r="P21" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
       </c>
       <c r="Q21" s="3">
-        <f t="shared" si="6"/>
-        <v>38</v>
+        <f t="shared" si="7"/>
+        <v>24</v>
       </c>
       <c r="R21" s="1">
         <v>0</v>
@@ -3320,7 +3334,7 @@
         <v>16</v>
       </c>
       <c r="Z21" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>900</v>
       </c>
       <c r="AA21" s="3">
@@ -3330,7 +3344,7 @@
         <v>15</v>
       </c>
       <c r="AC21" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>440</v>
       </c>
       <c r="AD21" s="1">
@@ -3388,12 +3402,13 @@
       <c r="O22" s="1">
         <v>16</v>
       </c>
-      <c r="P22" s="7">
-        <v>17</v>
+      <c r="P22" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" si="6"/>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="R22" s="1">
         <v>0</v>
@@ -3422,7 +3437,7 @@
         <v>17</v>
       </c>
       <c r="Z22" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="AA22" s="3">
@@ -3432,7 +3447,7 @@
         <v>16</v>
       </c>
       <c r="AC22" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>493</v>
       </c>
       <c r="AD22" s="1">
@@ -3446,105 +3461,106 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:33">
-      <c r="C23" s="1">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="C23" s="8">
         <v>18</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="8">
         <v>18</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="8">
         <v>1</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="8">
         <v>18</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="8">
         <v>120000</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="8">
         <v>36000</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="8">
         <v>2550000</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="8">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23" s="8">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="M23" s="1">
+      <c r="M23" s="8">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23" s="8">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O23" s="1">
+      <c r="O23" s="8">
         <v>17</v>
       </c>
-      <c r="P23" s="7">
-        <v>18</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="P23" s="2">
         <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
-      <c r="S23" s="1">
-        <v>0</v>
-      </c>
-      <c r="T23" s="7">
-        <v>0</v>
-      </c>
-      <c r="U23" s="7">
-        <v>0</v>
-      </c>
-      <c r="V23" s="1">
+        <v>17</v>
+      </c>
+      <c r="Q23" s="2">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="R23" s="8">
+        <v>0</v>
+      </c>
+      <c r="S23" s="8">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2">
+        <v>0</v>
+      </c>
+      <c r="V23" s="8">
         <f t="shared" si="4"/>
         <v>180</v>
       </c>
-      <c r="W23" s="1">
+      <c r="W23" s="8">
         <f t="shared" si="5"/>
         <v>180</v>
       </c>
-      <c r="X23" s="1">
+      <c r="X23" s="8">
         <v>18</v>
       </c>
-      <c r="Y23" s="1">
+      <c r="Y23" s="8">
         <v>18</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="2">
         <f>Z22+200</f>
         <v>1200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AA23" s="2">
         <v>41</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AB23" s="2">
         <v>17</v>
       </c>
-      <c r="AC23" s="3">
-        <f t="shared" si="7"/>
+      <c r="AC23" s="2">
+        <f t="shared" si="8"/>
         <v>552</v>
       </c>
-      <c r="AD23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AD23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="8"/>
+      <c r="AF23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="2">
         <v>61</v>
       </c>
     </row>
@@ -3592,12 +3608,13 @@
       <c r="O24" s="1">
         <v>18</v>
       </c>
-      <c r="P24" s="7">
-        <v>19</v>
+      <c r="P24" s="3">
+        <f t="shared" si="6"/>
+        <v>18</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" si="6"/>
-        <v>44</v>
+        <f t="shared" si="7"/>
+        <v>27</v>
       </c>
       <c r="R24" s="1">
         <v>0</v>
@@ -3636,7 +3653,7 @@
         <v>18</v>
       </c>
       <c r="AC24" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>613</v>
       </c>
       <c r="AD24" s="1">
@@ -3694,12 +3711,13 @@
       <c r="O25" s="1">
         <v>19</v>
       </c>
-      <c r="P25" s="7">
-        <v>20</v>
+      <c r="P25" s="3">
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="Q25" s="3">
-        <f t="shared" si="6"/>
-        <v>46</v>
+        <f t="shared" si="7"/>
+        <v>28</v>
       </c>
       <c r="R25" s="1">
         <v>0</v>
@@ -3738,7 +3756,7 @@
         <v>19</v>
       </c>
       <c r="AC25" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>680</v>
       </c>
       <c r="AD25" s="1">
@@ -3796,12 +3814,13 @@
       <c r="O26" s="1">
         <v>20</v>
       </c>
-      <c r="P26" s="7">
-        <v>21</v>
+      <c r="P26" s="3">
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="Q26" s="3">
-        <f t="shared" si="6"/>
-        <v>48</v>
+        <f t="shared" si="7"/>
+        <v>29</v>
       </c>
       <c r="R26" s="1">
         <v>0</v>
@@ -3840,7 +3859,7 @@
         <v>20</v>
       </c>
       <c r="AC26" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>751</v>
       </c>
       <c r="AD26" s="1">
@@ -3898,12 +3917,13 @@
       <c r="O27" s="1">
         <v>21</v>
       </c>
-      <c r="P27" s="7">
-        <v>22</v>
+      <c r="P27" s="3">
+        <f t="shared" si="6"/>
+        <v>21</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" si="6"/>
-        <v>50</v>
+        <f t="shared" si="7"/>
+        <v>30</v>
       </c>
       <c r="R27" s="1">
         <v>0</v>
@@ -3942,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="AC27" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>824</v>
       </c>
       <c r="AD27" s="1">
@@ -3966,7 +3986,7 @@
       <c r="E28" s="1">
         <v>1</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="9" t="s">
         <v>57</v>
       </c>
       <c r="G28" s="1">
@@ -4000,12 +4020,13 @@
       <c r="O28" s="1">
         <v>22</v>
       </c>
-      <c r="P28" s="7">
-        <v>23</v>
+      <c r="P28" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
       </c>
       <c r="Q28" s="3">
-        <f t="shared" ref="Q28:Q77" si="9">Q27+3</f>
-        <v>53</v>
+        <f t="shared" si="7"/>
+        <v>31</v>
       </c>
       <c r="R28" s="1">
         <v>0</v>
@@ -4044,7 +4065,7 @@
         <v>22</v>
       </c>
       <c r="AC28" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>903</v>
       </c>
       <c r="AD28" s="1">
@@ -4059,60 +4080,61 @@
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:33">
-      <c r="C29" s="9">
+      <c r="C29" s="8">
         <v>24</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>24</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <v>1</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="8">
         <v>24</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="8">
         <v>500000</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="8">
         <v>170000</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="8">
         <v>12000000</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="8">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="8">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="8">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="8">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="O29" s="9">
+      <c r="O29" s="8">
         <v>23</v>
       </c>
       <c r="P29" s="2">
-        <v>24</v>
+        <f t="shared" si="6"/>
+        <v>23</v>
       </c>
       <c r="Q29" s="2">
-        <f t="shared" si="9"/>
-        <v>56</v>
-      </c>
-      <c r="R29" s="9">
-        <v>0</v>
-      </c>
-      <c r="S29" s="9">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="R29" s="8">
+        <v>0</v>
+      </c>
+      <c r="S29" s="8">
         <v>0</v>
       </c>
       <c r="T29" s="2">
@@ -4121,18 +4143,18 @@
       <c r="U29" s="2">
         <v>0</v>
       </c>
-      <c r="V29" s="9">
+      <c r="V29" s="8">
         <f t="shared" si="4"/>
         <v>240</v>
       </c>
-      <c r="W29" s="9">
+      <c r="W29" s="8">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
-      <c r="X29" s="9">
+      <c r="X29" s="8">
         <v>24</v>
       </c>
-      <c r="Y29" s="9">
+      <c r="Y29" s="8">
         <v>24</v>
       </c>
       <c r="Z29" s="2">
@@ -4146,14 +4168,14 @@
         <v>23</v>
       </c>
       <c r="AC29" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>986</v>
       </c>
-      <c r="AD29" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="9"/>
-      <c r="AF29" s="9">
+      <c r="AD29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="8"/>
+      <c r="AF29" s="8">
         <v>0</v>
       </c>
       <c r="AG29" s="2">
@@ -4204,12 +4226,13 @@
       <c r="O30" s="1">
         <v>24</v>
       </c>
-      <c r="P30" s="7">
-        <v>25</v>
+      <c r="P30" s="3">
+        <f t="shared" si="6"/>
+        <v>24</v>
       </c>
       <c r="Q30" s="3">
-        <f t="shared" si="9"/>
-        <v>59</v>
+        <f t="shared" si="7"/>
+        <v>33</v>
       </c>
       <c r="R30" s="1">
         <v>0</v>
@@ -4248,7 +4271,7 @@
         <v>24</v>
       </c>
       <c r="AC30" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1075</v>
       </c>
       <c r="AD30" s="1">
@@ -4306,12 +4329,13 @@
       <c r="O31" s="1">
         <v>25</v>
       </c>
-      <c r="P31" s="7">
-        <v>26</v>
+      <c r="P31" s="3">
+        <f t="shared" si="6"/>
+        <v>25</v>
       </c>
       <c r="Q31" s="3">
-        <f t="shared" si="9"/>
-        <v>62</v>
+        <f t="shared" si="7"/>
+        <v>34</v>
       </c>
       <c r="R31" s="1">
         <v>0</v>
@@ -4350,7 +4374,7 @@
         <v>25</v>
       </c>
       <c r="AC31" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1172</v>
       </c>
       <c r="AD31" s="1">
@@ -4408,12 +4432,13 @@
       <c r="O32" s="1">
         <v>26</v>
       </c>
-      <c r="P32" s="7">
-        <v>27</v>
+      <c r="P32" s="3">
+        <f t="shared" si="6"/>
+        <v>26</v>
       </c>
       <c r="Q32" s="3">
-        <f t="shared" si="9"/>
-        <v>65</v>
+        <f t="shared" si="7"/>
+        <v>35</v>
       </c>
       <c r="R32" s="1">
         <v>0</v>
@@ -4452,7 +4477,7 @@
         <v>26</v>
       </c>
       <c r="AC32" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1273</v>
       </c>
       <c r="AD32" s="1">
@@ -4510,12 +4535,13 @@
       <c r="O33" s="1">
         <v>27</v>
       </c>
-      <c r="P33" s="7">
-        <v>28</v>
+      <c r="P33" s="3">
+        <f t="shared" si="6"/>
+        <v>27</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" si="9"/>
-        <v>68</v>
+        <f t="shared" si="7"/>
+        <v>36</v>
       </c>
       <c r="R33" s="1">
         <v>0</v>
@@ -4554,7 +4580,7 @@
         <v>27</v>
       </c>
       <c r="AC33" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1376</v>
       </c>
       <c r="AD33" s="1">
@@ -4612,12 +4638,13 @@
       <c r="O34" s="1">
         <v>28</v>
       </c>
-      <c r="P34" s="7">
-        <v>29</v>
+      <c r="P34" s="3">
+        <f t="shared" si="6"/>
+        <v>28</v>
       </c>
       <c r="Q34" s="3">
-        <f t="shared" si="9"/>
-        <v>71</v>
+        <f t="shared" si="7"/>
+        <v>37</v>
       </c>
       <c r="R34" s="1">
         <v>0</v>
@@ -4656,7 +4683,7 @@
         <v>28</v>
       </c>
       <c r="AC34" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1483</v>
       </c>
       <c r="AD34" s="1">
@@ -4670,105 +4697,106 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:33">
-      <c r="C35" s="1">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:33">
+      <c r="C35" s="8">
         <v>30</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="8">
         <v>30</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="8">
         <v>1</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" s="8">
         <v>30</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="8">
         <v>1800000</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35" s="8">
         <v>1000000</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="8">
         <v>30000000</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K35" s="8">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35" s="8">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="M35" s="1">
+      <c r="M35" s="8">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="N35" s="1">
+      <c r="N35" s="8">
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
-      <c r="O35" s="1">
+      <c r="O35" s="8">
         <v>29</v>
       </c>
-      <c r="P35" s="7">
-        <v>30</v>
-      </c>
-      <c r="Q35" s="3">
-        <f t="shared" si="9"/>
-        <v>74</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1">
-        <v>0</v>
-      </c>
-      <c r="T35" s="7">
-        <v>0</v>
-      </c>
-      <c r="U35" s="7">
-        <v>0</v>
-      </c>
-      <c r="V35" s="1">
+      <c r="P35" s="2">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+      <c r="Q35" s="2">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="R35" s="8">
+        <v>0</v>
+      </c>
+      <c r="S35" s="8">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2">
+        <v>0</v>
+      </c>
+      <c r="U35" s="2">
+        <v>0</v>
+      </c>
+      <c r="V35" s="8">
         <f t="shared" si="4"/>
         <v>300</v>
       </c>
-      <c r="W35" s="1">
+      <c r="W35" s="8">
         <f t="shared" si="5"/>
         <v>300</v>
       </c>
-      <c r="X35" s="1">
+      <c r="X35" s="8">
         <v>30</v>
       </c>
-      <c r="Y35" s="1">
+      <c r="Y35" s="8">
         <v>30</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="2">
         <f>Z34+1000</f>
         <v>7000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="2">
         <v>97</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AB35" s="2">
         <v>29</v>
       </c>
-      <c r="AC35" s="3">
-        <f t="shared" si="7"/>
+      <c r="AC35" s="2">
+        <f t="shared" si="8"/>
         <v>1592</v>
       </c>
-      <c r="AD35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="1"/>
-      <c r="AF35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AD35" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="8"/>
+      <c r="AF35" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="2">
         <v>113</v>
       </c>
     </row>
@@ -4819,12 +4847,13 @@
       <c r="O36" s="1">
         <v>30</v>
       </c>
-      <c r="P36" s="7">
-        <v>31</v>
+      <c r="P36" s="3">
+        <f t="shared" si="6"/>
+        <v>30</v>
       </c>
       <c r="Q36" s="3">
-        <f t="shared" si="9"/>
-        <v>77</v>
+        <f t="shared" si="7"/>
+        <v>39</v>
       </c>
       <c r="R36" s="1">
         <v>0</v>
@@ -4863,7 +4892,7 @@
         <v>30</v>
       </c>
       <c r="AC36" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1705</v>
       </c>
       <c r="AD36" s="1">
@@ -4924,12 +4953,13 @@
       <c r="O37" s="1">
         <v>31</v>
       </c>
-      <c r="P37" s="7">
-        <v>32</v>
+      <c r="P37" s="3">
+        <f t="shared" si="6"/>
+        <v>31</v>
       </c>
       <c r="Q37" s="3">
-        <f t="shared" si="9"/>
-        <v>80</v>
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
       <c r="R37" s="1">
         <v>0</v>
@@ -4968,7 +4998,7 @@
         <v>31</v>
       </c>
       <c r="AC37" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1832</v>
       </c>
       <c r="AD37" s="1">
@@ -5029,12 +5059,13 @@
       <c r="O38" s="1">
         <v>32</v>
       </c>
-      <c r="P38" s="7">
-        <v>33</v>
+      <c r="P38" s="3">
+        <f t="shared" si="6"/>
+        <v>32</v>
       </c>
       <c r="Q38" s="3">
-        <f t="shared" si="9"/>
-        <v>83</v>
+        <f t="shared" si="7"/>
+        <v>41</v>
       </c>
       <c r="R38" s="1">
         <v>0</v>
@@ -5073,7 +5104,7 @@
         <v>32</v>
       </c>
       <c r="AC38" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1963</v>
       </c>
       <c r="AD38" s="1">
@@ -5134,12 +5165,13 @@
       <c r="O39" s="1">
         <v>33</v>
       </c>
-      <c r="P39" s="7">
-        <v>34</v>
+      <c r="P39" s="3">
+        <f t="shared" si="6"/>
+        <v>33</v>
       </c>
       <c r="Q39" s="3">
-        <f t="shared" si="9"/>
-        <v>86</v>
+        <f t="shared" si="7"/>
+        <v>42</v>
       </c>
       <c r="R39" s="1">
         <v>0</v>
@@ -5178,7 +5210,7 @@
         <v>33</v>
       </c>
       <c r="AC39" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2100</v>
       </c>
       <c r="AD39" s="1">
@@ -5239,12 +5271,13 @@
       <c r="O40" s="1">
         <v>34</v>
       </c>
-      <c r="P40" s="7">
-        <v>35</v>
+      <c r="P40" s="3">
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="Q40" s="3">
-        <f t="shared" si="9"/>
-        <v>89</v>
+        <f t="shared" si="7"/>
+        <v>43</v>
       </c>
       <c r="R40" s="1">
         <v>0</v>
@@ -5283,7 +5316,7 @@
         <v>34</v>
       </c>
       <c r="AC40" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2239</v>
       </c>
       <c r="AD40" s="1">
@@ -5345,12 +5378,13 @@
       <c r="O41" s="1">
         <v>35</v>
       </c>
-      <c r="P41" s="7">
-        <v>36</v>
+      <c r="P41" s="3">
+        <f t="shared" si="6"/>
+        <v>35</v>
       </c>
       <c r="Q41" s="3">
-        <f t="shared" si="9"/>
-        <v>92</v>
+        <f t="shared" si="7"/>
+        <v>44</v>
       </c>
       <c r="R41" s="1">
         <v>0</v>
@@ -5389,7 +5423,7 @@
         <v>35</v>
       </c>
       <c r="AC41" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2388</v>
       </c>
       <c r="AD41" s="1">
@@ -5413,7 +5447,7 @@
       <c r="E42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G42" s="1">
@@ -5450,12 +5484,13 @@
       <c r="O42" s="1">
         <v>36</v>
       </c>
-      <c r="P42" s="7">
-        <v>37</v>
+      <c r="P42" s="3">
+        <f t="shared" si="6"/>
+        <v>36</v>
       </c>
       <c r="Q42" s="3">
-        <f t="shared" si="9"/>
-        <v>95</v>
+        <f t="shared" si="7"/>
+        <v>45</v>
       </c>
       <c r="R42" s="1">
         <v>0</v>
@@ -5494,7 +5529,7 @@
         <v>36</v>
       </c>
       <c r="AC42" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2539</v>
       </c>
       <c r="AD42" s="1">
@@ -5555,12 +5590,13 @@
       <c r="O43" s="1">
         <v>37</v>
       </c>
-      <c r="P43" s="7">
-        <v>38</v>
+      <c r="P43" s="3">
+        <f t="shared" si="6"/>
+        <v>37</v>
       </c>
       <c r="Q43" s="3">
-        <f t="shared" si="9"/>
-        <v>98</v>
+        <f t="shared" si="7"/>
+        <v>46</v>
       </c>
       <c r="R43" s="1">
         <v>0</v>
@@ -5599,7 +5635,7 @@
         <v>37</v>
       </c>
       <c r="AC43" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2696</v>
       </c>
       <c r="AD43" s="1">
@@ -5623,7 +5659,7 @@
       <c r="E44" s="1">
         <v>1</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="G44" s="1">
@@ -5660,12 +5696,13 @@
       <c r="O44" s="1">
         <v>38</v>
       </c>
-      <c r="P44" s="7">
-        <v>39</v>
+      <c r="P44" s="3">
+        <f t="shared" si="6"/>
+        <v>38</v>
       </c>
       <c r="Q44" s="3">
-        <f t="shared" si="9"/>
-        <v>101</v>
+        <f t="shared" si="7"/>
+        <v>47</v>
       </c>
       <c r="R44" s="1">
         <v>0</v>
@@ -5704,7 +5741,7 @@
         <v>38</v>
       </c>
       <c r="AC44" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2859</v>
       </c>
       <c r="AD44" s="1">
@@ -5765,12 +5802,13 @@
       <c r="O45" s="1">
         <v>39</v>
       </c>
-      <c r="P45" s="7">
-        <v>40</v>
+      <c r="P45" s="3">
+        <f t="shared" si="6"/>
+        <v>39</v>
       </c>
       <c r="Q45" s="3">
-        <f t="shared" si="9"/>
-        <v>104</v>
+        <f t="shared" si="7"/>
+        <v>48</v>
       </c>
       <c r="R45" s="1">
         <v>0</v>
@@ -5809,7 +5847,7 @@
         <v>39</v>
       </c>
       <c r="AC45" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3026</v>
       </c>
       <c r="AD45" s="1">
@@ -5870,12 +5908,13 @@
       <c r="O46" s="1">
         <v>40</v>
       </c>
-      <c r="P46" s="7">
-        <v>41</v>
+      <c r="P46" s="3">
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="Q46" s="3">
-        <f t="shared" si="9"/>
-        <v>107</v>
+        <f t="shared" si="7"/>
+        <v>49</v>
       </c>
       <c r="R46" s="1">
         <v>0</v>
@@ -5914,7 +5953,7 @@
         <v>39</v>
       </c>
       <c r="AC46" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3199</v>
       </c>
       <c r="AD46" s="1">
@@ -5937,7 +5976,7 @@
       <c r="E47" s="1">
         <v>1</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="9" t="s">
         <v>76</v>
       </c>
       <c r="G47" s="1">
@@ -5974,12 +6013,13 @@
       <c r="O47" s="1">
         <v>41</v>
       </c>
-      <c r="P47" s="7">
-        <v>42</v>
+      <c r="P47" s="3">
+        <f t="shared" si="6"/>
+        <v>41</v>
       </c>
       <c r="Q47" s="3">
-        <f t="shared" si="9"/>
-        <v>110</v>
+        <f t="shared" si="7"/>
+        <v>50</v>
       </c>
       <c r="R47" s="1">
         <v>0</v>
@@ -6018,7 +6058,7 @@
         <v>39</v>
       </c>
       <c r="AC47" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3378</v>
       </c>
       <c r="AD47" s="1">
@@ -6079,12 +6119,13 @@
       <c r="O48" s="1">
         <v>42</v>
       </c>
-      <c r="P48" s="7">
-        <v>43</v>
+      <c r="P48" s="3">
+        <f t="shared" si="6"/>
+        <v>42</v>
       </c>
       <c r="Q48" s="3">
-        <f t="shared" si="9"/>
-        <v>113</v>
+        <f t="shared" si="7"/>
+        <v>51</v>
       </c>
       <c r="R48" s="1">
         <v>0</v>
@@ -6123,7 +6164,7 @@
         <v>39</v>
       </c>
       <c r="AC48" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3559</v>
       </c>
       <c r="AD48" s="1">
@@ -6184,12 +6225,13 @@
       <c r="O49" s="1">
         <v>43</v>
       </c>
-      <c r="P49" s="7">
-        <v>44</v>
+      <c r="P49" s="3">
+        <f t="shared" si="6"/>
+        <v>43</v>
       </c>
       <c r="Q49" s="3">
-        <f t="shared" si="9"/>
-        <v>116</v>
+        <f t="shared" si="7"/>
+        <v>52</v>
       </c>
       <c r="R49" s="1">
         <v>0</v>
@@ -6228,7 +6270,7 @@
         <v>39</v>
       </c>
       <c r="AC49" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3750</v>
       </c>
       <c r="AD49" s="1">
@@ -6289,12 +6331,13 @@
       <c r="O50" s="1">
         <v>44</v>
       </c>
-      <c r="P50" s="7">
-        <v>45</v>
+      <c r="P50" s="3">
+        <f t="shared" si="6"/>
+        <v>44</v>
       </c>
       <c r="Q50" s="3">
-        <f t="shared" si="9"/>
-        <v>119</v>
+        <f t="shared" si="7"/>
+        <v>53</v>
       </c>
       <c r="R50" s="1">
         <v>0</v>
@@ -6333,7 +6376,7 @@
         <v>39</v>
       </c>
       <c r="AC50" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3943</v>
       </c>
       <c r="AD50" s="1">
@@ -6394,12 +6437,13 @@
       <c r="O51" s="1">
         <v>45</v>
       </c>
-      <c r="P51" s="7">
-        <v>46</v>
+      <c r="P51" s="3">
+        <f t="shared" si="6"/>
+        <v>45</v>
       </c>
       <c r="Q51" s="3">
-        <f t="shared" si="9"/>
-        <v>122</v>
+        <f t="shared" si="7"/>
+        <v>54</v>
       </c>
       <c r="R51" s="1">
         <v>0</v>
@@ -6438,7 +6482,7 @@
         <v>39</v>
       </c>
       <c r="AC51" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4140</v>
       </c>
       <c r="AD51" s="1">
@@ -6499,12 +6543,13 @@
       <c r="O52" s="1">
         <v>46</v>
       </c>
-      <c r="P52" s="7">
-        <v>47</v>
+      <c r="P52" s="3">
+        <f t="shared" si="6"/>
+        <v>46</v>
       </c>
       <c r="Q52" s="3">
-        <f t="shared" si="9"/>
-        <v>125</v>
+        <f t="shared" si="7"/>
+        <v>55</v>
       </c>
       <c r="R52" s="1">
         <v>0</v>
@@ -6543,7 +6588,7 @@
         <v>39</v>
       </c>
       <c r="AC52" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4339</v>
       </c>
       <c r="AD52" s="1">
@@ -6604,12 +6649,13 @@
       <c r="O53" s="1">
         <v>47</v>
       </c>
-      <c r="P53" s="7">
-        <v>48</v>
+      <c r="P53" s="3">
+        <f t="shared" si="6"/>
+        <v>47</v>
       </c>
       <c r="Q53" s="3">
-        <f t="shared" si="9"/>
-        <v>128</v>
+        <f t="shared" si="7"/>
+        <v>56</v>
       </c>
       <c r="R53" s="1">
         <v>0</v>
@@ -6648,7 +6694,7 @@
         <v>39</v>
       </c>
       <c r="AC53" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4550</v>
       </c>
       <c r="AD53" s="1">
@@ -6709,12 +6755,13 @@
       <c r="O54" s="1">
         <v>48</v>
       </c>
-      <c r="P54" s="7">
-        <v>49</v>
+      <c r="P54" s="3">
+        <f t="shared" si="6"/>
+        <v>48</v>
       </c>
       <c r="Q54" s="3">
-        <f t="shared" si="9"/>
-        <v>131</v>
+        <f t="shared" si="7"/>
+        <v>57</v>
       </c>
       <c r="R54" s="1">
         <v>0</v>
@@ -6753,7 +6800,7 @@
         <v>39</v>
       </c>
       <c r="AC54" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4773</v>
       </c>
       <c r="AD54" s="1">
@@ -6814,12 +6861,13 @@
       <c r="O55" s="1">
         <v>49</v>
       </c>
-      <c r="P55" s="7">
-        <v>50</v>
+      <c r="P55" s="3">
+        <f t="shared" si="6"/>
+        <v>49</v>
       </c>
       <c r="Q55" s="3">
-        <f t="shared" si="9"/>
-        <v>134</v>
+        <f t="shared" si="7"/>
+        <v>58</v>
       </c>
       <c r="R55" s="1">
         <v>0</v>
@@ -6858,7 +6906,7 @@
         <v>39</v>
       </c>
       <c r="AC55" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5000</v>
       </c>
       <c r="AD55" s="1">
@@ -6919,12 +6967,13 @@
       <c r="O56" s="1">
         <v>50</v>
       </c>
-      <c r="P56" s="7">
-        <v>51</v>
+      <c r="P56" s="3">
+        <f t="shared" si="6"/>
+        <v>50</v>
       </c>
       <c r="Q56" s="3">
-        <f t="shared" si="9"/>
-        <v>137</v>
+        <f t="shared" si="7"/>
+        <v>59</v>
       </c>
       <c r="R56" s="1">
         <v>0</v>
@@ -6963,7 +7012,7 @@
         <v>39</v>
       </c>
       <c r="AC56" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5229</v>
       </c>
       <c r="AD56" s="1">
@@ -7024,12 +7073,13 @@
       <c r="O57" s="1">
         <v>51</v>
       </c>
-      <c r="P57" s="7">
-        <v>52</v>
+      <c r="P57" s="3">
+        <f t="shared" si="6"/>
+        <v>51</v>
       </c>
       <c r="Q57" s="3">
-        <f t="shared" si="9"/>
-        <v>140</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="R57" s="1">
         <v>0</v>
@@ -7068,7 +7118,7 @@
         <v>39</v>
       </c>
       <c r="AC57" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5462</v>
       </c>
       <c r="AD57" s="1">
@@ -7129,12 +7179,13 @@
       <c r="O58" s="1">
         <v>52</v>
       </c>
-      <c r="P58" s="7">
-        <v>53</v>
+      <c r="P58" s="3">
+        <f t="shared" si="6"/>
+        <v>52</v>
       </c>
       <c r="Q58" s="3">
-        <f t="shared" si="9"/>
-        <v>143</v>
+        <f t="shared" si="7"/>
+        <v>61</v>
       </c>
       <c r="R58" s="1">
         <v>0</v>
@@ -7173,7 +7224,7 @@
         <v>39</v>
       </c>
       <c r="AC58" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5701</v>
       </c>
       <c r="AD58" s="1">
@@ -7234,12 +7285,13 @@
       <c r="O59" s="1">
         <v>53</v>
       </c>
-      <c r="P59" s="7">
-        <v>54</v>
+      <c r="P59" s="3">
+        <f t="shared" si="6"/>
+        <v>53</v>
       </c>
       <c r="Q59" s="3">
-        <f t="shared" si="9"/>
-        <v>146</v>
+        <f t="shared" si="7"/>
+        <v>62</v>
       </c>
       <c r="R59" s="1">
         <v>0</v>
@@ -7278,7 +7330,7 @@
         <v>39</v>
       </c>
       <c r="AC59" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5942</v>
       </c>
       <c r="AD59" s="1">
@@ -7339,12 +7391,13 @@
       <c r="O60" s="1">
         <v>54</v>
       </c>
-      <c r="P60" s="7">
-        <v>55</v>
+      <c r="P60" s="3">
+        <f t="shared" si="6"/>
+        <v>54</v>
       </c>
       <c r="Q60" s="3">
-        <f t="shared" si="9"/>
-        <v>149</v>
+        <f t="shared" si="7"/>
+        <v>63</v>
       </c>
       <c r="R60" s="1">
         <v>0</v>
@@ -7383,7 +7436,7 @@
         <v>39</v>
       </c>
       <c r="AC60" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6193</v>
       </c>
       <c r="AD60" s="1">
@@ -7444,12 +7497,13 @@
       <c r="O61" s="1">
         <v>55</v>
       </c>
-      <c r="P61" s="7">
-        <v>56</v>
+      <c r="P61" s="3">
+        <f t="shared" si="6"/>
+        <v>55</v>
       </c>
       <c r="Q61" s="3">
-        <f t="shared" si="9"/>
-        <v>152</v>
+        <f t="shared" si="7"/>
+        <v>64</v>
       </c>
       <c r="R61" s="1">
         <v>0</v>
@@ -7488,7 +7542,7 @@
         <v>39</v>
       </c>
       <c r="AC61" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6450</v>
       </c>
       <c r="AD61" s="1">
@@ -7549,12 +7603,13 @@
       <c r="O62" s="1">
         <v>56</v>
       </c>
-      <c r="P62" s="7">
-        <v>57</v>
+      <c r="P62" s="3">
+        <f t="shared" si="6"/>
+        <v>56</v>
       </c>
       <c r="Q62" s="3">
-        <f t="shared" si="9"/>
-        <v>155</v>
+        <f t="shared" si="7"/>
+        <v>65</v>
       </c>
       <c r="R62" s="1">
         <v>0</v>
@@ -7593,7 +7648,7 @@
         <v>39</v>
       </c>
       <c r="AC62" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6713</v>
       </c>
       <c r="AD62" s="1">
@@ -7617,7 +7672,7 @@
       <c r="E63" s="1">
         <v>1</v>
       </c>
-      <c r="F63" s="8" t="s">
+      <c r="F63" s="9" t="s">
         <v>92</v>
       </c>
       <c r="G63" s="1">
@@ -7654,12 +7709,13 @@
       <c r="O63" s="1">
         <v>57</v>
       </c>
-      <c r="P63" s="7">
-        <v>58</v>
+      <c r="P63" s="3">
+        <f t="shared" si="6"/>
+        <v>57</v>
       </c>
       <c r="Q63" s="3">
-        <f t="shared" si="9"/>
-        <v>158</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="R63" s="1">
         <v>0</v>
@@ -7698,7 +7754,7 @@
         <v>39</v>
       </c>
       <c r="AC63" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6982</v>
       </c>
       <c r="AD63" s="1">
@@ -7759,12 +7815,13 @@
       <c r="O64" s="1">
         <v>58</v>
       </c>
-      <c r="P64" s="7">
-        <v>59</v>
+      <c r="P64" s="3">
+        <f t="shared" si="6"/>
+        <v>58</v>
       </c>
       <c r="Q64" s="3">
-        <f t="shared" si="9"/>
-        <v>161</v>
+        <f t="shared" si="7"/>
+        <v>67</v>
       </c>
       <c r="R64" s="1">
         <v>0</v>
@@ -7803,7 +7860,7 @@
         <v>39</v>
       </c>
       <c r="AC64" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7253</v>
       </c>
       <c r="AD64" s="1">
@@ -7864,12 +7921,13 @@
       <c r="O65" s="1">
         <v>59</v>
       </c>
-      <c r="P65" s="7">
-        <v>60</v>
+      <c r="P65" s="3">
+        <f t="shared" si="6"/>
+        <v>59</v>
       </c>
       <c r="Q65" s="3">
-        <f t="shared" si="9"/>
-        <v>164</v>
+        <f t="shared" si="7"/>
+        <v>68</v>
       </c>
       <c r="R65" s="1">
         <v>0</v>
@@ -7908,7 +7966,7 @@
         <v>39</v>
       </c>
       <c r="AC65" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7530</v>
       </c>
       <c r="AD65" s="1">
@@ -7969,12 +8027,13 @@
       <c r="O66" s="1">
         <v>60</v>
       </c>
-      <c r="P66" s="7">
-        <v>61</v>
+      <c r="P66" s="3">
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="Q66" s="3">
-        <f t="shared" si="9"/>
-        <v>167</v>
+        <f t="shared" si="7"/>
+        <v>69</v>
       </c>
       <c r="R66" s="1">
         <v>0</v>
@@ -8013,7 +8072,7 @@
         <v>39</v>
       </c>
       <c r="AC66" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7811</v>
       </c>
       <c r="AD66" s="1">
@@ -8074,12 +8133,13 @@
       <c r="O67" s="1">
         <v>61</v>
       </c>
-      <c r="P67" s="7">
-        <v>62</v>
+      <c r="P67" s="3">
+        <f t="shared" si="6"/>
+        <v>61</v>
       </c>
       <c r="Q67" s="3">
-        <f t="shared" si="9"/>
-        <v>170</v>
+        <f t="shared" si="7"/>
+        <v>70</v>
       </c>
       <c r="R67" s="1">
         <v>0</v>
@@ -8118,7 +8178,7 @@
         <v>39</v>
       </c>
       <c r="AC67" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8094</v>
       </c>
       <c r="AD67" s="1">
@@ -8179,12 +8239,13 @@
       <c r="O68" s="1">
         <v>62</v>
       </c>
-      <c r="P68" s="7">
-        <v>63</v>
+      <c r="P68" s="3">
+        <f t="shared" si="6"/>
+        <v>62</v>
       </c>
       <c r="Q68" s="3">
-        <f t="shared" si="9"/>
-        <v>173</v>
+        <f t="shared" si="7"/>
+        <v>71</v>
       </c>
       <c r="R68" s="1">
         <v>0</v>
@@ -8223,7 +8284,7 @@
         <v>39</v>
       </c>
       <c r="AC68" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8387</v>
       </c>
       <c r="AD68" s="1">
@@ -8284,12 +8345,13 @@
       <c r="O69" s="1">
         <v>63</v>
       </c>
-      <c r="P69" s="7">
-        <v>64</v>
+      <c r="P69" s="3">
+        <f t="shared" si="6"/>
+        <v>63</v>
       </c>
       <c r="Q69" s="3">
-        <f t="shared" si="9"/>
-        <v>176</v>
+        <f t="shared" si="7"/>
+        <v>72</v>
       </c>
       <c r="R69" s="1">
         <v>0</v>
@@ -8328,7 +8390,7 @@
         <v>39</v>
       </c>
       <c r="AC69" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8694</v>
       </c>
       <c r="AD69" s="1">
@@ -8389,12 +8451,13 @@
       <c r="O70" s="1">
         <v>64</v>
       </c>
-      <c r="P70" s="7">
-        <v>65</v>
+      <c r="P70" s="3">
+        <f t="shared" si="6"/>
+        <v>64</v>
       </c>
       <c r="Q70" s="3">
-        <f t="shared" si="9"/>
-        <v>179</v>
+        <f t="shared" si="7"/>
+        <v>73</v>
       </c>
       <c r="R70" s="1">
         <v>0</v>
@@ -8433,7 +8496,7 @@
         <v>39</v>
       </c>
       <c r="AC70" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9005</v>
       </c>
       <c r="AD70" s="1">
@@ -8494,12 +8557,13 @@
       <c r="O71" s="1">
         <v>65</v>
       </c>
-      <c r="P71" s="7">
-        <v>66</v>
+      <c r="P71" s="3">
+        <f t="shared" si="6"/>
+        <v>65</v>
       </c>
       <c r="Q71" s="3">
-        <f t="shared" si="9"/>
-        <v>182</v>
+        <f t="shared" si="7"/>
+        <v>74</v>
       </c>
       <c r="R71" s="1">
         <v>0</v>
@@ -8538,7 +8602,7 @@
         <v>39</v>
       </c>
       <c r="AC71" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9318</v>
       </c>
       <c r="AD71" s="1">
@@ -8599,12 +8663,13 @@
       <c r="O72" s="1">
         <v>66</v>
       </c>
-      <c r="P72" s="7">
-        <v>67</v>
+      <c r="P72" s="3">
+        <f t="shared" ref="P72:P77" si="24">P71+1</f>
+        <v>66</v>
       </c>
       <c r="Q72" s="3">
-        <f t="shared" si="9"/>
-        <v>185</v>
+        <f t="shared" ref="Q72:Q77" si="25">Q71+1</f>
+        <v>75</v>
       </c>
       <c r="R72" s="1">
         <v>0</v>
@@ -8643,7 +8708,7 @@
         <v>39</v>
       </c>
       <c r="AC72" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9635</v>
       </c>
       <c r="AD72" s="1">
@@ -8682,7 +8747,7 @@
         <v>210171000</v>
       </c>
       <c r="J73" s="1">
-        <f t="shared" ref="J73:J77" si="24">Y73*Z73*AC73</f>
+        <f t="shared" ref="J73:J77" si="26">Y73*Z73*AC73</f>
         <v>67768800000</v>
       </c>
       <c r="K73" s="1">
@@ -8704,12 +8769,13 @@
       <c r="O73" s="1">
         <v>67</v>
       </c>
-      <c r="P73" s="7">
-        <v>68</v>
+      <c r="P73" s="3">
+        <f t="shared" si="24"/>
+        <v>67</v>
       </c>
       <c r="Q73" s="3">
-        <f t="shared" si="9"/>
-        <v>188</v>
+        <f t="shared" si="25"/>
+        <v>76</v>
       </c>
       <c r="R73" s="1">
         <v>0</v>
@@ -8748,7 +8814,7 @@
         <v>39</v>
       </c>
       <c r="AC73" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9966</v>
       </c>
       <c r="AD73" s="1">
@@ -8787,7 +8853,7 @@
         <v>225907500</v>
       </c>
       <c r="J74" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>72121000000</v>
       </c>
       <c r="K74" s="1">
@@ -8809,12 +8875,13 @@
       <c r="O74" s="1">
         <v>68</v>
       </c>
-      <c r="P74" s="7">
-        <v>69</v>
+      <c r="P74" s="3">
+        <f t="shared" si="24"/>
+        <v>68</v>
       </c>
       <c r="Q74" s="3">
-        <f t="shared" si="9"/>
-        <v>191</v>
+        <f t="shared" si="25"/>
+        <v>77</v>
       </c>
       <c r="R74" s="1">
         <v>0</v>
@@ -8853,7 +8920,7 @@
         <v>39</v>
       </c>
       <c r="AC74" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10303</v>
       </c>
       <c r="AD74" s="1">
@@ -8892,7 +8959,7 @@
         <v>236574000</v>
       </c>
       <c r="J75" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>76680000000</v>
       </c>
       <c r="K75" s="1">
@@ -8914,12 +8981,13 @@
       <c r="O75" s="1">
         <v>69</v>
       </c>
-      <c r="P75" s="7">
-        <v>70</v>
+      <c r="P75" s="3">
+        <f t="shared" si="24"/>
+        <v>69</v>
       </c>
       <c r="Q75" s="3">
-        <f t="shared" si="9"/>
-        <v>194</v>
+        <f t="shared" si="25"/>
+        <v>78</v>
       </c>
       <c r="R75" s="1">
         <v>0</v>
@@ -8958,7 +9026,7 @@
         <v>39</v>
       </c>
       <c r="AC75" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10650</v>
       </c>
       <c r="AD75" s="1">
@@ -8982,7 +9050,7 @@
       <c r="E76" s="1">
         <v>1</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G76" s="1">
@@ -8997,7 +9065,7 @@
         <v>250360500</v>
       </c>
       <c r="J76" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>81392600000</v>
       </c>
       <c r="K76" s="1">
@@ -9019,12 +9087,13 @@
       <c r="O76" s="1">
         <v>70</v>
       </c>
-      <c r="P76" s="7">
-        <v>71</v>
+      <c r="P76" s="3">
+        <f t="shared" si="24"/>
+        <v>70</v>
       </c>
       <c r="Q76" s="3">
-        <f t="shared" si="9"/>
-        <v>197</v>
+        <f t="shared" si="25"/>
+        <v>79</v>
       </c>
       <c r="R76" s="1">
         <v>0</v>
@@ -9102,7 +9171,7 @@
         <v>258609000</v>
       </c>
       <c r="J77" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>86275200000</v>
       </c>
       <c r="K77" s="1">
@@ -9124,12 +9193,13 @@
       <c r="O77" s="1">
         <v>71</v>
       </c>
-      <c r="P77" s="7">
-        <v>72</v>
+      <c r="P77" s="3">
+        <f t="shared" si="24"/>
+        <v>71</v>
       </c>
       <c r="Q77" s="3">
-        <f t="shared" si="9"/>
-        <v>200</v>
+        <f t="shared" si="25"/>
+        <v>80</v>
       </c>
       <c r="R77" s="1">
         <v>0</v>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -990,6 +990,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -999,7 +1000,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1328,82 +1328,82 @@
   <dimension ref="A1:AG103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
+    <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9" style="4"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="5" customWidth="1"/>
     <col min="7" max="7" width="9.58333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.0833333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15.0833333333333" style="3" customWidth="1"/>
-    <col min="10" max="10" width="18.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.4166666666667" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10.3333333333333" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.91666666666667" style="3" customWidth="1"/>
-    <col min="14" max="15" width="8.75" style="3" customWidth="1"/>
-    <col min="16" max="16" width="7.50833333333333" style="3" customWidth="1"/>
-    <col min="17" max="17" width="9.16666666666667" style="3" customWidth="1"/>
-    <col min="18" max="19" width="8.75" style="3" customWidth="1"/>
-    <col min="20" max="20" width="7.50833333333333" style="3" customWidth="1"/>
-    <col min="21" max="21" width="8.33333333333333" style="3" customWidth="1"/>
-    <col min="22" max="22" width="9.91666666666667" style="3" customWidth="1"/>
-    <col min="23" max="23" width="10.3333333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.0833333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="15.0833333333333" style="4" customWidth="1"/>
+    <col min="10" max="10" width="18.5" style="4" customWidth="1"/>
+    <col min="11" max="11" width="13.4166666666667" style="4" customWidth="1"/>
+    <col min="12" max="12" width="10.3333333333333" style="4" customWidth="1"/>
+    <col min="13" max="13" width="9.91666666666667" style="4" customWidth="1"/>
+    <col min="14" max="15" width="8.75" style="4" customWidth="1"/>
+    <col min="16" max="16" width="7.50833333333333" style="4" customWidth="1"/>
+    <col min="17" max="17" width="9.16666666666667" style="4" customWidth="1"/>
+    <col min="18" max="19" width="8.75" style="4" customWidth="1"/>
+    <col min="20" max="20" width="7.50833333333333" style="4" customWidth="1"/>
+    <col min="21" max="21" width="8.33333333333333" style="4" customWidth="1"/>
+    <col min="22" max="22" width="9.91666666666667" style="4" customWidth="1"/>
+    <col min="23" max="23" width="10.3333333333333" style="4" customWidth="1"/>
     <col min="24" max="24" width="8.33333333333333" style="1" customWidth="1"/>
     <col min="25" max="25" width="7.25" style="1" customWidth="1"/>
-    <col min="26" max="28" width="7.16666666666667" style="3" customWidth="1"/>
-    <col min="29" max="29" width="8.41666666666667" style="3" customWidth="1"/>
-    <col min="30" max="30" width="4.33333333333333" style="3" customWidth="1"/>
-    <col min="31" max="31" width="3.75" style="3" customWidth="1"/>
-    <col min="32" max="32" width="3" style="3" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="3"/>
+    <col min="26" max="28" width="7.16666666666667" style="4" customWidth="1"/>
+    <col min="29" max="29" width="8.41666666666667" style="4" customWidth="1"/>
+    <col min="30" max="30" width="4.33333333333333" style="4" customWidth="1"/>
+    <col min="31" max="31" width="3.75" style="4" customWidth="1"/>
+    <col min="32" max="32" width="3" style="4" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="F1" s="4"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="F1" s="5"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
       <c r="X1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Z1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="AG1" s="1" t="s">
@@ -1411,50 +1411,50 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="F2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
       <c r="X2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Y2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Z2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="3" t="s">
+      <c r="Z2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="AG2" s="1" t="s">
@@ -1462,69 +1462,69 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="T3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="V3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="6" t="s">
         <v>21</v>
       </c>
       <c r="X3" s="1" t="s">
@@ -1533,105 +1533,105 @@
       <c r="Y3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AA3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AB3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AC3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AD3" s="5" t="s">
+      <c r="AD3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AE3" s="5" t="s">
+      <c r="AE3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AF3" s="5" t="s">
+      <c r="AF3" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="S4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="T4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="U4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="V4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="5" t="s">
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AE4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AF4" s="6" t="s">
         <v>30</v>
       </c>
       <c r="AG4" s="1">
@@ -1639,85 +1639,85 @@
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="Q5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="R5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="S5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="T5" s="5" t="s">
+      <c r="T5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="U5" s="5" t="s">
+      <c r="U5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="V5" s="5" t="s">
+      <c r="V5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="5" t="s">
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AE5" s="5" t="s">
+      <c r="AE5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AF5" s="5" t="s">
+      <c r="AF5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AG5" s="3">
+      <c r="AG5" s="4">
         <v>1</v>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="1">
@@ -1765,10 +1765,10 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
         <v>0</v>
       </c>
       <c r="R6" s="1">
@@ -1777,10 +1777,10 @@
       <c r="S6" s="1">
         <v>0</v>
       </c>
-      <c r="T6" s="7">
-        <v>0</v>
-      </c>
-      <c r="U6" s="7">
+      <c r="T6" s="8">
+        <v>0</v>
+      </c>
+      <c r="U6" s="8">
         <v>0</v>
       </c>
       <c r="V6" s="1">
@@ -1797,16 +1797,16 @@
       <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z6" s="4">
         <v>100</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="4">
         <v>2</v>
       </c>
-      <c r="AB6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="3">
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
         <v>10</v>
       </c>
       <c r="AD6" s="1">
@@ -1816,7 +1816,7 @@
       <c r="AF6" s="1">
         <v>0</v>
       </c>
-      <c r="AG6" s="3">
+      <c r="AG6" s="4">
         <v>2</v>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="G7" s="1">
@@ -1864,10 +1864,10 @@
       <c r="O7" s="1">
         <v>1</v>
       </c>
-      <c r="P7" s="7">
+      <c r="P7" s="8">
         <v>1</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="Q7" s="8">
         <v>10</v>
       </c>
       <c r="R7" s="1">
@@ -1876,10 +1876,10 @@
       <c r="S7" s="1">
         <v>0</v>
       </c>
-      <c r="T7" s="7">
-        <v>0</v>
-      </c>
-      <c r="U7" s="7">
+      <c r="T7" s="8">
+        <v>0</v>
+      </c>
+      <c r="U7" s="8">
         <v>0</v>
       </c>
       <c r="V7" s="1">
@@ -1896,17 +1896,17 @@
       <c r="Y7" s="1">
         <v>2</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="Z7" s="4">
         <f>Z6+20</f>
         <v>120</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AA7" s="4">
         <v>3</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AB7" s="4">
         <v>1</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AC7" s="4">
         <v>20</v>
       </c>
       <c r="AD7" s="1">
@@ -1916,7 +1916,7 @@
       <c r="AF7" s="1">
         <v>0</v>
       </c>
-      <c r="AG7" s="3">
+      <c r="AG7" s="4">
         <v>3</v>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="1">
@@ -1964,11 +1964,11 @@
       <c r="O8" s="1">
         <v>2</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="4">
         <f t="shared" ref="P8:P71" si="6">P7+1</f>
         <v>2</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="4">
         <f t="shared" ref="Q8:Q71" si="7">Q7+1</f>
         <v>11</v>
       </c>
@@ -1978,10 +1978,10 @@
       <c r="S8" s="1">
         <v>0</v>
       </c>
-      <c r="T8" s="7">
-        <v>0</v>
-      </c>
-      <c r="U8" s="7">
+      <c r="T8" s="8">
+        <v>0</v>
+      </c>
+      <c r="U8" s="8">
         <v>0</v>
       </c>
       <c r="V8" s="1">
@@ -1998,17 +1998,17 @@
       <c r="Y8" s="1">
         <v>3</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="4">
         <f>Z7+20</f>
         <v>140</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="4">
         <v>4</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="4">
         <v>2</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="4">
         <v>40</v>
       </c>
       <c r="AD8" s="1">
@@ -2018,7 +2018,7 @@
       <c r="AF8" s="1">
         <v>0</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="4">
         <v>5</v>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="1">
@@ -2066,11 +2066,11 @@
       <c r="O9" s="1">
         <v>3</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="4">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="4">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
@@ -2080,10 +2080,10 @@
       <c r="S9" s="1">
         <v>0</v>
       </c>
-      <c r="T9" s="7">
-        <v>0</v>
-      </c>
-      <c r="U9" s="7">
+      <c r="T9" s="8">
+        <v>0</v>
+      </c>
+      <c r="U9" s="8">
         <v>0</v>
       </c>
       <c r="V9" s="1">
@@ -2100,17 +2100,17 @@
       <c r="Y9" s="1">
         <v>4</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="4">
         <f>Z8+20</f>
         <v>160</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="4">
         <v>5</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AB9" s="4">
         <v>3</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="4">
         <v>60</v>
       </c>
       <c r="AD9" s="1">
@@ -2120,7 +2120,7 @@
       <c r="AF9" s="1">
         <v>0</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AG9" s="4">
         <v>7</v>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="1">
@@ -2168,11 +2168,11 @@
       <c r="O10" s="1">
         <v>4</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="4">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="4">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
@@ -2182,10 +2182,10 @@
       <c r="S10" s="1">
         <v>0</v>
       </c>
-      <c r="T10" s="7">
-        <v>0</v>
-      </c>
-      <c r="U10" s="7">
+      <c r="T10" s="8">
+        <v>0</v>
+      </c>
+      <c r="U10" s="8">
         <v>0</v>
       </c>
       <c r="V10" s="1">
@@ -2202,17 +2202,17 @@
       <c r="Y10" s="1">
         <v>5</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="4">
         <f>Z9+20</f>
         <v>180</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="4">
         <v>6</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="4">
         <v>4</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="4">
         <v>100</v>
       </c>
       <c r="AD10" s="1">
@@ -2222,52 +2222,52 @@
       <c r="AF10" s="1">
         <v>0</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AG10" s="4">
         <v>11</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="1:33">
-      <c r="C11" s="8">
+      <c r="C11" s="3">
         <v>6</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="3">
         <v>6</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="3">
         <v>1</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="3">
         <v>6</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="3">
         <v>2500</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="3">
         <v>300</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="3">
         <v>20000</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="3">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="3">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="3">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="3">
         <v>5</v>
       </c>
       <c r="P11" s="2">
@@ -2278,10 +2278,10 @@
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="R11" s="8">
-        <v>0</v>
-      </c>
-      <c r="S11" s="8">
+      <c r="R11" s="3">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3">
         <v>0</v>
       </c>
       <c r="T11" s="2">
@@ -2290,18 +2290,18 @@
       <c r="U11" s="2">
         <v>0</v>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="3">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="W11" s="8">
+      <c r="W11" s="3">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="X11" s="8">
+      <c r="X11" s="3">
         <v>6</v>
       </c>
-      <c r="Y11" s="8">
+      <c r="Y11" s="3">
         <v>6</v>
       </c>
       <c r="Z11" s="2">
@@ -2317,11 +2317,11 @@
       <c r="AC11" s="2">
         <v>140</v>
       </c>
-      <c r="AD11" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="8"/>
-      <c r="AF11" s="8">
+      <c r="AD11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3">
         <v>0</v>
       </c>
       <c r="AG11" s="2">
@@ -2338,19 +2338,19 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <v>3500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <v>490</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="4">
         <v>35000</v>
       </c>
       <c r="K12" s="1">
@@ -2372,11 +2372,11 @@
       <c r="O12" s="1">
         <v>6</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="4">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="4">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
@@ -2386,10 +2386,10 @@
       <c r="S12" s="1">
         <v>0</v>
       </c>
-      <c r="T12" s="7">
-        <v>0</v>
-      </c>
-      <c r="U12" s="7">
+      <c r="T12" s="8">
+        <v>0</v>
+      </c>
+      <c r="U12" s="8">
         <v>0</v>
       </c>
       <c r="V12" s="1">
@@ -2406,17 +2406,17 @@
       <c r="Y12" s="1">
         <v>7</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="4">
         <f>Z11+40</f>
         <v>240</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="4">
         <v>8</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AB12" s="4">
         <v>6</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AC12" s="4">
         <f t="shared" ref="AC8:AC75" si="8">AC11+AG11</f>
         <v>153</v>
       </c>
@@ -2427,7 +2427,7 @@
       <c r="AF12" s="1">
         <v>0</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AG12" s="4">
         <v>17</v>
       </c>
     </row>
@@ -2475,11 +2475,11 @@
       <c r="O13" s="1">
         <v>7</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="4">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="4">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
@@ -2489,10 +2489,10 @@
       <c r="S13" s="1">
         <v>0</v>
       </c>
-      <c r="T13" s="7">
-        <v>0</v>
-      </c>
-      <c r="U13" s="7">
+      <c r="T13" s="8">
+        <v>0</v>
+      </c>
+      <c r="U13" s="8">
         <v>0</v>
       </c>
       <c r="V13" s="1">
@@ -2509,17 +2509,17 @@
       <c r="Y13" s="1">
         <v>8</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="Z13" s="4">
         <f>Z12+40</f>
         <v>280</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AA13" s="4">
         <v>9</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AB13" s="4">
         <v>7</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AC13" s="4">
         <f t="shared" si="8"/>
         <v>170</v>
       </c>
@@ -2530,7 +2530,7 @@
       <c r="AF13" s="1">
         <v>0</v>
       </c>
-      <c r="AG13" s="3">
+      <c r="AG13" s="4">
         <v>19</v>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="7" t="s">
         <v>43</v>
       </c>
       <c r="G14" s="1">
@@ -2578,11 +2578,11 @@
       <c r="O14" s="1">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="4">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="4">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
@@ -2592,10 +2592,10 @@
       <c r="S14" s="1">
         <v>0</v>
       </c>
-      <c r="T14" s="7">
-        <v>0</v>
-      </c>
-      <c r="U14" s="7">
+      <c r="T14" s="8">
+        <v>0</v>
+      </c>
+      <c r="U14" s="8">
         <v>0</v>
       </c>
       <c r="V14" s="1">
@@ -2612,17 +2612,17 @@
       <c r="Y14" s="1">
         <v>9</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="4">
         <f>Z13+40</f>
         <v>320</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="4">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="4">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="4">
         <f t="shared" si="8"/>
         <v>189</v>
       </c>
@@ -2633,7 +2633,7 @@
       <c r="AF14" s="1">
         <v>0</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="4">
         <v>23</v>
       </c>
     </row>
@@ -2681,11 +2681,11 @@
       <c r="O15" s="1">
         <v>9</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="4">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="4">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
@@ -2695,10 +2695,10 @@
       <c r="S15" s="1">
         <v>0</v>
       </c>
-      <c r="T15" s="7">
-        <v>0</v>
-      </c>
-      <c r="U15" s="7">
+      <c r="T15" s="8">
+        <v>0</v>
+      </c>
+      <c r="U15" s="8">
         <v>0</v>
       </c>
       <c r="V15" s="1">
@@ -2715,17 +2715,17 @@
       <c r="Y15" s="1">
         <v>10</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="4">
         <f>Z14+40</f>
         <v>360</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="4">
         <v>11</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="4">
         <v>9</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="4">
         <f t="shared" si="8"/>
         <v>212</v>
       </c>
@@ -2736,7 +2736,7 @@
       <c r="AF15" s="1">
         <v>0</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="4">
         <v>29</v>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="7" t="s">
         <v>45</v>
       </c>
       <c r="G16" s="1">
@@ -2784,11 +2784,11 @@
       <c r="O16" s="1">
         <v>10</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="4">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="Q16" s="4">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
@@ -2798,10 +2798,10 @@
       <c r="S16" s="1">
         <v>0</v>
       </c>
-      <c r="T16" s="7">
-        <v>0</v>
-      </c>
-      <c r="U16" s="7">
+      <c r="T16" s="8">
+        <v>0</v>
+      </c>
+      <c r="U16" s="8">
         <v>0</v>
       </c>
       <c r="V16" s="1">
@@ -2818,17 +2818,17 @@
       <c r="Y16" s="1">
         <v>11</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="Z16" s="4">
         <f>Z15+40</f>
         <v>400</v>
       </c>
-      <c r="AA16" s="3">
+      <c r="AA16" s="4">
         <v>13</v>
       </c>
-      <c r="AB16" s="3">
+      <c r="AB16" s="4">
         <v>10</v>
       </c>
-      <c r="AC16" s="3">
+      <c r="AC16" s="4">
         <f t="shared" si="8"/>
         <v>241</v>
       </c>
@@ -2839,52 +2839,52 @@
       <c r="AF16" s="1">
         <v>0</v>
       </c>
-      <c r="AG16" s="3">
+      <c r="AG16" s="4">
         <v>31</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:33">
-      <c r="C17" s="8">
+      <c r="C17" s="3">
         <v>12</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="3">
         <v>12</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="3">
         <v>1</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="3">
         <v>12</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="3">
         <v>25000</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="3">
         <v>3600</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="3">
         <v>300000</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="3">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="3">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="N17" s="8">
+      <c r="N17" s="3">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O17" s="3">
         <v>11</v>
       </c>
       <c r="P17" s="2">
@@ -2895,10 +2895,10 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="R17" s="8">
-        <v>0</v>
-      </c>
-      <c r="S17" s="8">
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
         <v>0</v>
       </c>
       <c r="T17" s="2">
@@ -2907,18 +2907,18 @@
       <c r="U17" s="2">
         <v>0</v>
       </c>
-      <c r="V17" s="8">
+      <c r="V17" s="3">
         <f t="shared" si="4"/>
         <v>120</v>
       </c>
-      <c r="W17" s="8">
+      <c r="W17" s="3">
         <f t="shared" si="5"/>
         <v>120</v>
       </c>
-      <c r="X17" s="8">
+      <c r="X17" s="3">
         <v>12</v>
       </c>
-      <c r="Y17" s="8">
+      <c r="Y17" s="3">
         <v>12</v>
       </c>
       <c r="Z17" s="2">
@@ -2935,11 +2935,11 @@
         <f t="shared" si="8"/>
         <v>272</v>
       </c>
-      <c r="AD17" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="8"/>
-      <c r="AF17" s="8">
+      <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="3">
         <v>0</v>
       </c>
       <c r="AG17" s="2">
@@ -2990,11 +2990,11 @@
       <c r="O18" s="1">
         <v>12</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="4">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="4">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
@@ -3004,10 +3004,10 @@
       <c r="S18" s="1">
         <v>0</v>
       </c>
-      <c r="T18" s="7">
-        <v>0</v>
-      </c>
-      <c r="U18" s="7">
+      <c r="T18" s="8">
+        <v>0</v>
+      </c>
+      <c r="U18" s="8">
         <v>0</v>
       </c>
       <c r="V18" s="1">
@@ -3024,17 +3024,17 @@
       <c r="Y18" s="1">
         <v>13</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="4">
         <f t="shared" si="9"/>
         <v>600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="4">
         <v>19</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="4">
         <v>12</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="4">
         <f t="shared" si="8"/>
         <v>309</v>
       </c>
@@ -3045,7 +3045,7 @@
       <c r="AF18" s="1">
         <v>0</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="4">
         <v>41</v>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>48</v>
       </c>
       <c r="G19" s="1">
@@ -3093,11 +3093,11 @@
       <c r="O19" s="1">
         <v>13</v>
       </c>
-      <c r="P19" s="3">
+      <c r="P19" s="4">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="Q19" s="4">
         <f t="shared" si="7"/>
         <v>22</v>
       </c>
@@ -3107,10 +3107,10 @@
       <c r="S19" s="1">
         <v>0</v>
       </c>
-      <c r="T19" s="7">
-        <v>0</v>
-      </c>
-      <c r="U19" s="7">
+      <c r="T19" s="8">
+        <v>0</v>
+      </c>
+      <c r="U19" s="8">
         <v>0</v>
       </c>
       <c r="V19" s="1">
@@ -3127,17 +3127,17 @@
       <c r="Y19" s="1">
         <v>14</v>
       </c>
-      <c r="Z19" s="3">
+      <c r="Z19" s="4">
         <f t="shared" si="9"/>
         <v>700</v>
       </c>
-      <c r="AA19" s="3">
+      <c r="AA19" s="4">
         <v>23</v>
       </c>
-      <c r="AB19" s="3">
+      <c r="AB19" s="4">
         <v>13</v>
       </c>
-      <c r="AC19" s="3">
+      <c r="AC19" s="4">
         <f t="shared" si="8"/>
         <v>350</v>
       </c>
@@ -3148,7 +3148,7 @@
       <c r="AF19" s="1">
         <v>0</v>
       </c>
-      <c r="AG19" s="3">
+      <c r="AG19" s="4">
         <v>43</v>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       <c r="E20" s="1">
         <v>1</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G20" s="1">
@@ -3196,11 +3196,11 @@
       <c r="O20" s="1">
         <v>14</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="4">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="4">
         <f t="shared" si="7"/>
         <v>23</v>
       </c>
@@ -3210,10 +3210,10 @@
       <c r="S20" s="1">
         <v>0</v>
       </c>
-      <c r="T20" s="7">
-        <v>0</v>
-      </c>
-      <c r="U20" s="7">
+      <c r="T20" s="8">
+        <v>0</v>
+      </c>
+      <c r="U20" s="8">
         <v>0</v>
       </c>
       <c r="V20" s="1">
@@ -3230,17 +3230,17 @@
       <c r="Y20" s="1">
         <v>15</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="4">
         <f t="shared" si="9"/>
         <v>800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="4">
         <v>29</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="4">
         <v>14</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="4">
         <f t="shared" si="8"/>
         <v>393</v>
       </c>
@@ -3251,7 +3251,7 @@
       <c r="AF20" s="1">
         <v>0</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="4">
         <v>47</v>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G21" s="1">
@@ -3299,11 +3299,11 @@
       <c r="O21" s="1">
         <v>15</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="4">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="4">
         <f t="shared" si="7"/>
         <v>24</v>
       </c>
@@ -3313,10 +3313,10 @@
       <c r="S21" s="1">
         <v>0</v>
       </c>
-      <c r="T21" s="7">
-        <v>0</v>
-      </c>
-      <c r="U21" s="7">
+      <c r="T21" s="8">
+        <v>0</v>
+      </c>
+      <c r="U21" s="8">
         <v>0</v>
       </c>
       <c r="V21" s="1">
@@ -3333,17 +3333,17 @@
       <c r="Y21" s="1">
         <v>16</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="4">
         <f t="shared" si="9"/>
         <v>900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="4">
         <v>31</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="4">
         <v>15</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="4">
         <f t="shared" si="8"/>
         <v>440</v>
       </c>
@@ -3354,7 +3354,7 @@
       <c r="AF21" s="1">
         <v>0</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="4">
         <v>53</v>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="7" t="s">
         <v>51</v>
       </c>
       <c r="G22" s="1">
@@ -3402,11 +3402,11 @@
       <c r="O22" s="1">
         <v>16</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="4">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="4">
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
@@ -3416,10 +3416,10 @@
       <c r="S22" s="1">
         <v>0</v>
       </c>
-      <c r="T22" s="7">
-        <v>0</v>
-      </c>
-      <c r="U22" s="7">
+      <c r="T22" s="8">
+        <v>0</v>
+      </c>
+      <c r="U22" s="8">
         <v>0</v>
       </c>
       <c r="V22" s="1">
@@ -3436,17 +3436,17 @@
       <c r="Y22" s="1">
         <v>17</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="4">
         <f t="shared" si="9"/>
         <v>1000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="4">
         <v>37</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="4">
         <v>16</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="4">
         <f t="shared" si="8"/>
         <v>493</v>
       </c>
@@ -3457,52 +3457,52 @@
       <c r="AF22" s="1">
         <v>0</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="4">
         <v>59</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:33">
-      <c r="C23" s="8">
+      <c r="C23" s="3">
         <v>18</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="3">
         <v>18</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="3">
         <v>1</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="3">
         <v>18</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="3">
         <v>120000</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="3">
         <v>36000</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="3">
         <v>2550000</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="3">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="3">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="3">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="3">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O23" s="8">
+      <c r="O23" s="3">
         <v>17</v>
       </c>
       <c r="P23" s="2">
@@ -3513,10 +3513,10 @@
         <f t="shared" si="7"/>
         <v>26</v>
       </c>
-      <c r="R23" s="8">
-        <v>0</v>
-      </c>
-      <c r="S23" s="8">
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>0</v>
       </c>
       <c r="T23" s="2">
@@ -3525,18 +3525,18 @@
       <c r="U23" s="2">
         <v>0</v>
       </c>
-      <c r="V23" s="8">
+      <c r="V23" s="3">
         <f t="shared" si="4"/>
         <v>180</v>
       </c>
-      <c r="W23" s="8">
+      <c r="W23" s="3">
         <f t="shared" si="5"/>
         <v>180</v>
       </c>
-      <c r="X23" s="8">
+      <c r="X23" s="3">
         <v>18</v>
       </c>
-      <c r="Y23" s="8">
+      <c r="Y23" s="3">
         <v>18</v>
       </c>
       <c r="Z23" s="2">
@@ -3553,11 +3553,11 @@
         <f t="shared" si="8"/>
         <v>552</v>
       </c>
-      <c r="AD23" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="8"/>
-      <c r="AF23" s="8">
+      <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3">
         <v>0</v>
       </c>
       <c r="AG23" s="2">
@@ -3574,7 +3574,7 @@
       <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="7" t="s">
         <v>53</v>
       </c>
       <c r="G24" s="1">
@@ -3608,11 +3608,11 @@
       <c r="O24" s="1">
         <v>18</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="4">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="4">
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
@@ -3622,10 +3622,10 @@
       <c r="S24" s="1">
         <v>0</v>
       </c>
-      <c r="T24" s="7">
-        <v>0</v>
-      </c>
-      <c r="U24" s="7">
+      <c r="T24" s="8">
+        <v>0</v>
+      </c>
+      <c r="U24" s="8">
         <v>0</v>
       </c>
       <c r="V24" s="1">
@@ -3642,17 +3642,17 @@
       <c r="Y24" s="1">
         <v>19</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="4">
         <f>Z23+200</f>
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AA24" s="4">
         <v>43</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AB24" s="4">
         <v>18</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="4">
         <f t="shared" si="8"/>
         <v>613</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="AF24" s="1">
         <v>0</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AG24" s="4">
         <v>67</v>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="7" t="s">
         <v>54</v>
       </c>
       <c r="G25" s="1">
@@ -3711,11 +3711,11 @@
       <c r="O25" s="1">
         <v>19</v>
       </c>
-      <c r="P25" s="3">
+      <c r="P25" s="4">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="Q25" s="4">
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
@@ -3725,10 +3725,10 @@
       <c r="S25" s="1">
         <v>0</v>
       </c>
-      <c r="T25" s="7">
-        <v>0</v>
-      </c>
-      <c r="U25" s="7">
+      <c r="T25" s="8">
+        <v>0</v>
+      </c>
+      <c r="U25" s="8">
         <v>0</v>
       </c>
       <c r="V25" s="1">
@@ -3745,17 +3745,17 @@
       <c r="Y25" s="1">
         <v>20</v>
       </c>
-      <c r="Z25" s="3">
+      <c r="Z25" s="4">
         <f>Z24+200</f>
         <v>1600</v>
       </c>
-      <c r="AA25" s="3">
+      <c r="AA25" s="4">
         <v>47</v>
       </c>
-      <c r="AB25" s="3">
+      <c r="AB25" s="4">
         <v>19</v>
       </c>
-      <c r="AC25" s="3">
+      <c r="AC25" s="4">
         <f t="shared" si="8"/>
         <v>680</v>
       </c>
@@ -3766,7 +3766,7 @@
       <c r="AF25" s="1">
         <v>0</v>
       </c>
-      <c r="AG25" s="3">
+      <c r="AG25" s="4">
         <v>71</v>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       <c r="E26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G26" s="1">
@@ -3814,11 +3814,11 @@
       <c r="O26" s="1">
         <v>20</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="4">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="4">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
@@ -3828,10 +3828,10 @@
       <c r="S26" s="1">
         <v>0</v>
       </c>
-      <c r="T26" s="7">
-        <v>0</v>
-      </c>
-      <c r="U26" s="7">
+      <c r="T26" s="8">
+        <v>0</v>
+      </c>
+      <c r="U26" s="8">
         <v>0</v>
       </c>
       <c r="V26" s="1">
@@ -3848,17 +3848,17 @@
       <c r="Y26" s="1">
         <v>21</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="4">
         <f>Z25+200</f>
         <v>1800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="4">
         <v>53</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AB26" s="4">
         <v>20</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="4">
         <f t="shared" si="8"/>
         <v>751</v>
       </c>
@@ -3869,7 +3869,7 @@
       <c r="AF26" s="1">
         <v>0</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AG26" s="4">
         <v>73</v>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="7" t="s">
         <v>56</v>
       </c>
       <c r="G27" s="1">
@@ -3917,11 +3917,11 @@
       <c r="O27" s="1">
         <v>21</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="4">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="4">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
@@ -3931,10 +3931,10 @@
       <c r="S27" s="1">
         <v>0</v>
       </c>
-      <c r="T27" s="7">
-        <v>0</v>
-      </c>
-      <c r="U27" s="7">
+      <c r="T27" s="8">
+        <v>0</v>
+      </c>
+      <c r="U27" s="8">
         <v>0</v>
       </c>
       <c r="V27" s="1">
@@ -3951,17 +3951,17 @@
       <c r="Y27" s="1">
         <v>22</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="4">
         <f>Z26+200</f>
         <v>2000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="4">
         <v>59</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AB27" s="4">
         <v>21</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="4">
         <f t="shared" si="8"/>
         <v>824</v>
       </c>
@@ -3972,7 +3972,7 @@
       <c r="AF27" s="1">
         <v>0</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AG27" s="4">
         <v>79</v>
       </c>
     </row>
@@ -4020,11 +4020,11 @@
       <c r="O28" s="1">
         <v>22</v>
       </c>
-      <c r="P28" s="3">
+      <c r="P28" s="4">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="Q28" s="4">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
@@ -4034,10 +4034,10 @@
       <c r="S28" s="1">
         <v>0</v>
       </c>
-      <c r="T28" s="7">
-        <v>0</v>
-      </c>
-      <c r="U28" s="7">
+      <c r="T28" s="8">
+        <v>0</v>
+      </c>
+      <c r="U28" s="8">
         <v>0</v>
       </c>
       <c r="V28" s="1">
@@ -4054,17 +4054,17 @@
       <c r="Y28" s="1">
         <v>23</v>
       </c>
-      <c r="Z28" s="3">
+      <c r="Z28" s="4">
         <f t="shared" ref="Z28:Z33" si="10">Z27+500</f>
         <v>2500</v>
       </c>
-      <c r="AA28" s="3">
+      <c r="AA28" s="4">
         <v>61</v>
       </c>
-      <c r="AB28" s="3">
+      <c r="AB28" s="4">
         <v>22</v>
       </c>
-      <c r="AC28" s="3">
+      <c r="AC28" s="4">
         <f t="shared" si="8"/>
         <v>903</v>
       </c>
@@ -4075,52 +4075,52 @@
       <c r="AF28" s="1">
         <v>0</v>
       </c>
-      <c r="AG28" s="3">
+      <c r="AG28" s="4">
         <v>83</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:33">
-      <c r="C29" s="8">
+      <c r="C29" s="3">
         <v>24</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="3">
         <v>24</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="3">
         <v>1</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="3">
         <v>24</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="3">
         <v>500000</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="3">
         <v>170000</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="3">
         <v>12000000</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="3">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="3">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="3">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="N29" s="8">
+      <c r="N29" s="3">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="O29" s="8">
+      <c r="O29" s="3">
         <v>23</v>
       </c>
       <c r="P29" s="2">
@@ -4131,10 +4131,10 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="R29" s="8">
-        <v>0</v>
-      </c>
-      <c r="S29" s="8">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>0</v>
       </c>
       <c r="T29" s="2">
@@ -4143,18 +4143,18 @@
       <c r="U29" s="2">
         <v>0</v>
       </c>
-      <c r="V29" s="8">
+      <c r="V29" s="3">
         <f t="shared" si="4"/>
         <v>240</v>
       </c>
-      <c r="W29" s="8">
+      <c r="W29" s="3">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
-      <c r="X29" s="8">
+      <c r="X29" s="3">
         <v>24</v>
       </c>
-      <c r="Y29" s="8">
+      <c r="Y29" s="3">
         <v>24</v>
       </c>
       <c r="Z29" s="2">
@@ -4171,11 +4171,11 @@
         <f t="shared" si="8"/>
         <v>986</v>
       </c>
-      <c r="AD29" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="8"/>
-      <c r="AF29" s="8">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3">
         <v>0</v>
       </c>
       <c r="AG29" s="2">
@@ -4192,7 +4192,7 @@
       <c r="E30" s="1">
         <v>1</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="7" t="s">
         <v>59</v>
       </c>
       <c r="G30" s="1">
@@ -4226,11 +4226,11 @@
       <c r="O30" s="1">
         <v>24</v>
       </c>
-      <c r="P30" s="3">
+      <c r="P30" s="4">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="Q30" s="4">
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
@@ -4240,10 +4240,10 @@
       <c r="S30" s="1">
         <v>0</v>
       </c>
-      <c r="T30" s="7">
-        <v>0</v>
-      </c>
-      <c r="U30" s="7">
+      <c r="T30" s="8">
+        <v>0</v>
+      </c>
+      <c r="U30" s="8">
         <v>0</v>
       </c>
       <c r="V30" s="1">
@@ -4260,17 +4260,17 @@
       <c r="Y30" s="1">
         <v>25</v>
       </c>
-      <c r="Z30" s="3">
+      <c r="Z30" s="4">
         <f t="shared" si="10"/>
         <v>3500</v>
       </c>
-      <c r="AA30" s="3">
+      <c r="AA30" s="4">
         <v>71</v>
       </c>
-      <c r="AB30" s="3">
+      <c r="AB30" s="4">
         <v>24</v>
       </c>
-      <c r="AC30" s="3">
+      <c r="AC30" s="4">
         <f t="shared" si="8"/>
         <v>1075</v>
       </c>
@@ -4281,7 +4281,7 @@
       <c r="AF30" s="1">
         <v>0</v>
       </c>
-      <c r="AG30" s="3">
+      <c r="AG30" s="4">
         <v>97</v>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       <c r="E31" s="1">
         <v>1</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G31" s="1">
@@ -4329,11 +4329,11 @@
       <c r="O31" s="1">
         <v>25</v>
       </c>
-      <c r="P31" s="3">
+      <c r="P31" s="4">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="Q31" s="4">
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
@@ -4343,10 +4343,10 @@
       <c r="S31" s="1">
         <v>0</v>
       </c>
-      <c r="T31" s="7">
-        <v>0</v>
-      </c>
-      <c r="U31" s="7">
+      <c r="T31" s="8">
+        <v>0</v>
+      </c>
+      <c r="U31" s="8">
         <v>0</v>
       </c>
       <c r="V31" s="1">
@@ -4363,17 +4363,17 @@
       <c r="Y31" s="1">
         <v>26</v>
       </c>
-      <c r="Z31" s="3">
+      <c r="Z31" s="4">
         <f t="shared" si="10"/>
         <v>4000</v>
       </c>
-      <c r="AA31" s="3">
+      <c r="AA31" s="4">
         <v>73</v>
       </c>
-      <c r="AB31" s="3">
+      <c r="AB31" s="4">
         <v>25</v>
       </c>
-      <c r="AC31" s="3">
+      <c r="AC31" s="4">
         <f t="shared" si="8"/>
         <v>1172</v>
       </c>
@@ -4384,7 +4384,7 @@
       <c r="AF31" s="1">
         <v>0</v>
       </c>
-      <c r="AG31" s="3">
+      <c r="AG31" s="4">
         <v>101</v>
       </c>
     </row>
@@ -4432,11 +4432,11 @@
       <c r="O32" s="1">
         <v>26</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="4">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="4">
         <f t="shared" si="7"/>
         <v>35</v>
       </c>
@@ -4446,10 +4446,10 @@
       <c r="S32" s="1">
         <v>0</v>
       </c>
-      <c r="T32" s="7">
-        <v>0</v>
-      </c>
-      <c r="U32" s="7">
+      <c r="T32" s="8">
+        <v>0</v>
+      </c>
+      <c r="U32" s="8">
         <v>0</v>
       </c>
       <c r="V32" s="1">
@@ -4466,17 +4466,17 @@
       <c r="Y32" s="1">
         <v>27</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="4">
         <f t="shared" si="10"/>
         <v>4500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="4">
         <v>79</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="4">
         <v>26</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="4">
         <f t="shared" si="8"/>
         <v>1273</v>
       </c>
@@ -4487,7 +4487,7 @@
       <c r="AF32" s="1">
         <v>0</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="4">
         <v>103</v>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       <c r="E33" s="1">
         <v>1</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G33" s="1">
@@ -4535,11 +4535,11 @@
       <c r="O33" s="1">
         <v>27</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="4">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="4">
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
@@ -4549,10 +4549,10 @@
       <c r="S33" s="1">
         <v>0</v>
       </c>
-      <c r="T33" s="7">
-        <v>0</v>
-      </c>
-      <c r="U33" s="7">
+      <c r="T33" s="8">
+        <v>0</v>
+      </c>
+      <c r="U33" s="8">
         <v>0</v>
       </c>
       <c r="V33" s="1">
@@ -4569,17 +4569,17 @@
       <c r="Y33" s="1">
         <v>28</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="4">
         <f t="shared" si="10"/>
         <v>5000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="4">
         <v>83</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AB33" s="4">
         <v>27</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="4">
         <f t="shared" si="8"/>
         <v>1376</v>
       </c>
@@ -4590,7 +4590,7 @@
       <c r="AF33" s="1">
         <v>0</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AG33" s="4">
         <v>107</v>
       </c>
     </row>
@@ -4638,11 +4638,11 @@
       <c r="O34" s="1">
         <v>28</v>
       </c>
-      <c r="P34" s="3">
+      <c r="P34" s="4">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="Q34" s="4">
         <f t="shared" si="7"/>
         <v>37</v>
       </c>
@@ -4652,10 +4652,10 @@
       <c r="S34" s="1">
         <v>0</v>
       </c>
-      <c r="T34" s="7">
-        <v>0</v>
-      </c>
-      <c r="U34" s="7">
+      <c r="T34" s="8">
+        <v>0</v>
+      </c>
+      <c r="U34" s="8">
         <v>0</v>
       </c>
       <c r="V34" s="1">
@@ -4672,17 +4672,17 @@
       <c r="Y34" s="1">
         <v>29</v>
       </c>
-      <c r="Z34" s="3">
+      <c r="Z34" s="4">
         <f>Z33+1000</f>
         <v>6000</v>
       </c>
-      <c r="AA34" s="3">
+      <c r="AA34" s="4">
         <v>89</v>
       </c>
-      <c r="AB34" s="3">
+      <c r="AB34" s="4">
         <v>28</v>
       </c>
-      <c r="AC34" s="3">
+      <c r="AC34" s="4">
         <f t="shared" si="8"/>
         <v>1483</v>
       </c>
@@ -4693,52 +4693,52 @@
       <c r="AF34" s="1">
         <v>0</v>
       </c>
-      <c r="AG34" s="3">
+      <c r="AG34" s="4">
         <v>109</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="1:33">
-      <c r="C35" s="8">
+      <c r="C35" s="3">
         <v>30</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="3">
         <v>30</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="3">
         <v>1</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="3">
         <v>30</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="3">
         <v>1800000</v>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="3">
         <v>1000000</v>
       </c>
-      <c r="J35" s="8">
+      <c r="J35" s="3">
         <v>30000000</v>
       </c>
-      <c r="K35" s="8">
+      <c r="K35" s="3">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="L35" s="8">
+      <c r="L35" s="3">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="M35" s="8">
+      <c r="M35" s="3">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="N35" s="8">
+      <c r="N35" s="3">
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
-      <c r="O35" s="8">
+      <c r="O35" s="3">
         <v>29</v>
       </c>
       <c r="P35" s="2">
@@ -4749,10 +4749,10 @@
         <f t="shared" si="7"/>
         <v>38</v>
       </c>
-      <c r="R35" s="8">
-        <v>0</v>
-      </c>
-      <c r="S35" s="8">
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>0</v>
       </c>
       <c r="T35" s="2">
@@ -4761,18 +4761,18 @@
       <c r="U35" s="2">
         <v>0</v>
       </c>
-      <c r="V35" s="8">
+      <c r="V35" s="3">
         <f t="shared" si="4"/>
         <v>300</v>
       </c>
-      <c r="W35" s="8">
+      <c r="W35" s="3">
         <f t="shared" si="5"/>
         <v>300</v>
       </c>
-      <c r="X35" s="8">
+      <c r="X35" s="3">
         <v>30</v>
       </c>
-      <c r="Y35" s="8">
+      <c r="Y35" s="3">
         <v>30</v>
       </c>
       <c r="Z35" s="2">
@@ -4789,11 +4789,11 @@
         <f t="shared" si="8"/>
         <v>1592</v>
       </c>
-      <c r="AD35" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="8"/>
-      <c r="AF35" s="8">
+      <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="3"/>
+      <c r="AF35" s="3">
         <v>0</v>
       </c>
       <c r="AG35" s="2">
@@ -4810,23 +4810,20 @@
       <c r="E36" s="1">
         <v>1</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G36" s="1">
         <v>31</v>
       </c>
       <c r="H36" s="1">
-        <f t="shared" ref="H7:H70" si="11">AG38*Z36*AA36/10</f>
-        <v>11069600</v>
+        <v>2200000</v>
       </c>
       <c r="I36" s="1">
-        <f t="shared" ref="I6:I69" si="12">AB36*AG34*Z36/10</f>
-        <v>2616000</v>
+        <v>1300000</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" ref="J7:J72" si="13">Y36*Z36*AC36</f>
-        <v>422840000</v>
+        <v>34000000</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" si="0"/>
@@ -4847,11 +4844,11 @@
       <c r="O36" s="1">
         <v>30</v>
       </c>
-      <c r="P36" s="3">
+      <c r="P36" s="4">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="Q36" s="3">
+      <c r="Q36" s="4">
         <f t="shared" si="7"/>
         <v>39</v>
       </c>
@@ -4861,10 +4858,10 @@
       <c r="S36" s="1">
         <v>0</v>
       </c>
-      <c r="T36" s="7">
-        <v>0</v>
-      </c>
-      <c r="U36" s="7">
+      <c r="T36" s="8">
+        <v>0</v>
+      </c>
+      <c r="U36" s="8">
         <v>0</v>
       </c>
       <c r="V36" s="1">
@@ -4881,17 +4878,17 @@
       <c r="Y36" s="1">
         <v>31</v>
       </c>
-      <c r="Z36" s="3">
+      <c r="Z36" s="4">
         <f>Z35+1000</f>
         <v>8000</v>
       </c>
-      <c r="AA36" s="3">
+      <c r="AA36" s="4">
         <v>101</v>
       </c>
-      <c r="AB36" s="3">
+      <c r="AB36" s="4">
         <v>30</v>
       </c>
-      <c r="AC36" s="3">
+      <c r="AC36" s="4">
         <f t="shared" si="8"/>
         <v>1705</v>
       </c>
@@ -4902,7 +4899,7 @@
       <c r="AF36" s="1">
         <v>0</v>
       </c>
-      <c r="AG36" s="3">
+      <c r="AG36" s="4">
         <v>127</v>
       </c>
     </row>
@@ -4916,23 +4913,20 @@
       <c r="E37" s="1">
         <v>1</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="7" t="s">
         <v>66</v>
       </c>
       <c r="G37" s="1">
         <v>32</v>
       </c>
       <c r="H37" s="1">
-        <f t="shared" si="11"/>
-        <v>12885300</v>
+        <v>2700000</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="12"/>
-        <v>3152700</v>
+        <v>1700000</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="13"/>
-        <v>527616000</v>
+        <v>39000000</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" si="0"/>
@@ -4953,11 +4947,11 @@
       <c r="O37" s="1">
         <v>31</v>
       </c>
-      <c r="P37" s="3">
+      <c r="P37" s="4">
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
-      <c r="Q37" s="3">
+      <c r="Q37" s="4">
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
@@ -4967,10 +4961,10 @@
       <c r="S37" s="1">
         <v>0</v>
       </c>
-      <c r="T37" s="7">
-        <v>0</v>
-      </c>
-      <c r="U37" s="7">
+      <c r="T37" s="8">
+        <v>0</v>
+      </c>
+      <c r="U37" s="8">
         <v>0</v>
       </c>
       <c r="V37" s="1">
@@ -4987,17 +4981,17 @@
       <c r="Y37" s="1">
         <v>32</v>
       </c>
-      <c r="Z37" s="3">
+      <c r="Z37" s="4">
         <f>Z36+1000</f>
         <v>9000</v>
       </c>
-      <c r="AA37" s="3">
+      <c r="AA37" s="4">
         <v>103</v>
       </c>
-      <c r="AB37" s="3">
+      <c r="AB37" s="4">
         <v>31</v>
       </c>
-      <c r="AC37" s="3">
+      <c r="AC37" s="4">
         <f t="shared" si="8"/>
         <v>1832</v>
       </c>
@@ -5008,7 +5002,7 @@
       <c r="AF37" s="1">
         <v>0</v>
       </c>
-      <c r="AG37" s="3">
+      <c r="AG37" s="4">
         <v>131</v>
       </c>
     </row>
@@ -5022,23 +5016,20 @@
       <c r="E38" s="1">
         <v>1</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="7" t="s">
         <v>67</v>
       </c>
       <c r="G38" s="1">
         <v>33</v>
       </c>
       <c r="H38" s="1">
-        <f t="shared" si="11"/>
-        <v>15943000</v>
+        <v>3300000</v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="12"/>
-        <v>4064000</v>
+        <v>2200000</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="13"/>
-        <v>647790000</v>
+        <v>45000000</v>
       </c>
       <c r="K38" s="1">
         <f t="shared" si="0"/>
@@ -5059,11 +5050,11 @@
       <c r="O38" s="1">
         <v>32</v>
       </c>
-      <c r="P38" s="3">
+      <c r="P38" s="4">
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
-      <c r="Q38" s="3">
+      <c r="Q38" s="4">
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
@@ -5073,10 +5064,10 @@
       <c r="S38" s="1">
         <v>0</v>
       </c>
-      <c r="T38" s="7">
-        <v>0</v>
-      </c>
-      <c r="U38" s="7">
+      <c r="T38" s="8">
+        <v>0</v>
+      </c>
+      <c r="U38" s="8">
         <v>0</v>
       </c>
       <c r="V38" s="1">
@@ -5093,17 +5084,17 @@
       <c r="Y38" s="1">
         <v>33</v>
       </c>
-      <c r="Z38" s="3">
+      <c r="Z38" s="4">
         <f>Z37+1000</f>
         <v>10000</v>
       </c>
-      <c r="AA38" s="3">
+      <c r="AA38" s="4">
         <v>107</v>
       </c>
-      <c r="AB38" s="3">
+      <c r="AB38" s="4">
         <v>32</v>
       </c>
-      <c r="AC38" s="3">
+      <c r="AC38" s="4">
         <f t="shared" si="8"/>
         <v>1963</v>
       </c>
@@ -5114,7 +5105,7 @@
       <c r="AF38" s="1">
         <v>0</v>
       </c>
-      <c r="AG38" s="3">
+      <c r="AG38" s="4">
         <v>137</v>
       </c>
     </row>
@@ -5128,23 +5119,20 @@
       <c r="E39" s="1">
         <v>1</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="1">
         <v>34</v>
       </c>
       <c r="H39" s="1">
-        <f t="shared" si="11"/>
-        <v>19750800</v>
+        <v>4000000</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="12"/>
-        <v>5187600</v>
+        <v>2800000</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="13"/>
-        <v>856800000</v>
+        <v>51000000</v>
       </c>
       <c r="K39" s="1">
         <f t="shared" si="0"/>
@@ -5165,11 +5153,11 @@
       <c r="O39" s="1">
         <v>33</v>
       </c>
-      <c r="P39" s="3">
+      <c r="P39" s="4">
         <f t="shared" si="6"/>
         <v>33</v>
       </c>
-      <c r="Q39" s="3">
+      <c r="Q39" s="4">
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
@@ -5179,10 +5167,10 @@
       <c r="S39" s="1">
         <v>0</v>
       </c>
-      <c r="T39" s="7">
-        <v>0</v>
-      </c>
-      <c r="U39" s="7">
+      <c r="T39" s="8">
+        <v>0</v>
+      </c>
+      <c r="U39" s="8">
         <v>0</v>
       </c>
       <c r="V39" s="1">
@@ -5199,17 +5187,17 @@
       <c r="Y39" s="1">
         <v>34</v>
       </c>
-      <c r="Z39" s="3">
-        <f t="shared" ref="Z39:Z45" si="14">Z38+2000</f>
+      <c r="Z39" s="4">
+        <f t="shared" ref="Z39:Z45" si="11">Z38+2000</f>
         <v>12000</v>
       </c>
-      <c r="AA39" s="3">
+      <c r="AA39" s="4">
         <v>109</v>
       </c>
-      <c r="AB39" s="3">
+      <c r="AB39" s="4">
         <v>33</v>
       </c>
-      <c r="AC39" s="3">
+      <c r="AC39" s="4">
         <f t="shared" si="8"/>
         <v>2100</v>
       </c>
@@ -5220,7 +5208,7 @@
       <c r="AF39" s="1">
         <v>0</v>
       </c>
-      <c r="AG39" s="3">
+      <c r="AG39" s="4">
         <v>139</v>
       </c>
     </row>
@@ -5234,23 +5222,20 @@
       <c r="E40" s="1">
         <v>1</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G40" s="1">
         <v>35</v>
       </c>
       <c r="H40" s="1">
-        <f t="shared" si="11"/>
-        <v>24837400</v>
+        <v>4800000</v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="12"/>
-        <v>6521200</v>
+        <v>3500000</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="13"/>
-        <v>1097110000</v>
+        <v>58000000</v>
       </c>
       <c r="K40" s="1">
         <f t="shared" si="0"/>
@@ -5271,11 +5256,11 @@
       <c r="O40" s="1">
         <v>34</v>
       </c>
-      <c r="P40" s="3">
+      <c r="P40" s="4">
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-      <c r="Q40" s="3">
+      <c r="Q40" s="4">
         <f t="shared" si="7"/>
         <v>43</v>
       </c>
@@ -5285,10 +5270,10 @@
       <c r="S40" s="1">
         <v>0</v>
       </c>
-      <c r="T40" s="7">
-        <v>0</v>
-      </c>
-      <c r="U40" s="7">
+      <c r="T40" s="8">
+        <v>0</v>
+      </c>
+      <c r="U40" s="8">
         <v>0</v>
       </c>
       <c r="V40" s="1">
@@ -5305,17 +5290,17 @@
       <c r="Y40" s="1">
         <v>35</v>
       </c>
-      <c r="Z40" s="3">
-        <f t="shared" si="14"/>
+      <c r="Z40" s="4">
+        <f t="shared" si="11"/>
         <v>14000</v>
       </c>
-      <c r="AA40" s="3">
+      <c r="AA40" s="4">
         <v>113</v>
       </c>
-      <c r="AB40" s="3">
+      <c r="AB40" s="4">
         <v>34</v>
       </c>
-      <c r="AC40" s="3">
+      <c r="AC40" s="4">
         <f t="shared" si="8"/>
         <v>2239</v>
       </c>
@@ -5330,114 +5315,111 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A41" s="3"/>
-      <c r="C41" s="1">
+    <row r="41" s="3" customFormat="1" customHeight="1" spans="1:33">
+      <c r="A41" s="2"/>
+      <c r="C41" s="3">
         <v>36</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="3">
         <v>36</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="3">
         <v>1</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" s="3">
         <v>36</v>
       </c>
       <c r="H41" s="1">
-        <f t="shared" si="11"/>
-        <v>33121600</v>
+        <v>5700000</v>
       </c>
       <c r="I41" s="1">
-        <f t="shared" si="12"/>
-        <v>7784000</v>
+        <v>4300000</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="13"/>
-        <v>1375488000</v>
-      </c>
-      <c r="K41" s="1">
+        <v>66000000</v>
+      </c>
+      <c r="K41" s="3">
         <f t="shared" si="0"/>
         <v>180</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L41" s="3">
         <f t="shared" si="1"/>
         <v>108</v>
       </c>
-      <c r="M41" s="1">
+      <c r="M41" s="3">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N41" s="3">
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="O41" s="1">
+      <c r="O41" s="3">
         <v>35</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="2">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="2">
         <f t="shared" si="7"/>
         <v>44</v>
       </c>
-      <c r="R41" s="1">
-        <v>0</v>
-      </c>
-      <c r="S41" s="1">
-        <v>0</v>
-      </c>
-      <c r="T41" s="7">
-        <v>0</v>
-      </c>
-      <c r="U41" s="7">
-        <v>0</v>
-      </c>
-      <c r="V41" s="1">
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2">
+        <v>0</v>
+      </c>
+      <c r="U41" s="2">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <f t="shared" si="4"/>
         <v>360</v>
       </c>
-      <c r="W41" s="1">
+      <c r="W41" s="3">
         <f t="shared" si="5"/>
         <v>360</v>
       </c>
-      <c r="X41" s="1">
+      <c r="X41" s="3">
         <v>36</v>
       </c>
-      <c r="Y41" s="1">
+      <c r="Y41" s="3">
         <v>36</v>
       </c>
-      <c r="Z41" s="3">
-        <f t="shared" si="14"/>
+      <c r="Z41" s="2">
+        <f t="shared" si="11"/>
         <v>16000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="2">
         <v>127</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="2">
         <v>35</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="2">
         <f t="shared" si="8"/>
         <v>2388</v>
       </c>
-      <c r="AD41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="1">
+      <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
         <v>151</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A42" s="3"/>
+      <c r="A42" s="4"/>
       <c r="C42" s="1">
         <v>37</v>
       </c>
@@ -5454,15 +5436,15 @@
         <v>37</v>
       </c>
       <c r="H42" s="1">
-        <f t="shared" si="11"/>
+        <f>AG44*Z42*AA42/10</f>
         <v>39378600</v>
       </c>
       <c r="I42" s="1">
-        <f t="shared" si="12"/>
+        <f>AB42*AG40*Z42/10</f>
         <v>9655200</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="13"/>
+        <f>Y42*Z42*AC42</f>
         <v>1690974000</v>
       </c>
       <c r="K42" s="1">
@@ -5484,11 +5466,11 @@
       <c r="O42" s="1">
         <v>36</v>
       </c>
-      <c r="P42" s="3">
+      <c r="P42" s="4">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="Q42" s="4">
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
@@ -5498,10 +5480,10 @@
       <c r="S42" s="1">
         <v>0</v>
       </c>
-      <c r="T42" s="7">
-        <v>0</v>
-      </c>
-      <c r="U42" s="7">
+      <c r="T42" s="8">
+        <v>0</v>
+      </c>
+      <c r="U42" s="8">
         <v>0</v>
       </c>
       <c r="V42" s="1">
@@ -5518,17 +5500,17 @@
       <c r="Y42" s="1">
         <v>37</v>
       </c>
-      <c r="Z42" s="3">
-        <f t="shared" si="14"/>
+      <c r="Z42" s="4">
+        <f t="shared" si="11"/>
         <v>18000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="4">
         <v>131</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="4">
         <v>36</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="4">
         <f t="shared" si="8"/>
         <v>2539</v>
       </c>
@@ -5543,7 +5525,7 @@
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A43" s="3"/>
+      <c r="A43" s="4"/>
       <c r="C43" s="1">
         <v>38</v>
       </c>
@@ -5553,22 +5535,22 @@
       <c r="E43" s="1">
         <v>1</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="7" t="s">
         <v>72</v>
       </c>
       <c r="G43" s="1">
         <v>38</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" si="11"/>
+        <f>AG45*Z43*AA43/10</f>
         <v>47402000</v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="12"/>
+        <f>AB43*AG41*Z43/10</f>
         <v>11174000</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="13"/>
+        <f>Y43*Z43*AC43</f>
         <v>2048960000</v>
       </c>
       <c r="K43" s="1">
@@ -5590,11 +5572,11 @@
       <c r="O43" s="1">
         <v>37</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="4">
         <f t="shared" si="6"/>
         <v>37</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="4">
         <f t="shared" si="7"/>
         <v>46</v>
       </c>
@@ -5604,10 +5586,10 @@
       <c r="S43" s="1">
         <v>0</v>
       </c>
-      <c r="T43" s="7">
-        <v>0</v>
-      </c>
-      <c r="U43" s="7">
+      <c r="T43" s="8">
+        <v>0</v>
+      </c>
+      <c r="U43" s="8">
         <v>0</v>
       </c>
       <c r="V43" s="1">
@@ -5624,17 +5606,17 @@
       <c r="Y43" s="1">
         <v>38</v>
       </c>
-      <c r="Z43" s="3">
-        <f t="shared" si="14"/>
+      <c r="Z43" s="4">
+        <f t="shared" si="11"/>
         <v>20000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="4">
         <v>137</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="4">
         <v>37</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="4">
         <f t="shared" si="8"/>
         <v>2696</v>
       </c>
@@ -5649,7 +5631,7 @@
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A44" s="3"/>
+      <c r="A44" s="4"/>
       <c r="C44" s="1">
         <v>39</v>
       </c>
@@ -5666,15 +5648,15 @@
         <v>39</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="11"/>
+        <f>AG46*Z44*AA44/10</f>
         <v>62202500</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="12"/>
+        <f>AB44*AG42*Z44/10</f>
         <v>14915000</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="13"/>
+        <f>Y44*Z44*AC44</f>
         <v>2787525000</v>
       </c>
       <c r="K44" s="1">
@@ -5696,11 +5678,11 @@
       <c r="O44" s="1">
         <v>38</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="4">
         <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="4">
         <f t="shared" si="7"/>
         <v>47</v>
       </c>
@@ -5710,10 +5692,10 @@
       <c r="S44" s="1">
         <v>0</v>
       </c>
-      <c r="T44" s="7">
-        <v>0</v>
-      </c>
-      <c r="U44" s="7">
+      <c r="T44" s="8">
+        <v>0</v>
+      </c>
+      <c r="U44" s="8">
         <v>0</v>
       </c>
       <c r="V44" s="1">
@@ -5730,17 +5712,17 @@
       <c r="Y44" s="1">
         <v>39</v>
       </c>
-      <c r="Z44" s="3">
-        <f t="shared" ref="Z44:Z77" si="15">Z43+5000</f>
+      <c r="Z44" s="4">
+        <f t="shared" ref="Z44:Z77" si="12">Z43+5000</f>
         <v>25000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="4">
         <v>139</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AB44" s="4">
         <v>38</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AC44" s="4">
         <f t="shared" si="8"/>
         <v>2859</v>
       </c>
@@ -5755,7 +5737,7 @@
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A45" s="3"/>
+      <c r="A45" s="4"/>
       <c r="C45" s="1">
         <v>40</v>
       </c>
@@ -5765,22 +5747,22 @@
       <c r="E45" s="1">
         <v>1</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="7" t="s">
         <v>74</v>
       </c>
       <c r="G45" s="1">
         <v>40</v>
       </c>
       <c r="H45" s="1">
-        <f t="shared" si="11"/>
+        <f>AG47*Z45*AA45/10</f>
         <v>80907000</v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="12"/>
+        <f>AB45*AG43*Z45/10</f>
         <v>19071000</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="13"/>
+        <f>Y45*Z45*AC45</f>
         <v>3631200000</v>
       </c>
       <c r="K45" s="1">
@@ -5802,11 +5784,11 @@
       <c r="O45" s="1">
         <v>39</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="4">
         <f t="shared" si="6"/>
         <v>39</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="4">
         <f t="shared" si="7"/>
         <v>48</v>
       </c>
@@ -5816,10 +5798,10 @@
       <c r="S45" s="1">
         <v>0</v>
       </c>
-      <c r="T45" s="7">
-        <v>0</v>
-      </c>
-      <c r="U45" s="7">
+      <c r="T45" s="8">
+        <v>0</v>
+      </c>
+      <c r="U45" s="8">
         <v>0</v>
       </c>
       <c r="V45" s="1">
@@ -5836,17 +5818,17 @@
       <c r="Y45" s="1">
         <v>40</v>
       </c>
-      <c r="Z45" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z45" s="4">
+        <f t="shared" si="12"/>
         <v>30000</v>
       </c>
       <c r="AA45" s="1">
         <v>149</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="4">
         <v>39</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="4">
         <f t="shared" si="8"/>
         <v>3026</v>
       </c>
@@ -5861,7 +5843,7 @@
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A46" s="3"/>
+      <c r="A46" s="4"/>
       <c r="C46" s="1">
         <v>41</v>
       </c>
@@ -5878,15 +5860,15 @@
         <v>41</v>
       </c>
       <c r="H46" s="1">
-        <f t="shared" si="11"/>
+        <f>AG48*Z46*AA46/10</f>
         <v>100943500</v>
       </c>
       <c r="I46" s="1">
-        <f t="shared" si="12"/>
+        <f>AB46*AG44*Z46/10</f>
         <v>22795500</v>
       </c>
       <c r="J46" s="1">
-        <f t="shared" si="13"/>
+        <f>Y46*Z46*AC46</f>
         <v>4478600000</v>
       </c>
       <c r="K46" s="1">
@@ -5908,11 +5890,11 @@
       <c r="O46" s="1">
         <v>40</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="4">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="4">
         <f t="shared" si="7"/>
         <v>49</v>
       </c>
@@ -5922,10 +5904,10 @@
       <c r="S46" s="1">
         <v>0</v>
       </c>
-      <c r="T46" s="7">
-        <v>0</v>
-      </c>
-      <c r="U46" s="7">
+      <c r="T46" s="8">
+        <v>0</v>
+      </c>
+      <c r="U46" s="8">
         <v>0</v>
       </c>
       <c r="V46" s="1">
@@ -5942,17 +5924,17 @@
       <c r="Y46" s="1">
         <v>40</v>
       </c>
-      <c r="Z46" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z46" s="4">
+        <f t="shared" si="12"/>
         <v>35000</v>
       </c>
       <c r="AA46" s="1">
         <v>151</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AB46" s="4">
         <v>39</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AC46" s="4">
         <f t="shared" si="8"/>
         <v>3199</v>
       </c>
@@ -5962,7 +5944,7 @@
       <c r="AF46" s="1">
         <v>0</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AG46" s="4">
         <v>179</v>
       </c>
     </row>
@@ -5983,15 +5965,15 @@
         <v>42</v>
       </c>
       <c r="H47" s="1">
-        <f t="shared" si="11"/>
+        <f>AG49*Z47*AA47/10</f>
         <v>116572000</v>
       </c>
       <c r="I47" s="1">
-        <f t="shared" si="12"/>
+        <f>AB47*AG45*Z47/10</f>
         <v>26988000</v>
       </c>
       <c r="J47" s="1">
-        <f t="shared" si="13"/>
+        <f>Y47*Z47*AC47</f>
         <v>5404800000</v>
       </c>
       <c r="K47" s="1">
@@ -6013,11 +5995,11 @@
       <c r="O47" s="1">
         <v>41</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="4">
         <f t="shared" si="6"/>
         <v>41</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="4">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
@@ -6027,10 +6009,10 @@
       <c r="S47" s="1">
         <v>0</v>
       </c>
-      <c r="T47" s="7">
-        <v>0</v>
-      </c>
-      <c r="U47" s="7">
+      <c r="T47" s="8">
+        <v>0</v>
+      </c>
+      <c r="U47" s="8">
         <v>0</v>
       </c>
       <c r="V47" s="1">
@@ -6047,17 +6029,17 @@
       <c r="Y47" s="1">
         <v>40</v>
       </c>
-      <c r="Z47" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z47" s="4">
+        <f t="shared" si="12"/>
         <v>40000</v>
       </c>
       <c r="AA47" s="1">
         <v>151</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="4">
         <v>39</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="4">
         <f t="shared" si="8"/>
         <v>3378</v>
       </c>
@@ -6068,7 +6050,7 @@
       <c r="AF47" s="1">
         <v>0</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="4">
         <v>181</v>
       </c>
     </row>
@@ -6082,22 +6064,22 @@
       <c r="E48" s="1">
         <v>1</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="7" t="s">
         <v>77</v>
       </c>
       <c r="G48" s="1">
         <v>43</v>
       </c>
       <c r="H48" s="1">
-        <f t="shared" si="11"/>
+        <f>AG50*Z48*AA48/10</f>
         <v>139180500</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="12"/>
+        <f>AB48*AG46*Z48/10</f>
         <v>31414500</v>
       </c>
       <c r="J48" s="1">
-        <f t="shared" si="13"/>
+        <f>Y48*Z48*AC48</f>
         <v>6406200000</v>
       </c>
       <c r="K48" s="1">
@@ -6119,11 +6101,11 @@
       <c r="O48" s="1">
         <v>42</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="4">
         <f t="shared" si="6"/>
         <v>42</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="4">
         <f t="shared" si="7"/>
         <v>51</v>
       </c>
@@ -6133,10 +6115,10 @@
       <c r="S48" s="1">
         <v>0</v>
       </c>
-      <c r="T48" s="7">
-        <v>0</v>
-      </c>
-      <c r="U48" s="7">
+      <c r="T48" s="8">
+        <v>0</v>
+      </c>
+      <c r="U48" s="8">
         <v>0</v>
       </c>
       <c r="V48" s="1">
@@ -6153,17 +6135,17 @@
       <c r="Y48" s="1">
         <v>40</v>
       </c>
-      <c r="Z48" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z48" s="4">
+        <f t="shared" si="12"/>
         <v>45000</v>
       </c>
       <c r="AA48" s="1">
         <v>157</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="4">
         <v>39</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="4">
         <f t="shared" si="8"/>
         <v>3559</v>
       </c>
@@ -6174,7 +6156,7 @@
       <c r="AF48" s="1">
         <v>0</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="4">
         <v>191</v>
       </c>
     </row>
@@ -6188,22 +6170,22 @@
       <c r="E49" s="1">
         <v>1</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="7" t="s">
         <v>78</v>
       </c>
       <c r="G49" s="1">
         <v>44</v>
       </c>
       <c r="H49" s="1">
-        <f t="shared" si="11"/>
+        <f>AG51*Z49*AA49/10</f>
         <v>172135000</v>
       </c>
       <c r="I49" s="1">
-        <f t="shared" si="12"/>
+        <f>AB49*AG47*Z49/10</f>
         <v>35295000</v>
       </c>
       <c r="J49" s="1">
-        <f t="shared" si="13"/>
+        <f>Y49*Z49*AC49</f>
         <v>7500000000</v>
       </c>
       <c r="K49" s="1">
@@ -6225,11 +6207,11 @@
       <c r="O49" s="1">
         <v>43</v>
       </c>
-      <c r="P49" s="3">
+      <c r="P49" s="4">
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="Q49" s="4">
         <f t="shared" si="7"/>
         <v>52</v>
       </c>
@@ -6239,10 +6221,10 @@
       <c r="S49" s="1">
         <v>0</v>
       </c>
-      <c r="T49" s="7">
-        <v>0</v>
-      </c>
-      <c r="U49" s="7">
+      <c r="T49" s="8">
+        <v>0</v>
+      </c>
+      <c r="U49" s="8">
         <v>0</v>
       </c>
       <c r="V49" s="1">
@@ -6259,17 +6241,17 @@
       <c r="Y49" s="1">
         <v>40</v>
       </c>
-      <c r="Z49" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z49" s="4">
+        <f t="shared" si="12"/>
         <v>50000</v>
       </c>
       <c r="AA49" s="1">
         <v>173</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="4">
         <v>39</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="4">
         <f t="shared" si="8"/>
         <v>3750</v>
       </c>
@@ -6280,7 +6262,7 @@
       <c r="AF49" s="1">
         <v>0</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="4">
         <v>193</v>
       </c>
     </row>
@@ -6294,22 +6276,22 @@
       <c r="E50" s="1">
         <v>1</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="7" t="s">
         <v>79</v>
       </c>
       <c r="G50" s="1">
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <f t="shared" si="11"/>
+        <f>AG52*Z50*AA50/10</f>
         <v>200766500</v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" si="12"/>
+        <f>AB50*AG48*Z50/10</f>
         <v>40969500</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" si="13"/>
+        <f>Y50*Z50*AC50</f>
         <v>8674600000</v>
       </c>
       <c r="K50" s="1">
@@ -6331,11 +6313,11 @@
       <c r="O50" s="1">
         <v>44</v>
       </c>
-      <c r="P50" s="3">
+      <c r="P50" s="4">
         <f t="shared" si="6"/>
         <v>44</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="Q50" s="4">
         <f t="shared" si="7"/>
         <v>53</v>
       </c>
@@ -6345,10 +6327,10 @@
       <c r="S50" s="1">
         <v>0</v>
       </c>
-      <c r="T50" s="7">
-        <v>0</v>
-      </c>
-      <c r="U50" s="7">
+      <c r="T50" s="8">
+        <v>0</v>
+      </c>
+      <c r="U50" s="8">
         <v>0</v>
       </c>
       <c r="V50" s="1">
@@ -6365,17 +6347,17 @@
       <c r="Y50" s="1">
         <v>40</v>
       </c>
-      <c r="Z50" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z50" s="4">
+        <f t="shared" si="12"/>
         <v>55000</v>
       </c>
       <c r="AA50" s="1">
         <v>173</v>
       </c>
-      <c r="AB50" s="3">
+      <c r="AB50" s="4">
         <v>39</v>
       </c>
-      <c r="AC50" s="3">
+      <c r="AC50" s="4">
         <f t="shared" si="8"/>
         <v>3943</v>
       </c>
@@ -6386,7 +6368,7 @@
       <c r="AF50" s="1">
         <v>0</v>
       </c>
-      <c r="AG50" s="3">
+      <c r="AG50" s="4">
         <v>197</v>
       </c>
     </row>
@@ -6407,15 +6389,15 @@
         <v>46</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="11"/>
+        <f>AG53*Z51*AA51/10</f>
         <v>231474000</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="12"/>
+        <f>AB51*AG49*Z51/10</f>
         <v>45162000</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" si="13"/>
+        <f>Y51*Z51*AC51</f>
         <v>9936000000</v>
       </c>
       <c r="K51" s="1">
@@ -6437,11 +6419,11 @@
       <c r="O51" s="1">
         <v>45</v>
       </c>
-      <c r="P51" s="3">
+      <c r="P51" s="4">
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="Q51" s="4">
         <f t="shared" si="7"/>
         <v>54</v>
       </c>
@@ -6451,10 +6433,10 @@
       <c r="S51" s="1">
         <v>0</v>
       </c>
-      <c r="T51" s="7">
-        <v>0</v>
-      </c>
-      <c r="U51" s="7">
+      <c r="T51" s="8">
+        <v>0</v>
+      </c>
+      <c r="U51" s="8">
         <v>0</v>
       </c>
       <c r="V51" s="1">
@@ -6471,17 +6453,17 @@
       <c r="Y51" s="1">
         <v>40</v>
       </c>
-      <c r="Z51" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z51" s="4">
+        <f t="shared" si="12"/>
         <v>60000</v>
       </c>
       <c r="AA51" s="1">
         <v>173</v>
       </c>
-      <c r="AB51" s="3">
+      <c r="AB51" s="4">
         <v>39</v>
       </c>
-      <c r="AC51" s="3">
+      <c r="AC51" s="4">
         <f t="shared" si="8"/>
         <v>4140</v>
       </c>
@@ -6492,7 +6474,7 @@
       <c r="AF51" s="1">
         <v>0</v>
       </c>
-      <c r="AG51" s="3">
+      <c r="AG51" s="4">
         <v>199</v>
       </c>
     </row>
@@ -6506,22 +6488,22 @@
       <c r="E52" s="1">
         <v>1</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="7" t="s">
         <v>81</v>
       </c>
       <c r="G52" s="1">
         <v>47</v>
       </c>
       <c r="H52" s="1">
-        <f t="shared" si="11"/>
+        <f>AG54*Z52*AA52/10</f>
         <v>255261500</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="12"/>
+        <f>AB52*AG50*Z52/10</f>
         <v>49939500</v>
       </c>
       <c r="J52" s="1">
-        <f t="shared" si="13"/>
+        <f>Y52*Z52*AC52</f>
         <v>11281400000</v>
       </c>
       <c r="K52" s="1">
@@ -6543,11 +6525,11 @@
       <c r="O52" s="1">
         <v>46</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="4">
         <f t="shared" si="6"/>
         <v>46</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="4">
         <f t="shared" si="7"/>
         <v>55</v>
       </c>
@@ -6557,10 +6539,10 @@
       <c r="S52" s="1">
         <v>0</v>
       </c>
-      <c r="T52" s="7">
-        <v>0</v>
-      </c>
-      <c r="U52" s="7">
+      <c r="T52" s="8">
+        <v>0</v>
+      </c>
+      <c r="U52" s="8">
         <v>0</v>
       </c>
       <c r="V52" s="1">
@@ -6577,17 +6559,17 @@
       <c r="Y52" s="1">
         <v>40</v>
       </c>
-      <c r="Z52" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z52" s="4">
+        <f t="shared" si="12"/>
         <v>65000</v>
       </c>
       <c r="AA52" s="1">
         <v>173</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="4">
         <v>39</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="4">
         <f t="shared" si="8"/>
         <v>4339</v>
       </c>
@@ -6598,7 +6580,7 @@
       <c r="AF52" s="1">
         <v>0</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="4">
         <v>211</v>
       </c>
     </row>
@@ -6612,22 +6594,22 @@
       <c r="E53" s="1">
         <v>1</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="5" t="s">
         <v>82</v>
       </c>
       <c r="G53" s="1">
         <v>48</v>
       </c>
       <c r="H53" s="1">
-        <f t="shared" si="11"/>
+        <f>AG55*Z53*AA53/10</f>
         <v>277319000</v>
       </c>
       <c r="I53" s="1">
-        <f t="shared" si="12"/>
+        <f>AB53*AG51*Z53/10</f>
         <v>54327000</v>
       </c>
       <c r="J53" s="1">
-        <f t="shared" si="13"/>
+        <f>Y53*Z53*AC53</f>
         <v>12740000000</v>
       </c>
       <c r="K53" s="1">
@@ -6649,11 +6631,11 @@
       <c r="O53" s="1">
         <v>47</v>
       </c>
-      <c r="P53" s="3">
+      <c r="P53" s="4">
         <f t="shared" si="6"/>
         <v>47</v>
       </c>
-      <c r="Q53" s="3">
+      <c r="Q53" s="4">
         <f t="shared" si="7"/>
         <v>56</v>
       </c>
@@ -6663,10 +6645,10 @@
       <c r="S53" s="1">
         <v>0</v>
       </c>
-      <c r="T53" s="7">
-        <v>0</v>
-      </c>
-      <c r="U53" s="7">
+      <c r="T53" s="8">
+        <v>0</v>
+      </c>
+      <c r="U53" s="8">
         <v>0</v>
       </c>
       <c r="V53" s="1">
@@ -6683,17 +6665,17 @@
       <c r="Y53" s="1">
         <v>40</v>
       </c>
-      <c r="Z53" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z53" s="4">
+        <f t="shared" si="12"/>
         <v>70000</v>
       </c>
       <c r="AA53" s="1">
         <v>173</v>
       </c>
-      <c r="AB53" s="3">
+      <c r="AB53" s="4">
         <v>39</v>
       </c>
-      <c r="AC53" s="3">
+      <c r="AC53" s="4">
         <f t="shared" si="8"/>
         <v>4550</v>
       </c>
@@ -6704,7 +6686,7 @@
       <c r="AF53" s="1">
         <v>0</v>
       </c>
-      <c r="AG53" s="3">
+      <c r="AG53" s="4">
         <v>223</v>
       </c>
     </row>
@@ -6718,22 +6700,22 @@
       <c r="E54" s="1">
         <v>1</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="7" t="s">
         <v>83</v>
       </c>
       <c r="G54" s="1">
         <v>49</v>
       </c>
       <c r="H54" s="1">
-        <f t="shared" si="11"/>
+        <f>AG56*Z54*AA54/10</f>
         <v>302317500</v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="12"/>
+        <f>AB54*AG52*Z54/10</f>
         <v>61717500</v>
       </c>
       <c r="J54" s="1">
-        <f t="shared" si="13"/>
+        <f>Y54*Z54*AC54</f>
         <v>14319000000</v>
       </c>
       <c r="K54" s="1">
@@ -6755,11 +6737,11 @@
       <c r="O54" s="1">
         <v>48</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="4">
         <f t="shared" si="6"/>
         <v>48</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="4">
         <f t="shared" si="7"/>
         <v>57</v>
       </c>
@@ -6769,10 +6751,10 @@
       <c r="S54" s="1">
         <v>0</v>
       </c>
-      <c r="T54" s="7">
-        <v>0</v>
-      </c>
-      <c r="U54" s="7">
+      <c r="T54" s="8">
+        <v>0</v>
+      </c>
+      <c r="U54" s="8">
         <v>0</v>
       </c>
       <c r="V54" s="1">
@@ -6789,17 +6771,17 @@
       <c r="Y54" s="1">
         <v>40</v>
       </c>
-      <c r="Z54" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z54" s="4">
+        <f t="shared" si="12"/>
         <v>75000</v>
       </c>
       <c r="AA54" s="1">
         <v>173</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="4">
         <v>39</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="4">
         <f t="shared" si="8"/>
         <v>4773</v>
       </c>
@@ -6810,7 +6792,7 @@
       <c r="AF54" s="1">
         <v>0</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="4">
         <v>227</v>
       </c>
     </row>
@@ -6824,22 +6806,22 @@
       <c r="E55" s="1">
         <v>1</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="7" t="s">
         <v>84</v>
       </c>
       <c r="G55" s="1">
         <v>50</v>
       </c>
       <c r="H55" s="1">
-        <f t="shared" si="11"/>
+        <f>AG57*Z55*AA55/10</f>
         <v>330776000</v>
       </c>
       <c r="I55" s="1">
-        <f t="shared" si="12"/>
+        <f>AB55*AG53*Z55/10</f>
         <v>69576000</v>
       </c>
       <c r="J55" s="1">
-        <f t="shared" si="13"/>
+        <f>Y55*Z55*AC55</f>
         <v>16000000000</v>
       </c>
       <c r="K55" s="1">
@@ -6861,11 +6843,11 @@
       <c r="O55" s="1">
         <v>49</v>
       </c>
-      <c r="P55" s="3">
+      <c r="P55" s="4">
         <f t="shared" si="6"/>
         <v>49</v>
       </c>
-      <c r="Q55" s="3">
+      <c r="Q55" s="4">
         <f t="shared" si="7"/>
         <v>58</v>
       </c>
@@ -6875,10 +6857,10 @@
       <c r="S55" s="1">
         <v>0</v>
       </c>
-      <c r="T55" s="7">
-        <v>0</v>
-      </c>
-      <c r="U55" s="7">
+      <c r="T55" s="8">
+        <v>0</v>
+      </c>
+      <c r="U55" s="8">
         <v>0</v>
       </c>
       <c r="V55" s="1">
@@ -6895,17 +6877,17 @@
       <c r="Y55" s="1">
         <v>40</v>
       </c>
-      <c r="Z55" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z55" s="4">
+        <f t="shared" si="12"/>
         <v>80000</v>
       </c>
       <c r="AA55" s="1">
         <v>173</v>
       </c>
-      <c r="AB55" s="3">
+      <c r="AB55" s="4">
         <v>39</v>
       </c>
-      <c r="AC55" s="3">
+      <c r="AC55" s="4">
         <f t="shared" si="8"/>
         <v>5000</v>
       </c>
@@ -6916,7 +6898,7 @@
       <c r="AF55" s="1">
         <v>0</v>
       </c>
-      <c r="AG55" s="3">
+      <c r="AG55" s="4">
         <v>229</v>
       </c>
     </row>
@@ -6930,22 +6912,22 @@
       <c r="E56" s="1">
         <v>1</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="7" t="s">
         <v>85</v>
       </c>
       <c r="G56" s="1">
         <v>51</v>
       </c>
       <c r="H56" s="1">
-        <f t="shared" si="11"/>
+        <f>AG58*Z56*AA56/10</f>
         <v>354390500</v>
       </c>
       <c r="I56" s="1">
-        <f t="shared" si="12"/>
+        <f>AB56*AG54*Z56/10</f>
         <v>75250500</v>
       </c>
       <c r="J56" s="1">
-        <f t="shared" si="13"/>
+        <f>Y56*Z56*AC56</f>
         <v>17778600000</v>
       </c>
       <c r="K56" s="1">
@@ -6967,11 +6949,11 @@
       <c r="O56" s="1">
         <v>50</v>
       </c>
-      <c r="P56" s="3">
+      <c r="P56" s="4">
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="Q56" s="4">
         <f t="shared" si="7"/>
         <v>59</v>
       </c>
@@ -6981,10 +6963,10 @@
       <c r="S56" s="1">
         <v>0</v>
       </c>
-      <c r="T56" s="7">
-        <v>0</v>
-      </c>
-      <c r="U56" s="7">
+      <c r="T56" s="8">
+        <v>0</v>
+      </c>
+      <c r="U56" s="8">
         <v>0</v>
       </c>
       <c r="V56" s="1">
@@ -7001,17 +6983,17 @@
       <c r="Y56" s="1">
         <v>40</v>
       </c>
-      <c r="Z56" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z56" s="4">
+        <f t="shared" si="12"/>
         <v>85000</v>
       </c>
       <c r="AA56" s="1">
         <v>173</v>
       </c>
-      <c r="AB56" s="3">
+      <c r="AB56" s="4">
         <v>39</v>
       </c>
-      <c r="AC56" s="3">
+      <c r="AC56" s="4">
         <f t="shared" si="8"/>
         <v>5229</v>
       </c>
@@ -7022,7 +7004,7 @@
       <c r="AF56" s="1">
         <v>0</v>
       </c>
-      <c r="AG56" s="3">
+      <c r="AG56" s="4">
         <v>233</v>
       </c>
     </row>
@@ -7036,22 +7018,22 @@
       <c r="E57" s="1">
         <v>1</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="7" t="s">
         <v>86</v>
       </c>
       <c r="G57" s="1">
         <v>52</v>
       </c>
       <c r="H57" s="1">
-        <f t="shared" si="11"/>
+        <f>AG59*Z57*AA57/10</f>
         <v>390807000</v>
       </c>
       <c r="I57" s="1">
-        <f t="shared" si="12"/>
+        <f>AB57*AG55*Z57/10</f>
         <v>80379000</v>
       </c>
       <c r="J57" s="1">
-        <f t="shared" si="13"/>
+        <f>Y57*Z57*AC57</f>
         <v>19663200000</v>
       </c>
       <c r="K57" s="1">
@@ -7073,11 +7055,11 @@
       <c r="O57" s="1">
         <v>51</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="4">
         <f t="shared" si="6"/>
         <v>51</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="4">
         <f t="shared" si="7"/>
         <v>60</v>
       </c>
@@ -7087,10 +7069,10 @@
       <c r="S57" s="1">
         <v>0</v>
       </c>
-      <c r="T57" s="7">
-        <v>0</v>
-      </c>
-      <c r="U57" s="7">
+      <c r="T57" s="8">
+        <v>0</v>
+      </c>
+      <c r="U57" s="8">
         <v>0</v>
       </c>
       <c r="V57" s="1">
@@ -7107,17 +7089,17 @@
       <c r="Y57" s="1">
         <v>40</v>
       </c>
-      <c r="Z57" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z57" s="4">
+        <f t="shared" si="12"/>
         <v>90000</v>
       </c>
       <c r="AA57" s="1">
         <v>173</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="4">
         <v>39</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="4">
         <f t="shared" si="8"/>
         <v>5462</v>
       </c>
@@ -7128,7 +7110,7 @@
       <c r="AF57" s="1">
         <v>0</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="4">
         <v>239</v>
       </c>
     </row>
@@ -7142,22 +7124,22 @@
       <c r="E58" s="1">
         <v>1</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="7" t="s">
         <v>87</v>
       </c>
       <c r="G58" s="1">
         <v>53</v>
       </c>
       <c r="H58" s="1">
-        <f t="shared" si="11"/>
+        <f>AG60*Z58*AA58/10</f>
         <v>422379500</v>
       </c>
       <c r="I58" s="1">
-        <f t="shared" si="12"/>
+        <f>AB58*AG56*Z58/10</f>
         <v>86326500</v>
       </c>
       <c r="J58" s="1">
-        <f t="shared" si="13"/>
+        <f>Y58*Z58*AC58</f>
         <v>21663800000</v>
       </c>
       <c r="K58" s="1">
@@ -7179,11 +7161,11 @@
       <c r="O58" s="1">
         <v>52</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="4">
         <f t="shared" si="6"/>
         <v>52</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="4">
         <f t="shared" si="7"/>
         <v>61</v>
       </c>
@@ -7193,10 +7175,10 @@
       <c r="S58" s="1">
         <v>0</v>
       </c>
-      <c r="T58" s="7">
-        <v>0</v>
-      </c>
-      <c r="U58" s="7">
+      <c r="T58" s="8">
+        <v>0</v>
+      </c>
+      <c r="U58" s="8">
         <v>0</v>
       </c>
       <c r="V58" s="1">
@@ -7213,17 +7195,17 @@
       <c r="Y58" s="1">
         <v>40</v>
       </c>
-      <c r="Z58" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z58" s="4">
+        <f t="shared" si="12"/>
         <v>95000</v>
       </c>
       <c r="AA58" s="1">
         <v>173</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="4">
         <v>39</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="4">
         <f t="shared" si="8"/>
         <v>5701</v>
       </c>
@@ -7234,7 +7216,7 @@
       <c r="AF58" s="1">
         <v>0</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="4">
         <v>241</v>
       </c>
     </row>
@@ -7248,22 +7230,22 @@
       <c r="E59" s="1">
         <v>1</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="5" t="s">
         <v>88</v>
       </c>
       <c r="G59" s="1">
         <v>54</v>
       </c>
       <c r="H59" s="1">
-        <f t="shared" si="11"/>
+        <f>AG61*Z59*AA59/10</f>
         <v>454990000</v>
       </c>
       <c r="I59" s="1">
-        <f t="shared" si="12"/>
+        <f>AB59*AG57*Z59/10</f>
         <v>93210000</v>
       </c>
       <c r="J59" s="1">
-        <f t="shared" si="13"/>
+        <f>Y59*Z59*AC59</f>
         <v>23768000000</v>
       </c>
       <c r="K59" s="1">
@@ -7285,11 +7267,11 @@
       <c r="O59" s="1">
         <v>53</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="4">
         <f t="shared" si="6"/>
         <v>53</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="4">
         <f t="shared" si="7"/>
         <v>62</v>
       </c>
@@ -7299,10 +7281,10 @@
       <c r="S59" s="1">
         <v>0</v>
       </c>
-      <c r="T59" s="7">
-        <v>0</v>
-      </c>
-      <c r="U59" s="7">
+      <c r="T59" s="8">
+        <v>0</v>
+      </c>
+      <c r="U59" s="8">
         <v>0</v>
       </c>
       <c r="V59" s="1">
@@ -7319,17 +7301,17 @@
       <c r="Y59" s="1">
         <v>40</v>
       </c>
-      <c r="Z59" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z59" s="4">
+        <f t="shared" si="12"/>
         <v>100000</v>
       </c>
       <c r="AA59" s="1">
         <v>173</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="4">
         <v>39</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="4">
         <f t="shared" si="8"/>
         <v>5942</v>
       </c>
@@ -7340,7 +7322,7 @@
       <c r="AF59" s="1">
         <v>0</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="4">
         <v>251</v>
       </c>
     </row>
@@ -7354,22 +7336,22 @@
       <c r="E60" s="1">
         <v>1</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F60" s="7" t="s">
         <v>89</v>
       </c>
       <c r="G60" s="1">
         <v>55</v>
       </c>
       <c r="H60" s="1">
-        <f t="shared" si="11"/>
+        <f>AG62*Z60*AA60/10</f>
         <v>488638500</v>
       </c>
       <c r="I60" s="1">
-        <f t="shared" si="12"/>
+        <f>AB60*AG58*Z60/10</f>
         <v>98689500</v>
       </c>
       <c r="J60" s="1">
-        <f t="shared" si="13"/>
+        <f>Y60*Z60*AC60</f>
         <v>26010600000</v>
       </c>
       <c r="K60" s="1">
@@ -7391,11 +7373,11 @@
       <c r="O60" s="1">
         <v>54</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="4">
         <f t="shared" si="6"/>
         <v>54</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="4">
         <f t="shared" si="7"/>
         <v>63</v>
       </c>
@@ -7405,10 +7387,10 @@
       <c r="S60" s="1">
         <v>0</v>
       </c>
-      <c r="T60" s="7">
-        <v>0</v>
-      </c>
-      <c r="U60" s="7">
+      <c r="T60" s="8">
+        <v>0</v>
+      </c>
+      <c r="U60" s="8">
         <v>0</v>
       </c>
       <c r="V60" s="1">
@@ -7425,17 +7407,17 @@
       <c r="Y60" s="1">
         <v>40</v>
       </c>
-      <c r="Z60" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z60" s="4">
+        <f t="shared" si="12"/>
         <v>105000</v>
       </c>
       <c r="AA60" s="1">
         <v>173</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AB60" s="4">
         <v>39</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AC60" s="4">
         <f t="shared" si="8"/>
         <v>6193</v>
       </c>
@@ -7446,7 +7428,7 @@
       <c r="AF60" s="1">
         <v>0</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AG60" s="4">
         <v>257</v>
       </c>
     </row>
@@ -7460,22 +7442,22 @@
       <c r="E61" s="1">
         <v>1</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="7" t="s">
         <v>90</v>
       </c>
       <c r="G61" s="1">
         <v>56</v>
       </c>
       <c r="H61" s="1">
-        <f t="shared" si="11"/>
+        <f>AG63*Z61*AA61/10</f>
         <v>515713000</v>
       </c>
       <c r="I61" s="1">
-        <f t="shared" si="12"/>
+        <f>AB61*AG59*Z61/10</f>
         <v>107679000</v>
       </c>
       <c r="J61" s="1">
-        <f t="shared" si="13"/>
+        <f>Y61*Z61*AC61</f>
         <v>28380000000</v>
       </c>
       <c r="K61" s="1">
@@ -7497,11 +7479,11 @@
       <c r="O61" s="1">
         <v>55</v>
       </c>
-      <c r="P61" s="3">
+      <c r="P61" s="4">
         <f t="shared" si="6"/>
         <v>55</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="Q61" s="4">
         <f t="shared" si="7"/>
         <v>64</v>
       </c>
@@ -7511,10 +7493,10 @@
       <c r="S61" s="1">
         <v>0</v>
       </c>
-      <c r="T61" s="7">
-        <v>0</v>
-      </c>
-      <c r="U61" s="7">
+      <c r="T61" s="8">
+        <v>0</v>
+      </c>
+      <c r="U61" s="8">
         <v>0</v>
       </c>
       <c r="V61" s="1">
@@ -7531,17 +7513,17 @@
       <c r="Y61" s="1">
         <v>40</v>
       </c>
-      <c r="Z61" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z61" s="4">
+        <f t="shared" si="12"/>
         <v>110000</v>
       </c>
       <c r="AA61" s="1">
         <v>173</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AB61" s="4">
         <v>39</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AC61" s="4">
         <f t="shared" si="8"/>
         <v>6450</v>
       </c>
@@ -7552,7 +7534,7 @@
       <c r="AF61" s="1">
         <v>0</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AG61" s="4">
         <v>263</v>
       </c>
     </row>
@@ -7566,22 +7548,22 @@
       <c r="E62" s="1">
         <v>1</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="7" t="s">
         <v>91</v>
       </c>
       <c r="G62" s="1">
         <v>57</v>
       </c>
       <c r="H62" s="1">
-        <f t="shared" si="11"/>
+        <f>AG64*Z62*AA62/10</f>
         <v>551091500</v>
       </c>
       <c r="I62" s="1">
-        <f t="shared" si="12"/>
+        <f>AB62*AG60*Z62/10</f>
         <v>115264500</v>
       </c>
       <c r="J62" s="1">
-        <f t="shared" si="13"/>
+        <f>Y62*Z62*AC62</f>
         <v>30879800000</v>
       </c>
       <c r="K62" s="1">
@@ -7603,11 +7585,11 @@
       <c r="O62" s="1">
         <v>56</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="4">
         <f t="shared" si="6"/>
         <v>56</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="4">
         <f t="shared" si="7"/>
         <v>65</v>
       </c>
@@ -7617,10 +7599,10 @@
       <c r="S62" s="1">
         <v>0</v>
       </c>
-      <c r="T62" s="7">
-        <v>0</v>
-      </c>
-      <c r="U62" s="7">
+      <c r="T62" s="8">
+        <v>0</v>
+      </c>
+      <c r="U62" s="8">
         <v>0</v>
       </c>
       <c r="V62" s="1">
@@ -7637,17 +7619,17 @@
       <c r="Y62" s="1">
         <v>40</v>
       </c>
-      <c r="Z62" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z62" s="4">
+        <f t="shared" si="12"/>
         <v>115000</v>
       </c>
       <c r="AA62" s="1">
         <v>173</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="4">
         <v>39</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="4">
         <f t="shared" si="8"/>
         <v>6713</v>
       </c>
@@ -7658,7 +7640,7 @@
       <c r="AF62" s="1">
         <v>0</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="4">
         <v>269</v>
       </c>
     </row>
@@ -7679,15 +7661,15 @@
         <v>58</v>
       </c>
       <c r="H63" s="1">
-        <f t="shared" si="11"/>
+        <f>AG65*Z63*AA63/10</f>
         <v>583356000</v>
       </c>
       <c r="I63" s="1">
-        <f t="shared" si="12"/>
+        <f>AB63*AG61*Z63/10</f>
         <v>123084000</v>
       </c>
       <c r="J63" s="1">
-        <f t="shared" si="13"/>
+        <f>Y63*Z63*AC63</f>
         <v>33513600000</v>
       </c>
       <c r="K63" s="1">
@@ -7709,11 +7691,11 @@
       <c r="O63" s="1">
         <v>57</v>
       </c>
-      <c r="P63" s="3">
+      <c r="P63" s="4">
         <f t="shared" si="6"/>
         <v>57</v>
       </c>
-      <c r="Q63" s="3">
+      <c r="Q63" s="4">
         <f t="shared" si="7"/>
         <v>66</v>
       </c>
@@ -7723,10 +7705,10 @@
       <c r="S63" s="1">
         <v>0</v>
       </c>
-      <c r="T63" s="7">
-        <v>0</v>
-      </c>
-      <c r="U63" s="7">
+      <c r="T63" s="8">
+        <v>0</v>
+      </c>
+      <c r="U63" s="8">
         <v>0</v>
       </c>
       <c r="V63" s="1">
@@ -7743,17 +7725,17 @@
       <c r="Y63" s="1">
         <v>40</v>
       </c>
-      <c r="Z63" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z63" s="4">
+        <f t="shared" si="12"/>
         <v>120000</v>
       </c>
       <c r="AA63" s="1">
         <v>173</v>
       </c>
-      <c r="AB63" s="3">
+      <c r="AB63" s="4">
         <v>39</v>
       </c>
-      <c r="AC63" s="3">
+      <c r="AC63" s="4">
         <f t="shared" si="8"/>
         <v>6982</v>
       </c>
@@ -7764,7 +7746,7 @@
       <c r="AF63" s="1">
         <v>0</v>
       </c>
-      <c r="AG63" s="3">
+      <c r="AG63" s="4">
         <v>271</v>
       </c>
     </row>
@@ -7778,22 +7760,22 @@
       <c r="E64" s="1">
         <v>1</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G64" s="1">
         <v>59</v>
       </c>
       <c r="H64" s="1">
-        <f t="shared" si="11"/>
+        <f>AG66*Z64*AA64/10</f>
         <v>611987500</v>
       </c>
       <c r="I64" s="1">
-        <f t="shared" si="12"/>
+        <f>AB64*AG62*Z64/10</f>
         <v>131137500</v>
       </c>
       <c r="J64" s="1">
-        <f t="shared" si="13"/>
+        <f>Y64*Z64*AC64</f>
         <v>36265000000</v>
       </c>
       <c r="K64" s="1">
@@ -7815,11 +7797,11 @@
       <c r="O64" s="1">
         <v>58</v>
       </c>
-      <c r="P64" s="3">
+      <c r="P64" s="4">
         <f t="shared" si="6"/>
         <v>58</v>
       </c>
-      <c r="Q64" s="3">
+      <c r="Q64" s="4">
         <f t="shared" si="7"/>
         <v>67</v>
       </c>
@@ -7829,10 +7811,10 @@
       <c r="S64" s="1">
         <v>0</v>
       </c>
-      <c r="T64" s="7">
-        <v>0</v>
-      </c>
-      <c r="U64" s="7">
+      <c r="T64" s="8">
+        <v>0</v>
+      </c>
+      <c r="U64" s="8">
         <v>0</v>
       </c>
       <c r="V64" s="1">
@@ -7849,17 +7831,17 @@
       <c r="Y64" s="1">
         <v>40</v>
       </c>
-      <c r="Z64" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z64" s="4">
+        <f t="shared" si="12"/>
         <v>125000</v>
       </c>
       <c r="AA64" s="1">
         <v>173</v>
       </c>
-      <c r="AB64" s="3">
+      <c r="AB64" s="4">
         <v>39</v>
       </c>
-      <c r="AC64" s="3">
+      <c r="AC64" s="4">
         <f t="shared" si="8"/>
         <v>7253</v>
       </c>
@@ -7870,7 +7852,7 @@
       <c r="AF64" s="1">
         <v>0</v>
       </c>
-      <c r="AG64" s="3">
+      <c r="AG64" s="4">
         <v>277</v>
       </c>
     </row>
@@ -7884,22 +7866,22 @@
       <c r="E65" s="1">
         <v>1</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="5" t="s">
         <v>94</v>
       </c>
       <c r="G65" s="1">
         <v>60</v>
       </c>
       <c r="H65" s="1">
-        <f t="shared" si="11"/>
+        <f>AG67*Z65*AA65/10</f>
         <v>658957000</v>
       </c>
       <c r="I65" s="1">
-        <f t="shared" si="12"/>
+        <f>AB65*AG63*Z65/10</f>
         <v>137397000</v>
       </c>
       <c r="J65" s="1">
-        <f t="shared" si="13"/>
+        <f>Y65*Z65*AC65</f>
         <v>39156000000</v>
       </c>
       <c r="K65" s="1">
@@ -7921,11 +7903,11 @@
       <c r="O65" s="1">
         <v>59</v>
       </c>
-      <c r="P65" s="3">
+      <c r="P65" s="4">
         <f t="shared" si="6"/>
         <v>59</v>
       </c>
-      <c r="Q65" s="3">
+      <c r="Q65" s="4">
         <f t="shared" si="7"/>
         <v>68</v>
       </c>
@@ -7935,10 +7917,10 @@
       <c r="S65" s="1">
         <v>0</v>
       </c>
-      <c r="T65" s="7">
-        <v>0</v>
-      </c>
-      <c r="U65" s="7">
+      <c r="T65" s="8">
+        <v>0</v>
+      </c>
+      <c r="U65" s="8">
         <v>0</v>
       </c>
       <c r="V65" s="1">
@@ -7955,17 +7937,17 @@
       <c r="Y65" s="1">
         <v>40</v>
       </c>
-      <c r="Z65" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z65" s="4">
+        <f t="shared" si="12"/>
         <v>130000</v>
       </c>
       <c r="AA65" s="1">
         <v>173</v>
       </c>
-      <c r="AB65" s="3">
+      <c r="AB65" s="4">
         <v>39</v>
       </c>
-      <c r="AC65" s="3">
+      <c r="AC65" s="4">
         <f t="shared" si="8"/>
         <v>7530</v>
       </c>
@@ -7976,7 +7958,7 @@
       <c r="AF65" s="1">
         <v>0</v>
       </c>
-      <c r="AG65" s="3">
+      <c r="AG65" s="4">
         <v>281</v>
       </c>
     </row>
@@ -7990,22 +7972,22 @@
       <c r="E66" s="1">
         <v>1</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G66" s="1">
         <v>61</v>
       </c>
       <c r="H66" s="1">
-        <f t="shared" si="11"/>
+        <f>AG68*Z66*AA66/10</f>
         <v>716998500</v>
       </c>
       <c r="I66" s="1">
-        <f t="shared" si="12"/>
+        <f>AB66*AG64*Z66/10</f>
         <v>145840500</v>
       </c>
       <c r="J66" s="1">
-        <f t="shared" si="13"/>
+        <f>Y66*Z66*AC66</f>
         <v>42179400000</v>
       </c>
       <c r="K66" s="1">
@@ -8027,11 +8009,11 @@
       <c r="O66" s="1">
         <v>60</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="4">
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="4">
         <f t="shared" si="7"/>
         <v>69</v>
       </c>
@@ -8041,10 +8023,10 @@
       <c r="S66" s="1">
         <v>0</v>
       </c>
-      <c r="T66" s="7">
-        <v>0</v>
-      </c>
-      <c r="U66" s="7">
+      <c r="T66" s="8">
+        <v>0</v>
+      </c>
+      <c r="U66" s="8">
         <v>0</v>
       </c>
       <c r="V66" s="1">
@@ -8061,17 +8043,17 @@
       <c r="Y66" s="1">
         <v>40</v>
       </c>
-      <c r="Z66" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z66" s="4">
+        <f t="shared" si="12"/>
         <v>135000</v>
       </c>
       <c r="AA66" s="1">
         <v>173</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="4">
         <v>39</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="4">
         <f t="shared" si="8"/>
         <v>7811</v>
       </c>
@@ -8082,7 +8064,7 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="4">
         <v>283</v>
       </c>
     </row>
@@ -8103,15 +8085,15 @@
         <v>62</v>
       </c>
       <c r="H67" s="1">
-        <f t="shared" si="11"/>
+        <f>AG69*Z67*AA67/10</f>
         <v>753242000</v>
       </c>
       <c r="I67" s="1">
-        <f t="shared" si="12"/>
+        <f>AB67*AG65*Z67/10</f>
         <v>153426000</v>
       </c>
       <c r="J67" s="1">
-        <f t="shared" si="13"/>
+        <f>Y67*Z67*AC67</f>
         <v>45326400000</v>
       </c>
       <c r="K67" s="1">
@@ -8133,11 +8115,11 @@
       <c r="O67" s="1">
         <v>61</v>
       </c>
-      <c r="P67" s="3">
+      <c r="P67" s="4">
         <f t="shared" si="6"/>
         <v>61</v>
       </c>
-      <c r="Q67" s="3">
+      <c r="Q67" s="4">
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
@@ -8147,10 +8129,10 @@
       <c r="S67" s="1">
         <v>0</v>
       </c>
-      <c r="T67" s="7">
-        <v>0</v>
-      </c>
-      <c r="U67" s="7">
+      <c r="T67" s="8">
+        <v>0</v>
+      </c>
+      <c r="U67" s="8">
         <v>0</v>
       </c>
       <c r="V67" s="1">
@@ -8167,17 +8149,17 @@
       <c r="Y67" s="1">
         <v>40</v>
       </c>
-      <c r="Z67" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z67" s="4">
+        <f t="shared" si="12"/>
         <v>140000</v>
       </c>
       <c r="AA67" s="1">
         <v>173</v>
       </c>
-      <c r="AB67" s="3">
+      <c r="AB67" s="4">
         <v>39</v>
       </c>
-      <c r="AC67" s="3">
+      <c r="AC67" s="4">
         <f t="shared" si="8"/>
         <v>8094</v>
       </c>
@@ -8188,7 +8170,7 @@
       <c r="AF67" s="1">
         <v>0</v>
       </c>
-      <c r="AG67" s="3">
+      <c r="AG67" s="4">
         <v>293</v>
       </c>
     </row>
@@ -8202,22 +8184,22 @@
       <c r="E68" s="1">
         <v>1</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="7" t="s">
         <v>97</v>
       </c>
       <c r="G68" s="1">
         <v>63</v>
       </c>
       <c r="H68" s="1">
-        <f t="shared" si="11"/>
+        <f>AG70*Z68*AA68/10</f>
         <v>785160500</v>
       </c>
       <c r="I68" s="1">
-        <f t="shared" si="12"/>
+        <f>AB68*AG66*Z68/10</f>
         <v>160036500</v>
       </c>
       <c r="J68" s="1">
-        <f t="shared" si="13"/>
+        <f>Y68*Z68*AC68</f>
         <v>48644600000</v>
       </c>
       <c r="K68" s="1">
@@ -8239,11 +8221,11 @@
       <c r="O68" s="1">
         <v>62</v>
       </c>
-      <c r="P68" s="3">
+      <c r="P68" s="4">
         <f t="shared" si="6"/>
         <v>62</v>
       </c>
-      <c r="Q68" s="3">
+      <c r="Q68" s="4">
         <f t="shared" si="7"/>
         <v>71</v>
       </c>
@@ -8253,10 +8235,10 @@
       <c r="S68" s="1">
         <v>0</v>
       </c>
-      <c r="T68" s="7">
-        <v>0</v>
-      </c>
-      <c r="U68" s="7">
+      <c r="T68" s="8">
+        <v>0</v>
+      </c>
+      <c r="U68" s="8">
         <v>0</v>
       </c>
       <c r="V68" s="1">
@@ -8273,17 +8255,17 @@
       <c r="Y68" s="1">
         <v>40</v>
       </c>
-      <c r="Z68" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z68" s="4">
+        <f t="shared" si="12"/>
         <v>145000</v>
       </c>
       <c r="AA68" s="1">
         <v>173</v>
       </c>
-      <c r="AB68" s="3">
+      <c r="AB68" s="4">
         <v>39</v>
       </c>
-      <c r="AC68" s="3">
+      <c r="AC68" s="4">
         <f t="shared" si="8"/>
         <v>8387</v>
       </c>
@@ -8294,7 +8276,7 @@
       <c r="AF68" s="1">
         <v>0</v>
       </c>
-      <c r="AG68" s="3">
+      <c r="AG68" s="4">
         <v>307</v>
       </c>
     </row>
@@ -8308,22 +8290,22 @@
       <c r="E69" s="1">
         <v>1</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="7" t="s">
         <v>98</v>
       </c>
       <c r="G69" s="1">
         <v>64</v>
       </c>
       <c r="H69" s="1">
-        <f t="shared" si="11"/>
+        <f>AG71*Z69*AA69/10</f>
         <v>822615000</v>
       </c>
       <c r="I69" s="1">
-        <f t="shared" si="12"/>
+        <f>AB69*AG67*Z69/10</f>
         <v>171405000</v>
       </c>
       <c r="J69" s="1">
-        <f t="shared" si="13"/>
+        <f>Y69*Z69*AC69</f>
         <v>52164000000</v>
       </c>
       <c r="K69" s="1">
@@ -8345,11 +8327,11 @@
       <c r="O69" s="1">
         <v>63</v>
       </c>
-      <c r="P69" s="3">
+      <c r="P69" s="4">
         <f t="shared" si="6"/>
         <v>63</v>
       </c>
-      <c r="Q69" s="3">
+      <c r="Q69" s="4">
         <f t="shared" si="7"/>
         <v>72</v>
       </c>
@@ -8359,10 +8341,10 @@
       <c r="S69" s="1">
         <v>0</v>
       </c>
-      <c r="T69" s="7">
-        <v>0</v>
-      </c>
-      <c r="U69" s="7">
+      <c r="T69" s="8">
+        <v>0</v>
+      </c>
+      <c r="U69" s="8">
         <v>0</v>
       </c>
       <c r="V69" s="1">
@@ -8379,17 +8361,17 @@
       <c r="Y69" s="1">
         <v>40</v>
       </c>
-      <c r="Z69" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z69" s="4">
+        <f t="shared" si="12"/>
         <v>150000</v>
       </c>
       <c r="AA69" s="1">
         <v>173</v>
       </c>
-      <c r="AB69" s="3">
+      <c r="AB69" s="4">
         <v>39</v>
       </c>
-      <c r="AC69" s="3">
+      <c r="AC69" s="4">
         <f t="shared" si="8"/>
         <v>8694</v>
       </c>
@@ -8400,7 +8382,7 @@
       <c r="AF69" s="1">
         <v>0</v>
       </c>
-      <c r="AG69" s="3">
+      <c r="AG69" s="4">
         <v>311</v>
       </c>
     </row>
@@ -8414,48 +8396,48 @@
       <c r="E70" s="1">
         <v>1</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="7" t="s">
         <v>99</v>
       </c>
       <c r="G70" s="1">
         <v>65</v>
       </c>
       <c r="H70" s="1">
-        <f t="shared" si="11"/>
+        <f>AG72*Z70*AA70/10</f>
         <v>887576500</v>
       </c>
       <c r="I70" s="1">
-        <f t="shared" ref="I70:I77" si="16">AB70*AG68*Z70/10</f>
+        <f t="shared" ref="I70:I77" si="13">AB70*AG68*Z70/10</f>
         <v>185581500</v>
       </c>
       <c r="J70" s="1">
-        <f t="shared" si="13"/>
+        <f>Y70*Z70*AC70</f>
         <v>55831000000</v>
       </c>
       <c r="K70" s="1">
-        <f t="shared" ref="K70:K77" si="17">Y70*5</f>
+        <f t="shared" ref="K70:K77" si="14">Y70*5</f>
         <v>200</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L77" si="18">Y70*3</f>
+        <f t="shared" ref="L70:L77" si="15">Y70*3</f>
         <v>120</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" ref="M70:M77" si="19">Y70*2</f>
+        <f t="shared" ref="M70:M77" si="16">Y70*2</f>
         <v>80</v>
       </c>
       <c r="N70" s="1">
-        <f t="shared" ref="N70:N77" si="20">Y70*4</f>
+        <f t="shared" ref="N70:N77" si="17">Y70*4</f>
         <v>160</v>
       </c>
       <c r="O70" s="1">
         <v>64</v>
       </c>
-      <c r="P70" s="3">
+      <c r="P70" s="4">
         <f t="shared" si="6"/>
         <v>64</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="Q70" s="4">
         <f t="shared" si="7"/>
         <v>73</v>
       </c>
@@ -8465,18 +8447,18 @@
       <c r="S70" s="1">
         <v>0</v>
       </c>
-      <c r="T70" s="7">
-        <v>0</v>
-      </c>
-      <c r="U70" s="7">
+      <c r="T70" s="8">
+        <v>0</v>
+      </c>
+      <c r="U70" s="8">
         <v>0</v>
       </c>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V77" si="21">X70*10</f>
+        <f t="shared" ref="V70:V77" si="18">X70*10</f>
         <v>650</v>
       </c>
       <c r="W70" s="1">
-        <f t="shared" ref="W70:W77" si="22">X70*10</f>
+        <f t="shared" ref="W70:W77" si="19">X70*10</f>
         <v>650</v>
       </c>
       <c r="X70" s="1">
@@ -8485,17 +8467,17 @@
       <c r="Y70" s="1">
         <v>40</v>
       </c>
-      <c r="Z70" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z70" s="4">
+        <f t="shared" si="12"/>
         <v>155000</v>
       </c>
       <c r="AA70" s="1">
         <v>173</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AB70" s="4">
         <v>39</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AC70" s="4">
         <f t="shared" si="8"/>
         <v>9005</v>
       </c>
@@ -8506,7 +8488,7 @@
       <c r="AF70" s="1">
         <v>0</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AG70" s="4">
         <v>313</v>
       </c>
     </row>
@@ -8520,48 +8502,48 @@
       <c r="E71" s="1">
         <v>1</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="5" t="s">
         <v>100</v>
       </c>
       <c r="G71" s="1">
         <v>66</v>
       </c>
       <c r="H71" s="1">
-        <f t="shared" ref="H71:H77" si="23">AG73*Z71*AA71/10</f>
+        <f t="shared" ref="H71:H77" si="20">AG73*Z71*AA71/10</f>
         <v>932816000</v>
       </c>
       <c r="I71" s="1">
+        <f t="shared" si="13"/>
+        <v>194064000</v>
+      </c>
+      <c r="J71" s="1">
+        <f>Y71*Z71*AC71</f>
+        <v>59635200000</v>
+      </c>
+      <c r="K71" s="1">
+        <f t="shared" si="14"/>
+        <v>200</v>
+      </c>
+      <c r="L71" s="1">
+        <f t="shared" si="15"/>
+        <v>120</v>
+      </c>
+      <c r="M71" s="1">
         <f t="shared" si="16"/>
-        <v>194064000</v>
-      </c>
-      <c r="J71" s="1">
-        <f t="shared" si="13"/>
-        <v>59635200000</v>
-      </c>
-      <c r="K71" s="1">
+        <v>80</v>
+      </c>
+      <c r="N71" s="1">
         <f t="shared" si="17"/>
-        <v>200</v>
-      </c>
-      <c r="L71" s="1">
-        <f t="shared" si="18"/>
-        <v>120</v>
-      </c>
-      <c r="M71" s="1">
-        <f t="shared" si="19"/>
-        <v>80</v>
-      </c>
-      <c r="N71" s="1">
-        <f t="shared" si="20"/>
         <v>160</v>
       </c>
       <c r="O71" s="1">
         <v>65</v>
       </c>
-      <c r="P71" s="3">
+      <c r="P71" s="4">
         <f t="shared" si="6"/>
         <v>65</v>
       </c>
-      <c r="Q71" s="3">
+      <c r="Q71" s="4">
         <f t="shared" si="7"/>
         <v>74</v>
       </c>
@@ -8571,18 +8553,18 @@
       <c r="S71" s="1">
         <v>0</v>
       </c>
-      <c r="T71" s="7">
-        <v>0</v>
-      </c>
-      <c r="U71" s="7">
+      <c r="T71" s="8">
+        <v>0</v>
+      </c>
+      <c r="U71" s="8">
         <v>0</v>
       </c>
       <c r="V71" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>660</v>
       </c>
       <c r="W71" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>660</v>
       </c>
       <c r="X71" s="1">
@@ -8591,17 +8573,17 @@
       <c r="Y71" s="1">
         <v>40</v>
       </c>
-      <c r="Z71" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z71" s="4">
+        <f t="shared" si="12"/>
         <v>160000</v>
       </c>
       <c r="AA71" s="1">
         <v>173</v>
       </c>
-      <c r="AB71" s="3">
+      <c r="AB71" s="4">
         <v>39</v>
       </c>
-      <c r="AC71" s="3">
+      <c r="AC71" s="4">
         <f t="shared" si="8"/>
         <v>9318</v>
       </c>
@@ -8612,7 +8594,7 @@
       <c r="AF71" s="1">
         <v>0</v>
       </c>
-      <c r="AG71" s="3">
+      <c r="AG71" s="4">
         <v>317</v>
       </c>
     </row>
@@ -8626,49 +8608,49 @@
       <c r="E72" s="1">
         <v>1</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="7" t="s">
         <v>101</v>
       </c>
       <c r="G72" s="1">
         <v>67</v>
       </c>
       <c r="H72" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>990511500</v>
       </c>
       <c r="I72" s="1">
+        <f t="shared" si="13"/>
+        <v>201415500</v>
+      </c>
+      <c r="J72" s="1">
+        <f>Y72*Z72*AC72</f>
+        <v>63591000000</v>
+      </c>
+      <c r="K72" s="1">
+        <f t="shared" si="14"/>
+        <v>200</v>
+      </c>
+      <c r="L72" s="1">
+        <f t="shared" si="15"/>
+        <v>120</v>
+      </c>
+      <c r="M72" s="1">
         <f t="shared" si="16"/>
-        <v>201415500</v>
-      </c>
-      <c r="J72" s="1">
-        <f t="shared" si="13"/>
-        <v>63591000000</v>
-      </c>
-      <c r="K72" s="1">
+        <v>80</v>
+      </c>
+      <c r="N72" s="1">
         <f t="shared" si="17"/>
-        <v>200</v>
-      </c>
-      <c r="L72" s="1">
-        <f t="shared" si="18"/>
-        <v>120</v>
-      </c>
-      <c r="M72" s="1">
-        <f t="shared" si="19"/>
-        <v>80</v>
-      </c>
-      <c r="N72" s="1">
-        <f t="shared" si="20"/>
         <v>160</v>
       </c>
       <c r="O72" s="1">
         <v>66</v>
       </c>
-      <c r="P72" s="3">
-        <f t="shared" ref="P72:P77" si="24">P71+1</f>
+      <c r="P72" s="4">
+        <f t="shared" ref="P72:P77" si="21">P71+1</f>
         <v>66</v>
       </c>
-      <c r="Q72" s="3">
-        <f t="shared" ref="Q72:Q77" si="25">Q71+1</f>
+      <c r="Q72" s="4">
+        <f t="shared" ref="Q72:Q77" si="22">Q71+1</f>
         <v>75</v>
       </c>
       <c r="R72" s="1">
@@ -8677,18 +8659,18 @@
       <c r="S72" s="1">
         <v>0</v>
       </c>
-      <c r="T72" s="7">
-        <v>0</v>
-      </c>
-      <c r="U72" s="7">
+      <c r="T72" s="8">
+        <v>0</v>
+      </c>
+      <c r="U72" s="8">
         <v>0</v>
       </c>
       <c r="V72" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>670</v>
       </c>
       <c r="W72" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>670</v>
       </c>
       <c r="X72" s="1">
@@ -8697,17 +8679,17 @@
       <c r="Y72" s="1">
         <v>40</v>
       </c>
-      <c r="Z72" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z72" s="4">
+        <f t="shared" si="12"/>
         <v>165000</v>
       </c>
       <c r="AA72" s="1">
         <v>173</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="4">
         <v>39</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="4">
         <f t="shared" si="8"/>
         <v>9635</v>
       </c>
@@ -8718,7 +8700,7 @@
       <c r="AF72" s="1">
         <v>0</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="4">
         <v>331</v>
       </c>
     </row>
@@ -8732,49 +8714,49 @@
       <c r="E73" s="1">
         <v>1</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="7" t="s">
         <v>102</v>
       </c>
       <c r="G73" s="1">
         <v>68</v>
       </c>
       <c r="H73" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1026409000</v>
       </c>
       <c r="I73" s="1">
+        <f t="shared" si="13"/>
+        <v>210171000</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" ref="J73:J77" si="23">Y73*Z73*AC73</f>
+        <v>67768800000</v>
+      </c>
+      <c r="K73" s="1">
+        <f t="shared" si="14"/>
+        <v>200</v>
+      </c>
+      <c r="L73" s="1">
+        <f t="shared" si="15"/>
+        <v>120</v>
+      </c>
+      <c r="M73" s="1">
         <f t="shared" si="16"/>
-        <v>210171000</v>
-      </c>
-      <c r="J73" s="1">
-        <f t="shared" ref="J73:J77" si="26">Y73*Z73*AC73</f>
-        <v>67768800000</v>
-      </c>
-      <c r="K73" s="1">
+        <v>80</v>
+      </c>
+      <c r="N73" s="1">
         <f t="shared" si="17"/>
-        <v>200</v>
-      </c>
-      <c r="L73" s="1">
-        <f t="shared" si="18"/>
-        <v>120</v>
-      </c>
-      <c r="M73" s="1">
-        <f t="shared" si="19"/>
-        <v>80</v>
-      </c>
-      <c r="N73" s="1">
-        <f t="shared" si="20"/>
         <v>160</v>
       </c>
       <c r="O73" s="1">
         <v>67</v>
       </c>
-      <c r="P73" s="3">
-        <f t="shared" si="24"/>
+      <c r="P73" s="4">
+        <f t="shared" si="21"/>
         <v>67</v>
       </c>
-      <c r="Q73" s="3">
-        <f t="shared" si="25"/>
+      <c r="Q73" s="4">
+        <f t="shared" si="22"/>
         <v>76</v>
       </c>
       <c r="R73" s="1">
@@ -8783,18 +8765,18 @@
       <c r="S73" s="1">
         <v>0</v>
       </c>
-      <c r="T73" s="7">
-        <v>0</v>
-      </c>
-      <c r="U73" s="7">
+      <c r="T73" s="8">
+        <v>0</v>
+      </c>
+      <c r="U73" s="8">
         <v>0</v>
       </c>
       <c r="V73" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>680</v>
       </c>
       <c r="W73" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>680</v>
       </c>
       <c r="X73" s="1">
@@ -8803,17 +8785,17 @@
       <c r="Y73" s="1">
         <v>40</v>
       </c>
-      <c r="Z73" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z73" s="4">
+        <f t="shared" si="12"/>
         <v>170000</v>
       </c>
       <c r="AA73" s="1">
         <v>173</v>
       </c>
-      <c r="AB73" s="3">
+      <c r="AB73" s="4">
         <v>39</v>
       </c>
-      <c r="AC73" s="3">
+      <c r="AC73" s="4">
         <f t="shared" si="8"/>
         <v>9966</v>
       </c>
@@ -8824,7 +8806,7 @@
       <c r="AF73" s="1">
         <v>0</v>
       </c>
-      <c r="AG73" s="3">
+      <c r="AG73" s="4">
         <v>337</v>
       </c>
     </row>
@@ -8838,49 +8820,49 @@
       <c r="E74" s="1">
         <v>1</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="7" t="s">
         <v>103</v>
       </c>
       <c r="G74" s="1">
         <v>69</v>
       </c>
       <c r="H74" s="1">
+        <f t="shared" si="20"/>
+        <v>1068707500</v>
+      </c>
+      <c r="I74" s="1">
+        <f t="shared" si="13"/>
+        <v>225907500</v>
+      </c>
+      <c r="J74" s="1">
         <f t="shared" si="23"/>
-        <v>1068707500</v>
-      </c>
-      <c r="I74" s="1">
+        <v>72121000000</v>
+      </c>
+      <c r="K74" s="1">
+        <f t="shared" si="14"/>
+        <v>200</v>
+      </c>
+      <c r="L74" s="1">
+        <f t="shared" si="15"/>
+        <v>120</v>
+      </c>
+      <c r="M74" s="1">
         <f t="shared" si="16"/>
-        <v>225907500</v>
-      </c>
-      <c r="J74" s="1">
-        <f t="shared" si="26"/>
-        <v>72121000000</v>
-      </c>
-      <c r="K74" s="1">
+        <v>80</v>
+      </c>
+      <c r="N74" s="1">
         <f t="shared" si="17"/>
-        <v>200</v>
-      </c>
-      <c r="L74" s="1">
-        <f t="shared" si="18"/>
-        <v>120</v>
-      </c>
-      <c r="M74" s="1">
-        <f t="shared" si="19"/>
-        <v>80</v>
-      </c>
-      <c r="N74" s="1">
-        <f t="shared" si="20"/>
         <v>160</v>
       </c>
       <c r="O74" s="1">
         <v>68</v>
       </c>
-      <c r="P74" s="3">
-        <f t="shared" si="24"/>
+      <c r="P74" s="4">
+        <f t="shared" si="21"/>
         <v>68</v>
       </c>
-      <c r="Q74" s="3">
-        <f t="shared" si="25"/>
+      <c r="Q74" s="4">
+        <f t="shared" si="22"/>
         <v>77</v>
       </c>
       <c r="R74" s="1">
@@ -8889,18 +8871,18 @@
       <c r="S74" s="1">
         <v>0</v>
       </c>
-      <c r="T74" s="7">
-        <v>0</v>
-      </c>
-      <c r="U74" s="7">
+      <c r="T74" s="8">
+        <v>0</v>
+      </c>
+      <c r="U74" s="8">
         <v>0</v>
       </c>
       <c r="V74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>690</v>
       </c>
       <c r="W74" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>690</v>
       </c>
       <c r="X74" s="1">
@@ -8909,17 +8891,17 @@
       <c r="Y74" s="1">
         <v>40</v>
       </c>
-      <c r="Z74" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z74" s="4">
+        <f t="shared" si="12"/>
         <v>175000</v>
       </c>
       <c r="AA74" s="1">
         <v>173</v>
       </c>
-      <c r="AB74" s="3">
+      <c r="AB74" s="4">
         <v>39</v>
       </c>
-      <c r="AC74" s="3">
+      <c r="AC74" s="4">
         <f t="shared" si="8"/>
         <v>10303</v>
       </c>
@@ -8930,7 +8912,7 @@
       <c r="AF74" s="1">
         <v>0</v>
       </c>
-      <c r="AG74" s="3">
+      <c r="AG74" s="4">
         <v>347</v>
       </c>
     </row>
@@ -8944,49 +8926,49 @@
       <c r="E75" s="1">
         <v>1</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="7" t="s">
         <v>104</v>
       </c>
       <c r="G75" s="1">
         <v>70</v>
       </c>
       <c r="H75" s="1">
+        <f t="shared" si="20"/>
+        <v>1117926000</v>
+      </c>
+      <c r="I75" s="1">
+        <f t="shared" si="13"/>
+        <v>236574000</v>
+      </c>
+      <c r="J75" s="1">
         <f t="shared" si="23"/>
-        <v>1117926000</v>
-      </c>
-      <c r="I75" s="1">
+        <v>76680000000</v>
+      </c>
+      <c r="K75" s="1">
+        <f t="shared" si="14"/>
+        <v>200</v>
+      </c>
+      <c r="L75" s="1">
+        <f t="shared" si="15"/>
+        <v>120</v>
+      </c>
+      <c r="M75" s="1">
         <f t="shared" si="16"/>
-        <v>236574000</v>
-      </c>
-      <c r="J75" s="1">
-        <f t="shared" si="26"/>
-        <v>76680000000</v>
-      </c>
-      <c r="K75" s="1">
+        <v>80</v>
+      </c>
+      <c r="N75" s="1">
         <f t="shared" si="17"/>
-        <v>200</v>
-      </c>
-      <c r="L75" s="1">
-        <f t="shared" si="18"/>
-        <v>120</v>
-      </c>
-      <c r="M75" s="1">
-        <f t="shared" si="19"/>
-        <v>80</v>
-      </c>
-      <c r="N75" s="1">
-        <f t="shared" si="20"/>
         <v>160</v>
       </c>
       <c r="O75" s="1">
         <v>69</v>
       </c>
-      <c r="P75" s="3">
-        <f t="shared" si="24"/>
+      <c r="P75" s="4">
+        <f t="shared" si="21"/>
         <v>69</v>
       </c>
-      <c r="Q75" s="3">
-        <f t="shared" si="25"/>
+      <c r="Q75" s="4">
+        <f t="shared" si="22"/>
         <v>78</v>
       </c>
       <c r="R75" s="1">
@@ -8995,18 +8977,18 @@
       <c r="S75" s="1">
         <v>0</v>
       </c>
-      <c r="T75" s="7">
-        <v>0</v>
-      </c>
-      <c r="U75" s="7">
+      <c r="T75" s="8">
+        <v>0</v>
+      </c>
+      <c r="U75" s="8">
         <v>0</v>
       </c>
       <c r="V75" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>700</v>
       </c>
       <c r="W75" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>700</v>
       </c>
       <c r="X75" s="1">
@@ -9015,17 +8997,17 @@
       <c r="Y75" s="1">
         <v>40</v>
       </c>
-      <c r="Z75" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z75" s="4">
+        <f t="shared" si="12"/>
         <v>180000</v>
       </c>
       <c r="AA75" s="1">
         <v>173</v>
       </c>
-      <c r="AB75" s="3">
+      <c r="AB75" s="4">
         <v>39</v>
       </c>
-      <c r="AC75" s="3">
+      <c r="AC75" s="4">
         <f t="shared" si="8"/>
         <v>10650</v>
       </c>
@@ -9036,7 +9018,7 @@
       <c r="AF75" s="1">
         <v>0</v>
       </c>
-      <c r="AG75" s="3">
+      <c r="AG75" s="4">
         <v>349</v>
       </c>
     </row>
@@ -9057,42 +9039,42 @@
         <v>71</v>
       </c>
       <c r="H76" s="1">
+        <f t="shared" si="20"/>
+        <v>1174583500</v>
+      </c>
+      <c r="I76" s="1">
+        <f t="shared" si="13"/>
+        <v>250360500</v>
+      </c>
+      <c r="J76" s="1">
         <f t="shared" si="23"/>
-        <v>1174583500</v>
-      </c>
-      <c r="I76" s="1">
+        <v>81392600000</v>
+      </c>
+      <c r="K76" s="1">
+        <f t="shared" si="14"/>
+        <v>200</v>
+      </c>
+      <c r="L76" s="1">
+        <f t="shared" si="15"/>
+        <v>120</v>
+      </c>
+      <c r="M76" s="1">
         <f t="shared" si="16"/>
-        <v>250360500</v>
-      </c>
-      <c r="J76" s="1">
-        <f t="shared" si="26"/>
-        <v>81392600000</v>
-      </c>
-      <c r="K76" s="1">
+        <v>80</v>
+      </c>
+      <c r="N76" s="1">
         <f t="shared" si="17"/>
-        <v>200</v>
-      </c>
-      <c r="L76" s="1">
-        <f t="shared" si="18"/>
-        <v>120</v>
-      </c>
-      <c r="M76" s="1">
-        <f t="shared" si="19"/>
-        <v>80</v>
-      </c>
-      <c r="N76" s="1">
-        <f t="shared" si="20"/>
         <v>160</v>
       </c>
       <c r="O76" s="1">
         <v>70</v>
       </c>
-      <c r="P76" s="3">
-        <f t="shared" si="24"/>
+      <c r="P76" s="4">
+        <f t="shared" si="21"/>
         <v>70</v>
       </c>
-      <c r="Q76" s="3">
-        <f t="shared" si="25"/>
+      <c r="Q76" s="4">
+        <f t="shared" si="22"/>
         <v>79</v>
       </c>
       <c r="R76" s="1">
@@ -9101,18 +9083,18 @@
       <c r="S76" s="1">
         <v>0</v>
       </c>
-      <c r="T76" s="7">
-        <v>0</v>
-      </c>
-      <c r="U76" s="7">
+      <c r="T76" s="8">
+        <v>0</v>
+      </c>
+      <c r="U76" s="8">
         <v>0</v>
       </c>
       <c r="V76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>710</v>
       </c>
       <c r="W76" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>710</v>
       </c>
       <c r="X76" s="1">
@@ -9121,17 +9103,17 @@
       <c r="Y76" s="1">
         <v>40</v>
       </c>
-      <c r="Z76" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z76" s="4">
+        <f t="shared" si="12"/>
         <v>185000</v>
       </c>
       <c r="AA76" s="1">
         <v>173</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="4">
         <v>39</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AC76" s="4">
         <f>AC75+AG75</f>
         <v>10999</v>
       </c>
@@ -9142,7 +9124,7 @@
       <c r="AF76" s="1">
         <v>0</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="4">
         <v>353</v>
       </c>
     </row>
@@ -9156,49 +9138,49 @@
       <c r="E77" s="1">
         <v>1</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="5" t="s">
         <v>106</v>
       </c>
       <c r="G77" s="1">
         <v>72</v>
       </c>
       <c r="H77" s="1">
+        <f t="shared" si="20"/>
+        <v>1226051000</v>
+      </c>
+      <c r="I77" s="1">
+        <f t="shared" si="13"/>
+        <v>258609000</v>
+      </c>
+      <c r="J77" s="1">
         <f t="shared" si="23"/>
-        <v>1226051000</v>
-      </c>
-      <c r="I77" s="1">
+        <v>86275200000</v>
+      </c>
+      <c r="K77" s="1">
+        <f t="shared" si="14"/>
+        <v>200</v>
+      </c>
+      <c r="L77" s="1">
+        <f t="shared" si="15"/>
+        <v>120</v>
+      </c>
+      <c r="M77" s="1">
         <f t="shared" si="16"/>
-        <v>258609000</v>
-      </c>
-      <c r="J77" s="1">
-        <f t="shared" si="26"/>
-        <v>86275200000</v>
-      </c>
-      <c r="K77" s="1">
+        <v>80</v>
+      </c>
+      <c r="N77" s="1">
         <f t="shared" si="17"/>
-        <v>200</v>
-      </c>
-      <c r="L77" s="1">
-        <f t="shared" si="18"/>
-        <v>120</v>
-      </c>
-      <c r="M77" s="1">
-        <f t="shared" si="19"/>
-        <v>80</v>
-      </c>
-      <c r="N77" s="1">
-        <f t="shared" si="20"/>
         <v>160</v>
       </c>
       <c r="O77" s="1">
         <v>71</v>
       </c>
-      <c r="P77" s="3">
-        <f t="shared" si="24"/>
+      <c r="P77" s="4">
+        <f t="shared" si="21"/>
         <v>71</v>
       </c>
-      <c r="Q77" s="3">
-        <f t="shared" si="25"/>
+      <c r="Q77" s="4">
+        <f t="shared" si="22"/>
         <v>80</v>
       </c>
       <c r="R77" s="1">
@@ -9207,18 +9189,18 @@
       <c r="S77" s="1">
         <v>0</v>
       </c>
-      <c r="T77" s="7">
-        <v>0</v>
-      </c>
-      <c r="U77" s="7">
+      <c r="T77" s="8">
+        <v>0</v>
+      </c>
+      <c r="U77" s="8">
         <v>0</v>
       </c>
       <c r="V77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>720</v>
       </c>
       <c r="W77" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>720</v>
       </c>
       <c r="X77" s="1">
@@ -9227,17 +9209,17 @@
       <c r="Y77" s="1">
         <v>40</v>
       </c>
-      <c r="Z77" s="3">
-        <f t="shared" si="15"/>
+      <c r="Z77" s="4">
+        <f t="shared" si="12"/>
         <v>190000</v>
       </c>
       <c r="AA77" s="1">
         <v>173</v>
       </c>
-      <c r="AB77" s="3">
+      <c r="AB77" s="4">
         <v>39</v>
       </c>
-      <c r="AC77" s="3">
+      <c r="AC77" s="4">
         <f>AC76+AG76</f>
         <v>11352</v>
       </c>
@@ -9248,137 +9230,137 @@
       <c r="AF77" s="1">
         <v>0</v>
       </c>
-      <c r="AG77" s="3">
+      <c r="AG77" s="4">
         <v>359</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:33">
-      <c r="AG78" s="3">
+      <c r="AG78" s="4">
         <v>367</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:33">
-      <c r="AG79" s="3">
+      <c r="AG79" s="4">
         <v>373</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:33">
-      <c r="AG80" s="3">
+      <c r="AG80" s="4">
         <v>379</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="33:33">
-      <c r="AG81" s="3">
+      <c r="AG81" s="4">
         <v>383</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="33:33">
-      <c r="AG82" s="3">
+      <c r="AG82" s="4">
         <v>389</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="33:33">
-      <c r="AG83" s="3">
+      <c r="AG83" s="4">
         <v>397</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="33:33">
-      <c r="AG84" s="3">
+      <c r="AG84" s="4">
         <v>401</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="33:33">
-      <c r="AG85" s="3">
+      <c r="AG85" s="4">
         <v>409</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="33:33">
-      <c r="AG86" s="3">
+      <c r="AG86" s="4">
         <v>419</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="33:33">
-      <c r="AG87" s="3">
+      <c r="AG87" s="4">
         <v>421</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="33:33">
-      <c r="AG88" s="3">
+      <c r="AG88" s="4">
         <v>431</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="33:33">
-      <c r="AG89" s="3">
+      <c r="AG89" s="4">
         <v>433</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="33:33">
-      <c r="AG90" s="3">
+      <c r="AG90" s="4">
         <v>439</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="33:33">
-      <c r="AG91" s="3">
+      <c r="AG91" s="4">
         <v>443</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="33:33">
-      <c r="AG92" s="3">
+      <c r="AG92" s="4">
         <v>449</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="33:33">
-      <c r="AG93" s="3">
+      <c r="AG93" s="4">
         <v>457</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="33:33">
-      <c r="AG94" s="3">
+      <c r="AG94" s="4">
         <v>461</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="33:33">
-      <c r="AG95" s="3">
+      <c r="AG95" s="4">
         <v>463</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="33:33">
-      <c r="AG96" s="3">
+      <c r="AG96" s="4">
         <v>467</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="33:33">
-      <c r="AG97" s="3">
+      <c r="AG97" s="4">
         <v>479</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="33:33">
-      <c r="AG98" s="3">
+      <c r="AG98" s="4">
         <v>487</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="33:33">
-      <c r="AG99" s="3">
+      <c r="AG99" s="4">
         <v>491</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="33:33">
-      <c r="AG100" s="3">
+      <c r="AG100" s="4">
         <v>499</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="33:33">
-      <c r="AG101" s="3">
+      <c r="AG101" s="4">
         <v>503</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="33:33">
-      <c r="AG102" s="3">
+      <c r="AG102" s="4">
         <v>509</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="33:33">
-      <c r="AG103" s="3">
+      <c r="AG103" s="4">
         <v>509</v>
       </c>
     </row>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -1843,7 +1843,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="1">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="0"/>
@@ -1943,7 +1943,7 @@
         <v>60</v>
       </c>
       <c r="J8" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="0"/>
@@ -2045,7 +2045,7 @@
         <v>120</v>
       </c>
       <c r="J9" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="0"/>
@@ -2147,7 +2147,7 @@
         <v>200</v>
       </c>
       <c r="J10" s="1">
-        <v>12000</v>
+        <v>30000</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="0"/>
@@ -2249,7 +2249,7 @@
         <v>300</v>
       </c>
       <c r="J11" s="3">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="K11" s="3">
         <f t="shared" si="0"/>
@@ -2351,7 +2351,7 @@
         <v>490</v>
       </c>
       <c r="J12" s="4">
-        <v>35000</v>
+        <v>80000</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="0"/>
@@ -2454,7 +2454,7 @@
         <v>700</v>
       </c>
       <c r="J13" s="1">
-        <v>58000</v>
+        <v>120000</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="0"/>
@@ -2557,7 +2557,7 @@
         <v>1000</v>
       </c>
       <c r="J14" s="1">
-        <v>90000</v>
+        <v>170000</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="0"/>
@@ -2660,7 +2660,7 @@
         <v>1500</v>
       </c>
       <c r="J15" s="1">
-        <v>140000</v>
+        <v>240000</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="0"/>
@@ -2763,7 +2763,7 @@
         <v>2400</v>
       </c>
       <c r="J16" s="1">
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="0"/>
@@ -2866,7 +2866,7 @@
         <v>3600</v>
       </c>
       <c r="J17" s="3">
-        <v>300000</v>
+        <v>480000</v>
       </c>
       <c r="K17" s="3">
         <f t="shared" si="0"/>
@@ -2969,7 +2969,7 @@
         <v>6000</v>
       </c>
       <c r="J18" s="1">
-        <v>450000</v>
+        <v>630000</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" si="0"/>
@@ -3072,7 +3072,7 @@
         <v>9600</v>
       </c>
       <c r="J19" s="1">
-        <v>650000</v>
+        <v>860000</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" si="0"/>
@@ -3175,7 +3175,7 @@
         <v>14000</v>
       </c>
       <c r="J20" s="1">
-        <v>950000</v>
+        <v>1150000</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" si="0"/>
@@ -5436,15 +5436,15 @@
         <v>37</v>
       </c>
       <c r="H42" s="1">
-        <f>AG44*Z42*AA42/10</f>
+        <f t="shared" ref="H42:H70" si="12">AG44*Z42*AA42/10</f>
         <v>39378600</v>
       </c>
       <c r="I42" s="1">
-        <f>AB42*AG40*Z42/10</f>
+        <f t="shared" ref="I42:I69" si="13">AB42*AG40*Z42/10</f>
         <v>9655200</v>
       </c>
       <c r="J42" s="1">
-        <f>Y42*Z42*AC42</f>
+        <f t="shared" ref="J42:J72" si="14">Y42*Z42*AC42</f>
         <v>1690974000</v>
       </c>
       <c r="K42" s="1">
@@ -5542,15 +5542,15 @@
         <v>38</v>
       </c>
       <c r="H43" s="1">
-        <f>AG45*Z43*AA43/10</f>
+        <f t="shared" si="12"/>
         <v>47402000</v>
       </c>
       <c r="I43" s="1">
-        <f>AB43*AG41*Z43/10</f>
+        <f t="shared" si="13"/>
         <v>11174000</v>
       </c>
       <c r="J43" s="1">
-        <f>Y43*Z43*AC43</f>
+        <f t="shared" si="14"/>
         <v>2048960000</v>
       </c>
       <c r="K43" s="1">
@@ -5648,15 +5648,15 @@
         <v>39</v>
       </c>
       <c r="H44" s="1">
-        <f>AG46*Z44*AA44/10</f>
+        <f t="shared" si="12"/>
         <v>62202500</v>
       </c>
       <c r="I44" s="1">
-        <f>AB44*AG42*Z44/10</f>
+        <f t="shared" si="13"/>
         <v>14915000</v>
       </c>
       <c r="J44" s="1">
-        <f>Y44*Z44*AC44</f>
+        <f t="shared" si="14"/>
         <v>2787525000</v>
       </c>
       <c r="K44" s="1">
@@ -5713,7 +5713,7 @@
         <v>39</v>
       </c>
       <c r="Z44" s="4">
-        <f t="shared" ref="Z44:Z77" si="12">Z43+5000</f>
+        <f t="shared" ref="Z44:Z77" si="15">Z43+5000</f>
         <v>25000</v>
       </c>
       <c r="AA44" s="4">
@@ -5754,15 +5754,15 @@
         <v>40</v>
       </c>
       <c r="H45" s="1">
-        <f>AG47*Z45*AA45/10</f>
+        <f t="shared" si="12"/>
         <v>80907000</v>
       </c>
       <c r="I45" s="1">
-        <f>AB45*AG43*Z45/10</f>
+        <f t="shared" si="13"/>
         <v>19071000</v>
       </c>
       <c r="J45" s="1">
-        <f>Y45*Z45*AC45</f>
+        <f t="shared" si="14"/>
         <v>3631200000</v>
       </c>
       <c r="K45" s="1">
@@ -5819,7 +5819,7 @@
         <v>40</v>
       </c>
       <c r="Z45" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>30000</v>
       </c>
       <c r="AA45" s="1">
@@ -5860,15 +5860,15 @@
         <v>41</v>
       </c>
       <c r="H46" s="1">
-        <f>AG48*Z46*AA46/10</f>
+        <f t="shared" si="12"/>
         <v>100943500</v>
       </c>
       <c r="I46" s="1">
-        <f>AB46*AG44*Z46/10</f>
+        <f t="shared" si="13"/>
         <v>22795500</v>
       </c>
       <c r="J46" s="1">
-        <f>Y46*Z46*AC46</f>
+        <f t="shared" si="14"/>
         <v>4478600000</v>
       </c>
       <c r="K46" s="1">
@@ -5925,7 +5925,7 @@
         <v>40</v>
       </c>
       <c r="Z46" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>35000</v>
       </c>
       <c r="AA46" s="1">
@@ -5965,15 +5965,15 @@
         <v>42</v>
       </c>
       <c r="H47" s="1">
-        <f>AG49*Z47*AA47/10</f>
+        <f t="shared" si="12"/>
         <v>116572000</v>
       </c>
       <c r="I47" s="1">
-        <f>AB47*AG45*Z47/10</f>
+        <f t="shared" si="13"/>
         <v>26988000</v>
       </c>
       <c r="J47" s="1">
-        <f>Y47*Z47*AC47</f>
+        <f t="shared" si="14"/>
         <v>5404800000</v>
       </c>
       <c r="K47" s="1">
@@ -6030,7 +6030,7 @@
         <v>40</v>
       </c>
       <c r="Z47" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>40000</v>
       </c>
       <c r="AA47" s="1">
@@ -6071,15 +6071,15 @@
         <v>43</v>
       </c>
       <c r="H48" s="1">
-        <f>AG50*Z48*AA48/10</f>
+        <f t="shared" si="12"/>
         <v>139180500</v>
       </c>
       <c r="I48" s="1">
-        <f>AB48*AG46*Z48/10</f>
+        <f t="shared" si="13"/>
         <v>31414500</v>
       </c>
       <c r="J48" s="1">
-        <f>Y48*Z48*AC48</f>
+        <f t="shared" si="14"/>
         <v>6406200000</v>
       </c>
       <c r="K48" s="1">
@@ -6136,7 +6136,7 @@
         <v>40</v>
       </c>
       <c r="Z48" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>45000</v>
       </c>
       <c r="AA48" s="1">
@@ -6177,15 +6177,15 @@
         <v>44</v>
       </c>
       <c r="H49" s="1">
-        <f>AG51*Z49*AA49/10</f>
+        <f t="shared" si="12"/>
         <v>172135000</v>
       </c>
       <c r="I49" s="1">
-        <f>AB49*AG47*Z49/10</f>
+        <f t="shared" si="13"/>
         <v>35295000</v>
       </c>
       <c r="J49" s="1">
-        <f>Y49*Z49*AC49</f>
+        <f t="shared" si="14"/>
         <v>7500000000</v>
       </c>
       <c r="K49" s="1">
@@ -6242,7 +6242,7 @@
         <v>40</v>
       </c>
       <c r="Z49" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>50000</v>
       </c>
       <c r="AA49" s="1">
@@ -6283,15 +6283,15 @@
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <f>AG52*Z50*AA50/10</f>
+        <f t="shared" si="12"/>
         <v>200766500</v>
       </c>
       <c r="I50" s="1">
-        <f>AB50*AG48*Z50/10</f>
+        <f t="shared" si="13"/>
         <v>40969500</v>
       </c>
       <c r="J50" s="1">
-        <f>Y50*Z50*AC50</f>
+        <f t="shared" si="14"/>
         <v>8674600000</v>
       </c>
       <c r="K50" s="1">
@@ -6348,7 +6348,7 @@
         <v>40</v>
       </c>
       <c r="Z50" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>55000</v>
       </c>
       <c r="AA50" s="1">
@@ -6389,15 +6389,15 @@
         <v>46</v>
       </c>
       <c r="H51" s="1">
-        <f>AG53*Z51*AA51/10</f>
+        <f t="shared" si="12"/>
         <v>231474000</v>
       </c>
       <c r="I51" s="1">
-        <f>AB51*AG49*Z51/10</f>
+        <f t="shared" si="13"/>
         <v>45162000</v>
       </c>
       <c r="J51" s="1">
-        <f>Y51*Z51*AC51</f>
+        <f t="shared" si="14"/>
         <v>9936000000</v>
       </c>
       <c r="K51" s="1">
@@ -6454,7 +6454,7 @@
         <v>40</v>
       </c>
       <c r="Z51" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>60000</v>
       </c>
       <c r="AA51" s="1">
@@ -6495,15 +6495,15 @@
         <v>47</v>
       </c>
       <c r="H52" s="1">
-        <f>AG54*Z52*AA52/10</f>
+        <f t="shared" si="12"/>
         <v>255261500</v>
       </c>
       <c r="I52" s="1">
-        <f>AB52*AG50*Z52/10</f>
+        <f t="shared" si="13"/>
         <v>49939500</v>
       </c>
       <c r="J52" s="1">
-        <f>Y52*Z52*AC52</f>
+        <f t="shared" si="14"/>
         <v>11281400000</v>
       </c>
       <c r="K52" s="1">
@@ -6560,7 +6560,7 @@
         <v>40</v>
       </c>
       <c r="Z52" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>65000</v>
       </c>
       <c r="AA52" s="1">
@@ -6601,15 +6601,15 @@
         <v>48</v>
       </c>
       <c r="H53" s="1">
-        <f>AG55*Z53*AA53/10</f>
+        <f t="shared" si="12"/>
         <v>277319000</v>
       </c>
       <c r="I53" s="1">
-        <f>AB53*AG51*Z53/10</f>
+        <f t="shared" si="13"/>
         <v>54327000</v>
       </c>
       <c r="J53" s="1">
-        <f>Y53*Z53*AC53</f>
+        <f t="shared" si="14"/>
         <v>12740000000</v>
       </c>
       <c r="K53" s="1">
@@ -6666,7 +6666,7 @@
         <v>40</v>
       </c>
       <c r="Z53" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>70000</v>
       </c>
       <c r="AA53" s="1">
@@ -6707,15 +6707,15 @@
         <v>49</v>
       </c>
       <c r="H54" s="1">
-        <f>AG56*Z54*AA54/10</f>
+        <f t="shared" si="12"/>
         <v>302317500</v>
       </c>
       <c r="I54" s="1">
-        <f>AB54*AG52*Z54/10</f>
+        <f t="shared" si="13"/>
         <v>61717500</v>
       </c>
       <c r="J54" s="1">
-        <f>Y54*Z54*AC54</f>
+        <f t="shared" si="14"/>
         <v>14319000000</v>
       </c>
       <c r="K54" s="1">
@@ -6772,7 +6772,7 @@
         <v>40</v>
       </c>
       <c r="Z54" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>75000</v>
       </c>
       <c r="AA54" s="1">
@@ -6813,15 +6813,15 @@
         <v>50</v>
       </c>
       <c r="H55" s="1">
-        <f>AG57*Z55*AA55/10</f>
+        <f t="shared" si="12"/>
         <v>330776000</v>
       </c>
       <c r="I55" s="1">
-        <f>AB55*AG53*Z55/10</f>
+        <f t="shared" si="13"/>
         <v>69576000</v>
       </c>
       <c r="J55" s="1">
-        <f>Y55*Z55*AC55</f>
+        <f t="shared" si="14"/>
         <v>16000000000</v>
       </c>
       <c r="K55" s="1">
@@ -6878,7 +6878,7 @@
         <v>40</v>
       </c>
       <c r="Z55" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>80000</v>
       </c>
       <c r="AA55" s="1">
@@ -6919,15 +6919,15 @@
         <v>51</v>
       </c>
       <c r="H56" s="1">
-        <f>AG58*Z56*AA56/10</f>
+        <f t="shared" si="12"/>
         <v>354390500</v>
       </c>
       <c r="I56" s="1">
-        <f>AB56*AG54*Z56/10</f>
+        <f t="shared" si="13"/>
         <v>75250500</v>
       </c>
       <c r="J56" s="1">
-        <f>Y56*Z56*AC56</f>
+        <f t="shared" si="14"/>
         <v>17778600000</v>
       </c>
       <c r="K56" s="1">
@@ -6984,7 +6984,7 @@
         <v>40</v>
       </c>
       <c r="Z56" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>85000</v>
       </c>
       <c r="AA56" s="1">
@@ -7025,15 +7025,15 @@
         <v>52</v>
       </c>
       <c r="H57" s="1">
-        <f>AG59*Z57*AA57/10</f>
+        <f t="shared" si="12"/>
         <v>390807000</v>
       </c>
       <c r="I57" s="1">
-        <f>AB57*AG55*Z57/10</f>
+        <f t="shared" si="13"/>
         <v>80379000</v>
       </c>
       <c r="J57" s="1">
-        <f>Y57*Z57*AC57</f>
+        <f t="shared" si="14"/>
         <v>19663200000</v>
       </c>
       <c r="K57" s="1">
@@ -7090,7 +7090,7 @@
         <v>40</v>
       </c>
       <c r="Z57" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>90000</v>
       </c>
       <c r="AA57" s="1">
@@ -7131,15 +7131,15 @@
         <v>53</v>
       </c>
       <c r="H58" s="1">
-        <f>AG60*Z58*AA58/10</f>
+        <f t="shared" si="12"/>
         <v>422379500</v>
       </c>
       <c r="I58" s="1">
-        <f>AB58*AG56*Z58/10</f>
+        <f t="shared" si="13"/>
         <v>86326500</v>
       </c>
       <c r="J58" s="1">
-        <f>Y58*Z58*AC58</f>
+        <f t="shared" si="14"/>
         <v>21663800000</v>
       </c>
       <c r="K58" s="1">
@@ -7196,7 +7196,7 @@
         <v>40</v>
       </c>
       <c r="Z58" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>95000</v>
       </c>
       <c r="AA58" s="1">
@@ -7237,15 +7237,15 @@
         <v>54</v>
       </c>
       <c r="H59" s="1">
-        <f>AG61*Z59*AA59/10</f>
+        <f t="shared" si="12"/>
         <v>454990000</v>
       </c>
       <c r="I59" s="1">
-        <f>AB59*AG57*Z59/10</f>
+        <f t="shared" si="13"/>
         <v>93210000</v>
       </c>
       <c r="J59" s="1">
-        <f>Y59*Z59*AC59</f>
+        <f t="shared" si="14"/>
         <v>23768000000</v>
       </c>
       <c r="K59" s="1">
@@ -7302,7 +7302,7 @@
         <v>40</v>
       </c>
       <c r="Z59" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>100000</v>
       </c>
       <c r="AA59" s="1">
@@ -7343,15 +7343,15 @@
         <v>55</v>
       </c>
       <c r="H60" s="1">
-        <f>AG62*Z60*AA60/10</f>
+        <f t="shared" si="12"/>
         <v>488638500</v>
       </c>
       <c r="I60" s="1">
-        <f>AB60*AG58*Z60/10</f>
+        <f t="shared" si="13"/>
         <v>98689500</v>
       </c>
       <c r="J60" s="1">
-        <f>Y60*Z60*AC60</f>
+        <f t="shared" si="14"/>
         <v>26010600000</v>
       </c>
       <c r="K60" s="1">
@@ -7408,7 +7408,7 @@
         <v>40</v>
       </c>
       <c r="Z60" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>105000</v>
       </c>
       <c r="AA60" s="1">
@@ -7449,15 +7449,15 @@
         <v>56</v>
       </c>
       <c r="H61" s="1">
-        <f>AG63*Z61*AA61/10</f>
+        <f t="shared" si="12"/>
         <v>515713000</v>
       </c>
       <c r="I61" s="1">
-        <f>AB61*AG59*Z61/10</f>
+        <f t="shared" si="13"/>
         <v>107679000</v>
       </c>
       <c r="J61" s="1">
-        <f>Y61*Z61*AC61</f>
+        <f t="shared" si="14"/>
         <v>28380000000</v>
       </c>
       <c r="K61" s="1">
@@ -7514,7 +7514,7 @@
         <v>40</v>
       </c>
       <c r="Z61" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>110000</v>
       </c>
       <c r="AA61" s="1">
@@ -7555,15 +7555,15 @@
         <v>57</v>
       </c>
       <c r="H62" s="1">
-        <f>AG64*Z62*AA62/10</f>
+        <f t="shared" si="12"/>
         <v>551091500</v>
       </c>
       <c r="I62" s="1">
-        <f>AB62*AG60*Z62/10</f>
+        <f t="shared" si="13"/>
         <v>115264500</v>
       </c>
       <c r="J62" s="1">
-        <f>Y62*Z62*AC62</f>
+        <f t="shared" si="14"/>
         <v>30879800000</v>
       </c>
       <c r="K62" s="1">
@@ -7620,7 +7620,7 @@
         <v>40</v>
       </c>
       <c r="Z62" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>115000</v>
       </c>
       <c r="AA62" s="1">
@@ -7661,15 +7661,15 @@
         <v>58</v>
       </c>
       <c r="H63" s="1">
-        <f>AG65*Z63*AA63/10</f>
+        <f t="shared" si="12"/>
         <v>583356000</v>
       </c>
       <c r="I63" s="1">
-        <f>AB63*AG61*Z63/10</f>
+        <f t="shared" si="13"/>
         <v>123084000</v>
       </c>
       <c r="J63" s="1">
-        <f>Y63*Z63*AC63</f>
+        <f t="shared" si="14"/>
         <v>33513600000</v>
       </c>
       <c r="K63" s="1">
@@ -7726,7 +7726,7 @@
         <v>40</v>
       </c>
       <c r="Z63" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>120000</v>
       </c>
       <c r="AA63" s="1">
@@ -7767,15 +7767,15 @@
         <v>59</v>
       </c>
       <c r="H64" s="1">
-        <f>AG66*Z64*AA64/10</f>
+        <f t="shared" si="12"/>
         <v>611987500</v>
       </c>
       <c r="I64" s="1">
-        <f>AB64*AG62*Z64/10</f>
+        <f t="shared" si="13"/>
         <v>131137500</v>
       </c>
       <c r="J64" s="1">
-        <f>Y64*Z64*AC64</f>
+        <f t="shared" si="14"/>
         <v>36265000000</v>
       </c>
       <c r="K64" s="1">
@@ -7832,7 +7832,7 @@
         <v>40</v>
       </c>
       <c r="Z64" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>125000</v>
       </c>
       <c r="AA64" s="1">
@@ -7873,15 +7873,15 @@
         <v>60</v>
       </c>
       <c r="H65" s="1">
-        <f>AG67*Z65*AA65/10</f>
+        <f t="shared" si="12"/>
         <v>658957000</v>
       </c>
       <c r="I65" s="1">
-        <f>AB65*AG63*Z65/10</f>
+        <f t="shared" si="13"/>
         <v>137397000</v>
       </c>
       <c r="J65" s="1">
-        <f>Y65*Z65*AC65</f>
+        <f t="shared" si="14"/>
         <v>39156000000</v>
       </c>
       <c r="K65" s="1">
@@ -7938,7 +7938,7 @@
         <v>40</v>
       </c>
       <c r="Z65" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>130000</v>
       </c>
       <c r="AA65" s="1">
@@ -7979,15 +7979,15 @@
         <v>61</v>
       </c>
       <c r="H66" s="1">
-        <f>AG68*Z66*AA66/10</f>
+        <f t="shared" si="12"/>
         <v>716998500</v>
       </c>
       <c r="I66" s="1">
-        <f>AB66*AG64*Z66/10</f>
+        <f t="shared" si="13"/>
         <v>145840500</v>
       </c>
       <c r="J66" s="1">
-        <f>Y66*Z66*AC66</f>
+        <f t="shared" si="14"/>
         <v>42179400000</v>
       </c>
       <c r="K66" s="1">
@@ -8044,7 +8044,7 @@
         <v>40</v>
       </c>
       <c r="Z66" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>135000</v>
       </c>
       <c r="AA66" s="1">
@@ -8085,15 +8085,15 @@
         <v>62</v>
       </c>
       <c r="H67" s="1">
-        <f>AG69*Z67*AA67/10</f>
+        <f t="shared" si="12"/>
         <v>753242000</v>
       </c>
       <c r="I67" s="1">
-        <f>AB67*AG65*Z67/10</f>
+        <f t="shared" si="13"/>
         <v>153426000</v>
       </c>
       <c r="J67" s="1">
-        <f>Y67*Z67*AC67</f>
+        <f t="shared" si="14"/>
         <v>45326400000</v>
       </c>
       <c r="K67" s="1">
@@ -8150,7 +8150,7 @@
         <v>40</v>
       </c>
       <c r="Z67" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>140000</v>
       </c>
       <c r="AA67" s="1">
@@ -8191,15 +8191,15 @@
         <v>63</v>
       </c>
       <c r="H68" s="1">
-        <f>AG70*Z68*AA68/10</f>
+        <f t="shared" si="12"/>
         <v>785160500</v>
       </c>
       <c r="I68" s="1">
-        <f>AB68*AG66*Z68/10</f>
+        <f t="shared" si="13"/>
         <v>160036500</v>
       </c>
       <c r="J68" s="1">
-        <f>Y68*Z68*AC68</f>
+        <f t="shared" si="14"/>
         <v>48644600000</v>
       </c>
       <c r="K68" s="1">
@@ -8256,7 +8256,7 @@
         <v>40</v>
       </c>
       <c r="Z68" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>145000</v>
       </c>
       <c r="AA68" s="1">
@@ -8297,15 +8297,15 @@
         <v>64</v>
       </c>
       <c r="H69" s="1">
-        <f>AG71*Z69*AA69/10</f>
+        <f t="shared" si="12"/>
         <v>822615000</v>
       </c>
       <c r="I69" s="1">
-        <f>AB69*AG67*Z69/10</f>
+        <f t="shared" si="13"/>
         <v>171405000</v>
       </c>
       <c r="J69" s="1">
-        <f>Y69*Z69*AC69</f>
+        <f t="shared" si="14"/>
         <v>52164000000</v>
       </c>
       <c r="K69" s="1">
@@ -8362,7 +8362,7 @@
         <v>40</v>
       </c>
       <c r="Z69" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>150000</v>
       </c>
       <c r="AA69" s="1">
@@ -8403,31 +8403,31 @@
         <v>65</v>
       </c>
       <c r="H70" s="1">
-        <f>AG72*Z70*AA70/10</f>
+        <f t="shared" si="12"/>
         <v>887576500</v>
       </c>
       <c r="I70" s="1">
-        <f t="shared" ref="I70:I77" si="13">AB70*AG68*Z70/10</f>
+        <f t="shared" ref="I70:I77" si="16">AB70*AG68*Z70/10</f>
         <v>185581500</v>
       </c>
       <c r="J70" s="1">
-        <f>Y70*Z70*AC70</f>
+        <f t="shared" si="14"/>
         <v>55831000000</v>
       </c>
       <c r="K70" s="1">
-        <f t="shared" ref="K70:K77" si="14">Y70*5</f>
+        <f t="shared" ref="K70:K77" si="17">Y70*5</f>
         <v>200</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L77" si="15">Y70*3</f>
+        <f t="shared" ref="L70:L77" si="18">Y70*3</f>
         <v>120</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" ref="M70:M77" si="16">Y70*2</f>
+        <f t="shared" ref="M70:M77" si="19">Y70*2</f>
         <v>80</v>
       </c>
       <c r="N70" s="1">
-        <f t="shared" ref="N70:N77" si="17">Y70*4</f>
+        <f t="shared" ref="N70:N77" si="20">Y70*4</f>
         <v>160</v>
       </c>
       <c r="O70" s="1">
@@ -8454,11 +8454,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V77" si="18">X70*10</f>
+        <f t="shared" ref="V70:V77" si="21">X70*10</f>
         <v>650</v>
       </c>
       <c r="W70" s="1">
-        <f t="shared" ref="W70:W77" si="19">X70*10</f>
+        <f t="shared" ref="W70:W77" si="22">X70*10</f>
         <v>650</v>
       </c>
       <c r="X70" s="1">
@@ -8468,7 +8468,7 @@
         <v>40</v>
       </c>
       <c r="Z70" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>155000</v>
       </c>
       <c r="AA70" s="1">
@@ -8509,31 +8509,31 @@
         <v>66</v>
       </c>
       <c r="H71" s="1">
-        <f t="shared" ref="H71:H77" si="20">AG73*Z71*AA71/10</f>
+        <f t="shared" ref="H71:H77" si="23">AG73*Z71*AA71/10</f>
         <v>932816000</v>
       </c>
       <c r="I71" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>194064000</v>
       </c>
       <c r="J71" s="1">
-        <f>Y71*Z71*AC71</f>
+        <f t="shared" si="14"/>
         <v>59635200000</v>
       </c>
       <c r="K71" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>200</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>120</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>80</v>
       </c>
       <c r="N71" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>160</v>
       </c>
       <c r="O71" s="1">
@@ -8560,11 +8560,11 @@
         <v>0</v>
       </c>
       <c r="V71" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>660</v>
       </c>
       <c r="W71" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>660</v>
       </c>
       <c r="X71" s="1">
@@ -8574,7 +8574,7 @@
         <v>40</v>
       </c>
       <c r="Z71" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>160000</v>
       </c>
       <c r="AA71" s="1">
@@ -8615,42 +8615,42 @@
         <v>67</v>
       </c>
       <c r="H72" s="1">
+        <f t="shared" si="23"/>
+        <v>990511500</v>
+      </c>
+      <c r="I72" s="1">
+        <f t="shared" si="16"/>
+        <v>201415500</v>
+      </c>
+      <c r="J72" s="1">
+        <f t="shared" si="14"/>
+        <v>63591000000</v>
+      </c>
+      <c r="K72" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L72" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M72" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N72" s="1">
         <f t="shared" si="20"/>
-        <v>990511500</v>
-      </c>
-      <c r="I72" s="1">
-        <f t="shared" si="13"/>
-        <v>201415500</v>
-      </c>
-      <c r="J72" s="1">
-        <f>Y72*Z72*AC72</f>
-        <v>63591000000</v>
-      </c>
-      <c r="K72" s="1">
-        <f t="shared" si="14"/>
-        <v>200</v>
-      </c>
-      <c r="L72" s="1">
-        <f t="shared" si="15"/>
-        <v>120</v>
-      </c>
-      <c r="M72" s="1">
-        <f t="shared" si="16"/>
-        <v>80</v>
-      </c>
-      <c r="N72" s="1">
-        <f t="shared" si="17"/>
         <v>160</v>
       </c>
       <c r="O72" s="1">
         <v>66</v>
       </c>
       <c r="P72" s="4">
-        <f t="shared" ref="P72:P77" si="21">P71+1</f>
+        <f t="shared" ref="P72:P77" si="24">P71+1</f>
         <v>66</v>
       </c>
       <c r="Q72" s="4">
-        <f t="shared" ref="Q72:Q77" si="22">Q71+1</f>
+        <f t="shared" ref="Q72:Q77" si="25">Q71+1</f>
         <v>75</v>
       </c>
       <c r="R72" s="1">
@@ -8666,11 +8666,11 @@
         <v>0</v>
       </c>
       <c r="V72" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>670</v>
       </c>
       <c r="W72" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>670</v>
       </c>
       <c r="X72" s="1">
@@ -8680,7 +8680,7 @@
         <v>40</v>
       </c>
       <c r="Z72" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>165000</v>
       </c>
       <c r="AA72" s="1">
@@ -8721,62 +8721,62 @@
         <v>68</v>
       </c>
       <c r="H73" s="1">
+        <f t="shared" si="23"/>
+        <v>1026409000</v>
+      </c>
+      <c r="I73" s="1">
+        <f t="shared" si="16"/>
+        <v>210171000</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" ref="J73:J77" si="26">Y73*Z73*AC73</f>
+        <v>67768800000</v>
+      </c>
+      <c r="K73" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L73" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M73" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N73" s="1">
         <f t="shared" si="20"/>
-        <v>1026409000</v>
-      </c>
-      <c r="I73" s="1">
-        <f t="shared" si="13"/>
-        <v>210171000</v>
-      </c>
-      <c r="J73" s="1">
-        <f t="shared" ref="J73:J77" si="23">Y73*Z73*AC73</f>
-        <v>67768800000</v>
-      </c>
-      <c r="K73" s="1">
-        <f t="shared" si="14"/>
-        <v>200</v>
-      </c>
-      <c r="L73" s="1">
-        <f t="shared" si="15"/>
-        <v>120</v>
-      </c>
-      <c r="M73" s="1">
-        <f t="shared" si="16"/>
-        <v>80</v>
-      </c>
-      <c r="N73" s="1">
-        <f t="shared" si="17"/>
         <v>160</v>
       </c>
       <c r="O73" s="1">
         <v>67</v>
       </c>
       <c r="P73" s="4">
+        <f t="shared" si="24"/>
+        <v>67</v>
+      </c>
+      <c r="Q73" s="4">
+        <f t="shared" si="25"/>
+        <v>76</v>
+      </c>
+      <c r="R73" s="1">
+        <v>0</v>
+      </c>
+      <c r="S73" s="1">
+        <v>0</v>
+      </c>
+      <c r="T73" s="8">
+        <v>0</v>
+      </c>
+      <c r="U73" s="8">
+        <v>0</v>
+      </c>
+      <c r="V73" s="1">
         <f t="shared" si="21"/>
-        <v>67</v>
-      </c>
-      <c r="Q73" s="4">
+        <v>680</v>
+      </c>
+      <c r="W73" s="1">
         <f t="shared" si="22"/>
-        <v>76</v>
-      </c>
-      <c r="R73" s="1">
-        <v>0</v>
-      </c>
-      <c r="S73" s="1">
-        <v>0</v>
-      </c>
-      <c r="T73" s="8">
-        <v>0</v>
-      </c>
-      <c r="U73" s="8">
-        <v>0</v>
-      </c>
-      <c r="V73" s="1">
-        <f t="shared" si="18"/>
-        <v>680</v>
-      </c>
-      <c r="W73" s="1">
-        <f t="shared" si="19"/>
         <v>680</v>
       </c>
       <c r="X73" s="1">
@@ -8786,7 +8786,7 @@
         <v>40</v>
       </c>
       <c r="Z73" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>170000</v>
       </c>
       <c r="AA73" s="1">
@@ -8827,62 +8827,62 @@
         <v>69</v>
       </c>
       <c r="H74" s="1">
+        <f t="shared" si="23"/>
+        <v>1068707500</v>
+      </c>
+      <c r="I74" s="1">
+        <f t="shared" si="16"/>
+        <v>225907500</v>
+      </c>
+      <c r="J74" s="1">
+        <f t="shared" si="26"/>
+        <v>72121000000</v>
+      </c>
+      <c r="K74" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L74" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M74" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N74" s="1">
         <f t="shared" si="20"/>
-        <v>1068707500</v>
-      </c>
-      <c r="I74" s="1">
-        <f t="shared" si="13"/>
-        <v>225907500</v>
-      </c>
-      <c r="J74" s="1">
-        <f t="shared" si="23"/>
-        <v>72121000000</v>
-      </c>
-      <c r="K74" s="1">
-        <f t="shared" si="14"/>
-        <v>200</v>
-      </c>
-      <c r="L74" s="1">
-        <f t="shared" si="15"/>
-        <v>120</v>
-      </c>
-      <c r="M74" s="1">
-        <f t="shared" si="16"/>
-        <v>80</v>
-      </c>
-      <c r="N74" s="1">
-        <f t="shared" si="17"/>
         <v>160</v>
       </c>
       <c r="O74" s="1">
         <v>68</v>
       </c>
       <c r="P74" s="4">
+        <f t="shared" si="24"/>
+        <v>68</v>
+      </c>
+      <c r="Q74" s="4">
+        <f t="shared" si="25"/>
+        <v>77</v>
+      </c>
+      <c r="R74" s="1">
+        <v>0</v>
+      </c>
+      <c r="S74" s="1">
+        <v>0</v>
+      </c>
+      <c r="T74" s="8">
+        <v>0</v>
+      </c>
+      <c r="U74" s="8">
+        <v>0</v>
+      </c>
+      <c r="V74" s="1">
         <f t="shared" si="21"/>
-        <v>68</v>
-      </c>
-      <c r="Q74" s="4">
+        <v>690</v>
+      </c>
+      <c r="W74" s="1">
         <f t="shared" si="22"/>
-        <v>77</v>
-      </c>
-      <c r="R74" s="1">
-        <v>0</v>
-      </c>
-      <c r="S74" s="1">
-        <v>0</v>
-      </c>
-      <c r="T74" s="8">
-        <v>0</v>
-      </c>
-      <c r="U74" s="8">
-        <v>0</v>
-      </c>
-      <c r="V74" s="1">
-        <f t="shared" si="18"/>
-        <v>690</v>
-      </c>
-      <c r="W74" s="1">
-        <f t="shared" si="19"/>
         <v>690</v>
       </c>
       <c r="X74" s="1">
@@ -8892,7 +8892,7 @@
         <v>40</v>
       </c>
       <c r="Z74" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>175000</v>
       </c>
       <c r="AA74" s="1">
@@ -8933,62 +8933,62 @@
         <v>70</v>
       </c>
       <c r="H75" s="1">
+        <f t="shared" si="23"/>
+        <v>1117926000</v>
+      </c>
+      <c r="I75" s="1">
+        <f t="shared" si="16"/>
+        <v>236574000</v>
+      </c>
+      <c r="J75" s="1">
+        <f t="shared" si="26"/>
+        <v>76680000000</v>
+      </c>
+      <c r="K75" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L75" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M75" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N75" s="1">
         <f t="shared" si="20"/>
-        <v>1117926000</v>
-      </c>
-      <c r="I75" s="1">
-        <f t="shared" si="13"/>
-        <v>236574000</v>
-      </c>
-      <c r="J75" s="1">
-        <f t="shared" si="23"/>
-        <v>76680000000</v>
-      </c>
-      <c r="K75" s="1">
-        <f t="shared" si="14"/>
-        <v>200</v>
-      </c>
-      <c r="L75" s="1">
-        <f t="shared" si="15"/>
-        <v>120</v>
-      </c>
-      <c r="M75" s="1">
-        <f t="shared" si="16"/>
-        <v>80</v>
-      </c>
-      <c r="N75" s="1">
-        <f t="shared" si="17"/>
         <v>160</v>
       </c>
       <c r="O75" s="1">
         <v>69</v>
       </c>
       <c r="P75" s="4">
+        <f t="shared" si="24"/>
+        <v>69</v>
+      </c>
+      <c r="Q75" s="4">
+        <f t="shared" si="25"/>
+        <v>78</v>
+      </c>
+      <c r="R75" s="1">
+        <v>0</v>
+      </c>
+      <c r="S75" s="1">
+        <v>0</v>
+      </c>
+      <c r="T75" s="8">
+        <v>0</v>
+      </c>
+      <c r="U75" s="8">
+        <v>0</v>
+      </c>
+      <c r="V75" s="1">
         <f t="shared" si="21"/>
-        <v>69</v>
-      </c>
-      <c r="Q75" s="4">
+        <v>700</v>
+      </c>
+      <c r="W75" s="1">
         <f t="shared" si="22"/>
-        <v>78</v>
-      </c>
-      <c r="R75" s="1">
-        <v>0</v>
-      </c>
-      <c r="S75" s="1">
-        <v>0</v>
-      </c>
-      <c r="T75" s="8">
-        <v>0</v>
-      </c>
-      <c r="U75" s="8">
-        <v>0</v>
-      </c>
-      <c r="V75" s="1">
-        <f t="shared" si="18"/>
-        <v>700</v>
-      </c>
-      <c r="W75" s="1">
-        <f t="shared" si="19"/>
         <v>700</v>
       </c>
       <c r="X75" s="1">
@@ -8998,7 +8998,7 @@
         <v>40</v>
       </c>
       <c r="Z75" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>180000</v>
       </c>
       <c r="AA75" s="1">
@@ -9039,62 +9039,62 @@
         <v>71</v>
       </c>
       <c r="H76" s="1">
+        <f t="shared" si="23"/>
+        <v>1174583500</v>
+      </c>
+      <c r="I76" s="1">
+        <f t="shared" si="16"/>
+        <v>250360500</v>
+      </c>
+      <c r="J76" s="1">
+        <f t="shared" si="26"/>
+        <v>81392600000</v>
+      </c>
+      <c r="K76" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L76" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M76" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N76" s="1">
         <f t="shared" si="20"/>
-        <v>1174583500</v>
-      </c>
-      <c r="I76" s="1">
-        <f t="shared" si="13"/>
-        <v>250360500</v>
-      </c>
-      <c r="J76" s="1">
-        <f t="shared" si="23"/>
-        <v>81392600000</v>
-      </c>
-      <c r="K76" s="1">
-        <f t="shared" si="14"/>
-        <v>200</v>
-      </c>
-      <c r="L76" s="1">
-        <f t="shared" si="15"/>
-        <v>120</v>
-      </c>
-      <c r="M76" s="1">
-        <f t="shared" si="16"/>
-        <v>80</v>
-      </c>
-      <c r="N76" s="1">
-        <f t="shared" si="17"/>
         <v>160</v>
       </c>
       <c r="O76" s="1">
         <v>70</v>
       </c>
       <c r="P76" s="4">
+        <f t="shared" si="24"/>
+        <v>70</v>
+      </c>
+      <c r="Q76" s="4">
+        <f t="shared" si="25"/>
+        <v>79</v>
+      </c>
+      <c r="R76" s="1">
+        <v>0</v>
+      </c>
+      <c r="S76" s="1">
+        <v>0</v>
+      </c>
+      <c r="T76" s="8">
+        <v>0</v>
+      </c>
+      <c r="U76" s="8">
+        <v>0</v>
+      </c>
+      <c r="V76" s="1">
         <f t="shared" si="21"/>
-        <v>70</v>
-      </c>
-      <c r="Q76" s="4">
+        <v>710</v>
+      </c>
+      <c r="W76" s="1">
         <f t="shared" si="22"/>
-        <v>79</v>
-      </c>
-      <c r="R76" s="1">
-        <v>0</v>
-      </c>
-      <c r="S76" s="1">
-        <v>0</v>
-      </c>
-      <c r="T76" s="8">
-        <v>0</v>
-      </c>
-      <c r="U76" s="8">
-        <v>0</v>
-      </c>
-      <c r="V76" s="1">
-        <f t="shared" si="18"/>
-        <v>710</v>
-      </c>
-      <c r="W76" s="1">
-        <f t="shared" si="19"/>
         <v>710</v>
       </c>
       <c r="X76" s="1">
@@ -9104,7 +9104,7 @@
         <v>40</v>
       </c>
       <c r="Z76" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>185000</v>
       </c>
       <c r="AA76" s="1">
@@ -9145,62 +9145,62 @@
         <v>72</v>
       </c>
       <c r="H77" s="1">
+        <f t="shared" si="23"/>
+        <v>1226051000</v>
+      </c>
+      <c r="I77" s="1">
+        <f t="shared" si="16"/>
+        <v>258609000</v>
+      </c>
+      <c r="J77" s="1">
+        <f t="shared" si="26"/>
+        <v>86275200000</v>
+      </c>
+      <c r="K77" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L77" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M77" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N77" s="1">
         <f t="shared" si="20"/>
-        <v>1226051000</v>
-      </c>
-      <c r="I77" s="1">
-        <f t="shared" si="13"/>
-        <v>258609000</v>
-      </c>
-      <c r="J77" s="1">
-        <f t="shared" si="23"/>
-        <v>86275200000</v>
-      </c>
-      <c r="K77" s="1">
-        <f t="shared" si="14"/>
-        <v>200</v>
-      </c>
-      <c r="L77" s="1">
-        <f t="shared" si="15"/>
-        <v>120</v>
-      </c>
-      <c r="M77" s="1">
-        <f t="shared" si="16"/>
-        <v>80</v>
-      </c>
-      <c r="N77" s="1">
-        <f t="shared" si="17"/>
         <v>160</v>
       </c>
       <c r="O77" s="1">
         <v>71</v>
       </c>
       <c r="P77" s="4">
+        <f t="shared" si="24"/>
+        <v>71</v>
+      </c>
+      <c r="Q77" s="4">
+        <f t="shared" si="25"/>
+        <v>80</v>
+      </c>
+      <c r="R77" s="1">
+        <v>0</v>
+      </c>
+      <c r="S77" s="1">
+        <v>0</v>
+      </c>
+      <c r="T77" s="8">
+        <v>0</v>
+      </c>
+      <c r="U77" s="8">
+        <v>0</v>
+      </c>
+      <c r="V77" s="1">
         <f t="shared" si="21"/>
-        <v>71</v>
-      </c>
-      <c r="Q77" s="4">
+        <v>720</v>
+      </c>
+      <c r="W77" s="1">
         <f t="shared" si="22"/>
-        <v>80</v>
-      </c>
-      <c r="R77" s="1">
-        <v>0</v>
-      </c>
-      <c r="S77" s="1">
-        <v>0</v>
-      </c>
-      <c r="T77" s="8">
-        <v>0</v>
-      </c>
-      <c r="U77" s="8">
-        <v>0</v>
-      </c>
-      <c r="V77" s="1">
-        <f t="shared" si="18"/>
-        <v>720</v>
-      </c>
-      <c r="W77" s="1">
-        <f t="shared" si="19"/>
         <v>720</v>
       </c>
       <c r="X77" s="1">
@@ -9210,7 +9210,7 @@
         <v>40</v>
       </c>
       <c r="Z77" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>190000</v>
       </c>
       <c r="AA77" s="1">

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
@@ -1867,8 +1867,9 @@
       <c r="P7" s="8">
         <v>1</v>
       </c>
-      <c r="Q7" s="8">
-        <v>10</v>
+      <c r="Q7" s="4">
+        <f>Q6+1</f>
+        <v>2</v>
       </c>
       <c r="R7" s="1">
         <v>0</v>
@@ -1969,8 +1970,8 @@
         <v>2</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" ref="Q8:Q71" si="7">Q7+1</f>
-        <v>11</v>
+        <f>Q7+1</f>
+        <v>3</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
@@ -2071,8 +2072,8 @@
         <v>3</v>
       </c>
       <c r="Q9" s="4">
-        <f t="shared" si="7"/>
-        <v>12</v>
+        <f t="shared" ref="Q8:Q71" si="7">Q8+1</f>
+        <v>4</v>
       </c>
       <c r="R9" s="1">
         <v>0</v>
@@ -2174,7 +2175,7 @@
       </c>
       <c r="Q10" s="4">
         <f t="shared" si="7"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R10" s="1">
         <v>0</v>
@@ -2276,7 +2277,7 @@
       </c>
       <c r="Q11" s="2">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R11" s="3">
         <v>0</v>
@@ -2378,7 +2379,7 @@
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R12" s="1">
         <v>0</v>
@@ -2481,7 +2482,7 @@
       </c>
       <c r="Q13" s="4">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
@@ -2584,7 +2585,7 @@
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="R14" s="1">
         <v>0</v>
@@ -2687,7 +2688,7 @@
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="R15" s="1">
         <v>0</v>
@@ -2790,7 +2791,7 @@
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R16" s="1">
         <v>0</v>
@@ -2893,7 +2894,7 @@
       </c>
       <c r="Q17" s="2">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="R17" s="3">
         <v>0</v>
@@ -2996,7 +2997,7 @@
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="R18" s="1">
         <v>0</v>
@@ -3099,7 +3100,7 @@
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="R19" s="1">
         <v>0</v>
@@ -3202,7 +3203,7 @@
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="7"/>
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -3305,7 +3306,7 @@
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="R21" s="1">
         <v>0</v>
@@ -3408,7 +3409,7 @@
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="R22" s="1">
         <v>0</v>
@@ -3511,7 +3512,7 @@
       </c>
       <c r="Q23" s="2">
         <f t="shared" si="7"/>
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R23" s="3">
         <v>0</v>
@@ -3614,7 +3615,7 @@
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="7"/>
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="R24" s="1">
         <v>0</v>
@@ -3717,7 +3718,7 @@
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="R25" s="1">
         <v>0</v>
@@ -3820,7 +3821,7 @@
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="R26" s="1">
         <v>0</v>
@@ -3923,7 +3924,7 @@
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R27" s="1">
         <v>0</v>
@@ -4026,7 +4027,7 @@
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="7"/>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R28" s="1">
         <v>0</v>
@@ -4129,7 +4130,7 @@
       </c>
       <c r="Q29" s="2">
         <f t="shared" si="7"/>
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -4232,7 +4233,7 @@
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="7"/>
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R30" s="1">
         <v>0</v>
@@ -4335,7 +4336,7 @@
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="7"/>
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="R31" s="1">
         <v>0</v>
@@ -4438,7 +4439,7 @@
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="7"/>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R32" s="1">
         <v>0</v>
@@ -4541,7 +4542,7 @@
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="7"/>
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R33" s="1">
         <v>0</v>
@@ -4644,7 +4645,7 @@
       </c>
       <c r="Q34" s="4">
         <f t="shared" si="7"/>
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="R34" s="1">
         <v>0</v>
@@ -4747,7 +4748,7 @@
       </c>
       <c r="Q35" s="2">
         <f t="shared" si="7"/>
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="R35" s="3">
         <v>0</v>
@@ -4850,7 +4851,7 @@
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="7"/>
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="R36" s="1">
         <v>0</v>
@@ -4953,7 +4954,7 @@
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="R37" s="1">
         <v>0</v>
@@ -5056,7 +5057,7 @@
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="7"/>
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="R38" s="1">
         <v>0</v>
@@ -5159,7 +5160,7 @@
       </c>
       <c r="Q39" s="4">
         <f t="shared" si="7"/>
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="R39" s="1">
         <v>0</v>
@@ -5262,7 +5263,7 @@
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="7"/>
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="R40" s="1">
         <v>0</v>
@@ -5366,7 +5367,7 @@
       </c>
       <c r="Q41" s="2">
         <f t="shared" si="7"/>
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="R41" s="3">
         <v>0</v>
@@ -5472,7 +5473,7 @@
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="R42" s="1">
         <v>0</v>
@@ -5578,7 +5579,7 @@
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="7"/>
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R43" s="1">
         <v>0</v>
@@ -5684,7 +5685,7 @@
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="7"/>
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1">
         <v>0</v>
@@ -5790,7 +5791,7 @@
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="7"/>
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="R45" s="1">
         <v>0</v>
@@ -5896,7 +5897,7 @@
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="7"/>
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="R46" s="1">
         <v>0</v>
@@ -6001,7 +6002,7 @@
       </c>
       <c r="Q47" s="4">
         <f t="shared" si="7"/>
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R47" s="1">
         <v>0</v>
@@ -6107,7 +6108,7 @@
       </c>
       <c r="Q48" s="4">
         <f t="shared" si="7"/>
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="R48" s="1">
         <v>0</v>
@@ -6213,7 +6214,7 @@
       </c>
       <c r="Q49" s="4">
         <f t="shared" si="7"/>
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="R49" s="1">
         <v>0</v>
@@ -6319,7 +6320,7 @@
       </c>
       <c r="Q50" s="4">
         <f t="shared" si="7"/>
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="R50" s="1">
         <v>0</v>
@@ -6425,7 +6426,7 @@
       </c>
       <c r="Q51" s="4">
         <f t="shared" si="7"/>
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R51" s="1">
         <v>0</v>
@@ -6531,7 +6532,7 @@
       </c>
       <c r="Q52" s="4">
         <f t="shared" si="7"/>
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="R52" s="1">
         <v>0</v>
@@ -6637,7 +6638,7 @@
       </c>
       <c r="Q53" s="4">
         <f t="shared" si="7"/>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="R53" s="1">
         <v>0</v>
@@ -6743,7 +6744,7 @@
       </c>
       <c r="Q54" s="4">
         <f t="shared" si="7"/>
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="R54" s="1">
         <v>0</v>
@@ -6849,7 +6850,7 @@
       </c>
       <c r="Q55" s="4">
         <f t="shared" si="7"/>
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="R55" s="1">
         <v>0</v>
@@ -6955,7 +6956,7 @@
       </c>
       <c r="Q56" s="4">
         <f t="shared" si="7"/>
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="R56" s="1">
         <v>0</v>
@@ -7061,7 +7062,7 @@
       </c>
       <c r="Q57" s="4">
         <f t="shared" si="7"/>
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="R57" s="1">
         <v>0</v>
@@ -7167,7 +7168,7 @@
       </c>
       <c r="Q58" s="4">
         <f t="shared" si="7"/>
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="R58" s="1">
         <v>0</v>
@@ -7273,7 +7274,7 @@
       </c>
       <c r="Q59" s="4">
         <f t="shared" si="7"/>
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="R59" s="1">
         <v>0</v>
@@ -7379,7 +7380,7 @@
       </c>
       <c r="Q60" s="4">
         <f t="shared" si="7"/>
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="R60" s="1">
         <v>0</v>
@@ -7485,7 +7486,7 @@
       </c>
       <c r="Q61" s="4">
         <f t="shared" si="7"/>
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="R61" s="1">
         <v>0</v>
@@ -7591,7 +7592,7 @@
       </c>
       <c r="Q62" s="4">
         <f t="shared" si="7"/>
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="R62" s="1">
         <v>0</v>
@@ -7697,7 +7698,7 @@
       </c>
       <c r="Q63" s="4">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="R63" s="1">
         <v>0</v>
@@ -7803,7 +7804,7 @@
       </c>
       <c r="Q64" s="4">
         <f t="shared" si="7"/>
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="R64" s="1">
         <v>0</v>
@@ -7909,7 +7910,7 @@
       </c>
       <c r="Q65" s="4">
         <f t="shared" si="7"/>
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="R65" s="1">
         <v>0</v>
@@ -8015,7 +8016,7 @@
       </c>
       <c r="Q66" s="4">
         <f t="shared" si="7"/>
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="R66" s="1">
         <v>0</v>
@@ -8121,7 +8122,7 @@
       </c>
       <c r="Q67" s="4">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="R67" s="1">
         <v>0</v>
@@ -8227,7 +8228,7 @@
       </c>
       <c r="Q68" s="4">
         <f t="shared" si="7"/>
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="R68" s="1">
         <v>0</v>
@@ -8333,7 +8334,7 @@
       </c>
       <c r="Q69" s="4">
         <f t="shared" si="7"/>
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="R69" s="1">
         <v>0</v>
@@ -8439,7 +8440,7 @@
       </c>
       <c r="Q70" s="4">
         <f t="shared" si="7"/>
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="R70" s="1">
         <v>0</v>
@@ -8545,7 +8546,7 @@
       </c>
       <c r="Q71" s="4">
         <f t="shared" si="7"/>
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="R71" s="1">
         <v>0</v>
@@ -8651,7 +8652,7 @@
       </c>
       <c r="Q72" s="4">
         <f t="shared" ref="Q72:Q77" si="25">Q71+1</f>
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="R72" s="1">
         <v>0</v>
@@ -8757,7 +8758,7 @@
       </c>
       <c r="Q73" s="4">
         <f t="shared" si="25"/>
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="R73" s="1">
         <v>0</v>
@@ -8863,7 +8864,7 @@
       </c>
       <c r="Q74" s="4">
         <f t="shared" si="25"/>
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="R74" s="1">
         <v>0</v>
@@ -8969,7 +8970,7 @@
       </c>
       <c r="Q75" s="4">
         <f t="shared" si="25"/>
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="R75" s="1">
         <v>0</v>
@@ -9075,7 +9076,7 @@
       </c>
       <c r="Q76" s="4">
         <f t="shared" si="25"/>
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="R76" s="1">
         <v>0</v>
@@ -9181,7 +9182,7 @@
       </c>
       <c r="Q77" s="4">
         <f t="shared" si="25"/>
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="R77" s="1">
         <v>0</v>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -2148,7 +2148,7 @@
         <v>200</v>
       </c>
       <c r="J10" s="1">
-        <v>30000</v>
+        <v>31000</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="0"/>
@@ -2250,7 +2250,7 @@
         <v>300</v>
       </c>
       <c r="J11" s="3">
-        <v>50000</v>
+        <v>53000</v>
       </c>
       <c r="K11" s="3">
         <f t="shared" si="0"/>
@@ -2352,7 +2352,7 @@
         <v>490</v>
       </c>
       <c r="J12" s="4">
-        <v>80000</v>
+        <v>82000</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="0"/>
@@ -2455,7 +2455,7 @@
         <v>700</v>
       </c>
       <c r="J13" s="1">
-        <v>120000</v>
+        <v>125000</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="0"/>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="J14" s="1">
-        <v>170000</v>
+        <v>177000</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="0"/>
@@ -2661,7 +2661,7 @@
         <v>1500</v>
       </c>
       <c r="J15" s="1">
-        <v>240000</v>
+        <v>249000</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="0"/>
@@ -2764,7 +2764,7 @@
         <v>2400</v>
       </c>
       <c r="J16" s="1">
-        <v>350000</v>
+        <v>357000</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="0"/>
@@ -2867,7 +2867,7 @@
         <v>3600</v>
       </c>
       <c r="J17" s="3">
-        <v>480000</v>
+        <v>531000</v>
       </c>
       <c r="K17" s="3">
         <f t="shared" si="0"/>
@@ -2970,7 +2970,7 @@
         <v>6000</v>
       </c>
       <c r="J18" s="1">
-        <v>630000</v>
+        <v>733000</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" si="0"/>
@@ -3073,7 +3073,7 @@
         <v>9600</v>
       </c>
       <c r="J19" s="1">
-        <v>860000</v>
+        <v>917000</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" si="0"/>
@@ -3176,7 +3176,7 @@
         <v>14000</v>
       </c>
       <c r="J20" s="1">
-        <v>1150000</v>
+        <v>1230000</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" si="0"/>
@@ -3279,7 +3279,7 @@
         <v>20000</v>
       </c>
       <c r="J21" s="1">
-        <v>1350000</v>
+        <v>1510000</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" si="0"/>
@@ -3382,7 +3382,7 @@
         <v>27000</v>
       </c>
       <c r="J22" s="1">
-        <v>1900000</v>
+        <v>2370000</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" si="0"/>
@@ -3485,7 +3485,7 @@
         <v>36000</v>
       </c>
       <c r="J23" s="3">
-        <v>2550000</v>
+        <v>3590000</v>
       </c>
       <c r="K23" s="3">
         <f t="shared" si="0"/>
@@ -3588,7 +3588,7 @@
         <v>48000</v>
       </c>
       <c r="J24" s="1">
-        <v>3400000</v>
+        <v>5300000</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" si="0"/>
@@ -3691,7 +3691,7 @@
         <v>63000</v>
       </c>
       <c r="J25" s="1">
-        <v>4500000</v>
+        <v>7100000</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" si="0"/>
@@ -3794,7 +3794,7 @@
         <v>80000</v>
       </c>
       <c r="J26" s="1">
-        <v>6000000</v>
+        <v>10100000</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" si="0"/>
@@ -3897,7 +3897,7 @@
         <v>100000</v>
       </c>
       <c r="J27" s="1">
-        <v>8000000</v>
+        <v>15000000</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" si="0"/>
@@ -4000,7 +4000,7 @@
         <v>130000</v>
       </c>
       <c r="J28" s="1">
-        <v>10000000</v>
+        <v>21200000</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="0"/>
@@ -4103,7 +4103,7 @@
         <v>170000</v>
       </c>
       <c r="J29" s="3">
-        <v>12000000</v>
+        <v>29900000</v>
       </c>
       <c r="K29" s="3">
         <f t="shared" si="0"/>
@@ -4206,7 +4206,7 @@
         <v>270000</v>
       </c>
       <c r="J30" s="1">
-        <v>15000000</v>
+        <v>41400000</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="0"/>
@@ -4309,7 +4309,7 @@
         <v>390000</v>
       </c>
       <c r="J31" s="1">
-        <v>18000000</v>
+        <v>58600000</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" si="0"/>
@@ -4412,7 +4412,7 @@
         <v>500000</v>
       </c>
       <c r="J32" s="1">
-        <v>22000000</v>
+        <v>76500000</v>
       </c>
       <c r="K32" s="1">
         <f t="shared" si="0"/>
@@ -4515,7 +4515,7 @@
         <v>630000</v>
       </c>
       <c r="J33" s="1">
-        <v>24000000</v>
+        <v>1020000000</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" si="0"/>
@@ -4618,7 +4618,7 @@
         <v>800000</v>
       </c>
       <c r="J34" s="1">
-        <v>27000000</v>
+        <v>1420000000</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" si="0"/>
@@ -4721,7 +4721,7 @@
         <v>1000000</v>
       </c>
       <c r="J35" s="3">
-        <v>30000000</v>
+        <v>1910000000</v>
       </c>
       <c r="K35" s="3">
         <f t="shared" si="0"/>
@@ -4824,7 +4824,7 @@
         <v>1300000</v>
       </c>
       <c r="J36" s="1">
-        <v>34000000</v>
+        <v>2540000000</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" si="0"/>
@@ -4927,7 +4927,7 @@
         <v>1700000</v>
       </c>
       <c r="J37" s="1">
-        <v>39000000</v>
+        <v>3390000000</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" si="0"/>
@@ -5030,7 +5030,7 @@
         <v>2200000</v>
       </c>
       <c r="J38" s="1">
-        <v>45000000</v>
+        <v>4450000000</v>
       </c>
       <c r="K38" s="1">
         <f t="shared" si="0"/>
@@ -5133,7 +5133,7 @@
         <v>2800000</v>
       </c>
       <c r="J39" s="1">
-        <v>51000000</v>
+        <v>5510000000</v>
       </c>
       <c r="K39" s="1">
         <f t="shared" si="0"/>
@@ -5236,7 +5236,7 @@
         <v>3500000</v>
       </c>
       <c r="J40" s="1">
-        <v>58000000</v>
+        <v>6580000000</v>
       </c>
       <c r="K40" s="1">
         <f t="shared" si="0"/>
@@ -5340,7 +5340,7 @@
         <v>4300000</v>
       </c>
       <c r="J41" s="1">
-        <v>66000000</v>
+        <v>7660000000</v>
       </c>
       <c r="K41" s="3">
         <f t="shared" si="0"/>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -986,7 +986,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1005,6 +1005,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4515,7 +4518,7 @@
         <v>630000</v>
       </c>
       <c r="J33" s="1">
-        <v>1020000000</v>
+        <v>102000000</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" si="0"/>
@@ -4618,7 +4621,7 @@
         <v>800000</v>
       </c>
       <c r="J34" s="1">
-        <v>1420000000</v>
+        <v>142000000</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" si="0"/>
@@ -4721,7 +4724,7 @@
         <v>1000000</v>
       </c>
       <c r="J35" s="3">
-        <v>1910000000</v>
+        <v>191000000</v>
       </c>
       <c r="K35" s="3">
         <f t="shared" si="0"/>
@@ -4824,7 +4827,7 @@
         <v>1300000</v>
       </c>
       <c r="J36" s="1">
-        <v>2540000000</v>
+        <v>254000000</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" si="0"/>
@@ -4927,7 +4930,7 @@
         <v>1700000</v>
       </c>
       <c r="J37" s="1">
-        <v>3390000000</v>
+        <v>339000000</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" si="0"/>
@@ -5030,7 +5033,7 @@
         <v>2200000</v>
       </c>
       <c r="J38" s="1">
-        <v>4450000000</v>
+        <v>445000000</v>
       </c>
       <c r="K38" s="1">
         <f t="shared" si="0"/>
@@ -5133,7 +5136,7 @@
         <v>2800000</v>
       </c>
       <c r="J39" s="1">
-        <v>5510000000</v>
+        <v>551000000</v>
       </c>
       <c r="K39" s="1">
         <f t="shared" si="0"/>
@@ -5236,7 +5239,7 @@
         <v>3500000</v>
       </c>
       <c r="J40" s="1">
-        <v>6580000000</v>
+        <v>658000000</v>
       </c>
       <c r="K40" s="1">
         <f t="shared" si="0"/>
@@ -5340,7 +5343,7 @@
         <v>4300000</v>
       </c>
       <c r="J41" s="1">
-        <v>7660000000</v>
+        <v>766000000</v>
       </c>
       <c r="K41" s="3">
         <f t="shared" si="0"/>
@@ -5949,109 +5952,109 @@
         <v>179</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:33">
-      <c r="C47" s="1">
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:33">
+      <c r="C47" s="3">
         <v>42</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="3">
         <v>42</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="3">
         <v>1</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G47" s="3">
         <v>42</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H47" s="3">
         <f t="shared" si="12"/>
         <v>116572000</v>
       </c>
-      <c r="I47" s="1">
+      <c r="I47" s="3">
         <f t="shared" si="13"/>
         <v>26988000</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="3">
         <f t="shared" si="14"/>
         <v>5404800000</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K47" s="3">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="L47" s="1">
+      <c r="L47" s="3">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="M47" s="1">
+      <c r="M47" s="3">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47" s="3">
         <f t="shared" si="3"/>
         <v>160</v>
       </c>
-      <c r="O47" s="1">
+      <c r="O47" s="3">
         <v>41</v>
       </c>
-      <c r="P47" s="4">
+      <c r="P47" s="2">
         <f t="shared" si="6"/>
         <v>41</v>
       </c>
-      <c r="Q47" s="4">
+      <c r="Q47" s="2">
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="R47" s="1">
-        <v>0</v>
-      </c>
-      <c r="S47" s="1">
-        <v>0</v>
-      </c>
-      <c r="T47" s="8">
-        <v>0</v>
-      </c>
-      <c r="U47" s="8">
-        <v>0</v>
-      </c>
-      <c r="V47" s="1">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2">
+        <v>0</v>
+      </c>
+      <c r="U47" s="2">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
         <f t="shared" si="4"/>
         <v>420</v>
       </c>
-      <c r="W47" s="1">
+      <c r="W47" s="3">
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
-      <c r="X47" s="1">
+      <c r="X47" s="3">
         <v>42</v>
       </c>
-      <c r="Y47" s="1">
+      <c r="Y47" s="3">
         <v>40</v>
       </c>
-      <c r="Z47" s="4">
+      <c r="Z47" s="2">
         <f t="shared" si="15"/>
         <v>40000</v>
       </c>
-      <c r="AA47" s="1">
+      <c r="AA47" s="3">
         <v>151</v>
       </c>
-      <c r="AB47" s="4">
+      <c r="AB47" s="2">
         <v>39</v>
       </c>
-      <c r="AC47" s="4">
+      <c r="AC47" s="2">
         <f t="shared" si="8"/>
         <v>3378</v>
       </c>
-      <c r="AD47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="1"/>
-      <c r="AF47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="4">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3"/>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="2">
         <v>181</v>
       </c>
     </row>
@@ -6585,109 +6588,109 @@
         <v>211</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:33">
-      <c r="C53" s="1">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="C53" s="3">
         <v>48</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="3">
         <v>48</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="3">
         <v>1</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G53" s="3">
         <v>48</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H53" s="3">
         <f t="shared" si="12"/>
         <v>277319000</v>
       </c>
-      <c r="I53" s="1">
+      <c r="I53" s="3">
         <f t="shared" si="13"/>
         <v>54327000</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="3">
         <f t="shared" si="14"/>
         <v>12740000000</v>
       </c>
-      <c r="K53" s="1">
+      <c r="K53" s="3">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="L53" s="1">
+      <c r="L53" s="3">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="M53" s="1">
+      <c r="M53" s="3">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="N53" s="1">
+      <c r="N53" s="3">
         <f t="shared" si="3"/>
         <v>160</v>
       </c>
-      <c r="O53" s="1">
+      <c r="O53" s="3">
         <v>47</v>
       </c>
-      <c r="P53" s="4">
+      <c r="P53" s="2">
         <f t="shared" si="6"/>
         <v>47</v>
       </c>
-      <c r="Q53" s="4">
+      <c r="Q53" s="2">
         <f t="shared" si="7"/>
         <v>48</v>
       </c>
-      <c r="R53" s="1">
-        <v>0</v>
-      </c>
-      <c r="S53" s="1">
-        <v>0</v>
-      </c>
-      <c r="T53" s="8">
-        <v>0</v>
-      </c>
-      <c r="U53" s="8">
-        <v>0</v>
-      </c>
-      <c r="V53" s="1">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
         <f t="shared" si="4"/>
         <v>480</v>
       </c>
-      <c r="W53" s="1">
+      <c r="W53" s="3">
         <f t="shared" si="5"/>
         <v>480</v>
       </c>
-      <c r="X53" s="1">
+      <c r="X53" s="3">
         <v>48</v>
       </c>
-      <c r="Y53" s="1">
+      <c r="Y53" s="3">
         <v>40</v>
       </c>
-      <c r="Z53" s="4">
+      <c r="Z53" s="2">
         <f t="shared" si="15"/>
         <v>70000</v>
       </c>
-      <c r="AA53" s="1">
+      <c r="AA53" s="3">
         <v>173</v>
       </c>
-      <c r="AB53" s="4">
+      <c r="AB53" s="2">
         <v>39</v>
       </c>
-      <c r="AC53" s="4">
+      <c r="AC53" s="2">
         <f t="shared" si="8"/>
         <v>4550</v>
       </c>
-      <c r="AD53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE53" s="1"/>
-      <c r="AF53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG53" s="4">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3"/>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="2">
         <v>223</v>
       </c>
     </row>
@@ -7221,109 +7224,109 @@
         <v>241</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="3:33">
-      <c r="C59" s="1">
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="C59" s="3">
         <v>54</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="3">
         <v>54</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="3">
         <v>1</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" s="3">
         <v>54</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59" s="3">
         <f t="shared" si="12"/>
         <v>454990000</v>
       </c>
-      <c r="I59" s="1">
+      <c r="I59" s="3">
         <f t="shared" si="13"/>
         <v>93210000</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J59" s="3">
         <f t="shared" si="14"/>
         <v>23768000000</v>
       </c>
-      <c r="K59" s="1">
+      <c r="K59" s="3">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="L59" s="1">
+      <c r="L59" s="3">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="M59" s="1">
+      <c r="M59" s="3">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="N59" s="1">
+      <c r="N59" s="3">
         <f t="shared" si="3"/>
         <v>160</v>
       </c>
-      <c r="O59" s="1">
+      <c r="O59" s="3">
         <v>53</v>
       </c>
-      <c r="P59" s="4">
+      <c r="P59" s="2">
         <f t="shared" si="6"/>
         <v>53</v>
       </c>
-      <c r="Q59" s="4">
+      <c r="Q59" s="2">
         <f t="shared" si="7"/>
         <v>54</v>
       </c>
-      <c r="R59" s="1">
-        <v>0</v>
-      </c>
-      <c r="S59" s="1">
-        <v>0</v>
-      </c>
-      <c r="T59" s="8">
-        <v>0</v>
-      </c>
-      <c r="U59" s="8">
-        <v>0</v>
-      </c>
-      <c r="V59" s="1">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
         <f t="shared" si="4"/>
         <v>540</v>
       </c>
-      <c r="W59" s="1">
+      <c r="W59" s="3">
         <f t="shared" si="5"/>
         <v>540</v>
       </c>
-      <c r="X59" s="1">
+      <c r="X59" s="3">
         <v>54</v>
       </c>
-      <c r="Y59" s="1">
+      <c r="Y59" s="3">
         <v>40</v>
       </c>
-      <c r="Z59" s="4">
+      <c r="Z59" s="2">
         <f t="shared" si="15"/>
         <v>100000</v>
       </c>
-      <c r="AA59" s="1">
+      <c r="AA59" s="3">
         <v>173</v>
       </c>
-      <c r="AB59" s="4">
+      <c r="AB59" s="2">
         <v>39</v>
       </c>
-      <c r="AC59" s="4">
+      <c r="AC59" s="2">
         <f t="shared" si="8"/>
         <v>5942</v>
       </c>
-      <c r="AD59" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="1"/>
-      <c r="AF59" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="4">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="2">
         <v>251</v>
       </c>
     </row>
@@ -7857,109 +7860,109 @@
         <v>277</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="3:33">
-      <c r="C65" s="1">
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="C65" s="3">
         <v>60</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="3">
         <v>60</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="3">
         <v>1</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G65" s="1">
+      <c r="G65" s="3">
         <v>60</v>
       </c>
-      <c r="H65" s="1">
+      <c r="H65" s="3">
         <f t="shared" si="12"/>
         <v>658957000</v>
       </c>
-      <c r="I65" s="1">
+      <c r="I65" s="3">
         <f t="shared" si="13"/>
         <v>137397000</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J65" s="3">
         <f t="shared" si="14"/>
         <v>39156000000</v>
       </c>
-      <c r="K65" s="1">
+      <c r="K65" s="3">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="L65" s="1">
+      <c r="L65" s="3">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="M65" s="1">
+      <c r="M65" s="3">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="N65" s="1">
+      <c r="N65" s="3">
         <f t="shared" si="3"/>
         <v>160</v>
       </c>
-      <c r="O65" s="1">
+      <c r="O65" s="3">
         <v>59</v>
       </c>
-      <c r="P65" s="4">
+      <c r="P65" s="2">
         <f t="shared" si="6"/>
         <v>59</v>
       </c>
-      <c r="Q65" s="4">
+      <c r="Q65" s="2">
         <f t="shared" si="7"/>
         <v>60</v>
       </c>
-      <c r="R65" s="1">
-        <v>0</v>
-      </c>
-      <c r="S65" s="1">
-        <v>0</v>
-      </c>
-      <c r="T65" s="8">
-        <v>0</v>
-      </c>
-      <c r="U65" s="8">
-        <v>0</v>
-      </c>
-      <c r="V65" s="1">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2">
+        <v>0</v>
+      </c>
+      <c r="U65" s="2">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
         <f t="shared" si="4"/>
         <v>600</v>
       </c>
-      <c r="W65" s="1">
+      <c r="W65" s="3">
         <f t="shared" si="5"/>
         <v>600</v>
       </c>
-      <c r="X65" s="1">
+      <c r="X65" s="3">
         <v>60</v>
       </c>
-      <c r="Y65" s="1">
+      <c r="Y65" s="3">
         <v>40</v>
       </c>
-      <c r="Z65" s="4">
+      <c r="Z65" s="2">
         <f t="shared" si="15"/>
         <v>130000</v>
       </c>
-      <c r="AA65" s="1">
+      <c r="AA65" s="3">
         <v>173</v>
       </c>
-      <c r="AB65" s="4">
+      <c r="AB65" s="2">
         <v>39</v>
       </c>
-      <c r="AC65" s="4">
+      <c r="AC65" s="2">
         <f t="shared" si="8"/>
         <v>7530</v>
       </c>
-      <c r="AD65" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE65" s="1"/>
-      <c r="AF65" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG65" s="4">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3"/>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="2">
         <v>281</v>
       </c>
     </row>
@@ -8493,109 +8496,109 @@
         <v>313</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="3:33">
-      <c r="C71" s="1">
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="C71" s="3">
         <v>66</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71" s="3">
         <v>66</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="3">
         <v>1</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G71" s="3">
         <v>66</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H71" s="3">
         <f t="shared" ref="H71:H77" si="23">AG73*Z71*AA71/10</f>
         <v>932816000</v>
       </c>
-      <c r="I71" s="1">
+      <c r="I71" s="3">
         <f t="shared" si="16"/>
         <v>194064000</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J71" s="3">
         <f t="shared" si="14"/>
         <v>59635200000</v>
       </c>
-      <c r="K71" s="1">
+      <c r="K71" s="3">
         <f t="shared" si="17"/>
         <v>200</v>
       </c>
-      <c r="L71" s="1">
+      <c r="L71" s="3">
         <f t="shared" si="18"/>
         <v>120</v>
       </c>
-      <c r="M71" s="1">
+      <c r="M71" s="3">
         <f t="shared" si="19"/>
         <v>80</v>
       </c>
-      <c r="N71" s="1">
+      <c r="N71" s="3">
         <f t="shared" si="20"/>
         <v>160</v>
       </c>
-      <c r="O71" s="1">
+      <c r="O71" s="3">
         <v>65</v>
       </c>
-      <c r="P71" s="4">
+      <c r="P71" s="2">
         <f t="shared" si="6"/>
         <v>65</v>
       </c>
-      <c r="Q71" s="4">
+      <c r="Q71" s="2">
         <f t="shared" si="7"/>
         <v>66</v>
       </c>
-      <c r="R71" s="1">
-        <v>0</v>
-      </c>
-      <c r="S71" s="1">
-        <v>0</v>
-      </c>
-      <c r="T71" s="8">
-        <v>0</v>
-      </c>
-      <c r="U71" s="8">
-        <v>0</v>
-      </c>
-      <c r="V71" s="1">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2">
+        <v>0</v>
+      </c>
+      <c r="U71" s="2">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
         <f t="shared" si="21"/>
         <v>660</v>
       </c>
-      <c r="W71" s="1">
+      <c r="W71" s="3">
         <f t="shared" si="22"/>
         <v>660</v>
       </c>
-      <c r="X71" s="1">
+      <c r="X71" s="3">
         <v>66</v>
       </c>
-      <c r="Y71" s="1">
+      <c r="Y71" s="3">
         <v>40</v>
       </c>
-      <c r="Z71" s="4">
+      <c r="Z71" s="2">
         <f t="shared" si="15"/>
         <v>160000</v>
       </c>
-      <c r="AA71" s="1">
+      <c r="AA71" s="3">
         <v>173</v>
       </c>
-      <c r="AB71" s="4">
+      <c r="AB71" s="2">
         <v>39</v>
       </c>
-      <c r="AC71" s="4">
+      <c r="AC71" s="2">
         <f t="shared" si="8"/>
         <v>9318</v>
       </c>
-      <c r="AD71" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE71" s="1"/>
-      <c r="AF71" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG71" s="4">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3"/>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="2">
         <v>317</v>
       </c>
     </row>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -334,25 +334,49 @@
     <t>黑锋骑士</t>
   </si>
   <si>
+    <t>114E+9</t>
+  </si>
+  <si>
     <t>异界巫师</t>
   </si>
   <si>
+    <t>142E+9</t>
+  </si>
+  <si>
     <t>长角恶魔</t>
   </si>
   <si>
+    <t>178E+9</t>
+  </si>
+  <si>
     <t>地狱三头犬</t>
   </si>
   <si>
+    <t>222E+9</t>
+  </si>
+  <si>
     <t>恶魔女巫</t>
   </si>
   <si>
+    <t>277E+9</t>
+  </si>
+  <si>
     <t>魇兽</t>
   </si>
   <si>
+    <t>346E+9</t>
+  </si>
+  <si>
     <t>大恶魔</t>
   </si>
   <si>
+    <t>432E+9</t>
+  </si>
+  <si>
     <t>深渊领主</t>
+  </si>
+  <si>
+    <t>540E+9</t>
   </si>
 </sst>
 </file>
@@ -531,7 +555,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -547,12 +571,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -873,7 +891,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -897,16 +915,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -915,89 +933,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1020,8 +1038,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1737,7 +1756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="14" spans="1:33">
+    <row r="6" spans="1:33">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -5459,7 +5478,7 @@
         <v>5200000</v>
       </c>
       <c r="J42" s="1">
-        <v>244000000</v>
+        <v>230000000</v>
       </c>
       <c r="K42" s="1">
         <f t="shared" si="0"/>
@@ -5562,7 +5581,7 @@
         <v>6200000</v>
       </c>
       <c r="J43" s="1">
-        <v>319000000</v>
+        <v>288000000</v>
       </c>
       <c r="K43" s="1">
         <f t="shared" si="0"/>
@@ -5659,13 +5678,13 @@
         <v>39</v>
       </c>
       <c r="H44" s="1">
-        <v>3840000</v>
+        <v>3800000</v>
       </c>
       <c r="I44" s="1">
-        <v>7300000</v>
+        <v>7400000</v>
       </c>
       <c r="J44" s="1">
-        <v>405000000</v>
+        <v>370000000</v>
       </c>
       <c r="K44" s="1">
         <f t="shared" si="0"/>
@@ -5762,13 +5781,13 @@
         <v>40</v>
       </c>
       <c r="H45" s="1">
-        <v>4380000</v>
+        <v>4300000</v>
       </c>
       <c r="I45" s="1">
-        <v>8700000</v>
+        <v>8880000</v>
       </c>
       <c r="J45" s="1">
-        <v>521000000</v>
+        <v>460000000</v>
       </c>
       <c r="K45" s="1">
         <f t="shared" si="0"/>
@@ -5865,13 +5884,13 @@
         <v>41</v>
       </c>
       <c r="H46" s="1">
-        <v>5000000</v>
+        <v>4900000</v>
       </c>
       <c r="I46" s="1">
         <v>10200000</v>
       </c>
       <c r="J46" s="1">
-        <v>640000000</v>
+        <v>580000000</v>
       </c>
       <c r="K46" s="1">
         <f t="shared" si="0"/>
@@ -5966,39 +5985,39 @@
       <c r="G47" s="4">
         <v>42</v>
       </c>
-      <c r="H47" s="12">
-        <v>5700000</v>
-      </c>
-      <c r="I47" s="12">
+      <c r="H47" s="4">
+        <v>5600000</v>
+      </c>
+      <c r="I47" s="4">
         <v>12000000</v>
       </c>
-      <c r="J47" s="12">
-        <v>766000000</v>
-      </c>
-      <c r="K47" s="12">
+      <c r="J47" s="4">
+        <v>720000000</v>
+      </c>
+      <c r="K47" s="4">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-      <c r="L47" s="12">
+      <c r="L47" s="4">
         <f t="shared" si="1"/>
         <v>126</v>
       </c>
-      <c r="M47" s="12">
+      <c r="M47" s="4">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="N47" s="12">
+      <c r="N47" s="4">
         <f t="shared" si="3"/>
         <v>168</v>
       </c>
-      <c r="O47" s="12">
+      <c r="O47" s="4">
         <v>38</v>
       </c>
-      <c r="P47" s="13">
+      <c r="P47" s="2">
         <f t="shared" si="6"/>
         <v>41</v>
       </c>
-      <c r="Q47" s="13">
+      <c r="Q47" s="2">
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
@@ -6025,7 +6044,7 @@
       <c r="X47" s="4">
         <v>42</v>
       </c>
-      <c r="Y47" s="12">
+      <c r="Y47" s="4">
         <v>42</v>
       </c>
       <c r="Z47" s="2">
@@ -6035,7 +6054,7 @@
       <c r="AA47" s="4">
         <v>151</v>
       </c>
-      <c r="AB47" s="13">
+      <c r="AB47" s="2">
         <v>41</v>
       </c>
       <c r="AC47" s="2">
@@ -6070,16 +6089,13 @@
         <v>43</v>
       </c>
       <c r="H48" s="1">
-        <f t="shared" ref="H42:H70" si="13">AG50*Z48*AA48/10</f>
-        <v>139180500</v>
+        <v>6400000</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" ref="I42:I69" si="14">AB48*AG46*Z48/10</f>
-        <v>33831000</v>
+        <v>14400000</v>
       </c>
       <c r="J48" s="1">
-        <f t="shared" ref="J42:J72" si="15">Y48*Z48*AC48</f>
-        <v>6886665000</v>
+        <v>900000000</v>
       </c>
       <c r="K48" s="1">
         <f t="shared" si="0"/>
@@ -6176,16 +6192,13 @@
         <v>44</v>
       </c>
       <c r="H49" s="1">
-        <f t="shared" si="13"/>
-        <v>172135000</v>
+        <v>7300000</v>
       </c>
       <c r="I49" s="1">
-        <f t="shared" si="14"/>
-        <v>38915000</v>
+        <v>17000000</v>
       </c>
       <c r="J49" s="1">
-        <f t="shared" si="15"/>
-        <v>8250000000</v>
+        <v>1120000000</v>
       </c>
       <c r="K49" s="1">
         <f t="shared" si="0"/>
@@ -6282,16 +6295,13 @@
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <f t="shared" si="13"/>
-        <v>210050500</v>
+        <v>8300000</v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" si="14"/>
-        <v>46222000</v>
+        <v>20000000</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" si="15"/>
-        <v>9758925000</v>
+        <v>1400000000</v>
       </c>
       <c r="K50" s="1">
         <f t="shared" si="0"/>
@@ -6388,16 +6398,13 @@
         <v>46</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="13"/>
-        <v>255558000</v>
+        <v>9400000</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="14"/>
-        <v>52110000</v>
+        <v>24000000</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" si="15"/>
-        <v>11426400000</v>
+        <v>1750000000</v>
       </c>
       <c r="K51" s="1">
         <f t="shared" si="0"/>
@@ -6494,16 +6501,13 @@
         <v>47</v>
       </c>
       <c r="H52" s="1">
-        <f t="shared" si="13"/>
-        <v>284771500</v>
+        <v>10000000</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="14"/>
-        <v>58903000</v>
+        <v>28800000</v>
       </c>
       <c r="J52" s="1">
-        <f t="shared" si="15"/>
-        <v>13255645000</v>
+        <v>2180000000</v>
       </c>
       <c r="K52" s="1">
         <f t="shared" si="0"/>
@@ -6600,41 +6604,38 @@
         <v>48</v>
       </c>
       <c r="H53" s="4">
-        <f t="shared" si="13"/>
-        <v>315791000</v>
+        <v>11400000</v>
       </c>
       <c r="I53" s="4">
-        <f t="shared" si="14"/>
-        <v>65471000</v>
+        <v>34500000</v>
       </c>
       <c r="J53" s="4">
-        <f t="shared" si="15"/>
-        <v>15288000000</v>
-      </c>
-      <c r="K53" s="12">
+        <v>2720000000</v>
+      </c>
+      <c r="K53" s="4">
         <f t="shared" si="0"/>
         <v>240</v>
       </c>
-      <c r="L53" s="12">
+      <c r="L53" s="4">
         <f t="shared" si="1"/>
         <v>144</v>
       </c>
-      <c r="M53" s="12">
+      <c r="M53" s="4">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
-      <c r="N53" s="12">
+      <c r="N53" s="4">
         <f t="shared" si="3"/>
         <v>192</v>
       </c>
-      <c r="O53" s="12">
+      <c r="O53" s="4">
         <v>38</v>
       </c>
-      <c r="P53" s="13">
+      <c r="P53" s="2">
         <f t="shared" si="6"/>
         <v>47</v>
       </c>
-      <c r="Q53" s="13">
+      <c r="Q53" s="2">
         <f t="shared" si="7"/>
         <v>48</v>
       </c>
@@ -6661,17 +6662,17 @@
       <c r="X53" s="4">
         <v>48</v>
       </c>
-      <c r="Y53" s="12">
+      <c r="Y53" s="4">
         <v>48</v>
       </c>
       <c r="Z53" s="2">
         <f t="shared" si="12"/>
         <v>70000</v>
       </c>
-      <c r="AA53" s="13">
+      <c r="AA53" s="2">
         <v>197</v>
       </c>
-      <c r="AB53" s="13">
+      <c r="AB53" s="2">
         <v>47</v>
       </c>
       <c r="AC53" s="2">
@@ -6705,17 +6706,14 @@
       <c r="G54" s="1">
         <v>49</v>
       </c>
-      <c r="H54" s="1">
-        <f t="shared" si="13"/>
-        <v>347752500</v>
-      </c>
-      <c r="I54" s="1">
-        <f t="shared" si="14"/>
-        <v>75960000</v>
-      </c>
-      <c r="J54" s="1">
-        <f t="shared" si="15"/>
-        <v>17540775000</v>
+      <c r="H54" s="12">
+        <v>13000000</v>
+      </c>
+      <c r="I54" s="12">
+        <v>41400000</v>
+      </c>
+      <c r="J54" s="12">
+        <v>3400000000</v>
       </c>
       <c r="K54" s="1">
         <f t="shared" si="0"/>
@@ -6811,17 +6809,14 @@
       <c r="G55" s="1">
         <v>50</v>
       </c>
-      <c r="H55" s="1">
-        <f t="shared" si="13"/>
-        <v>403432000</v>
-      </c>
-      <c r="I55" s="1">
-        <f t="shared" si="14"/>
-        <v>87416000</v>
-      </c>
-      <c r="J55" s="1">
-        <f t="shared" si="15"/>
-        <v>20000000000</v>
+      <c r="H55" s="12">
+        <v>14800000</v>
+      </c>
+      <c r="I55" s="12">
+        <v>50000000</v>
+      </c>
+      <c r="J55" s="12">
+        <v>4250000000</v>
       </c>
       <c r="K55" s="1">
         <f t="shared" si="0"/>
@@ -6917,17 +6912,14 @@
       <c r="G56" s="1">
         <v>51</v>
       </c>
-      <c r="H56" s="1">
-        <f t="shared" si="13"/>
-        <v>456815500</v>
-      </c>
-      <c r="I56" s="1">
-        <f t="shared" si="14"/>
-        <v>96475000</v>
-      </c>
-      <c r="J56" s="1">
-        <f t="shared" si="15"/>
-        <v>22667715000</v>
+      <c r="H56" s="12">
+        <v>16800000</v>
+      </c>
+      <c r="I56" s="12">
+        <v>60000000</v>
+      </c>
+      <c r="J56" s="12">
+        <v>5310000000</v>
       </c>
       <c r="K56" s="1">
         <f t="shared" si="0"/>
@@ -7023,17 +7015,14 @@
       <c r="G57" s="1">
         <v>52</v>
       </c>
-      <c r="H57" s="1">
-        <f t="shared" si="13"/>
-        <v>512793000</v>
-      </c>
-      <c r="I57" s="1">
-        <f t="shared" si="14"/>
-        <v>105111000</v>
-      </c>
-      <c r="J57" s="1">
-        <f t="shared" si="15"/>
-        <v>25562160000</v>
+      <c r="H57" s="12">
+        <v>19100000</v>
+      </c>
+      <c r="I57" s="12">
+        <v>72000000</v>
+      </c>
+      <c r="J57" s="12">
+        <v>6630000000</v>
       </c>
       <c r="K57" s="1">
         <f t="shared" si="0"/>
@@ -7129,17 +7118,14 @@
       <c r="G58" s="1">
         <v>53</v>
       </c>
-      <c r="H58" s="1">
-        <f t="shared" si="13"/>
-        <v>559103500</v>
-      </c>
-      <c r="I58" s="1">
-        <f t="shared" si="14"/>
-        <v>115102000</v>
-      </c>
-      <c r="J58" s="1">
-        <f t="shared" si="15"/>
-        <v>28704535000</v>
+      <c r="H58" s="12">
+        <v>21700000</v>
+      </c>
+      <c r="I58" s="12">
+        <v>86400000</v>
+      </c>
+      <c r="J58" s="12">
+        <v>8280000000</v>
       </c>
       <c r="K58" s="1">
         <f t="shared" si="0"/>
@@ -7236,16 +7222,13 @@
         <v>54</v>
       </c>
       <c r="H59" s="4">
-        <f t="shared" si="13"/>
-        <v>612790000</v>
+        <v>24700000</v>
       </c>
       <c r="I59" s="4">
-        <f t="shared" si="14"/>
-        <v>126670000</v>
+        <v>100000000</v>
       </c>
       <c r="J59" s="4">
-        <f t="shared" si="15"/>
-        <v>32086800000</v>
+        <v>10000000000</v>
       </c>
       <c r="K59" s="1">
         <f t="shared" si="0"/>
@@ -7341,17 +7324,14 @@
       <c r="G60" s="1">
         <v>55</v>
       </c>
-      <c r="H60" s="1">
-        <f t="shared" si="13"/>
-        <v>675055500</v>
-      </c>
-      <c r="I60" s="1">
-        <f t="shared" si="14"/>
-        <v>136647000</v>
-      </c>
-      <c r="J60" s="1">
-        <f t="shared" si="15"/>
-        <v>35764575000</v>
+      <c r="H60" s="12">
+        <v>28100000</v>
+      </c>
+      <c r="I60" s="12">
+        <v>120000000</v>
+      </c>
+      <c r="J60" s="12">
+        <v>12500000000</v>
       </c>
       <c r="K60" s="1">
         <f t="shared" si="0"/>
@@ -7447,17 +7427,14 @@
       <c r="G61" s="1">
         <v>56</v>
       </c>
-      <c r="H61" s="1">
-        <f t="shared" si="13"/>
-        <v>718421000</v>
-      </c>
-      <c r="I61" s="1">
-        <f t="shared" si="14"/>
-        <v>151855000</v>
-      </c>
-      <c r="J61" s="1">
-        <f t="shared" si="15"/>
-        <v>39732000000</v>
+      <c r="H61" s="12">
+        <v>32000000</v>
+      </c>
+      <c r="I61" s="12">
+        <v>144000000</v>
+      </c>
+      <c r="J61" s="12">
+        <v>15600000000</v>
       </c>
       <c r="K61" s="1">
         <f t="shared" si="0"/>
@@ -7553,17 +7530,14 @@
       <c r="G62" s="1">
         <v>57</v>
       </c>
-      <c r="H62" s="1">
-        <f t="shared" si="13"/>
-        <v>799560500</v>
-      </c>
-      <c r="I62" s="1">
-        <f t="shared" si="14"/>
-        <v>165508000</v>
-      </c>
-      <c r="J62" s="1">
-        <f t="shared" si="15"/>
-        <v>44003715000</v>
+      <c r="H62" s="12">
+        <v>36400000</v>
+      </c>
+      <c r="I62" s="12">
+        <v>172000000</v>
+      </c>
+      <c r="J62" s="12">
+        <v>19500000000</v>
       </c>
       <c r="K62" s="1">
         <f t="shared" si="0"/>
@@ -7659,17 +7633,14 @@
       <c r="G63" s="1">
         <v>58</v>
       </c>
-      <c r="H63" s="1">
-        <f t="shared" si="13"/>
-        <v>866604000</v>
-      </c>
-      <c r="I63" s="1">
-        <f t="shared" si="14"/>
-        <v>179892000</v>
-      </c>
-      <c r="J63" s="1">
-        <f t="shared" si="15"/>
-        <v>48594720000</v>
+      <c r="H63" s="12">
+        <v>41500000</v>
+      </c>
+      <c r="I63" s="12">
+        <v>200000000</v>
+      </c>
+      <c r="J63" s="12">
+        <v>24300000000</v>
       </c>
       <c r="K63" s="1">
         <f t="shared" si="0"/>
@@ -7765,17 +7736,14 @@
       <c r="G64" s="1">
         <v>59</v>
       </c>
-      <c r="H64" s="1">
-        <f t="shared" si="13"/>
-        <v>930362500</v>
-      </c>
-      <c r="I64" s="1">
-        <f t="shared" si="14"/>
-        <v>195025000</v>
-      </c>
-      <c r="J64" s="1">
-        <f t="shared" si="15"/>
-        <v>53490875000</v>
+      <c r="H64" s="12">
+        <v>47300000</v>
+      </c>
+      <c r="I64" s="12">
+        <v>240000000</v>
+      </c>
+      <c r="J64" s="12">
+        <v>30000000000</v>
       </c>
       <c r="K64" s="1">
         <f t="shared" si="0"/>
@@ -7872,16 +7840,13 @@
         <v>60</v>
       </c>
       <c r="H65" s="4">
-        <f t="shared" si="13"/>
-        <v>1024621000</v>
+        <v>53900000</v>
       </c>
       <c r="I65" s="4">
-        <f t="shared" si="14"/>
-        <v>207857000</v>
+        <v>288000000</v>
       </c>
       <c r="J65" s="4">
-        <f t="shared" si="15"/>
-        <v>58734000000</v>
+        <v>37500000000</v>
       </c>
       <c r="K65" s="1">
         <f t="shared" si="0"/>
@@ -7977,17 +7942,14 @@
       <c r="G66" s="1">
         <v>61</v>
       </c>
-      <c r="H66" s="1">
-        <f t="shared" si="13"/>
-        <v>1123159500</v>
-      </c>
-      <c r="I66" s="1">
-        <f t="shared" si="14"/>
-        <v>224370000</v>
-      </c>
-      <c r="J66" s="1">
-        <f t="shared" si="15"/>
-        <v>64323585000</v>
+      <c r="H66" s="12">
+        <v>61400000</v>
+      </c>
+      <c r="I66" s="12">
+        <v>345000000</v>
+      </c>
+      <c r="J66" s="12">
+        <v>46800000000</v>
       </c>
       <c r="K66" s="1">
         <f t="shared" si="0"/>
@@ -8083,17 +8045,14 @@
       <c r="G67" s="1">
         <v>62</v>
       </c>
-      <c r="H67" s="1">
-        <f t="shared" si="13"/>
-        <v>1206058000</v>
-      </c>
-      <c r="I67" s="1">
-        <f t="shared" si="14"/>
-        <v>239974000</v>
-      </c>
-      <c r="J67" s="1">
-        <f t="shared" si="15"/>
-        <v>70255920000</v>
+      <c r="H67" s="12">
+        <v>70000000</v>
+      </c>
+      <c r="I67" s="12">
+        <v>414000000</v>
+      </c>
+      <c r="J67" s="12">
+        <v>58500000000</v>
       </c>
       <c r="K67" s="1">
         <f t="shared" si="0"/>
@@ -8189,17 +8148,14 @@
       <c r="G68" s="1">
         <v>63</v>
       </c>
-      <c r="H68" s="1">
-        <f t="shared" si="13"/>
-        <v>1275318500</v>
-      </c>
-      <c r="I68" s="1">
-        <f t="shared" si="14"/>
-        <v>254417000</v>
-      </c>
-      <c r="J68" s="1">
-        <f t="shared" si="15"/>
-        <v>76615245000</v>
+      <c r="H68" s="12">
+        <v>79800000</v>
+      </c>
+      <c r="I68" s="12">
+        <v>496000000</v>
+      </c>
+      <c r="J68" s="12">
+        <v>73100000000</v>
       </c>
       <c r="K68" s="1">
         <f t="shared" si="0"/>
@@ -8295,17 +8251,14 @@
       <c r="G69" s="1">
         <v>64</v>
       </c>
-      <c r="H69" s="1">
-        <f t="shared" si="13"/>
-        <v>1345665000</v>
-      </c>
-      <c r="I69" s="1">
-        <f t="shared" si="14"/>
-        <v>276885000</v>
-      </c>
-      <c r="J69" s="1">
-        <f t="shared" si="15"/>
-        <v>83462400000</v>
+      <c r="H69" s="12">
+        <v>90000000</v>
+      </c>
+      <c r="I69" s="12">
+        <v>595000000</v>
+      </c>
+      <c r="J69" s="12">
+        <v>91300000000</v>
       </c>
       <c r="K69" s="1">
         <f t="shared" si="0"/>
@@ -8401,32 +8354,29 @@
       <c r="G70" s="1">
         <v>65</v>
       </c>
-      <c r="H70" s="1">
-        <f t="shared" si="13"/>
-        <v>1503236500</v>
-      </c>
-      <c r="I70" s="1">
-        <f t="shared" ref="I70:I77" si="16">AB70*AG68*Z70/10</f>
-        <v>304544000</v>
-      </c>
-      <c r="J70" s="1">
-        <f t="shared" si="15"/>
-        <v>90725375000</v>
+      <c r="H70" s="12">
+        <v>100000000</v>
+      </c>
+      <c r="I70" s="12">
+        <v>714000000</v>
+      </c>
+      <c r="J70" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="K70" s="1">
-        <f t="shared" ref="K70:K77" si="17">Y70*5</f>
+        <f t="shared" ref="K70:K77" si="13">Y70*5</f>
         <v>325</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L77" si="18">Y70*3</f>
+        <f t="shared" ref="L70:L77" si="14">Y70*3</f>
         <v>195</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" ref="M70:M77" si="19">Y70*2</f>
+        <f t="shared" ref="M70:M77" si="15">Y70*2</f>
         <v>130</v>
       </c>
       <c r="N70" s="1">
-        <f t="shared" ref="N70:N77" si="20">Y70*4</f>
+        <f t="shared" ref="N70:N77" si="16">Y70*4</f>
         <v>260</v>
       </c>
       <c r="O70" s="1">
@@ -8453,11 +8403,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V77" si="21">X70*10</f>
+        <f t="shared" ref="V70:V77" si="17">X70*10</f>
         <v>650</v>
       </c>
       <c r="W70" s="1">
-        <f t="shared" ref="W70:W77" si="22">X70*10</f>
+        <f t="shared" ref="W70:W77" si="18">X70*10</f>
         <v>650</v>
       </c>
       <c r="X70" s="1">
@@ -8502,37 +8452,34 @@
         <v>1</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G71" s="4">
         <v>66</v>
       </c>
       <c r="H71" s="4">
-        <f t="shared" ref="H71:H77" si="23">AG73*Z71*AA71/10</f>
-        <v>1655344000</v>
+        <v>114000000</v>
       </c>
       <c r="I71" s="4">
+        <v>856000000</v>
+      </c>
+      <c r="J71" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K71" s="1">
+        <f t="shared" si="13"/>
+        <v>330</v>
+      </c>
+      <c r="L71" s="1">
+        <f t="shared" si="14"/>
+        <v>198</v>
+      </c>
+      <c r="M71" s="1">
+        <f t="shared" si="15"/>
+        <v>132</v>
+      </c>
+      <c r="N71" s="1">
         <f t="shared" si="16"/>
-        <v>323440000</v>
-      </c>
-      <c r="J71" s="4">
-        <f t="shared" si="15"/>
-        <v>98398080000</v>
-      </c>
-      <c r="K71" s="1">
-        <f t="shared" si="17"/>
-        <v>330</v>
-      </c>
-      <c r="L71" s="1">
-        <f t="shared" si="18"/>
-        <v>198</v>
-      </c>
-      <c r="M71" s="1">
-        <f t="shared" si="19"/>
-        <v>132</v>
-      </c>
-      <c r="N71" s="1">
-        <f t="shared" si="20"/>
         <v>264</v>
       </c>
       <c r="O71" s="1">
@@ -8559,11 +8506,11 @@
         <v>0</v>
       </c>
       <c r="V71" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>660</v>
       </c>
       <c r="W71" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>660</v>
       </c>
       <c r="X71" s="4">
@@ -8608,44 +8555,41 @@
         <v>1</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G72" s="1">
         <v>67</v>
       </c>
-      <c r="H72" s="1">
-        <f t="shared" si="23"/>
-        <v>1780630500</v>
-      </c>
-      <c r="I72" s="1">
+      <c r="H72" s="12">
+        <v>130000000</v>
+      </c>
+      <c r="I72" s="12">
+        <v>1000000000</v>
+      </c>
+      <c r="J72" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="K72" s="1">
+        <f t="shared" si="13"/>
+        <v>335</v>
+      </c>
+      <c r="L72" s="1">
+        <f t="shared" si="14"/>
+        <v>201</v>
+      </c>
+      <c r="M72" s="1">
+        <f t="shared" si="15"/>
+        <v>134</v>
+      </c>
+      <c r="N72" s="1">
         <f t="shared" si="16"/>
-        <v>340857000</v>
-      </c>
-      <c r="J72" s="1">
-        <f t="shared" si="15"/>
-        <v>106514925000</v>
-      </c>
-      <c r="K72" s="1">
-        <f t="shared" si="17"/>
-        <v>335</v>
-      </c>
-      <c r="L72" s="1">
-        <f t="shared" si="18"/>
-        <v>201</v>
-      </c>
-      <c r="M72" s="1">
-        <f t="shared" si="19"/>
-        <v>134</v>
-      </c>
-      <c r="N72" s="1">
-        <f t="shared" si="20"/>
         <v>268</v>
       </c>
       <c r="O72" s="1">
         <v>38</v>
       </c>
       <c r="P72" s="5">
-        <f t="shared" ref="P72:P77" si="24">P71+1</f>
+        <f t="shared" ref="P72:P77" si="19">P71+1</f>
         <v>66</v>
       </c>
       <c r="Q72" s="5">
@@ -8665,11 +8609,11 @@
         <v>0</v>
       </c>
       <c r="V72" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>670</v>
       </c>
       <c r="W72" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>670</v>
       </c>
       <c r="X72" s="1">
@@ -8714,48 +8658,45 @@
         <v>1</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G73" s="1">
         <v>68</v>
       </c>
-      <c r="H73" s="1">
-        <f t="shared" si="23"/>
-        <v>1857029000</v>
-      </c>
-      <c r="I73" s="1">
+      <c r="H73" s="12">
+        <v>148000000</v>
+      </c>
+      <c r="I73" s="12">
+        <v>1200000000</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="K73" s="1">
+        <f t="shared" si="13"/>
+        <v>340</v>
+      </c>
+      <c r="L73" s="1">
+        <f t="shared" si="14"/>
+        <v>204</v>
+      </c>
+      <c r="M73" s="1">
+        <f t="shared" si="15"/>
+        <v>136</v>
+      </c>
+      <c r="N73" s="1">
         <f t="shared" si="16"/>
-        <v>361063000</v>
-      </c>
-      <c r="J73" s="1">
-        <f t="shared" ref="J73:J77" si="25">Y73*Z73*AC73</f>
-        <v>115206960000</v>
-      </c>
-      <c r="K73" s="1">
-        <f t="shared" si="17"/>
-        <v>340</v>
-      </c>
-      <c r="L73" s="1">
-        <f t="shared" si="18"/>
-        <v>204</v>
-      </c>
-      <c r="M73" s="1">
-        <f t="shared" si="19"/>
-        <v>136</v>
-      </c>
-      <c r="N73" s="1">
-        <f t="shared" si="20"/>
         <v>272</v>
       </c>
       <c r="O73" s="1">
         <v>38</v>
       </c>
       <c r="P73" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>67</v>
       </c>
       <c r="Q73" s="5">
-        <f t="shared" ref="Q73:Q77" si="26">Q72+1</f>
+        <f t="shared" ref="Q73:Q77" si="20">Q72+1</f>
         <v>68</v>
       </c>
       <c r="R73" s="1">
@@ -8771,11 +8712,11 @@
         <v>0</v>
       </c>
       <c r="V73" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>680</v>
       </c>
       <c r="W73" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>680</v>
       </c>
       <c r="X73" s="1">
@@ -8820,48 +8761,45 @@
         <v>1</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G74" s="1">
         <v>69</v>
       </c>
-      <c r="H74" s="1">
-        <f t="shared" si="23"/>
-        <v>1958267500</v>
-      </c>
-      <c r="I74" s="1">
+      <c r="H74" s="12">
+        <v>168000000</v>
+      </c>
+      <c r="I74" s="12">
+        <v>1440000000</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="K74" s="1">
+        <f t="shared" si="13"/>
+        <v>345</v>
+      </c>
+      <c r="L74" s="1">
+        <f t="shared" si="14"/>
+        <v>207</v>
+      </c>
+      <c r="M74" s="1">
+        <f t="shared" si="15"/>
+        <v>138</v>
+      </c>
+      <c r="N74" s="1">
         <f t="shared" si="16"/>
-        <v>393890000</v>
-      </c>
-      <c r="J74" s="1">
-        <f t="shared" si="25"/>
-        <v>124408725000</v>
-      </c>
-      <c r="K74" s="1">
-        <f t="shared" si="17"/>
-        <v>345</v>
-      </c>
-      <c r="L74" s="1">
-        <f t="shared" si="18"/>
-        <v>207</v>
-      </c>
-      <c r="M74" s="1">
-        <f t="shared" si="19"/>
-        <v>138</v>
-      </c>
-      <c r="N74" s="1">
-        <f t="shared" si="20"/>
         <v>276</v>
       </c>
       <c r="O74" s="1">
         <v>38</v>
       </c>
       <c r="P74" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>68</v>
       </c>
       <c r="Q74" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>69</v>
       </c>
       <c r="R74" s="1">
@@ -8877,11 +8815,11 @@
         <v>0</v>
       </c>
       <c r="V74" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>690</v>
       </c>
       <c r="W74" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>690</v>
       </c>
       <c r="X74" s="1">
@@ -8926,48 +8864,45 @@
         <v>1</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G75" s="1">
         <v>70</v>
       </c>
-      <c r="H75" s="1">
-        <f t="shared" si="23"/>
-        <v>2138922000</v>
-      </c>
-      <c r="I75" s="1">
+      <c r="H75" s="12">
+        <v>192000000</v>
+      </c>
+      <c r="I75" s="12">
+        <v>1720000000</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="K75" s="1">
+        <f t="shared" si="13"/>
+        <v>350</v>
+      </c>
+      <c r="L75" s="1">
+        <f t="shared" si="14"/>
+        <v>210</v>
+      </c>
+      <c r="M75" s="1">
+        <f t="shared" si="15"/>
+        <v>140</v>
+      </c>
+      <c r="N75" s="1">
         <f t="shared" si="16"/>
-        <v>418554000</v>
-      </c>
-      <c r="J75" s="1">
-        <f t="shared" si="25"/>
-        <v>134190000000</v>
-      </c>
-      <c r="K75" s="1">
-        <f t="shared" si="17"/>
-        <v>350</v>
-      </c>
-      <c r="L75" s="1">
-        <f t="shared" si="18"/>
-        <v>210</v>
-      </c>
-      <c r="M75" s="1">
-        <f t="shared" si="19"/>
-        <v>140</v>
-      </c>
-      <c r="N75" s="1">
-        <f t="shared" si="20"/>
         <v>280</v>
       </c>
       <c r="O75" s="1">
         <v>38</v>
       </c>
       <c r="P75" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>69</v>
       </c>
       <c r="Q75" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>70</v>
       </c>
       <c r="R75" s="1">
@@ -8983,11 +8918,11 @@
         <v>0</v>
       </c>
       <c r="V75" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>700</v>
       </c>
       <c r="W75" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>700</v>
       </c>
       <c r="X75" s="1">
@@ -9032,48 +8967,45 @@
         <v>1</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G76" s="1">
         <v>71</v>
       </c>
-      <c r="H76" s="1">
-        <f t="shared" si="23"/>
-        <v>2288061500</v>
-      </c>
-      <c r="I76" s="1">
+      <c r="H76" s="12">
+        <v>218000000</v>
+      </c>
+      <c r="I76" s="12">
+        <v>2060000000</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="K76" s="1">
+        <f t="shared" si="13"/>
+        <v>355</v>
+      </c>
+      <c r="L76" s="1">
+        <f t="shared" si="14"/>
+        <v>213</v>
+      </c>
+      <c r="M76" s="1">
+        <f t="shared" si="15"/>
+        <v>142</v>
+      </c>
+      <c r="N76" s="1">
         <f t="shared" si="16"/>
-        <v>449365000</v>
-      </c>
-      <c r="J76" s="1">
-        <f t="shared" si="25"/>
-        <v>144471865000</v>
-      </c>
-      <c r="K76" s="1">
-        <f t="shared" si="17"/>
-        <v>355</v>
-      </c>
-      <c r="L76" s="1">
-        <f t="shared" si="18"/>
-        <v>213</v>
-      </c>
-      <c r="M76" s="1">
-        <f t="shared" si="19"/>
-        <v>142</v>
-      </c>
-      <c r="N76" s="1">
-        <f t="shared" si="20"/>
         <v>284</v>
       </c>
       <c r="O76" s="1">
         <v>38</v>
       </c>
       <c r="P76" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>70</v>
       </c>
       <c r="Q76" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>71</v>
       </c>
       <c r="R76" s="1">
@@ -9089,11 +9021,11 @@
         <v>0</v>
       </c>
       <c r="V76" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>710</v>
       </c>
       <c r="W76" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>710</v>
       </c>
       <c r="X76" s="1">
@@ -9138,48 +9070,45 @@
         <v>1</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G77" s="1">
         <v>72</v>
       </c>
-      <c r="H77" s="1">
-        <f t="shared" si="23"/>
-        <v>2459189000</v>
-      </c>
-      <c r="I77" s="1">
+      <c r="H77" s="4">
+        <v>249000000</v>
+      </c>
+      <c r="I77" s="4">
+        <v>2470000000</v>
+      </c>
+      <c r="J77" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="K77" s="1">
+        <f t="shared" si="13"/>
+        <v>360</v>
+      </c>
+      <c r="L77" s="1">
+        <f t="shared" si="14"/>
+        <v>216</v>
+      </c>
+      <c r="M77" s="1">
+        <f t="shared" si="15"/>
+        <v>144</v>
+      </c>
+      <c r="N77" s="1">
         <f t="shared" si="16"/>
-        <v>470801000</v>
-      </c>
-      <c r="J77" s="1">
-        <f t="shared" si="25"/>
-        <v>155295360000</v>
-      </c>
-      <c r="K77" s="1">
-        <f t="shared" si="17"/>
-        <v>360</v>
-      </c>
-      <c r="L77" s="1">
-        <f t="shared" si="18"/>
-        <v>216</v>
-      </c>
-      <c r="M77" s="1">
-        <f t="shared" si="19"/>
-        <v>144</v>
-      </c>
-      <c r="N77" s="1">
-        <f t="shared" si="20"/>
         <v>288</v>
       </c>
       <c r="O77" s="1">
         <v>38</v>
       </c>
       <c r="P77" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>71</v>
       </c>
       <c r="Q77" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>72</v>
       </c>
       <c r="R77" s="1">
@@ -9195,11 +9124,11 @@
         <v>0</v>
       </c>
       <c r="V77" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="17"/>
         <v>720</v>
       </c>
       <c r="W77" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>720</v>
       </c>
       <c r="X77" s="1">
@@ -9365,7 +9294,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:U5 AD3:AF5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5 K3:U5 AD3:AF5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -332,9 +332,6 @@
   </si>
   <si>
     <t>黑锋骑士</t>
-  </si>
-  <si>
-    <t>114E+9</t>
   </si>
   <si>
     <t>异界巫师</t>
@@ -1015,7 +1012,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1038,9 +1035,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1973,13 +1969,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="1">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="I8" s="1">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="J8" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="0"/>
@@ -2075,13 +2071,13 @@
         <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="I9" s="1">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="J9" s="1">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="0"/>
@@ -2177,13 +2173,13 @@
         <v>5</v>
       </c>
       <c r="H10" s="1">
-        <v>1350</v>
+        <v>1080</v>
       </c>
       <c r="I10" s="1">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="J10" s="1">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="0"/>
@@ -2279,13 +2275,13 @@
         <v>6</v>
       </c>
       <c r="H11" s="4">
-        <v>2100</v>
+        <v>1680</v>
       </c>
       <c r="I11" s="4">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="J11" s="4">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="K11" s="4">
         <f t="shared" si="0"/>
@@ -2381,13 +2377,13 @@
         <v>7</v>
       </c>
       <c r="H12" s="3">
-        <v>3100</v>
+        <v>2480</v>
       </c>
       <c r="I12" s="3">
-        <v>490</v>
+        <v>392</v>
       </c>
       <c r="J12" s="3">
-        <v>56000</v>
+        <v>44800</v>
       </c>
       <c r="K12" s="6">
         <f t="shared" si="0"/>
@@ -2484,13 +2480,13 @@
         <v>8</v>
       </c>
       <c r="H13" s="3">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="I13" s="6">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="J13" s="3">
-        <v>82000</v>
+        <v>65600</v>
       </c>
       <c r="K13" s="6">
         <f t="shared" si="0"/>
@@ -2587,13 +2583,13 @@
         <v>9</v>
       </c>
       <c r="H14" s="6">
-        <v>6700</v>
+        <v>5360</v>
       </c>
       <c r="I14" s="6">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J14" s="6">
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="K14" s="6">
         <f t="shared" si="0"/>
@@ -2690,13 +2686,13 @@
         <v>10</v>
       </c>
       <c r="H15" s="6">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="I15" s="6">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="6">
-        <v>177000</v>
+        <v>141600</v>
       </c>
       <c r="K15" s="6">
         <f t="shared" si="0"/>
@@ -2793,13 +2789,13 @@
         <v>11</v>
       </c>
       <c r="H16" s="6">
-        <v>15800</v>
+        <v>12640</v>
       </c>
       <c r="I16" s="6">
-        <v>2400</v>
+        <v>1920</v>
       </c>
       <c r="J16" s="6">
-        <v>249000</v>
+        <v>199200</v>
       </c>
       <c r="K16" s="6">
         <f t="shared" si="0"/>
@@ -2896,13 +2892,13 @@
         <v>12</v>
       </c>
       <c r="H17" s="4">
-        <v>22000</v>
+        <v>17600</v>
       </c>
       <c r="I17" s="4">
-        <v>3600</v>
+        <v>2880</v>
       </c>
       <c r="J17" s="4">
-        <v>357000</v>
+        <v>285600</v>
       </c>
       <c r="K17" s="4">
         <f t="shared" si="0"/>
@@ -2999,13 +2995,13 @@
         <v>13</v>
       </c>
       <c r="H18" s="6">
-        <v>33000</v>
+        <v>26400</v>
       </c>
       <c r="I18" s="6">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="J18" s="6">
-        <v>531000</v>
+        <v>424800</v>
       </c>
       <c r="K18" s="6">
         <f t="shared" si="0"/>
@@ -3102,13 +3098,13 @@
         <v>14</v>
       </c>
       <c r="H19" s="6">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="I19" s="6">
-        <v>9600</v>
+        <v>7680</v>
       </c>
       <c r="J19" s="6">
-        <v>733000</v>
+        <v>586400</v>
       </c>
       <c r="K19" s="6">
         <f t="shared" si="0"/>
@@ -3205,13 +3201,13 @@
         <v>15</v>
       </c>
       <c r="H20" s="6">
-        <v>69000</v>
+        <v>55200</v>
       </c>
       <c r="I20" s="6">
-        <v>14000</v>
+        <v>11200</v>
       </c>
       <c r="J20" s="6">
-        <v>917000</v>
+        <v>733600</v>
       </c>
       <c r="K20" s="6">
         <f t="shared" si="0"/>
@@ -3308,13 +3304,13 @@
         <v>16</v>
       </c>
       <c r="H21" s="6">
-        <v>83000</v>
+        <v>66400</v>
       </c>
       <c r="I21" s="6">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="J21" s="6">
-        <v>1230000</v>
+        <v>984000</v>
       </c>
       <c r="K21" s="6">
         <f t="shared" si="0"/>
@@ -3411,13 +3407,13 @@
         <v>17</v>
       </c>
       <c r="H22" s="6">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="I22" s="6">
-        <v>27000</v>
+        <v>21600</v>
       </c>
       <c r="J22" s="6">
-        <v>1510000</v>
+        <v>1208000</v>
       </c>
       <c r="K22" s="6">
         <f t="shared" si="0"/>
@@ -3514,13 +3510,13 @@
         <v>18</v>
       </c>
       <c r="H23" s="4">
-        <v>125000</v>
+        <v>100000</v>
       </c>
       <c r="I23" s="4">
-        <v>36000</v>
+        <v>28800</v>
       </c>
       <c r="J23" s="2">
-        <v>1850000</v>
+        <v>1480000</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="0"/>
@@ -3617,13 +3613,13 @@
         <v>19</v>
       </c>
       <c r="H24" s="6">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="I24" s="6">
-        <v>48000</v>
+        <v>38400</v>
       </c>
       <c r="J24" s="6">
-        <v>2570000</v>
+        <v>2056000</v>
       </c>
       <c r="K24" s="6">
         <f t="shared" si="0"/>
@@ -3720,13 +3716,13 @@
         <v>20</v>
       </c>
       <c r="H25" s="6">
-        <v>190000</v>
+        <v>152000</v>
       </c>
       <c r="I25" s="6">
-        <v>63000</v>
+        <v>50400</v>
       </c>
       <c r="J25" s="3">
-        <v>3390000</v>
+        <v>2712000</v>
       </c>
       <c r="K25" s="6">
         <f t="shared" si="0"/>
@@ -3823,13 +3819,13 @@
         <v>21</v>
       </c>
       <c r="H26" s="6">
-        <v>230000</v>
+        <v>184000</v>
       </c>
       <c r="I26" s="6">
-        <v>80000</v>
+        <v>64000</v>
       </c>
       <c r="J26" s="6">
-        <v>4490000</v>
+        <v>3592000</v>
       </c>
       <c r="K26" s="6">
         <f t="shared" si="0"/>
@@ -3926,13 +3922,13 @@
         <v>22</v>
       </c>
       <c r="H27" s="6">
-        <v>280000</v>
+        <v>224000</v>
       </c>
       <c r="I27" s="6">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="J27" s="6">
-        <v>5600000</v>
+        <v>4480000</v>
       </c>
       <c r="K27" s="6">
         <f t="shared" si="0"/>
@@ -4029,13 +4025,13 @@
         <v>23</v>
       </c>
       <c r="H28" s="6">
-        <v>340000</v>
+        <v>272000</v>
       </c>
       <c r="I28" s="6">
-        <v>130000</v>
+        <v>104000</v>
       </c>
       <c r="J28" s="6">
-        <v>7100000</v>
+        <v>5680000</v>
       </c>
       <c r="K28" s="6">
         <f t="shared" si="0"/>
@@ -4132,13 +4128,13 @@
         <v>24</v>
       </c>
       <c r="H29" s="4">
-        <v>410000</v>
+        <v>328000</v>
       </c>
       <c r="I29" s="4">
-        <v>170000</v>
+        <v>136000</v>
       </c>
       <c r="J29" s="2">
-        <v>9000000</v>
+        <v>7200000</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="0"/>
@@ -4235,13 +4231,13 @@
         <v>25</v>
       </c>
       <c r="H30" s="6">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="I30" s="6">
-        <v>270000</v>
+        <v>216000</v>
       </c>
       <c r="J30" s="6">
-        <v>11800000</v>
+        <v>9440000</v>
       </c>
       <c r="K30" s="6">
         <f t="shared" si="0"/>
@@ -4338,13 +4334,13 @@
         <v>26</v>
       </c>
       <c r="H31" s="6">
-        <v>600000</v>
+        <v>480000</v>
       </c>
       <c r="I31" s="6">
-        <v>390000</v>
+        <v>312000</v>
       </c>
       <c r="J31" s="6">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="K31" s="6">
         <f t="shared" si="0"/>
@@ -4441,13 +4437,13 @@
         <v>27</v>
       </c>
       <c r="H32" s="6">
-        <v>725000</v>
+        <v>580000</v>
       </c>
       <c r="I32" s="6">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="J32" s="6">
-        <v>21200000</v>
+        <v>16960000</v>
       </c>
       <c r="K32" s="6">
         <f t="shared" si="0"/>
@@ -4544,13 +4540,13 @@
         <v>28</v>
       </c>
       <c r="H33" s="6">
-        <v>830000</v>
+        <v>664000</v>
       </c>
       <c r="I33" s="6">
-        <v>630000</v>
+        <v>504000</v>
       </c>
       <c r="J33" s="6">
-        <v>29900000</v>
+        <v>23920000</v>
       </c>
       <c r="K33" s="6">
         <f t="shared" si="0"/>
@@ -4647,13 +4643,13 @@
         <v>29</v>
       </c>
       <c r="H34" s="6">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="I34" s="6">
-        <v>800000</v>
+        <v>640000</v>
       </c>
       <c r="J34" s="6">
-        <v>38400000</v>
+        <v>30720000</v>
       </c>
       <c r="K34" s="6">
         <f t="shared" si="0"/>
@@ -4750,13 +4746,13 @@
         <v>30</v>
       </c>
       <c r="H35" s="4">
-        <v>1140000</v>
+        <v>912000</v>
       </c>
       <c r="I35" s="4">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="J35" s="4">
-        <v>49600000</v>
+        <v>39680000</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="0"/>
@@ -4853,13 +4849,13 @@
         <v>31</v>
       </c>
       <c r="H36" s="6">
-        <v>1310000</v>
+        <v>1048000</v>
       </c>
       <c r="I36" s="6">
-        <v>1300000</v>
+        <v>1040000</v>
       </c>
       <c r="J36" s="6">
-        <v>66500000</v>
+        <v>53200000</v>
       </c>
       <c r="K36" s="6">
         <f t="shared" si="0"/>
@@ -4956,13 +4952,13 @@
         <v>32</v>
       </c>
       <c r="H37" s="6">
-        <v>1500000</v>
+        <v>1200000</v>
       </c>
       <c r="I37" s="6">
-        <v>1700000</v>
+        <v>1360000</v>
       </c>
       <c r="J37" s="3">
-        <v>85000000</v>
+        <v>68000000</v>
       </c>
       <c r="K37" s="6">
         <f t="shared" si="0"/>
@@ -5059,13 +5055,13 @@
         <v>33</v>
       </c>
       <c r="H38" s="6">
-        <v>1720000</v>
+        <v>1376000</v>
       </c>
       <c r="I38" s="6">
-        <v>2200000</v>
+        <v>1760000</v>
       </c>
       <c r="J38" s="6">
-        <v>102000000</v>
+        <v>81600000</v>
       </c>
       <c r="K38" s="6">
         <f t="shared" si="0"/>
@@ -5162,13 +5158,13 @@
         <v>34</v>
       </c>
       <c r="H39" s="6">
-        <v>1970000</v>
+        <v>1576000</v>
       </c>
       <c r="I39" s="6">
-        <v>2800000</v>
+        <v>2240000</v>
       </c>
       <c r="J39" s="3">
-        <v>120000000</v>
+        <v>96000000</v>
       </c>
       <c r="K39" s="6">
         <f t="shared" si="0"/>
@@ -5265,13 +5261,13 @@
         <v>35</v>
       </c>
       <c r="H40" s="6">
-        <v>2250000</v>
+        <v>1800000</v>
       </c>
       <c r="I40" s="6">
-        <v>3500000</v>
+        <v>2800000</v>
       </c>
       <c r="J40" s="6">
-        <v>142000000</v>
+        <v>113600000</v>
       </c>
       <c r="K40" s="6">
         <f t="shared" si="0"/>
@@ -5369,13 +5365,13 @@
         <v>36</v>
       </c>
       <c r="H41" s="4">
-        <v>2570000</v>
+        <v>2056000</v>
       </c>
       <c r="I41" s="4">
-        <v>4300000</v>
+        <v>3440000</v>
       </c>
       <c r="J41" s="4">
-        <v>181000000</v>
+        <v>144800000</v>
       </c>
       <c r="K41" s="4">
         <f t="shared" si="0"/>
@@ -5472,13 +5468,13 @@
         <v>37</v>
       </c>
       <c r="H42" s="1">
-        <v>2940000</v>
+        <v>2352000</v>
       </c>
       <c r="I42" s="1">
-        <v>5200000</v>
+        <v>4160000</v>
       </c>
       <c r="J42" s="1">
-        <v>230000000</v>
+        <v>184000000</v>
       </c>
       <c r="K42" s="1">
         <f t="shared" si="0"/>
@@ -5575,13 +5571,13 @@
         <v>38</v>
       </c>
       <c r="H43" s="1">
-        <v>3360000</v>
+        <v>2688000</v>
       </c>
       <c r="I43" s="1">
-        <v>6200000</v>
+        <v>4960000</v>
       </c>
       <c r="J43" s="1">
-        <v>288000000</v>
+        <v>230400000</v>
       </c>
       <c r="K43" s="1">
         <f t="shared" si="0"/>
@@ -5678,13 +5674,13 @@
         <v>39</v>
       </c>
       <c r="H44" s="1">
-        <v>3800000</v>
+        <v>3040000</v>
       </c>
       <c r="I44" s="1">
-        <v>7400000</v>
+        <v>5920000</v>
       </c>
       <c r="J44" s="1">
-        <v>370000000</v>
+        <v>296000000</v>
       </c>
       <c r="K44" s="1">
         <f t="shared" si="0"/>
@@ -5781,13 +5777,13 @@
         <v>40</v>
       </c>
       <c r="H45" s="1">
-        <v>4300000</v>
+        <v>3440000</v>
       </c>
       <c r="I45" s="1">
-        <v>8880000</v>
+        <v>7104000</v>
       </c>
       <c r="J45" s="1">
-        <v>460000000</v>
+        <v>368000000</v>
       </c>
       <c r="K45" s="1">
         <f t="shared" si="0"/>
@@ -5884,13 +5880,13 @@
         <v>41</v>
       </c>
       <c r="H46" s="1">
-        <v>4900000</v>
+        <v>3920000</v>
       </c>
       <c r="I46" s="1">
-        <v>10200000</v>
+        <v>8160000</v>
       </c>
       <c r="J46" s="1">
-        <v>580000000</v>
+        <v>464000000</v>
       </c>
       <c r="K46" s="1">
         <f t="shared" si="0"/>
@@ -5986,13 +5982,13 @@
         <v>42</v>
       </c>
       <c r="H47" s="4">
-        <v>5600000</v>
+        <v>4480000</v>
       </c>
       <c r="I47" s="4">
-        <v>12000000</v>
+        <v>9600000</v>
       </c>
       <c r="J47" s="4">
-        <v>720000000</v>
+        <v>576000000</v>
       </c>
       <c r="K47" s="4">
         <f t="shared" si="0"/>
@@ -6089,13 +6085,13 @@
         <v>43</v>
       </c>
       <c r="H48" s="1">
-        <v>6400000</v>
+        <v>5120000</v>
       </c>
       <c r="I48" s="1">
-        <v>14400000</v>
+        <v>11520000</v>
       </c>
       <c r="J48" s="1">
-        <v>900000000</v>
+        <v>720000000</v>
       </c>
       <c r="K48" s="1">
         <f t="shared" si="0"/>
@@ -6192,13 +6188,13 @@
         <v>44</v>
       </c>
       <c r="H49" s="1">
-        <v>7300000</v>
+        <v>5840000</v>
       </c>
       <c r="I49" s="1">
-        <v>17000000</v>
+        <v>13600000</v>
       </c>
       <c r="J49" s="1">
-        <v>1120000000</v>
+        <v>896000000</v>
       </c>
       <c r="K49" s="1">
         <f t="shared" si="0"/>
@@ -6295,13 +6291,13 @@
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <v>8300000</v>
+        <v>6640000</v>
       </c>
       <c r="I50" s="1">
-        <v>20000000</v>
+        <v>16000000</v>
       </c>
       <c r="J50" s="1">
-        <v>1400000000</v>
+        <v>1120000000</v>
       </c>
       <c r="K50" s="1">
         <f t="shared" si="0"/>
@@ -6398,13 +6394,13 @@
         <v>46</v>
       </c>
       <c r="H51" s="1">
-        <v>9400000</v>
+        <v>7520000</v>
       </c>
       <c r="I51" s="1">
-        <v>24000000</v>
+        <v>19200000</v>
       </c>
       <c r="J51" s="1">
-        <v>1750000000</v>
+        <v>1400000000</v>
       </c>
       <c r="K51" s="1">
         <f t="shared" si="0"/>
@@ -6501,13 +6497,13 @@
         <v>47</v>
       </c>
       <c r="H52" s="1">
-        <v>10000000</v>
+        <v>8000000</v>
       </c>
       <c r="I52" s="1">
-        <v>28800000</v>
+        <v>23040000</v>
       </c>
       <c r="J52" s="1">
-        <v>2180000000</v>
+        <v>1744000000</v>
       </c>
       <c r="K52" s="1">
         <f t="shared" si="0"/>
@@ -6604,13 +6600,13 @@
         <v>48</v>
       </c>
       <c r="H53" s="4">
-        <v>11400000</v>
+        <v>9120000</v>
       </c>
       <c r="I53" s="4">
-        <v>34500000</v>
+        <v>27600000</v>
       </c>
       <c r="J53" s="4">
-        <v>2720000000</v>
+        <v>2176000000</v>
       </c>
       <c r="K53" s="4">
         <f t="shared" si="0"/>
@@ -6706,14 +6702,14 @@
       <c r="G54" s="1">
         <v>49</v>
       </c>
-      <c r="H54" s="12">
-        <v>13000000</v>
-      </c>
-      <c r="I54" s="12">
-        <v>41400000</v>
-      </c>
-      <c r="J54" s="12">
-        <v>3400000000</v>
+      <c r="H54" s="6">
+        <v>10400000</v>
+      </c>
+      <c r="I54" s="6">
+        <v>33120000</v>
+      </c>
+      <c r="J54" s="6">
+        <v>2720000000</v>
       </c>
       <c r="K54" s="1">
         <f t="shared" si="0"/>
@@ -6809,14 +6805,14 @@
       <c r="G55" s="1">
         <v>50</v>
       </c>
-      <c r="H55" s="12">
-        <v>14800000</v>
-      </c>
-      <c r="I55" s="12">
-        <v>50000000</v>
-      </c>
-      <c r="J55" s="12">
-        <v>4250000000</v>
+      <c r="H55" s="6">
+        <v>11840000</v>
+      </c>
+      <c r="I55" s="6">
+        <v>40000000</v>
+      </c>
+      <c r="J55" s="6">
+        <v>3400000000</v>
       </c>
       <c r="K55" s="1">
         <f t="shared" si="0"/>
@@ -6912,14 +6908,14 @@
       <c r="G56" s="1">
         <v>51</v>
       </c>
-      <c r="H56" s="12">
-        <v>16800000</v>
-      </c>
-      <c r="I56" s="12">
-        <v>60000000</v>
-      </c>
-      <c r="J56" s="12">
-        <v>5310000000</v>
+      <c r="H56" s="6">
+        <v>13440000</v>
+      </c>
+      <c r="I56" s="6">
+        <v>48000000</v>
+      </c>
+      <c r="J56" s="6">
+        <v>4248000000</v>
       </c>
       <c r="K56" s="1">
         <f t="shared" si="0"/>
@@ -7015,14 +7011,14 @@
       <c r="G57" s="1">
         <v>52</v>
       </c>
-      <c r="H57" s="12">
-        <v>19100000</v>
-      </c>
-      <c r="I57" s="12">
-        <v>72000000</v>
-      </c>
-      <c r="J57" s="12">
-        <v>6630000000</v>
+      <c r="H57" s="6">
+        <v>15280000</v>
+      </c>
+      <c r="I57" s="6">
+        <v>57600000</v>
+      </c>
+      <c r="J57" s="6">
+        <v>5304000000</v>
       </c>
       <c r="K57" s="1">
         <f t="shared" si="0"/>
@@ -7118,14 +7114,14 @@
       <c r="G58" s="1">
         <v>53</v>
       </c>
-      <c r="H58" s="12">
-        <v>21700000</v>
-      </c>
-      <c r="I58" s="12">
-        <v>86400000</v>
-      </c>
-      <c r="J58" s="12">
-        <v>8280000000</v>
+      <c r="H58" s="6">
+        <v>17360000</v>
+      </c>
+      <c r="I58" s="6">
+        <v>69120000</v>
+      </c>
+      <c r="J58" s="6">
+        <v>6624000000</v>
       </c>
       <c r="K58" s="1">
         <f t="shared" si="0"/>
@@ -7222,13 +7218,13 @@
         <v>54</v>
       </c>
       <c r="H59" s="4">
-        <v>24700000</v>
+        <v>19760000</v>
       </c>
       <c r="I59" s="4">
-        <v>100000000</v>
+        <v>80000000</v>
       </c>
       <c r="J59" s="4">
-        <v>10000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="K59" s="1">
         <f t="shared" si="0"/>
@@ -7324,14 +7320,14 @@
       <c r="G60" s="1">
         <v>55</v>
       </c>
-      <c r="H60" s="12">
-        <v>28100000</v>
-      </c>
-      <c r="I60" s="12">
-        <v>120000000</v>
-      </c>
-      <c r="J60" s="12">
-        <v>12500000000</v>
+      <c r="H60" s="6">
+        <v>22480000</v>
+      </c>
+      <c r="I60" s="6">
+        <v>96000000</v>
+      </c>
+      <c r="J60" s="6">
+        <v>10000000000</v>
       </c>
       <c r="K60" s="1">
         <f t="shared" si="0"/>
@@ -7427,14 +7423,14 @@
       <c r="G61" s="1">
         <v>56</v>
       </c>
-      <c r="H61" s="12">
-        <v>32000000</v>
-      </c>
-      <c r="I61" s="12">
-        <v>144000000</v>
-      </c>
-      <c r="J61" s="12">
-        <v>15600000000</v>
+      <c r="H61" s="6">
+        <v>25600000</v>
+      </c>
+      <c r="I61" s="6">
+        <v>115200000</v>
+      </c>
+      <c r="J61" s="6">
+        <v>12480000000</v>
       </c>
       <c r="K61" s="1">
         <f t="shared" si="0"/>
@@ -7530,14 +7526,14 @@
       <c r="G62" s="1">
         <v>57</v>
       </c>
-      <c r="H62" s="12">
-        <v>36400000</v>
-      </c>
-      <c r="I62" s="12">
-        <v>172000000</v>
-      </c>
-      <c r="J62" s="12">
-        <v>19500000000</v>
+      <c r="H62" s="6">
+        <v>29120000</v>
+      </c>
+      <c r="I62" s="6">
+        <v>137600000</v>
+      </c>
+      <c r="J62" s="6">
+        <v>15600000000</v>
       </c>
       <c r="K62" s="1">
         <f t="shared" si="0"/>
@@ -7633,14 +7629,14 @@
       <c r="G63" s="1">
         <v>58</v>
       </c>
-      <c r="H63" s="12">
-        <v>41500000</v>
-      </c>
-      <c r="I63" s="12">
-        <v>200000000</v>
-      </c>
-      <c r="J63" s="12">
-        <v>24300000000</v>
+      <c r="H63" s="6">
+        <v>33200000</v>
+      </c>
+      <c r="I63" s="6">
+        <v>160000000</v>
+      </c>
+      <c r="J63" s="6">
+        <v>19440000000</v>
       </c>
       <c r="K63" s="1">
         <f t="shared" si="0"/>
@@ -7736,14 +7732,14 @@
       <c r="G64" s="1">
         <v>59</v>
       </c>
-      <c r="H64" s="12">
-        <v>47300000</v>
-      </c>
-      <c r="I64" s="12">
-        <v>240000000</v>
-      </c>
-      <c r="J64" s="12">
-        <v>30000000000</v>
+      <c r="H64" s="6">
+        <v>37840000</v>
+      </c>
+      <c r="I64" s="6">
+        <v>192000000</v>
+      </c>
+      <c r="J64" s="6">
+        <v>24000000000</v>
       </c>
       <c r="K64" s="1">
         <f t="shared" si="0"/>
@@ -7840,13 +7836,13 @@
         <v>60</v>
       </c>
       <c r="H65" s="4">
-        <v>53900000</v>
+        <v>43120000</v>
       </c>
       <c r="I65" s="4">
-        <v>288000000</v>
+        <v>230400000</v>
       </c>
       <c r="J65" s="4">
-        <v>37500000000</v>
+        <v>30000000000</v>
       </c>
       <c r="K65" s="1">
         <f t="shared" si="0"/>
@@ -7942,14 +7938,14 @@
       <c r="G66" s="1">
         <v>61</v>
       </c>
-      <c r="H66" s="12">
-        <v>61400000</v>
-      </c>
-      <c r="I66" s="12">
-        <v>345000000</v>
-      </c>
-      <c r="J66" s="12">
-        <v>46800000000</v>
+      <c r="H66" s="6">
+        <v>49120000</v>
+      </c>
+      <c r="I66" s="6">
+        <v>276000000</v>
+      </c>
+      <c r="J66" s="6">
+        <v>37440000000</v>
       </c>
       <c r="K66" s="1">
         <f t="shared" si="0"/>
@@ -8045,14 +8041,14 @@
       <c r="G67" s="1">
         <v>62</v>
       </c>
-      <c r="H67" s="12">
-        <v>70000000</v>
-      </c>
-      <c r="I67" s="12">
-        <v>414000000</v>
-      </c>
-      <c r="J67" s="12">
-        <v>58500000000</v>
+      <c r="H67" s="6">
+        <v>56000000</v>
+      </c>
+      <c r="I67" s="6">
+        <v>331200000</v>
+      </c>
+      <c r="J67" s="6">
+        <v>46800000000</v>
       </c>
       <c r="K67" s="1">
         <f t="shared" si="0"/>
@@ -8148,14 +8144,14 @@
       <c r="G68" s="1">
         <v>63</v>
       </c>
-      <c r="H68" s="12">
-        <v>79800000</v>
-      </c>
-      <c r="I68" s="12">
-        <v>496000000</v>
-      </c>
-      <c r="J68" s="12">
-        <v>73100000000</v>
+      <c r="H68" s="6">
+        <v>63840000</v>
+      </c>
+      <c r="I68" s="6">
+        <v>396800000</v>
+      </c>
+      <c r="J68" s="6">
+        <v>58480000000</v>
       </c>
       <c r="K68" s="1">
         <f t="shared" si="0"/>
@@ -8251,14 +8247,14 @@
       <c r="G69" s="1">
         <v>64</v>
       </c>
-      <c r="H69" s="12">
-        <v>90000000</v>
-      </c>
-      <c r="I69" s="12">
-        <v>595000000</v>
-      </c>
-      <c r="J69" s="12">
-        <v>91300000000</v>
+      <c r="H69" s="6">
+        <v>72000000</v>
+      </c>
+      <c r="I69" s="6">
+        <v>476000000</v>
+      </c>
+      <c r="J69" s="6">
+        <v>73040000000</v>
       </c>
       <c r="K69" s="1">
         <f t="shared" si="0"/>
@@ -8354,14 +8350,14 @@
       <c r="G70" s="1">
         <v>65</v>
       </c>
-      <c r="H70" s="12">
-        <v>100000000</v>
-      </c>
-      <c r="I70" s="12">
-        <v>714000000</v>
-      </c>
-      <c r="J70" s="13" t="s">
-        <v>100</v>
+      <c r="H70" s="6">
+        <v>80000000</v>
+      </c>
+      <c r="I70" s="6">
+        <v>571200000</v>
+      </c>
+      <c r="J70" s="6">
+        <v>91200000000</v>
       </c>
       <c r="K70" s="1">
         <f t="shared" ref="K70:K77" si="13">Y70*5</f>
@@ -8452,7 +8448,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G71" s="4">
         <v>66</v>
@@ -8463,8 +8459,8 @@
       <c r="I71" s="4">
         <v>856000000</v>
       </c>
-      <c r="J71" s="14" t="s">
-        <v>102</v>
+      <c r="J71" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="K71" s="1">
         <f t="shared" si="13"/>
@@ -8555,19 +8551,19 @@
         <v>1</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G72" s="1">
         <v>67</v>
       </c>
-      <c r="H72" s="12">
+      <c r="H72" s="6">
         <v>130000000</v>
       </c>
-      <c r="I72" s="12">
+      <c r="I72" s="6">
         <v>1000000000</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K72" s="1">
         <f t="shared" si="13"/>
@@ -8658,19 +8654,19 @@
         <v>1</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G73" s="1">
         <v>68</v>
       </c>
-      <c r="H73" s="12">
+      <c r="H73" s="6">
         <v>148000000</v>
       </c>
-      <c r="I73" s="12">
+      <c r="I73" s="6">
         <v>1200000000</v>
       </c>
       <c r="J73" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K73" s="1">
         <f t="shared" si="13"/>
@@ -8761,19 +8757,19 @@
         <v>1</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G74" s="1">
         <v>69</v>
       </c>
-      <c r="H74" s="12">
+      <c r="H74" s="6">
         <v>168000000</v>
       </c>
-      <c r="I74" s="12">
+      <c r="I74" s="6">
         <v>1440000000</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K74" s="1">
         <f t="shared" si="13"/>
@@ -8864,19 +8860,19 @@
         <v>1</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G75" s="1">
         <v>70</v>
       </c>
-      <c r="H75" s="12">
+      <c r="H75" s="6">
         <v>192000000</v>
       </c>
-      <c r="I75" s="12">
+      <c r="I75" s="6">
         <v>1720000000</v>
       </c>
       <c r="J75" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K75" s="1">
         <f t="shared" si="13"/>
@@ -8967,19 +8963,19 @@
         <v>1</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G76" s="1">
         <v>71</v>
       </c>
-      <c r="H76" s="12">
+      <c r="H76" s="6">
         <v>218000000</v>
       </c>
-      <c r="I76" s="12">
+      <c r="I76" s="6">
         <v>2060000000</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K76" s="1">
         <f t="shared" si="13"/>
@@ -9070,7 +9066,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G77" s="1">
         <v>72</v>
@@ -9081,8 +9077,8 @@
       <c r="I77" s="4">
         <v>2470000000</v>
       </c>
-      <c r="J77" s="14" t="s">
-        <v>114</v>
+      <c r="J77" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="K77" s="1">
         <f t="shared" si="13"/>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -1752,7 +1752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" ht="14" spans="1:33">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1868,13 +1868,13 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="I7" s="1">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J7" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="0"/>
@@ -1969,13 +1969,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="1">
-        <v>280</v>
+        <v>175</v>
       </c>
       <c r="I8" s="1">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J8" s="1">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="0"/>
@@ -2071,13 +2071,13 @@
         <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>600</v>
+        <v>375</v>
       </c>
       <c r="I9" s="1">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J9" s="1">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="0"/>
@@ -2173,13 +2173,13 @@
         <v>5</v>
       </c>
       <c r="H10" s="1">
-        <v>1080</v>
+        <v>675</v>
       </c>
       <c r="I10" s="1">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="J10" s="1">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="0"/>
@@ -2275,13 +2275,13 @@
         <v>6</v>
       </c>
       <c r="H11" s="4">
-        <v>1680</v>
+        <v>1050</v>
       </c>
       <c r="I11" s="4">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="J11" s="4">
-        <v>28000</v>
+        <v>17500</v>
       </c>
       <c r="K11" s="4">
         <f t="shared" si="0"/>
@@ -2377,13 +2377,13 @@
         <v>7</v>
       </c>
       <c r="H12" s="3">
-        <v>2480</v>
+        <v>1550</v>
       </c>
       <c r="I12" s="3">
-        <v>392</v>
+        <v>245</v>
       </c>
       <c r="J12" s="3">
-        <v>44800</v>
+        <v>28000</v>
       </c>
       <c r="K12" s="6">
         <f t="shared" si="0"/>
@@ -2480,13 +2480,13 @@
         <v>8</v>
       </c>
       <c r="H13" s="3">
-        <v>3600</v>
+        <v>2250</v>
       </c>
       <c r="I13" s="6">
-        <v>560</v>
+        <v>350</v>
       </c>
       <c r="J13" s="3">
-        <v>65600</v>
+        <v>41000</v>
       </c>
       <c r="K13" s="6">
         <f t="shared" si="0"/>
@@ -2583,13 +2583,13 @@
         <v>9</v>
       </c>
       <c r="H14" s="6">
-        <v>5360</v>
+        <v>3350</v>
       </c>
       <c r="I14" s="6">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="J14" s="6">
-        <v>100000</v>
+        <v>62500</v>
       </c>
       <c r="K14" s="6">
         <f t="shared" si="0"/>
@@ -2686,13 +2686,13 @@
         <v>10</v>
       </c>
       <c r="H15" s="6">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="I15" s="6">
-        <v>1200</v>
+        <v>750</v>
       </c>
       <c r="J15" s="6">
-        <v>141600</v>
+        <v>88500</v>
       </c>
       <c r="K15" s="6">
         <f t="shared" si="0"/>
@@ -2789,13 +2789,13 @@
         <v>11</v>
       </c>
       <c r="H16" s="6">
-        <v>12640</v>
+        <v>7900</v>
       </c>
       <c r="I16" s="6">
-        <v>1920</v>
+        <v>1200</v>
       </c>
       <c r="J16" s="6">
-        <v>199200</v>
+        <v>124500</v>
       </c>
       <c r="K16" s="6">
         <f t="shared" si="0"/>
@@ -2892,13 +2892,13 @@
         <v>12</v>
       </c>
       <c r="H17" s="4">
-        <v>17600</v>
+        <v>11000</v>
       </c>
       <c r="I17" s="4">
-        <v>2880</v>
+        <v>1800</v>
       </c>
       <c r="J17" s="4">
-        <v>285600</v>
+        <v>178500</v>
       </c>
       <c r="K17" s="4">
         <f t="shared" si="0"/>
@@ -2995,13 +2995,13 @@
         <v>13</v>
       </c>
       <c r="H18" s="6">
-        <v>26400</v>
+        <v>16500</v>
       </c>
       <c r="I18" s="6">
-        <v>4800</v>
+        <v>3000</v>
       </c>
       <c r="J18" s="6">
-        <v>424800</v>
+        <v>265500</v>
       </c>
       <c r="K18" s="6">
         <f t="shared" si="0"/>
@@ -3098,13 +3098,13 @@
         <v>14</v>
       </c>
       <c r="H19" s="6">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="I19" s="6">
-        <v>7680</v>
+        <v>4800</v>
       </c>
       <c r="J19" s="6">
-        <v>586400</v>
+        <v>366500</v>
       </c>
       <c r="K19" s="6">
         <f t="shared" si="0"/>
@@ -3201,13 +3201,13 @@
         <v>15</v>
       </c>
       <c r="H20" s="6">
-        <v>55200</v>
+        <v>34500</v>
       </c>
       <c r="I20" s="6">
-        <v>11200</v>
+        <v>7000</v>
       </c>
       <c r="J20" s="6">
-        <v>733600</v>
+        <v>458500</v>
       </c>
       <c r="K20" s="6">
         <f t="shared" si="0"/>
@@ -3304,13 +3304,13 @@
         <v>16</v>
       </c>
       <c r="H21" s="6">
-        <v>66400</v>
+        <v>41500</v>
       </c>
       <c r="I21" s="6">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="J21" s="6">
-        <v>984000</v>
+        <v>615000</v>
       </c>
       <c r="K21" s="6">
         <f t="shared" si="0"/>
@@ -3407,13 +3407,13 @@
         <v>17</v>
       </c>
       <c r="H22" s="6">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="I22" s="6">
-        <v>21600</v>
+        <v>13500</v>
       </c>
       <c r="J22" s="6">
-        <v>1208000</v>
+        <v>755000</v>
       </c>
       <c r="K22" s="6">
         <f t="shared" si="0"/>
@@ -3510,13 +3510,13 @@
         <v>18</v>
       </c>
       <c r="H23" s="4">
-        <v>100000</v>
+        <v>62500</v>
       </c>
       <c r="I23" s="4">
-        <v>28800</v>
+        <v>18000</v>
       </c>
       <c r="J23" s="2">
-        <v>1480000</v>
+        <v>925000</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="0"/>
@@ -3613,13 +3613,13 @@
         <v>19</v>
       </c>
       <c r="H24" s="6">
-        <v>120000</v>
+        <v>75000</v>
       </c>
       <c r="I24" s="6">
-        <v>38400</v>
+        <v>24000</v>
       </c>
       <c r="J24" s="6">
-        <v>2056000</v>
+        <v>1285000</v>
       </c>
       <c r="K24" s="6">
         <f t="shared" si="0"/>
@@ -3716,13 +3716,13 @@
         <v>20</v>
       </c>
       <c r="H25" s="6">
-        <v>152000</v>
+        <v>95000</v>
       </c>
       <c r="I25" s="6">
-        <v>50400</v>
+        <v>31500</v>
       </c>
       <c r="J25" s="3">
-        <v>2712000</v>
+        <v>1695000</v>
       </c>
       <c r="K25" s="6">
         <f t="shared" si="0"/>
@@ -3819,13 +3819,13 @@
         <v>21</v>
       </c>
       <c r="H26" s="6">
-        <v>184000</v>
+        <v>115000</v>
       </c>
       <c r="I26" s="6">
-        <v>64000</v>
+        <v>40000</v>
       </c>
       <c r="J26" s="6">
-        <v>3592000</v>
+        <v>2245000</v>
       </c>
       <c r="K26" s="6">
         <f t="shared" si="0"/>
@@ -3922,13 +3922,13 @@
         <v>22</v>
       </c>
       <c r="H27" s="6">
-        <v>224000</v>
+        <v>140000</v>
       </c>
       <c r="I27" s="6">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="J27" s="6">
-        <v>4480000</v>
+        <v>2800000</v>
       </c>
       <c r="K27" s="6">
         <f t="shared" si="0"/>
@@ -4025,13 +4025,13 @@
         <v>23</v>
       </c>
       <c r="H28" s="6">
-        <v>272000</v>
+        <v>170000</v>
       </c>
       <c r="I28" s="6">
-        <v>104000</v>
+        <v>65000</v>
       </c>
       <c r="J28" s="6">
-        <v>5680000</v>
+        <v>3550000</v>
       </c>
       <c r="K28" s="6">
         <f t="shared" si="0"/>
@@ -4128,13 +4128,13 @@
         <v>24</v>
       </c>
       <c r="H29" s="4">
-        <v>328000</v>
+        <v>205000</v>
       </c>
       <c r="I29" s="4">
-        <v>136000</v>
+        <v>85000</v>
       </c>
       <c r="J29" s="2">
-        <v>7200000</v>
+        <v>4500000</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="0"/>
@@ -4231,13 +4231,13 @@
         <v>25</v>
       </c>
       <c r="H30" s="6">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="I30" s="6">
-        <v>216000</v>
+        <v>135000</v>
       </c>
       <c r="J30" s="6">
-        <v>9440000</v>
+        <v>5900000</v>
       </c>
       <c r="K30" s="6">
         <f t="shared" si="0"/>
@@ -4334,13 +4334,13 @@
         <v>26</v>
       </c>
       <c r="H31" s="6">
-        <v>480000</v>
+        <v>300000</v>
       </c>
       <c r="I31" s="6">
-        <v>312000</v>
+        <v>195000</v>
       </c>
       <c r="J31" s="6">
-        <v>12000000</v>
+        <v>7500000</v>
       </c>
       <c r="K31" s="6">
         <f t="shared" si="0"/>
@@ -4437,13 +4437,13 @@
         <v>27</v>
       </c>
       <c r="H32" s="6">
-        <v>580000</v>
+        <v>362500</v>
       </c>
       <c r="I32" s="6">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="J32" s="6">
-        <v>16960000</v>
+        <v>10600000</v>
       </c>
       <c r="K32" s="6">
         <f t="shared" si="0"/>
@@ -4540,13 +4540,13 @@
         <v>28</v>
       </c>
       <c r="H33" s="6">
-        <v>664000</v>
+        <v>415000</v>
       </c>
       <c r="I33" s="6">
-        <v>504000</v>
+        <v>315000</v>
       </c>
       <c r="J33" s="6">
-        <v>23920000</v>
+        <v>14950000</v>
       </c>
       <c r="K33" s="6">
         <f t="shared" si="0"/>
@@ -4643,13 +4643,13 @@
         <v>29</v>
       </c>
       <c r="H34" s="6">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="I34" s="6">
-        <v>640000</v>
+        <v>400000</v>
       </c>
       <c r="J34" s="6">
-        <v>30720000</v>
+        <v>19200000</v>
       </c>
       <c r="K34" s="6">
         <f t="shared" si="0"/>
@@ -4746,13 +4746,13 @@
         <v>30</v>
       </c>
       <c r="H35" s="4">
-        <v>912000</v>
+        <v>570000</v>
       </c>
       <c r="I35" s="4">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="J35" s="4">
-        <v>39680000</v>
+        <v>24800000</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="0"/>
@@ -4849,13 +4849,13 @@
         <v>31</v>
       </c>
       <c r="H36" s="6">
-        <v>1048000</v>
+        <v>655000</v>
       </c>
       <c r="I36" s="6">
-        <v>1040000</v>
+        <v>650000</v>
       </c>
       <c r="J36" s="6">
-        <v>53200000</v>
+        <v>33250000</v>
       </c>
       <c r="K36" s="6">
         <f t="shared" si="0"/>
@@ -4952,13 +4952,13 @@
         <v>32</v>
       </c>
       <c r="H37" s="6">
-        <v>1200000</v>
+        <v>750000</v>
       </c>
       <c r="I37" s="6">
-        <v>1360000</v>
+        <v>850000</v>
       </c>
       <c r="J37" s="3">
-        <v>68000000</v>
+        <v>42500000</v>
       </c>
       <c r="K37" s="6">
         <f t="shared" si="0"/>
@@ -5055,13 +5055,13 @@
         <v>33</v>
       </c>
       <c r="H38" s="6">
-        <v>1376000</v>
+        <v>860000</v>
       </c>
       <c r="I38" s="6">
-        <v>1760000</v>
+        <v>1100000</v>
       </c>
       <c r="J38" s="6">
-        <v>81600000</v>
+        <v>51000000</v>
       </c>
       <c r="K38" s="6">
         <f t="shared" si="0"/>
@@ -5158,13 +5158,13 @@
         <v>34</v>
       </c>
       <c r="H39" s="6">
-        <v>1576000</v>
+        <v>985000</v>
       </c>
       <c r="I39" s="6">
-        <v>2240000</v>
+        <v>1400000</v>
       </c>
       <c r="J39" s="3">
-        <v>96000000</v>
+        <v>60000000</v>
       </c>
       <c r="K39" s="6">
         <f t="shared" si="0"/>
@@ -5261,13 +5261,13 @@
         <v>35</v>
       </c>
       <c r="H40" s="6">
-        <v>1800000</v>
+        <v>1125000</v>
       </c>
       <c r="I40" s="6">
-        <v>2800000</v>
+        <v>1750000</v>
       </c>
       <c r="J40" s="6">
-        <v>113600000</v>
+        <v>71000000</v>
       </c>
       <c r="K40" s="6">
         <f t="shared" si="0"/>
@@ -5365,13 +5365,13 @@
         <v>36</v>
       </c>
       <c r="H41" s="4">
-        <v>2056000</v>
+        <v>1285000</v>
       </c>
       <c r="I41" s="4">
-        <v>3440000</v>
+        <v>2150000</v>
       </c>
       <c r="J41" s="4">
-        <v>144800000</v>
+        <v>90500000</v>
       </c>
       <c r="K41" s="4">
         <f t="shared" si="0"/>
@@ -5468,13 +5468,13 @@
         <v>37</v>
       </c>
       <c r="H42" s="1">
-        <v>2352000</v>
+        <v>1470000</v>
       </c>
       <c r="I42" s="1">
-        <v>4160000</v>
+        <v>2600000</v>
       </c>
       <c r="J42" s="1">
-        <v>184000000</v>
+        <v>115000000</v>
       </c>
       <c r="K42" s="1">
         <f t="shared" si="0"/>
@@ -5571,13 +5571,13 @@
         <v>38</v>
       </c>
       <c r="H43" s="1">
-        <v>2688000</v>
+        <v>1680000</v>
       </c>
       <c r="I43" s="1">
-        <v>4960000</v>
+        <v>3100000</v>
       </c>
       <c r="J43" s="1">
-        <v>230400000</v>
+        <v>144000000</v>
       </c>
       <c r="K43" s="1">
         <f t="shared" si="0"/>
@@ -5674,13 +5674,13 @@
         <v>39</v>
       </c>
       <c r="H44" s="1">
-        <v>3040000</v>
+        <v>1900000</v>
       </c>
       <c r="I44" s="1">
-        <v>5920000</v>
+        <v>3700000</v>
       </c>
       <c r="J44" s="1">
-        <v>296000000</v>
+        <v>185000000</v>
       </c>
       <c r="K44" s="1">
         <f t="shared" si="0"/>
@@ -5777,13 +5777,13 @@
         <v>40</v>
       </c>
       <c r="H45" s="1">
-        <v>3440000</v>
+        <v>2150000</v>
       </c>
       <c r="I45" s="1">
-        <v>7104000</v>
+        <v>4440000</v>
       </c>
       <c r="J45" s="1">
-        <v>368000000</v>
+        <v>230000000</v>
       </c>
       <c r="K45" s="1">
         <f t="shared" si="0"/>
@@ -5880,13 +5880,13 @@
         <v>41</v>
       </c>
       <c r="H46" s="1">
-        <v>3920000</v>
+        <v>2450000</v>
       </c>
       <c r="I46" s="1">
-        <v>8160000</v>
+        <v>5100000</v>
       </c>
       <c r="J46" s="1">
-        <v>464000000</v>
+        <v>290000000</v>
       </c>
       <c r="K46" s="1">
         <f t="shared" si="0"/>
@@ -5982,13 +5982,13 @@
         <v>42</v>
       </c>
       <c r="H47" s="4">
-        <v>4480000</v>
+        <v>2800000</v>
       </c>
       <c r="I47" s="4">
-        <v>9600000</v>
+        <v>6000000</v>
       </c>
       <c r="J47" s="4">
-        <v>576000000</v>
+        <v>360000000</v>
       </c>
       <c r="K47" s="4">
         <f t="shared" si="0"/>
@@ -6085,13 +6085,13 @@
         <v>43</v>
       </c>
       <c r="H48" s="1">
-        <v>5120000</v>
+        <v>3200000</v>
       </c>
       <c r="I48" s="1">
-        <v>11520000</v>
+        <v>7200000</v>
       </c>
       <c r="J48" s="1">
-        <v>720000000</v>
+        <v>450000000</v>
       </c>
       <c r="K48" s="1">
         <f t="shared" si="0"/>
@@ -6188,13 +6188,13 @@
         <v>44</v>
       </c>
       <c r="H49" s="1">
-        <v>5840000</v>
+        <v>3650000</v>
       </c>
       <c r="I49" s="1">
-        <v>13600000</v>
+        <v>8500000</v>
       </c>
       <c r="J49" s="1">
-        <v>896000000</v>
+        <v>560000000</v>
       </c>
       <c r="K49" s="1">
         <f t="shared" si="0"/>
@@ -6291,13 +6291,13 @@
         <v>45</v>
       </c>
       <c r="H50" s="1">
-        <v>6640000</v>
+        <v>4150000</v>
       </c>
       <c r="I50" s="1">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="J50" s="1">
-        <v>1120000000</v>
+        <v>700000000</v>
       </c>
       <c r="K50" s="1">
         <f t="shared" si="0"/>
@@ -6394,13 +6394,13 @@
         <v>46</v>
       </c>
       <c r="H51" s="1">
-        <v>7520000</v>
+        <v>4700000</v>
       </c>
       <c r="I51" s="1">
-        <v>19200000</v>
+        <v>12000000</v>
       </c>
       <c r="J51" s="1">
-        <v>1400000000</v>
+        <v>875000000</v>
       </c>
       <c r="K51" s="1">
         <f t="shared" si="0"/>
@@ -6497,13 +6497,13 @@
         <v>47</v>
       </c>
       <c r="H52" s="1">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
       <c r="I52" s="1">
-        <v>23040000</v>
+        <v>14400000</v>
       </c>
       <c r="J52" s="1">
-        <v>1744000000</v>
+        <v>1090000000</v>
       </c>
       <c r="K52" s="1">
         <f t="shared" si="0"/>
@@ -6600,13 +6600,13 @@
         <v>48</v>
       </c>
       <c r="H53" s="4">
-        <v>9120000</v>
+        <v>5700000</v>
       </c>
       <c r="I53" s="4">
-        <v>27600000</v>
+        <v>17250000</v>
       </c>
       <c r="J53" s="4">
-        <v>2176000000</v>
+        <v>1360000000</v>
       </c>
       <c r="K53" s="4">
         <f t="shared" si="0"/>
@@ -6703,13 +6703,13 @@
         <v>49</v>
       </c>
       <c r="H54" s="6">
-        <v>10400000</v>
+        <v>6500000</v>
       </c>
       <c r="I54" s="6">
-        <v>33120000</v>
+        <v>20700000</v>
       </c>
       <c r="J54" s="6">
-        <v>2720000000</v>
+        <v>1700000000</v>
       </c>
       <c r="K54" s="1">
         <f t="shared" si="0"/>
@@ -6806,13 +6806,13 @@
         <v>50</v>
       </c>
       <c r="H55" s="6">
-        <v>11840000</v>
+        <v>7400000</v>
       </c>
       <c r="I55" s="6">
-        <v>40000000</v>
+        <v>25000000</v>
       </c>
       <c r="J55" s="6">
-        <v>3400000000</v>
+        <v>2125000000</v>
       </c>
       <c r="K55" s="1">
         <f t="shared" si="0"/>
@@ -6909,13 +6909,13 @@
         <v>51</v>
       </c>
       <c r="H56" s="6">
-        <v>13440000</v>
+        <v>8400000</v>
       </c>
       <c r="I56" s="6">
-        <v>48000000</v>
+        <v>30000000</v>
       </c>
       <c r="J56" s="6">
-        <v>4248000000</v>
+        <v>2655000000</v>
       </c>
       <c r="K56" s="1">
         <f t="shared" si="0"/>
@@ -7012,13 +7012,13 @@
         <v>52</v>
       </c>
       <c r="H57" s="6">
-        <v>15280000</v>
+        <v>9550000</v>
       </c>
       <c r="I57" s="6">
-        <v>57600000</v>
+        <v>36000000</v>
       </c>
       <c r="J57" s="6">
-        <v>5304000000</v>
+        <v>3315000000</v>
       </c>
       <c r="K57" s="1">
         <f t="shared" si="0"/>
@@ -7115,13 +7115,13 @@
         <v>53</v>
       </c>
       <c r="H58" s="6">
-        <v>17360000</v>
+        <v>10850000</v>
       </c>
       <c r="I58" s="6">
-        <v>69120000</v>
+        <v>43200000</v>
       </c>
       <c r="J58" s="6">
-        <v>6624000000</v>
+        <v>4140000000</v>
       </c>
       <c r="K58" s="1">
         <f t="shared" si="0"/>
@@ -7218,13 +7218,13 @@
         <v>54</v>
       </c>
       <c r="H59" s="4">
-        <v>19760000</v>
+        <v>12350000</v>
       </c>
       <c r="I59" s="4">
-        <v>80000000</v>
+        <v>50000000</v>
       </c>
       <c r="J59" s="4">
-        <v>8000000000</v>
+        <v>5000000000</v>
       </c>
       <c r="K59" s="1">
         <f t="shared" si="0"/>
@@ -7321,13 +7321,13 @@
         <v>55</v>
       </c>
       <c r="H60" s="6">
-        <v>22480000</v>
+        <v>14050000</v>
       </c>
       <c r="I60" s="6">
-        <v>96000000</v>
+        <v>60000000</v>
       </c>
       <c r="J60" s="6">
-        <v>10000000000</v>
+        <v>6250000000</v>
       </c>
       <c r="K60" s="1">
         <f t="shared" si="0"/>
@@ -7424,13 +7424,13 @@
         <v>56</v>
       </c>
       <c r="H61" s="6">
-        <v>25600000</v>
+        <v>16000000</v>
       </c>
       <c r="I61" s="6">
-        <v>115200000</v>
+        <v>72000000</v>
       </c>
       <c r="J61" s="6">
-        <v>12480000000</v>
+        <v>7800000000</v>
       </c>
       <c r="K61" s="1">
         <f t="shared" si="0"/>
@@ -7527,13 +7527,13 @@
         <v>57</v>
       </c>
       <c r="H62" s="6">
-        <v>29120000</v>
+        <v>18200000</v>
       </c>
       <c r="I62" s="6">
-        <v>137600000</v>
+        <v>86000000</v>
       </c>
       <c r="J62" s="6">
-        <v>15600000000</v>
+        <v>9750000000</v>
       </c>
       <c r="K62" s="1">
         <f t="shared" si="0"/>
@@ -7630,13 +7630,13 @@
         <v>58</v>
       </c>
       <c r="H63" s="6">
-        <v>33200000</v>
+        <v>20750000</v>
       </c>
       <c r="I63" s="6">
-        <v>160000000</v>
+        <v>100000000</v>
       </c>
       <c r="J63" s="6">
-        <v>19440000000</v>
+        <v>12150000000</v>
       </c>
       <c r="K63" s="1">
         <f t="shared" si="0"/>
@@ -7733,13 +7733,13 @@
         <v>59</v>
       </c>
       <c r="H64" s="6">
-        <v>37840000</v>
+        <v>23650000</v>
       </c>
       <c r="I64" s="6">
-        <v>192000000</v>
+        <v>120000000</v>
       </c>
       <c r="J64" s="6">
-        <v>24000000000</v>
+        <v>15000000000</v>
       </c>
       <c r="K64" s="1">
         <f t="shared" si="0"/>
@@ -7836,13 +7836,13 @@
         <v>60</v>
       </c>
       <c r="H65" s="4">
-        <v>43120000</v>
+        <v>26950000</v>
       </c>
       <c r="I65" s="4">
-        <v>230400000</v>
+        <v>144000000</v>
       </c>
       <c r="J65" s="4">
-        <v>30000000000</v>
+        <v>18750000000</v>
       </c>
       <c r="K65" s="1">
         <f t="shared" si="0"/>
@@ -7939,13 +7939,13 @@
         <v>61</v>
       </c>
       <c r="H66" s="6">
-        <v>49120000</v>
+        <v>30700000</v>
       </c>
       <c r="I66" s="6">
-        <v>276000000</v>
+        <v>172500000</v>
       </c>
       <c r="J66" s="6">
-        <v>37440000000</v>
+        <v>23400000000</v>
       </c>
       <c r="K66" s="1">
         <f t="shared" si="0"/>
@@ -8042,13 +8042,13 @@
         <v>62</v>
       </c>
       <c r="H67" s="6">
-        <v>56000000</v>
+        <v>35000000</v>
       </c>
       <c r="I67" s="6">
-        <v>331200000</v>
+        <v>207000000</v>
       </c>
       <c r="J67" s="6">
-        <v>46800000000</v>
+        <v>29250000000</v>
       </c>
       <c r="K67" s="1">
         <f t="shared" si="0"/>
@@ -8145,13 +8145,13 @@
         <v>63</v>
       </c>
       <c r="H68" s="6">
-        <v>63840000</v>
+        <v>39900000</v>
       </c>
       <c r="I68" s="6">
-        <v>396800000</v>
+        <v>248000000</v>
       </c>
       <c r="J68" s="6">
-        <v>58480000000</v>
+        <v>36550000000</v>
       </c>
       <c r="K68" s="1">
         <f t="shared" si="0"/>
@@ -8248,13 +8248,13 @@
         <v>64</v>
       </c>
       <c r="H69" s="6">
-        <v>72000000</v>
+        <v>45000000</v>
       </c>
       <c r="I69" s="6">
-        <v>476000000</v>
+        <v>297500000</v>
       </c>
       <c r="J69" s="6">
-        <v>73040000000</v>
+        <v>45650000000</v>
       </c>
       <c r="K69" s="1">
         <f t="shared" si="0"/>
@@ -9290,7 +9290,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5 K3:U5 AD3:AF5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:U5 AD3:AF5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -7819,7 +7819,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:33">
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="1:33">
       <c r="C65" s="4">
         <v>60</v>
       </c>
@@ -7922,7 +7922,13 @@
         <v>281</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="3:33">
+    <row r="66" customHeight="1" spans="1:33">
+      <c r="A66" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C66" s="1">
         <v>61</v>
       </c>
@@ -8025,7 +8031,13 @@
         <v>283</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="3:33">
+    <row r="67" customHeight="1" spans="1:33">
+      <c r="A67" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C67" s="1">
         <v>62</v>
       </c>
@@ -8128,7 +8140,13 @@
         <v>293</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="3:33">
+    <row r="68" customHeight="1" spans="1:33">
+      <c r="A68" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C68" s="1">
         <v>63</v>
       </c>
@@ -8231,7 +8249,13 @@
         <v>307</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="3:33">
+    <row r="69" customHeight="1" spans="1:33">
+      <c r="A69" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C69" s="1">
         <v>64</v>
       </c>
@@ -8334,7 +8358,13 @@
         <v>311</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="3:33">
+    <row r="70" customHeight="1" spans="1:33">
+      <c r="A70" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C70" s="1">
         <v>65</v>
       </c>
@@ -8437,7 +8467,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:33">
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="1:33">
+      <c r="A71" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C71" s="4">
         <v>66</v>
       </c>
@@ -8540,7 +8576,13 @@
         <v>317</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="3:33">
+    <row r="72" customHeight="1" spans="1:33">
+      <c r="A72" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C72" s="1">
         <v>67</v>
       </c>
@@ -8643,7 +8685,13 @@
         <v>331</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="3:33">
+    <row r="73" customHeight="1" spans="1:33">
+      <c r="A73" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C73" s="1">
         <v>68</v>
       </c>
@@ -8746,7 +8794,13 @@
         <v>337</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="3:33">
+    <row r="74" customHeight="1" spans="1:33">
+      <c r="A74" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C74" s="1">
         <v>69</v>
       </c>
@@ -8849,7 +8903,13 @@
         <v>347</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="3:33">
+    <row r="75" customHeight="1" spans="1:33">
+      <c r="A75" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C75" s="1">
         <v>70</v>
       </c>
@@ -8952,7 +9012,13 @@
         <v>349</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="3:33">
+    <row r="76" customHeight="1" spans="1:33">
+      <c r="A76" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C76" s="1">
         <v>71</v>
       </c>
@@ -9055,7 +9121,13 @@
         <v>353</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="3:33">
+    <row r="77" customHeight="1" spans="1:33">
+      <c r="A77" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>0</v>
+      </c>
       <c r="C77" s="1">
         <v>72</v>
       </c>
@@ -9158,17 +9230,17 @@
         <v>359</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="3:33">
+    <row r="78" customHeight="1" spans="1:33">
       <c r="AG78" s="5">
         <v>367</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="3:33">
+    <row r="79" customHeight="1" spans="1:33">
       <c r="AG79" s="5">
         <v>373</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="3:33">
+    <row r="80" customHeight="1" spans="1:33">
       <c r="AG80" s="5">
         <v>379</v>
       </c>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -7923,12 +7923,6 @@
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:33">
-      <c r="A66" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C66" s="1">
         <v>61</v>
       </c>
@@ -7954,12 +7948,12 @@
         <v>23400000000</v>
       </c>
       <c r="K66" s="1">
-        <f t="shared" si="0"/>
-        <v>305</v>
+        <f t="shared" ref="K66:K77" si="13">K65+10</f>
+        <v>310</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="1"/>
-        <v>183</v>
+        <f t="shared" ref="L66:L77" si="14">L65+5</f>
+        <v>185</v>
       </c>
       <c r="M66" s="1">
         <f t="shared" si="2"/>
@@ -8032,12 +8026,6 @@
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:33">
-      <c r="A67" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C67" s="1">
         <v>62</v>
       </c>
@@ -8063,12 +8051,12 @@
         <v>29250000000</v>
       </c>
       <c r="K67" s="1">
-        <f t="shared" si="0"/>
-        <v>310</v>
+        <f t="shared" si="13"/>
+        <v>320</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="1"/>
-        <v>186</v>
+        <f t="shared" si="14"/>
+        <v>190</v>
       </c>
       <c r="M67" s="1">
         <f t="shared" si="2"/>
@@ -8141,12 +8129,6 @@
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:33">
-      <c r="A68" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C68" s="1">
         <v>63</v>
       </c>
@@ -8172,12 +8154,12 @@
         <v>36550000000</v>
       </c>
       <c r="K68" s="1">
-        <f t="shared" si="0"/>
-        <v>315</v>
+        <f t="shared" si="13"/>
+        <v>330</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="1"/>
-        <v>189</v>
+        <f t="shared" si="14"/>
+        <v>195</v>
       </c>
       <c r="M68" s="1">
         <f t="shared" si="2"/>
@@ -8250,12 +8232,6 @@
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:33">
-      <c r="A69" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C69" s="1">
         <v>64</v>
       </c>
@@ -8281,12 +8257,12 @@
         <v>45650000000</v>
       </c>
       <c r="K69" s="1">
-        <f t="shared" si="0"/>
-        <v>320</v>
+        <f t="shared" si="13"/>
+        <v>340</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="1"/>
-        <v>192</v>
+        <f t="shared" si="14"/>
+        <v>200</v>
       </c>
       <c r="M69" s="1">
         <f t="shared" si="2"/>
@@ -8359,12 +8335,6 @@
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:33">
-      <c r="A70" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C70" s="1">
         <v>65</v>
       </c>
@@ -8390,12 +8360,12 @@
         <v>91200000000</v>
       </c>
       <c r="K70" s="1">
-        <f t="shared" ref="K70:K77" si="13">Y70*5</f>
-        <v>325</v>
+        <f t="shared" si="13"/>
+        <v>350</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L77" si="14">Y70*3</f>
-        <v>195</v>
+        <f t="shared" si="14"/>
+        <v>205</v>
       </c>
       <c r="M70" s="1">
         <f t="shared" ref="M70:M77" si="15">Y70*2</f>
@@ -8468,12 +8438,8 @@
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="1:33">
-      <c r="A71" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>0</v>
-      </c>
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
       <c r="C71" s="4">
         <v>66</v>
       </c>
@@ -8500,11 +8466,11 @@
       </c>
       <c r="K71" s="1">
         <f t="shared" si="13"/>
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="L71" s="1">
         <f t="shared" si="14"/>
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="M71" s="1">
         <f t="shared" si="15"/>
@@ -8577,12 +8543,6 @@
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:33">
-      <c r="A72" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C72" s="1">
         <v>67</v>
       </c>
@@ -8609,11 +8569,11 @@
       </c>
       <c r="K72" s="1">
         <f t="shared" si="13"/>
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="L72" s="1">
         <f t="shared" si="14"/>
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="M72" s="1">
         <f t="shared" si="15"/>
@@ -8686,12 +8646,6 @@
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:33">
-      <c r="A73" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C73" s="1">
         <v>68</v>
       </c>
@@ -8718,11 +8672,11 @@
       </c>
       <c r="K73" s="1">
         <f t="shared" si="13"/>
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="L73" s="1">
         <f t="shared" si="14"/>
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="M73" s="1">
         <f t="shared" si="15"/>
@@ -8795,12 +8749,6 @@
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:33">
-      <c r="A74" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C74" s="1">
         <v>69</v>
       </c>
@@ -8827,11 +8775,11 @@
       </c>
       <c r="K74" s="1">
         <f t="shared" si="13"/>
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="L74" s="1">
         <f t="shared" si="14"/>
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="M74" s="1">
         <f t="shared" si="15"/>
@@ -8904,12 +8852,6 @@
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:33">
-      <c r="A75" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C75" s="1">
         <v>70</v>
       </c>
@@ -8936,11 +8878,11 @@
       </c>
       <c r="K75" s="1">
         <f t="shared" si="13"/>
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="L75" s="1">
         <f t="shared" si="14"/>
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="M75" s="1">
         <f t="shared" si="15"/>
@@ -9013,12 +8955,6 @@
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:33">
-      <c r="A76" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C76" s="1">
         <v>71</v>
       </c>
@@ -9045,11 +8981,11 @@
       </c>
       <c r="K76" s="1">
         <f t="shared" si="13"/>
-        <v>355</v>
+        <v>410</v>
       </c>
       <c r="L76" s="1">
         <f t="shared" si="14"/>
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="M76" s="1">
         <f t="shared" si="15"/>
@@ -9122,12 +9058,6 @@
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:33">
-      <c r="A77" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>0</v>
-      </c>
       <c r="C77" s="1">
         <v>72</v>
       </c>
@@ -9154,11 +9084,11 @@
       </c>
       <c r="K77" s="1">
         <f t="shared" si="13"/>
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="L77" s="1">
         <f t="shared" si="14"/>
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="M77" s="1">
         <f t="shared" si="15"/>
